--- a/General.xlsx
+++ b/General.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Personal\cff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DF39B6-5836-426B-B6D7-7B010242D6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="2340" windowWidth="38640" windowHeight="21120"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IPOSME" sheetId="1" r:id="rId1"/>
     <sheet name="IPOMB" sheetId="2" r:id="rId2"/>
     <sheet name="IPOSME (2)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="367">
   <si>
     <t>URL</t>
   </si>
@@ -1120,11 +1121,14 @@
   <si>
     <t>0: NA, 1: RII, 2: NIIA, 3: NIIB</t>
   </si>
+  <si>
+    <t>Tipco Eng</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -1693,787 +1697,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="194">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="109">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2609,6 +1833,136 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -3183,85 +2537,85 @@
     </dxf>
   </dxfs>
   <tableStyles count="19" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="193"/>
-      <tableStyleElement type="firstRowStripe" dxfId="192"/>
-      <tableStyleElement type="secondRowStripe" dxfId="191"/>
+    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="108"/>
+      <tableStyleElement type="firstRowStripe" dxfId="107"/>
+      <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="190"/>
-      <tableStyleElement type="firstRowStripe" dxfId="189"/>
-      <tableStyleElement type="secondRowStripe" dxfId="188"/>
+    <tableStyle name="SME IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="headerRow" dxfId="105"/>
+      <tableStyleElement type="firstRowStripe" dxfId="104"/>
+      <tableStyleElement type="secondRowStripe" dxfId="103"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="187"/>
-      <tableStyleElement type="secondRowStripe" dxfId="186"/>
+    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="102"/>
+      <tableStyleElement type="secondRowStripe" dxfId="101"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="185"/>
-      <tableStyleElement type="secondRowStripe" dxfId="184"/>
+    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="100"/>
+      <tableStyleElement type="secondRowStripe" dxfId="99"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="183"/>
-      <tableStyleElement type="secondRowStripe" dxfId="182"/>
+    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="98"/>
+      <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="181"/>
-      <tableStyleElement type="secondRowStripe" dxfId="180"/>
+    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="96"/>
+      <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="179"/>
-      <tableStyleElement type="secondRowStripe" dxfId="178"/>
+    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="94"/>
+      <tableStyleElement type="secondRowStripe" dxfId="93"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="177"/>
-      <tableStyleElement type="firstRowStripe" dxfId="176"/>
-      <tableStyleElement type="secondRowStripe" dxfId="175"/>
+    <tableStyle name="SME IPO v2-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
+      <tableStyleElement type="headerRow" dxfId="92"/>
+      <tableStyleElement type="firstRowStripe" dxfId="91"/>
+      <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="174"/>
-      <tableStyleElement type="secondRowStripe" dxfId="173"/>
+    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="89"/>
+      <tableStyleElement type="secondRowStripe" dxfId="88"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="172"/>
-      <tableStyleElement type="secondRowStripe" dxfId="171"/>
+    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="87"/>
+      <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="170"/>
-      <tableStyleElement type="secondRowStripe" dxfId="169"/>
+    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="85"/>
+      <tableStyleElement type="secondRowStripe" dxfId="84"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="168"/>
-      <tableStyleElement type="secondRowStripe" dxfId="167"/>
+    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="83"/>
+      <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="166"/>
-      <tableStyleElement type="secondRowStripe" dxfId="165"/>
+    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="81"/>
+      <tableStyleElement type="secondRowStripe" dxfId="80"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="164"/>
-      <tableStyleElement type="firstRowStripe" dxfId="163"/>
-      <tableStyleElement type="secondRowStripe" dxfId="162"/>
+    <tableStyle name="SME IPO v3-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
+      <tableStyleElement type="headerRow" dxfId="79"/>
+      <tableStyleElement type="firstRowStripe" dxfId="78"/>
+      <tableStyleElement type="secondRowStripe" dxfId="77"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="161"/>
-      <tableStyleElement type="secondRowStripe" dxfId="160"/>
+    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="76"/>
+      <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="159"/>
-      <tableStyleElement type="secondRowStripe" dxfId="158"/>
+    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="74"/>
+      <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="157"/>
-      <tableStyleElement type="secondRowStripe" dxfId="156"/>
+    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF10000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="72"/>
+      <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="155"/>
-      <tableStyleElement type="secondRowStripe" dxfId="154"/>
+    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF11000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="70"/>
+      <tableStyleElement type="secondRowStripe" dxfId="69"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="153"/>
-      <tableStyleElement type="secondRowStripe" dxfId="152"/>
+    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF12000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="68"/>
+      <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3472,51 +2826,51 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DF477"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" style="108" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" customWidth="1"/>
-    <col min="24" max="24" width="7.28515625" customWidth="1"/>
-    <col min="25" max="25" width="10.28515625" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" customWidth="1"/>
-    <col min="27" max="27" width="5.85546875" customWidth="1"/>
-    <col min="28" max="28" width="7.28515625" customWidth="1"/>
-    <col min="29" max="29" width="5.85546875" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" customWidth="1"/>
-    <col min="31" max="31" width="7.7109375" customWidth="1"/>
-    <col min="32" max="32" width="8.42578125" customWidth="1"/>
-    <col min="33" max="33" width="7.28515625" customWidth="1"/>
-    <col min="34" max="36" width="6.28515625" customWidth="1"/>
-    <col min="37" max="37" width="8.85546875" customWidth="1"/>
-    <col min="38" max="38" width="4.42578125" customWidth="1"/>
-    <col min="39" max="39" width="20.140625" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" style="108" customWidth="1"/>
+    <col min="20" max="20" width="5.33203125" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" customWidth="1"/>
+    <col min="24" max="24" width="7.33203125" customWidth="1"/>
+    <col min="25" max="25" width="10.33203125" customWidth="1"/>
+    <col min="26" max="26" width="8.5546875" customWidth="1"/>
+    <col min="27" max="27" width="5.88671875" customWidth="1"/>
+    <col min="28" max="28" width="7.33203125" customWidth="1"/>
+    <col min="29" max="29" width="5.88671875" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" customWidth="1"/>
+    <col min="31" max="31" width="7.6640625" customWidth="1"/>
+    <col min="32" max="32" width="8.44140625" customWidth="1"/>
+    <col min="33" max="33" width="7.33203125" customWidth="1"/>
+    <col min="34" max="36" width="6.33203125" customWidth="1"/>
+    <col min="37" max="37" width="8.88671875" customWidth="1"/>
+    <col min="38" max="38" width="4.44140625" customWidth="1"/>
+    <col min="39" max="39" width="20.109375" customWidth="1"/>
     <col min="42" max="48" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" ht="92.45" customHeight="1">
+    <row r="1" spans="1:59" ht="92.4" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -18246,7 +17600,7 @@
         <v>20.73</v>
       </c>
       <c r="G98" s="16">
-        <f t="shared" ref="G98:G129" si="29">100*(F98-E98)/F98</f>
+        <f t="shared" ref="G98:G117" si="29">100*(F98-E98)/F98</f>
         <v>-6.5605402797877446</v>
       </c>
       <c r="H98" s="37">
@@ -18268,7 +17622,7 @@
         <v>78.900000000000006</v>
       </c>
       <c r="P98" s="16">
-        <f t="shared" ref="P98:P129" si="30">O98/I98</f>
+        <f t="shared" ref="P98:P117" si="30">O98/I98</f>
         <v>8.7959866220735794</v>
       </c>
       <c r="Q98" s="9">
@@ -18342,7 +17696,7 @@
         <v>2</v>
       </c>
       <c r="AO98" s="17">
-        <f t="shared" ref="AO98:AO129" si="33">AN98+1</f>
+        <f t="shared" ref="AO98:AO123" si="33">AN98+1</f>
         <v>3</v>
       </c>
       <c r="AP98" s="17">
@@ -22864,7 +22218,7 @@
         <v>1</v>
       </c>
       <c r="AK130" s="16">
-        <f t="shared" ref="AK130:AK161" si="37">(1.2*AG130+AH130)*AJ130</f>
+        <f t="shared" ref="AK130:AK135" si="37">(1.2*AG130+AH130)*AJ130</f>
         <v>9.6195833333333329</v>
       </c>
       <c r="AL130" s="15" t="str">
@@ -23979,61 +23333,117 @@
       <c r="AR138" s="17"/>
     </row>
     <row r="139" spans="1:44">
-      <c r="G139" s="16" t="e">
+      <c r="B139" t="s">
+        <v>366</v>
+      </c>
+      <c r="E139">
+        <v>37.229999999999997</v>
+      </c>
+      <c r="F139">
+        <v>33.229999999999997</v>
+      </c>
+      <c r="G139" s="16">
         <f t="shared" ref="G139:G202" si="43">100*(F139-E139)/F139</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P139" s="16" t="e">
+        <v>-12.037315678603672</v>
+      </c>
+      <c r="H139">
+        <v>100.96</v>
+      </c>
+      <c r="I139">
+        <v>15.61</v>
+      </c>
+      <c r="J139">
+        <v>11.72</v>
+      </c>
+      <c r="K139">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="O139">
+        <v>133.57</v>
+      </c>
+      <c r="P139" s="16">
         <f t="shared" ref="P139:P202" si="44">O139/I139</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R139" s="111"/>
+        <v>8.5566944266495835</v>
+      </c>
+      <c r="Q139">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="R139" s="111">
+        <v>10.5</v>
+      </c>
       <c r="S139" s="118">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>1</v>
+      </c>
+      <c r="W139">
+        <v>1</v>
+      </c>
+      <c r="X139">
+        <v>3</v>
+      </c>
+      <c r="Y139">
         <v>5</v>
+      </c>
+      <c r="Z139">
+        <v>1</v>
       </c>
       <c r="AA139" s="2">
         <f t="shared" si="34"/>
         <v>1</v>
       </c>
+      <c r="AB139">
+        <v>1</v>
+      </c>
       <c r="AC139" s="16">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AG139" s="118" t="e">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="AD139">
+        <v>90</v>
+      </c>
+      <c r="AE139">
+        <v>33</v>
+      </c>
+      <c r="AF139">
+        <v>120</v>
+      </c>
+      <c r="AG139" s="118">
         <f t="shared" si="35"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH139" s="16" t="e">
+        <v>4.5</v>
+      </c>
+      <c r="AH139" s="16">
         <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+        <v>7.583333333333333</v>
       </c>
       <c r="AI139" s="16"/>
       <c r="AJ139" s="16">
         <v>1</v>
       </c>
-      <c r="AK139" s="16" t="e">
+      <c r="AK139" s="16">
         <f t="shared" si="42"/>
-        <v>#DIV/0!</v>
+        <v>12.983333333333333</v>
       </c>
       <c r="AL139" s="15">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AM139" s="15">
+      <c r="AM139" s="15" t="str">
         <f t="shared" ref="AM139:AM202" si="45">B139</f>
-        <v>0</v>
+        <v>Tipco Eng</v>
       </c>
       <c r="AO139" s="17">
         <f t="shared" ref="AO139:AO202" si="46">AN139+1</f>
         <v>1</v>
       </c>
-      <c r="AP139" s="17" t="e">
+      <c r="AP139" s="17">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AQ139" s="17" t="e">
+        <v>0</v>
+      </c>
+      <c r="AQ139" s="17">
         <f t="shared" si="40"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="AR139" s="17"/>
     </row>
@@ -31053,7 +30463,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ258" s="17" t="e">
-        <f t="shared" ref="AQ258:AQ321" si="64">IF(AP258&gt;0,IF(AB258&gt;10,(AB258/Z258),10/Z258),0)</f>
+        <f t="shared" ref="AQ258:AQ288" si="64">IF(AP258&gt;0,IF(AB258&gt;10,(AB258/Z258),10/Z258),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR258" s="17"/>
@@ -34682,7 +34092,7 @@
         <v>1</v>
       </c>
       <c r="AC323" s="16">
-        <f t="shared" ref="AC323:AC386" si="76">IF(AB323&gt;4,1,0)+AB323/12</f>
+        <f t="shared" ref="AC323:AC345" si="76">IF(AB323&gt;4,1,0)+AB323/12</f>
         <v>0</v>
       </c>
       <c r="AG323" s="118" t="e">
@@ -35022,7 +34432,7 @@
         <v>1</v>
       </c>
       <c r="AK329" s="16" t="e">
-        <f t="shared" ref="AK329:AK392" si="77">(1.2*AG329+AH329)*AJ329</f>
+        <f t="shared" ref="AK329:AK356" si="77">(1.2*AG329+AH329)*AJ329</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL329" s="15">
@@ -35142,7 +34552,7 @@
         <v>0</v>
       </c>
       <c r="AO331" s="17">
-        <f t="shared" ref="AO331:AO394" si="81">AN331+1</f>
+        <f t="shared" ref="AO331:AO357" si="81">AN331+1</f>
         <v>1</v>
       </c>
       <c r="AP331" s="17" t="e">
@@ -40986,7 +40396,7 @@
         <v>5</v>
       </c>
       <c r="AA450" s="2">
-        <f t="shared" ref="AA450:AA513" si="100">IF(X450&lt;50,IF(Y450&gt;(2.3*X450),0,1),1)-IF(Z450&gt;Y450,1.7,0)</f>
+        <f t="shared" ref="AA450:AA458" si="100">IF(X450&lt;50,IF(Y450&gt;(2.3*X450),0,1),1)-IF(Z450&gt;Y450,1.7,0)</f>
         <v>1</v>
       </c>
       <c r="AC450" s="16">
@@ -40998,7 +40408,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH450" s="16" t="e">
-        <f t="shared" ref="AH450:AH513" si="101">AG450+IF(X450&lt;1.35,0,1)+IF(Y450&lt;1.35,0,1)+AC450+AA450</f>
+        <f t="shared" ref="AH450:AH466" si="101">AG450+IF(X450&lt;1.35,0,1)+IF(Y450&lt;1.35,0,1)+AC450+AA450</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI450" s="16"/>
@@ -41148,7 +40558,7 @@
       <c r="AI453" s="16"/>
       <c r="AJ453" s="16"/>
       <c r="AK453" s="16" t="e">
-        <f t="shared" ref="AK453:AK484" si="104">(2*AG453+AH453)*AJ453</f>
+        <f t="shared" ref="AK453:AK460" si="104">(2*AG453+AH453)*AJ453</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL453" s="15">
@@ -41406,11 +40816,11 @@
     </row>
     <row r="459" spans="7:42">
       <c r="G459" s="16" t="e">
-        <f t="shared" ref="G459:G522" si="105">100*(F459-E459)/F459</f>
+        <f t="shared" ref="G459:G466" si="105">100*(F459-E459)/F459</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P459" s="16" t="e">
-        <f t="shared" ref="P459:P522" si="106">O459/I459</f>
+        <f t="shared" ref="P459:P466" si="106">O459/I459</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R459" s="111"/>
@@ -41797,111 +41207,111 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D155">
-    <cfRule type="containsText" dxfId="151" priority="37" operator="containsText" text="neg">
+    <cfRule type="containsText" dxfId="66" priority="37" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH(("neg"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G466">
-    <cfRule type="cellIs" dxfId="150" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="65" priority="30" operator="lessThan">
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P466">
-    <cfRule type="cellIs" dxfId="149" priority="31" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="64" priority="31" operator="greaterThan">
       <formula>14.56</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q154">
-    <cfRule type="cellIs" dxfId="148" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="34" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R163">
-    <cfRule type="cellIs" dxfId="147" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="62" priority="26" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2">
-    <cfRule type="notContainsBlanks" dxfId="146" priority="38">
+    <cfRule type="notContainsBlanks" dxfId="61" priority="38">
       <formula>LEN(TRIM(X2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE155">
-    <cfRule type="cellIs" dxfId="145" priority="29" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="29" operator="lessThan">
       <formula>10.56</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG466">
-    <cfRule type="cellIs" dxfId="144" priority="35" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="35" operator="greaterThan">
       <formula>4.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AJ466">
-    <cfRule type="cellIs" dxfId="143" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="33" operator="greaterThan">
       <formula>8.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK466">
-    <cfRule type="cellIs" dxfId="142" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="36" operator="greaterThan">
       <formula>13.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL466">
-    <cfRule type="containsText" dxfId="141" priority="8" operator="containsText" text="Rec">
+    <cfRule type="containsText" dxfId="56" priority="8" operator="containsText" text="Rec">
       <formula>NOT(ISERROR(SEARCH("Rec",AL2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="140" priority="11" operator="containsText" text="neg">
+    <cfRule type="containsText" dxfId="55" priority="11" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH(("neg"),(AL2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="139" priority="27" operator="containsText" text="Pos">
+    <cfRule type="containsText" dxfId="54" priority="27" operator="containsText" text="Pos">
       <formula>NOT(ISERROR(SEARCH("Pos",AL2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN175">
-    <cfRule type="endsWith" dxfId="138" priority="13" operator="endsWith" text="4">
+    <cfRule type="endsWith" dxfId="53" priority="13" operator="endsWith" text="4">
       <formula>RIGHT(AN2,LEN("4"))="4"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="137" priority="14" operator="endsWith" text="2">
+    <cfRule type="endsWith" dxfId="52" priority="14" operator="endsWith" text="2">
       <formula>RIGHT(AN2,LEN("2"))="2"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="136" priority="15" operator="endsWith" text="7">
+    <cfRule type="endsWith" dxfId="51" priority="15" operator="endsWith" text="7">
       <formula>RIGHT(AN2,LEN("7"))="7"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="135" priority="16" operator="endsWith" text="0">
+    <cfRule type="endsWith" dxfId="50" priority="16" operator="endsWith" text="0">
       <formula>RIGHT(AN2,LEN("0"))="0"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="134" priority="17" operator="endsWith" text="8">
+    <cfRule type="endsWith" dxfId="49" priority="17" operator="endsWith" text="8">
       <formula>RIGHT(AN2,LEN("8"))="8"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="133" priority="19" operator="endsWith" text="9">
+    <cfRule type="endsWith" dxfId="48" priority="19" operator="endsWith" text="9">
       <formula>RIGHT(AN2,LEN("9"))="9"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="132" priority="20" operator="endsWith" text="6">
+    <cfRule type="endsWith" dxfId="47" priority="20" operator="endsWith" text="6">
       <formula>RIGHT(AN2,LEN("6"))="6"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="131" priority="21" operator="endsWith" text="1">
+    <cfRule type="endsWith" dxfId="46" priority="21" operator="endsWith" text="1">
       <formula>RIGHT(AN2,LEN("1"))="1"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="130" priority="22" operator="endsWith" text="3">
+    <cfRule type="endsWith" dxfId="45" priority="22" operator="endsWith" text="3">
       <formula>RIGHT(AN2,LEN("3"))="3"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="129" priority="23" operator="endsWith" text="5">
+    <cfRule type="endsWith" dxfId="44" priority="23" operator="endsWith" text="5">
       <formula>RIGHT(AN2,LEN("5"))="5"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP469">
-    <cfRule type="containsText" dxfId="128" priority="1" operator="containsText" text="2">
+    <cfRule type="containsText" dxfId="43" priority="1" operator="containsText" text="2">
       <formula>NOT(ISERROR(SEARCH("2",AP2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="4" operator="equal">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AY2:BG81 AY82 AY83:BG85 AY86:AZ86 AY87:BG97 BA82:BG82 BB86:BG86">
-    <cfRule type="cellIs" dxfId="125" priority="32" operator="lessThan">
+  <conditionalFormatting sqref="AY2:BG81 AY82 BA82:BG82 AY83:BG85 AY86:AZ86 BB86:BG86 AY87:BG97">
+    <cfRule type="cellIs" dxfId="40" priority="32" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41911,59 +41321,59 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BB183"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" customWidth="1"/>
-    <col min="12" max="12" width="4.140625" customWidth="1"/>
-    <col min="13" max="14" width="6.5703125" customWidth="1"/>
-    <col min="15" max="15" width="7.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="4.88671875" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" customWidth="1"/>
+    <col min="12" max="12" width="4.109375" customWidth="1"/>
+    <col min="13" max="14" width="6.5546875" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.140625" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="5.5703125" customWidth="1"/>
-    <col min="22" max="22" width="6.140625" customWidth="1"/>
-    <col min="23" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="8.28515625" customWidth="1"/>
-    <col min="26" max="26" width="5.42578125" customWidth="1"/>
-    <col min="27" max="27" width="5.140625" customWidth="1"/>
-    <col min="28" max="28" width="4.5703125" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" customWidth="1"/>
-    <col min="30" max="30" width="6.5703125" customWidth="1"/>
-    <col min="31" max="31" width="5.7109375" customWidth="1"/>
-    <col min="32" max="32" width="6.28515625" customWidth="1"/>
-    <col min="33" max="36" width="4.85546875" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
+    <col min="21" max="21" width="5.5546875" customWidth="1"/>
+    <col min="22" max="22" width="6.109375" customWidth="1"/>
+    <col min="23" max="24" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="8.33203125" customWidth="1"/>
+    <col min="26" max="26" width="5.44140625" customWidth="1"/>
+    <col min="27" max="27" width="5.109375" customWidth="1"/>
+    <col min="28" max="28" width="4.5546875" customWidth="1"/>
+    <col min="29" max="29" width="4.88671875" customWidth="1"/>
+    <col min="30" max="30" width="6.5546875" customWidth="1"/>
+    <col min="31" max="31" width="5.6640625" customWidth="1"/>
+    <col min="32" max="32" width="6.33203125" customWidth="1"/>
+    <col min="33" max="36" width="4.88671875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
-    <col min="38" max="38" width="5.7109375" customWidth="1"/>
-    <col min="39" max="39" width="13.7109375" customWidth="1"/>
-    <col min="40" max="40" width="4.5703125" customWidth="1"/>
-    <col min="41" max="41" width="5.42578125" customWidth="1"/>
-    <col min="42" max="44" width="10.85546875" customWidth="1"/>
+    <col min="38" max="38" width="5.6640625" customWidth="1"/>
+    <col min="39" max="39" width="13.6640625" customWidth="1"/>
+    <col min="40" max="40" width="4.5546875" customWidth="1"/>
+    <col min="41" max="41" width="5.44140625" customWidth="1"/>
+    <col min="42" max="44" width="10.88671875" customWidth="1"/>
     <col min="45" max="45" width="6" customWidth="1"/>
-    <col min="46" max="46" width="6.140625" customWidth="1"/>
+    <col min="46" max="46" width="6.109375" customWidth="1"/>
     <col min="47" max="47" width="4" customWidth="1"/>
-    <col min="48" max="48" width="4.140625" customWidth="1"/>
-    <col min="49" max="50" width="5.28515625" customWidth="1"/>
-    <col min="51" max="51" width="6.7109375" customWidth="1"/>
-    <col min="52" max="52" width="3.85546875" customWidth="1"/>
+    <col min="48" max="48" width="4.109375" customWidth="1"/>
+    <col min="49" max="50" width="5.33203125" customWidth="1"/>
+    <col min="51" max="51" width="6.6640625" customWidth="1"/>
+    <col min="52" max="52" width="3.88671875" customWidth="1"/>
     <col min="53" max="53" width="4" customWidth="1"/>
-    <col min="54" max="54" width="4.7109375" customWidth="1"/>
+    <col min="54" max="54" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="92.45" customHeight="1">
+    <row r="1" spans="1:54" ht="92.4" customHeight="1">
       <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
@@ -51197,7 +50607,7 @@
         <v>660.43</v>
       </c>
       <c r="G66" s="47">
-        <f t="shared" ref="G66:G97" si="21">100*(F66-E66)/F66</f>
+        <f t="shared" ref="G66:G67" si="21">100*(F66-E66)/F66</f>
         <v>79.978196023802667</v>
       </c>
       <c r="H66" s="101">
@@ -51225,7 +50635,7 @@
         <v>2514.66</v>
       </c>
       <c r="P66" s="47">
-        <f t="shared" ref="P66:P97" si="22">O66/I66</f>
+        <f t="shared" ref="P66:P67" si="22">O66/I66</f>
         <v>414.96039603960395</v>
       </c>
       <c r="Q66" s="101">
@@ -53144,7 +52554,7 @@
         <v>21.65</v>
       </c>
       <c r="S79" s="47">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="T79" s="101">
         <v>1842.12</v>
@@ -53189,17 +52599,17 @@
       </c>
       <c r="AG79" s="49">
         <f t="shared" si="25"/>
-        <v>8.1</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="AH79" s="49">
         <f t="shared" si="26"/>
-        <v>14.363333333333333</v>
+        <v>13.463333333333331</v>
       </c>
       <c r="AI79" s="49"/>
       <c r="AJ79" s="49"/>
       <c r="AK79" s="49">
         <f t="shared" si="29"/>
-        <v>35.423333333333332</v>
+        <v>32.18333333333333</v>
       </c>
       <c r="AL79" s="2">
         <f t="shared" si="27"/>
@@ -55072,7 +54482,7 @@
       </c>
       <c r="AB98" s="101"/>
       <c r="AC98" s="52">
-        <f t="shared" ref="AC98:AC129" si="35">IF(AB98&gt;9,1,0)+AB98/3</f>
+        <f t="shared" ref="AC98:AC123" si="35">IF(AB98&gt;9,1,0)+AB98/3</f>
         <v>0</v>
       </c>
       <c r="AD98" s="101"/>
@@ -60786,11 +60196,11 @@
       <c r="AE162" s="101"/>
       <c r="AF162" s="101"/>
       <c r="AG162" s="49" t="e">
-        <f t="shared" ref="AG162:AG193" si="55">IF(G162&lt;0,0,1.2)+IF(G162&lt;14,0,0.9)+IF(P162&lt;0,0.7,0)+IF(P162&lt;6.5,1,0)+IF(P162&lt;23,1,0)+IF(R162&gt;88,0,1)+IF(S162=5,0,S162)+IF(AD162&lt;20,0,1)+IF(AE162&lt;14,0,1)+IF(AF162&lt;26,0,1)</f>
+        <f t="shared" ref="AG162:AG177" si="55">IF(G162&lt;0,0,1.2)+IF(G162&lt;14,0,0.9)+IF(P162&lt;0,0.7,0)+IF(P162&lt;6.5,1,0)+IF(P162&lt;23,1,0)+IF(R162&gt;88,0,1)+IF(S162=5,0,S162)+IF(AD162&lt;20,0,1)+IF(AE162&lt;14,0,1)+IF(AF162&lt;26,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH162" s="49" t="e">
-        <f t="shared" ref="AH162:AH193" si="56">AG162+IF(AG162&gt;6,1,0)+IF(X162&lt;17,0,1)+IF(Y162&lt;11,0,1)+IF(Z162&lt;1.35,0,1)+AC162+AA162</f>
+        <f t="shared" ref="AH162:AH175" si="56">AG162+IF(AG162&gt;6,1,0)+IF(X162&lt;17,0,1)+IF(Y162&lt;11,0,1)+IF(Z162&lt;1.35,0,1)+AC162+AA162</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI162" s="49"/>
@@ -60814,7 +60224,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ162" s="16" t="e">
-        <f t="shared" ref="AQ162:AQ193" si="58">IF(AP162&gt;0,IF(AB162&gt;10,(AB162/Z162),10/Z162),0)</f>
+        <f t="shared" ref="AQ162:AQ174" si="58">IF(AP162&gt;0,IF(AB162&gt;10,(AB162/Z162),10/Z162),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR162" s="101"/>
@@ -61338,7 +60748,7 @@
       <c r="AN168" s="101"/>
       <c r="AO168" s="101"/>
       <c r="AP168" s="17" t="e">
-        <f t="shared" ref="AP162:AP171" si="60">IF(AK168&gt;13.8,IF(Z168&lt;101,IF(Z168&lt;35,IF(Z168&lt;8,3,2),1),0),0)</f>
+        <f t="shared" ref="AP168:AP171" si="60">IF(AK168&gt;13.8,IF(Z168&lt;101,IF(Z168&lt;35,IF(Z168&lt;8,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ168" s="16" t="e">
@@ -62177,7 +61587,7 @@
       <c r="E179" s="101"/>
       <c r="F179" s="101"/>
       <c r="G179" s="47" t="e">
-        <f t="shared" ref="G179:G210" si="61">100*(F179-E179)/F179</f>
+        <f t="shared" ref="G179:G183" si="61">100*(F179-E179)/F179</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H179" s="101"/>
@@ -62189,7 +61599,7 @@
       <c r="N179" s="101"/>
       <c r="O179" s="101"/>
       <c r="P179" s="47" t="e">
-        <f t="shared" ref="P179:P210" si="62">O179/I179</f>
+        <f t="shared" ref="P179:P183" si="62">O179/I179</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q179" s="101"/>
@@ -62481,81 +61891,81 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G183 H56">
-    <cfRule type="cellIs" dxfId="33" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P183 Q60:R60">
-    <cfRule type="cellIs" dxfId="32" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="17" operator="greaterThan">
       <formula>23</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R420">
-    <cfRule type="cellIs" dxfId="31" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="19" operator="greaterThan">
       <formula>88</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X63">
-    <cfRule type="cellIs" dxfId="30" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="16" operator="lessThan">
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X48">
-    <cfRule type="cellIs" dxfId="29" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="9" operator="lessThan">
       <formula>19</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y63">
-    <cfRule type="cellIs" dxfId="28" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="13" operator="lessThan">
       <formula>11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y48">
-    <cfRule type="cellIs" dxfId="27" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="8" operator="lessThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z48">
-    <cfRule type="cellIs" dxfId="26" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="10" operator="lessThan">
       <formula>3.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA177">
-    <cfRule type="cellIs" dxfId="25" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="18" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF63">
-    <cfRule type="cellIs" dxfId="24" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="12" operator="lessThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG1:AJ531">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
       <formula>6.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK1:AK231">
-    <cfRule type="cellIs" dxfId="23" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="20" operator="greaterThan">
       <formula>22.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL477">
-    <cfRule type="containsText" dxfId="22" priority="6" operator="containsText" text="Neg">
+    <cfRule type="containsText" dxfId="27" priority="6" operator="containsText" text="Neg">
       <formula>NOT(ISERROR(SEARCH("Neg",AL2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="7" operator="containsText" text="Pos">
+    <cfRule type="containsText" dxfId="26" priority="7" operator="containsText" text="Pos">
       <formula>NOT(ISERROR(SEARCH("Pos",AL2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP174">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62565,52 +61975,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:DA484"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" customWidth="1"/>
-    <col min="25" max="25" width="5.5703125" customWidth="1"/>
-    <col min="26" max="26" width="3.42578125" customWidth="1"/>
-    <col min="27" max="27" width="5.85546875" customWidth="1"/>
-    <col min="28" max="28" width="7.28515625" customWidth="1"/>
-    <col min="29" max="29" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="7.140625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="5.5703125" customWidth="1"/>
-    <col min="34" max="34" width="6.28515625" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" customWidth="1"/>
-    <col min="36" max="36" width="4.42578125" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" customWidth="1"/>
+    <col min="20" max="20" width="5.33203125" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.33203125" customWidth="1"/>
+    <col min="25" max="25" width="5.5546875" customWidth="1"/>
+    <col min="26" max="26" width="3.44140625" customWidth="1"/>
+    <col min="27" max="27" width="5.88671875" customWidth="1"/>
+    <col min="28" max="28" width="7.33203125" customWidth="1"/>
+    <col min="29" max="29" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.109375" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="5.5546875" customWidth="1"/>
+    <col min="34" max="34" width="6.33203125" customWidth="1"/>
+    <col min="35" max="35" width="8.88671875" customWidth="1"/>
+    <col min="36" max="36" width="4.44140625" customWidth="1"/>
     <col min="38" max="42" width="13" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="1.5703125" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="1.5546875" hidden="1" customWidth="1"/>
     <col min="53" max="54" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104" ht="92.45" customHeight="1">
+    <row r="1" spans="1:104" ht="92.4" customHeight="1">
       <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
@@ -71412,7 +70822,7 @@
         <v>15.6</v>
       </c>
       <c r="G66" s="70">
-        <f t="shared" ref="G66:G97" si="18">100*(F66-E66)/F66</f>
+        <f t="shared" ref="G66:G89" si="18">100*(F66-E66)/F66</f>
         <v>82.371794871794876</v>
       </c>
       <c r="H66" s="75">
@@ -71434,7 +70844,7 @@
         <v>120.99</v>
       </c>
       <c r="P66" s="70">
-        <f t="shared" ref="P66:P97" si="19">O66/I66</f>
+        <f t="shared" ref="P66:P89" si="19">O66/I66</f>
         <v>16.003968253968253</v>
       </c>
       <c r="Q66" s="75">
@@ -71467,7 +70877,7 @@
         <v>4</v>
       </c>
       <c r="AC66" s="70">
-        <f t="shared" ref="AC66:AC97" si="21">IF(AB66&gt;6.2,1,0)+AB66/5</f>
+        <f t="shared" ref="AC66:AC89" si="21">IF(AB66&gt;6.2,1,0)+AB66/5</f>
         <v>0.8</v>
       </c>
       <c r="AD66" s="71">
@@ -71484,11 +70894,11 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="AH66" s="70">
-        <f t="shared" ref="AH66:AH97" si="23">AG66+IF(X66&lt;1.35,0,1)+IF(Y66&lt;1.35,0,1)+AC66+AA66</f>
+        <f t="shared" ref="AH66:AH89" si="23">AG66+IF(X66&lt;1.35,0,1)+IF(Y66&lt;1.35,0,1)+AC66+AA66</f>
         <v>8.8999999999999986</v>
       </c>
       <c r="AI66" s="70">
-        <f t="shared" ref="AI66:AI97" si="24">AG66+AH66*1.4</f>
+        <f t="shared" ref="AI66:AI89" si="24">AG66+AH66*1.4</f>
         <v>17.559999999999995</v>
       </c>
       <c r="AJ66" s="71" t="str">
@@ -78924,97 +78334,97 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D173">
-    <cfRule type="containsText" dxfId="124" priority="23" operator="containsText" text="neg">
+    <cfRule type="containsText" dxfId="22" priority="23" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH(("neg"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G484">
-    <cfRule type="cellIs" dxfId="123" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="16" operator="lessThan">
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P484">
-    <cfRule type="cellIs" dxfId="122" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="17" operator="greaterThan">
       <formula>14.56</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q172">
-    <cfRule type="cellIs" dxfId="121" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R181">
-    <cfRule type="cellIs" dxfId="120" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="13" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB90">
-    <cfRule type="cellIs" dxfId="119" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE173">
-    <cfRule type="cellIs" dxfId="118" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="15" operator="lessThan">
       <formula>10.56</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG474">
-    <cfRule type="cellIs" dxfId="117" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="21" operator="greaterThan">
       <formula>4.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH474">
-    <cfRule type="cellIs" dxfId="116" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="19" operator="greaterThan">
       <formula>8.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AI474">
-    <cfRule type="cellIs" dxfId="115" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="22" operator="greaterThan">
       <formula>16.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ474">
-    <cfRule type="containsText" dxfId="114" priority="2" operator="containsText" text="neg">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH(("neg"),(AJ2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="113" priority="14" operator="containsText" text="Pos">
+    <cfRule type="containsText" dxfId="11" priority="14" operator="containsText" text="Pos">
       <formula>NOT(ISERROR(SEARCH("Pos",AJ2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL193">
-    <cfRule type="endsWith" dxfId="112" priority="3" operator="endsWith" text="4">
+    <cfRule type="endsWith" dxfId="10" priority="3" operator="endsWith" text="4">
       <formula>RIGHT(AL2,LEN("4"))="4"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="111" priority="4" operator="endsWith" text="2">
+    <cfRule type="endsWith" dxfId="9" priority="4" operator="endsWith" text="2">
       <formula>RIGHT(AL2,LEN("2"))="2"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="110" priority="5" operator="endsWith" text="7">
+    <cfRule type="endsWith" dxfId="8" priority="5" operator="endsWith" text="7">
       <formula>RIGHT(AL2,LEN("7"))="7"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="109" priority="6" operator="endsWith" text="0">
+    <cfRule type="endsWith" dxfId="7" priority="6" operator="endsWith" text="0">
       <formula>RIGHT(AL2,LEN("0"))="0"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="108" priority="7" operator="endsWith" text="8">
+    <cfRule type="endsWith" dxfId="6" priority="7" operator="endsWith" text="8">
       <formula>RIGHT(AL2,LEN("8"))="8"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="107" priority="8" operator="endsWith" text="9">
+    <cfRule type="endsWith" dxfId="5" priority="8" operator="endsWith" text="9">
       <formula>RIGHT(AL2,LEN("9"))="9"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="106" priority="9" operator="endsWith" text="6">
+    <cfRule type="endsWith" dxfId="4" priority="9" operator="endsWith" text="6">
       <formula>RIGHT(AL2,LEN("6"))="6"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="105" priority="10" operator="endsWith" text="1">
+    <cfRule type="endsWith" dxfId="3" priority="10" operator="endsWith" text="1">
       <formula>RIGHT(AL2,LEN("1"))="1"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="104" priority="11" operator="endsWith" text="3">
+    <cfRule type="endsWith" dxfId="2" priority="11" operator="endsWith" text="3">
       <formula>RIGHT(AL2,LEN("3"))="3"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="103" priority="12" operator="endsWith" text="5">
+    <cfRule type="endsWith" dxfId="1" priority="12" operator="endsWith" text="5">
       <formula>RIGHT(AL2,LEN("5"))="5"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT2:AT200">
-    <cfRule type="cellIs" dxfId="102" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/General.xlsx
+++ b/General.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Personal\cff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2433D8-CCCC-4524-B945-17184C55D533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="2340" windowWidth="38640" windowHeight="21120"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IPOSME" sheetId="1" r:id="rId1"/>
     <sheet name="IPOMB" sheetId="2" r:id="rId2"/>
     <sheet name="IPOSME (2)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1124,7 +1125,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -2533,83 +2534,83 @@
     </dxf>
   </dxfs>
   <tableStyles count="19" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3">
+    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="headerRow" dxfId="108"/>
       <tableStyleElement type="firstRowStripe" dxfId="107"/>
       <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style" pivot="0" count="3">
+    <tableStyle name="SME IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="105"/>
       <tableStyleElement type="firstRowStripe" dxfId="104"/>
       <tableStyleElement type="secondRowStripe" dxfId="103"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="firstRowStripe" dxfId="102"/>
       <tableStyleElement type="secondRowStripe" dxfId="101"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
       <tableStyleElement type="firstRowStripe" dxfId="100"/>
       <tableStyleElement type="secondRowStripe" dxfId="99"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
       <tableStyleElement type="firstRowStripe" dxfId="98"/>
       <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
       <tableStyleElement type="firstRowStripe" dxfId="96"/>
       <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
       <tableStyleElement type="firstRowStripe" dxfId="94"/>
       <tableStyleElement type="secondRowStripe" dxfId="93"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style" pivot="0" count="3">
+    <tableStyle name="SME IPO v2-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
       <tableStyleElement type="headerRow" dxfId="92"/>
       <tableStyleElement type="firstRowStripe" dxfId="91"/>
       <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
       <tableStyleElement type="firstRowStripe" dxfId="89"/>
       <tableStyleElement type="secondRowStripe" dxfId="88"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
       <tableStyleElement type="firstRowStripe" dxfId="87"/>
       <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
       <tableStyleElement type="firstRowStripe" dxfId="85"/>
       <tableStyleElement type="secondRowStripe" dxfId="84"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
       <tableStyleElement type="firstRowStripe" dxfId="83"/>
       <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
       <tableStyleElement type="firstRowStripe" dxfId="81"/>
       <tableStyleElement type="secondRowStripe" dxfId="80"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style" pivot="0" count="3">
+    <tableStyle name="SME IPO v3-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
       <tableStyleElement type="headerRow" dxfId="79"/>
       <tableStyleElement type="firstRowStripe" dxfId="78"/>
       <tableStyleElement type="secondRowStripe" dxfId="77"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
       <tableStyleElement type="firstRowStripe" dxfId="76"/>
       <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
       <tableStyleElement type="firstRowStripe" dxfId="74"/>
       <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF10000000}">
       <tableStyleElement type="firstRowStripe" dxfId="72"/>
       <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF11000000}">
       <tableStyleElement type="firstRowStripe" dxfId="70"/>
       <tableStyleElement type="secondRowStripe" dxfId="69"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF12000000}">
       <tableStyleElement type="firstRowStripe" dxfId="68"/>
       <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
@@ -2822,51 +2823,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DF471"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:DF470"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" style="108" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" customWidth="1"/>
-    <col min="24" max="24" width="7.28515625" customWidth="1"/>
-    <col min="25" max="25" width="10.28515625" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" customWidth="1"/>
-    <col min="27" max="27" width="5.85546875" customWidth="1"/>
-    <col min="28" max="28" width="7.28515625" customWidth="1"/>
-    <col min="29" max="29" width="5.85546875" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" customWidth="1"/>
-    <col min="31" max="31" width="7.7109375" customWidth="1"/>
-    <col min="32" max="32" width="8.42578125" customWidth="1"/>
-    <col min="33" max="33" width="7.28515625" customWidth="1"/>
-    <col min="34" max="36" width="6.28515625" customWidth="1"/>
-    <col min="37" max="37" width="8.85546875" customWidth="1"/>
-    <col min="38" max="38" width="4.42578125" customWidth="1"/>
-    <col min="39" max="39" width="20.140625" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" style="108" customWidth="1"/>
+    <col min="20" max="20" width="5.33203125" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" customWidth="1"/>
+    <col min="24" max="24" width="7.33203125" customWidth="1"/>
+    <col min="25" max="25" width="10.33203125" customWidth="1"/>
+    <col min="26" max="26" width="8.5546875" customWidth="1"/>
+    <col min="27" max="27" width="5.88671875" customWidth="1"/>
+    <col min="28" max="28" width="7.33203125" customWidth="1"/>
+    <col min="29" max="29" width="5.88671875" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" customWidth="1"/>
+    <col min="31" max="31" width="7.6640625" customWidth="1"/>
+    <col min="32" max="32" width="8.44140625" customWidth="1"/>
+    <col min="33" max="33" width="7.33203125" customWidth="1"/>
+    <col min="34" max="36" width="6.33203125" customWidth="1"/>
+    <col min="37" max="37" width="8.88671875" customWidth="1"/>
+    <col min="38" max="38" width="4.44140625" customWidth="1"/>
+    <col min="39" max="39" width="20.109375" customWidth="1"/>
+    <col min="40" max="40" width="6.5546875" customWidth="1"/>
     <col min="42" max="48" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" ht="92.45" customHeight="1">
+    <row r="1" spans="1:59" ht="92.4" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -17596,7 +17598,7 @@
         <v>20.73</v>
       </c>
       <c r="G98" s="16">
-        <f t="shared" ref="G98:G129" si="28">100*(F98-E98)/F98</f>
+        <f t="shared" ref="G98:G117" si="28">100*(F98-E98)/F98</f>
         <v>-6.5605402797877446</v>
       </c>
       <c r="H98" s="37">
@@ -17618,7 +17620,7 @@
         <v>78.900000000000006</v>
       </c>
       <c r="P98" s="16">
-        <f t="shared" ref="P98:P129" si="29">O98/I98</f>
+        <f t="shared" ref="P98:P117" si="29">O98/I98</f>
         <v>8.7959866220735794</v>
       </c>
       <c r="Q98" s="9">
@@ -17692,7 +17694,7 @@
         <v>2</v>
       </c>
       <c r="AO98" s="17">
-        <f t="shared" ref="AO98:AO129" si="31">AN98+1</f>
+        <f t="shared" ref="AO98:AO123" si="31">AN98+1</f>
         <v>3</v>
       </c>
       <c r="AP98" s="17">
@@ -30372,7 +30374,7 @@
         <v>0</v>
       </c>
       <c r="AG258" s="118" t="e">
-        <f t="shared" ref="AG258:AG326" si="57">IF(G258&lt;52,0,0.7)+IF(G258&lt;34,0,0.7)+IF(G258&lt;1,0,0.7)+IF(P258&gt;14.56,0,1)+IF(R258&lt;9,0.5,0)+IF(R258&lt;33.8,0.5,0)+IF(R258&lt;50,0.5,0)+IF(R258&lt;80,0.5,0)+IF(S258=5,0,S258)+IF(V258&gt;0,1,0)+IF(AE258&lt;10.56,0,1)-IF(AE258&lt;3,1,0)-IF(AE258&lt;1,1,0)</f>
+        <f t="shared" ref="AG258:AG325" si="57">IF(G258&lt;52,0,0.7)+IF(G258&lt;34,0,0.7)+IF(G258&lt;1,0,0.7)+IF(P258&gt;14.56,0,1)+IF(R258&lt;9,0.5,0)+IF(R258&lt;33.8,0.5,0)+IF(R258&lt;50,0.5,0)+IF(R258&lt;80,0.5,0)+IF(S258=5,0,S258)+IF(V258&gt;0,1,0)+IF(AE258&lt;10.56,0,1)-IF(AE258&lt;3,1,0)-IF(AE258&lt;1,1,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH258" s="16" t="e">
@@ -30404,7 +30406,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ258" s="17" t="e">
-        <f t="shared" ref="AQ258:AQ321" si="62">IF(AP258&gt;0,IF(AB258&gt;10,(AB258/Z258),10/Z258),0)</f>
+        <f t="shared" ref="AQ258:AQ281" si="62">IF(AP258&gt;0,IF(AB258&gt;10,(AB258/Z258),10/Z258),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR258" s="17"/>
@@ -31819,11 +31821,6 @@
         <f t="shared" si="61"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ282" s="17" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AR282" s="17"/>
     </row>
     <row r="283" spans="7:44">
       <c r="G283" s="16" t="e">
@@ -33965,7 +33962,7 @@
         <v>1</v>
       </c>
       <c r="AK322" s="16" t="e">
-        <f t="shared" ref="AK322:AK385" si="70">(1.2*AG322+AH322)*AJ322</f>
+        <f t="shared" ref="AK322:AK349" si="70">(1.2*AG322+AH322)*AJ322</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL322" s="15">
@@ -34003,7 +34000,7 @@
         <v>1</v>
       </c>
       <c r="AC323" s="16">
-        <f t="shared" ref="AC323:AC386" si="73">IF(AB323&gt;4,1,0)+AB323/12</f>
+        <f t="shared" ref="AC323:AC338" si="73">IF(AB323&gt;4,1,0)+AB323/12</f>
         <v>0</v>
       </c>
       <c r="AG323" s="118" t="e">
@@ -34168,8 +34165,8 @@
         <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="AG326" s="118" t="e">
-        <f t="shared" si="57"/>
+      <c r="AG326" s="15" t="e">
+        <f t="shared" ref="AG326:AG357" si="74">IF(G326&lt;52,0,0.7)+IF(G326&lt;34,0,0.7)+IF(G326&lt;1,0,0.7)+IF(P326&gt;14.56,0,1)+IF(R326&lt;9,0.5,0)+IF(R326&lt;33.8,0.5,0)+IF(R326&lt;50,0.5,0)+IF(R326&lt;80,0.5,0)+IF(V326&gt;0,1,0)+IF(AE326&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH326" s="16" t="e">
@@ -34223,7 +34220,7 @@
         <v>0</v>
       </c>
       <c r="AG327" s="15" t="e">
-        <f t="shared" ref="AG327:AG358" si="74">IF(G327&lt;52,0,0.7)+IF(G327&lt;34,0,0.7)+IF(G327&lt;1,0,0.7)+IF(P327&gt;14.56,0,1)+IF(R327&lt;9,0.5,0)+IF(R327&lt;33.8,0.5,0)+IF(R327&lt;50,0.5,0)+IF(R327&lt;80,0.5,0)+IF(V327&gt;0,1,0)+IF(AE327&lt;10.56,0,1)</f>
+        <f t="shared" si="74"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH327" s="16" t="e">
@@ -34463,7 +34460,7 @@
         <v>0</v>
       </c>
       <c r="AO331" s="17">
-        <f t="shared" ref="AO331:AO394" si="78">AN331+1</f>
+        <f t="shared" ref="AO331:AO350" si="78">AN331+1</f>
         <v>1</v>
       </c>
       <c r="AP331" s="17" t="e">
@@ -34867,7 +34864,7 @@
         <v>1</v>
       </c>
       <c r="AC339" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" ref="AC339:AC363" si="79">IF(AB339&gt;9,1,0)+AB339/3</f>
         <v>0</v>
       </c>
       <c r="AG339" s="15" t="e">
@@ -34921,7 +34918,7 @@
         <v>1</v>
       </c>
       <c r="AC340" s="16">
-        <f t="shared" ref="AC340:AC364" si="79">IF(AB340&gt;9,1,0)+AB340/3</f>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG340" s="15" t="e">
@@ -35477,7 +35474,7 @@
         <v>1</v>
       </c>
       <c r="AK350" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" ref="AK350:AK381" si="80">(2*AG350+AH350)*AJ350</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL350" s="15">
@@ -35531,7 +35528,7 @@
         <v>1</v>
       </c>
       <c r="AK351" s="16" t="e">
-        <f t="shared" ref="AK351:AK382" si="80">(2*AG351+AH351)*AJ351</f>
+        <f t="shared" si="80"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL351" s="15">
@@ -35541,10 +35538,6 @@
       <c r="AM351" s="15">
         <f t="shared" si="77"/>
         <v>0</v>
-      </c>
-      <c r="AO351" s="17">
-        <f t="shared" si="78"/>
-        <v>1</v>
       </c>
       <c r="AP351" s="17" t="e">
         <f t="shared" si="72"/>
@@ -35581,9 +35574,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AI352" s="16"/>
-      <c r="AJ352" s="16">
-        <v>1</v>
-      </c>
+      <c r="AJ352" s="16"/>
       <c r="AK352" s="16" t="e">
         <f t="shared" si="80"/>
         <v>#DIV/0!</v>
@@ -35863,7 +35854,7 @@
         <v>0</v>
       </c>
       <c r="AG358" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" ref="AG358:AG389" si="81">IF(G358&lt;52,0,0.7)+IF(G358&lt;34,0,0.7)+IF(G358&lt;1,0,0.7)+IF(P358&gt;14.56,0,1)+IF(R358&lt;9,0.5,0)+IF(R358&lt;33.8,0.5,0)+IF(R358&lt;50,0.5,0)+IF(R358&lt;80,0.5,0)+IF(V358&gt;0,1,0)+IF(AE358&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH358" s="16" t="e">
@@ -35911,7 +35902,7 @@
         <v>0</v>
       </c>
       <c r="AG359" s="15" t="e">
-        <f t="shared" ref="AG359:AG390" si="81">IF(G359&lt;52,0,0.7)+IF(G359&lt;34,0,0.7)+IF(G359&lt;1,0,0.7)+IF(P359&gt;14.56,0,1)+IF(R359&lt;9,0.5,0)+IF(R359&lt;33.8,0.5,0)+IF(R359&lt;50,0.5,0)+IF(R359&lt;80,0.5,0)+IF(V359&gt;0,1,0)+IF(AE359&lt;10.56,0,1)</f>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH359" s="16" t="e">
@@ -36147,7 +36138,7 @@
         <v>1</v>
       </c>
       <c r="AC364" s="16">
-        <f t="shared" si="79"/>
+        <f t="shared" ref="AC364:AC395" si="82">IF(U365&gt;9,1,0)+U365/3</f>
         <v>0</v>
       </c>
       <c r="AG364" s="15" t="e">
@@ -36195,7 +36186,7 @@
         <v>1</v>
       </c>
       <c r="AC365" s="16">
-        <f t="shared" ref="AC365:AC396" si="82">IF(U366&gt;9,1,0)+U366/3</f>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="AG365" s="15" t="e">
@@ -37025,7 +37016,7 @@
       <c r="AI382" s="16"/>
       <c r="AJ382" s="16"/>
       <c r="AK382" s="16" t="e">
-        <f t="shared" si="80"/>
+        <f t="shared" ref="AK382:AK413" si="83">(2*AG382+AH382)*AJ382</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL382" s="15">
@@ -37073,7 +37064,7 @@
       <c r="AI383" s="16"/>
       <c r="AJ383" s="16"/>
       <c r="AK383" s="16" t="e">
-        <f t="shared" ref="AK383:AK414" si="83">(2*AG383+AH383)*AJ383</f>
+        <f t="shared" si="83"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL383" s="15">
@@ -37399,7 +37390,7 @@
         <v>0</v>
       </c>
       <c r="AG390" s="15" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" ref="AG390:AG421" si="88">IF(G390&lt;52,0,0.7)+IF(G390&lt;34,0,0.7)+IF(G390&lt;1,0,0.7)+IF(P390&gt;14.56,0,1)+IF(R390&lt;9,0.5,0)+IF(R390&lt;33.8,0.5,0)+IF(R390&lt;50,0.5,0)+IF(R390&lt;80,0.5,0)+IF(V390&gt;0,1,0)+IF(AE390&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH390" s="16" t="e">
@@ -37447,7 +37438,7 @@
         <v>0</v>
       </c>
       <c r="AG391" s="15" t="e">
-        <f t="shared" ref="AG391:AG422" si="88">IF(G391&lt;52,0,0.7)+IF(G391&lt;34,0,0.7)+IF(G391&lt;1,0,0.7)+IF(P391&gt;14.56,0,1)+IF(R391&lt;9,0.5,0)+IF(R391&lt;33.8,0.5,0)+IF(R391&lt;50,0.5,0)+IF(R391&lt;80,0.5,0)+IF(V391&gt;0,1,0)+IF(AE391&lt;10.56,0,1)</f>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH391" s="16" t="e">
@@ -37657,7 +37648,7 @@
         <v>0</v>
       </c>
       <c r="AM395" s="15">
-        <f t="shared" ref="AM395:AM460" si="91">B395</f>
+        <f t="shared" ref="AM395:AM459" si="91">B395</f>
         <v>0</v>
       </c>
       <c r="AP395" s="17" t="e">
@@ -37683,7 +37674,7 @@
         <v>1</v>
       </c>
       <c r="AC396" s="16">
-        <f t="shared" si="82"/>
+        <f t="shared" ref="AC396:AC427" si="92">IF(U397&gt;9,1,0)+U397/3</f>
         <v>0</v>
       </c>
       <c r="AG396" s="15" t="e">
@@ -37731,7 +37722,7 @@
         <v>1</v>
       </c>
       <c r="AC397" s="16">
-        <f t="shared" ref="AC397:AC428" si="92">IF(U398&gt;9,1,0)+U398/3</f>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AG397" s="15" t="e">
@@ -38561,7 +38552,7 @@
       <c r="AI414" s="16"/>
       <c r="AJ414" s="16"/>
       <c r="AK414" s="16" t="e">
-        <f t="shared" si="83"/>
+        <f t="shared" ref="AK414:AK445" si="93">(2*AG414+AH414)*AJ414</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL414" s="15">
@@ -38609,7 +38600,7 @@
       <c r="AI415" s="16"/>
       <c r="AJ415" s="16"/>
       <c r="AK415" s="16" t="e">
-        <f t="shared" ref="AK415:AK446" si="93">(2*AG415+AH415)*AJ415</f>
+        <f t="shared" si="93"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL415" s="15">
@@ -38935,7 +38926,7 @@
         <v>0</v>
       </c>
       <c r="AG422" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" ref="AG422:AG455" si="94">IF(G422&lt;52,0,0.7)+IF(G422&lt;34,0,0.7)+IF(G422&lt;1,0,0.7)+IF(P422&gt;14.56,0,1)+IF(R422&lt;9,0.5,0)+IF(R422&lt;33.8,0.5,0)+IF(R422&lt;50,0.5,0)+IF(R422&lt;80,0.5,0)+IF(V422&gt;0,1,0)+IF(AE422&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH422" s="16" t="e">
@@ -38983,7 +38974,7 @@
         <v>0</v>
       </c>
       <c r="AG423" s="15" t="e">
-        <f t="shared" ref="AG423:AG456" si="94">IF(G423&lt;52,0,0.7)+IF(G423&lt;34,0,0.7)+IF(G423&lt;1,0,0.7)+IF(P423&gt;14.56,0,1)+IF(R423&lt;9,0.5,0)+IF(R423&lt;33.8,0.5,0)+IF(R423&lt;50,0.5,0)+IF(R423&lt;80,0.5,0)+IF(V423&gt;0,1,0)+IF(AE423&lt;10.56,0,1)</f>
+        <f t="shared" si="94"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH423" s="16" t="e">
@@ -39219,7 +39210,7 @@
         <v>1</v>
       </c>
       <c r="AC428" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="AC428:AC453" si="95">IF(U429&gt;9,1,0)+U429/3</f>
         <v>0</v>
       </c>
       <c r="AG428" s="15" t="e">
@@ -39267,7 +39258,7 @@
         <v>1</v>
       </c>
       <c r="AC429" s="16">
-        <f t="shared" ref="AC429:AC454" si="95">IF(U430&gt;9,1,0)+U430/3</f>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="AG429" s="15" t="e">
@@ -40097,7 +40088,7 @@
       <c r="AI446" s="16"/>
       <c r="AJ446" s="16"/>
       <c r="AK446" s="16" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" ref="AK446:AK453" si="96">(2*AG446+AH446)*AJ446</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL446" s="15">
@@ -40145,7 +40136,7 @@
       <c r="AI447" s="16"/>
       <c r="AJ447" s="16"/>
       <c r="AK447" s="16" t="e">
-        <f t="shared" ref="AK447:AK478" si="96">(2*AG447+AH447)*AJ447</f>
+        <f t="shared" si="96"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL447" s="15">
@@ -40271,7 +40262,7 @@
         <v>5</v>
       </c>
       <c r="AA450" s="2">
-        <f t="shared" ref="AA450:AA513" si="97">IF(X450&lt;50,IF(Y450&gt;(2.3*X450),0,1),1)-IF(Z450&gt;Y450,1.7,0)</f>
+        <f t="shared" ref="AA450:AA451" si="97">IF(X450&lt;50,IF(Y450&gt;(2.3*X450),0,1),1)-IF(Z450&gt;Y450,1.7,0)</f>
         <v>1</v>
       </c>
       <c r="AC450" s="16">
@@ -40283,7 +40274,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH450" s="16" t="e">
-        <f t="shared" ref="AH450:AH513" si="98">AG450+IF(X450&lt;1.35,0,1)+IF(Y450&lt;1.35,0,1)+AC450+AA450</f>
+        <f t="shared" ref="AH450:AH459" si="98">AG450+IF(X450&lt;1.35,0,1)+IF(Y450&lt;1.35,0,1)+AC450+AA450</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI450" s="16"/>
@@ -40293,7 +40284,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL450" s="15">
-        <f t="shared" ref="AL450:AL460" si="99">D450</f>
+        <f t="shared" ref="AL450:AL459" si="99">D450</f>
         <v>0</v>
       </c>
       <c r="AM450" s="15">
@@ -40301,7 +40292,7 @@
         <v>0</v>
       </c>
       <c r="AP450" s="17" t="e">
-        <f t="shared" ref="AP450:AP459" si="100">IF(AK450&gt;13.8,IF(Z450&lt;101,IF(Z450&lt;35,IF(Z450&lt;8,3,2),1),0),0)</f>
+        <f t="shared" ref="AP450:AP458" si="100">IF(AK450&gt;13.8,IF(Z450&lt;101,IF(Z450&lt;35,IF(Z450&lt;8,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40364,10 +40355,10 @@
       </c>
       <c r="R452" s="111"/>
       <c r="S452" s="118">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA452" s="2">
-        <f t="shared" si="97"/>
+        <f>IF(X452&lt;50,IF(Y452&gt;(2.3*X452),0,1),1)-IF(Z452&gt;Y452,1.5,0)</f>
         <v>1</v>
       </c>
       <c r="AC452" s="16">
@@ -40459,15 +40450,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R454" s="111"/>
-      <c r="S454" s="118">
-        <v>0</v>
-      </c>
       <c r="AA454" s="2">
-        <f>IF(X454&lt;50,IF(Y454&gt;(2.3*X454),0,1),1)-IF(Z454&gt;Y454,1.5,0)</f>
+        <f t="shared" ref="AA454:AA459" si="101">IF(X454&lt;50,IF(Y454&gt;(2.3*X454),0,1),1)</f>
         <v>1</v>
       </c>
       <c r="AC454" s="16">
-        <f t="shared" si="95"/>
+        <f>IF(AB454&gt;6.2,1,0)+AB454/5</f>
         <v>0</v>
       </c>
       <c r="AG454" s="15" t="e">
@@ -40481,7 +40469,7 @@
       <c r="AI454" s="16"/>
       <c r="AJ454" s="16"/>
       <c r="AK454" s="16" t="e">
-        <f t="shared" si="96"/>
+        <f t="shared" ref="AK454:AK459" si="102">AG454+AH454*1.4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL454" s="15">
@@ -40508,7 +40496,7 @@
       </c>
       <c r="R455" s="111"/>
       <c r="AA455" s="2">
-        <f t="shared" ref="AA455:AA460" si="101">IF(X455&lt;50,IF(Y455&gt;(2.3*X455),0,1),1)</f>
+        <f t="shared" si="101"/>
         <v>1</v>
       </c>
       <c r="AC455" s="16">
@@ -40526,7 +40514,7 @@
       <c r="AI455" s="16"/>
       <c r="AJ455" s="16"/>
       <c r="AK455" s="16" t="e">
-        <f t="shared" ref="AK455:AK460" si="102">AG455+AH455*1.4</f>
+        <f t="shared" si="102"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL455" s="15">
@@ -40561,7 +40549,7 @@
         <v>0</v>
       </c>
       <c r="AG456" s="15" t="e">
-        <f t="shared" si="94"/>
+        <f>IF(G456&lt;52,0,0.7)+IF(G456&lt;34,0,0.7)+IF(G456&lt;1,0,0.7)+IF(P456&gt;14.56,0,1)+IF(Q456&gt;33.8,0,1)+IF(V456&gt;0,1,0)+IF(AE456&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH456" s="16" t="e">
@@ -40679,21 +40667,17 @@
     </row>
     <row r="459" spans="7:42">
       <c r="G459" s="16" t="e">
-        <f t="shared" ref="G459:G522" si="103">100*(F459-E459)/F459</f>
+        <f t="shared" ref="G459" si="103">100*(F459-E459)/F459</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P459" s="16" t="e">
-        <f t="shared" ref="P459:P522" si="104">O459/I459</f>
+        <f t="shared" ref="P459" si="104">O459/I459</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R459" s="111"/>
       <c r="AA459" s="2">
         <f t="shared" si="101"/>
         <v>1</v>
-      </c>
-      <c r="AC459" s="16">
-        <f>IF(AB459&gt;6.2,1,0)+AB459/5</f>
-        <v>0</v>
       </c>
       <c r="AG459" s="15" t="e">
         <f>IF(G459&lt;52,0,0.7)+IF(G459&lt;34,0,0.7)+IF(G459&lt;1,0,0.7)+IF(P459&gt;14.56,0,1)+IF(Q459&gt;33.8,0,1)+IF(V459&gt;0,1,0)+IF(AE459&lt;10.56,0,1)</f>
@@ -40717,47 +40701,9 @@
         <f t="shared" si="91"/>
         <v>0</v>
       </c>
-      <c r="AP459" s="17" t="e">
-        <f t="shared" si="100"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="460" spans="7:42">
-      <c r="G460" s="16" t="e">
-        <f t="shared" si="103"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P460" s="16" t="e">
-        <f t="shared" si="104"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="R460" s="111"/>
-      <c r="AA460" s="2">
-        <f t="shared" si="101"/>
-        <v>1</v>
-      </c>
-      <c r="AG460" s="15" t="e">
-        <f>IF(G460&lt;52,0,0.7)+IF(G460&lt;34,0,0.7)+IF(G460&lt;1,0,0.7)+IF(P460&gt;14.56,0,1)+IF(Q460&gt;33.8,0,1)+IF(V460&gt;0,1,0)+IF(AE460&lt;10.56,0,1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH460" s="16" t="e">
-        <f t="shared" si="98"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI460" s="16"/>
-      <c r="AJ460" s="16"/>
-      <c r="AK460" s="16" t="e">
-        <f t="shared" si="102"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL460" s="15">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="AM460" s="15">
-        <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="461" spans="7:42">
       <c r="R461" s="111"/>
@@ -40789,31 +40735,28 @@
     <row r="470" spans="18:18">
       <c r="R470" s="111"/>
     </row>
-    <row r="471" spans="18:18">
-      <c r="R471" s="111"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D149">
+  <conditionalFormatting sqref="D2:D148">
     <cfRule type="containsText" dxfId="66" priority="37" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH(("neg"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G460">
+  <conditionalFormatting sqref="G2:G459">
     <cfRule type="cellIs" dxfId="65" priority="30" operator="lessThan">
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P460">
+  <conditionalFormatting sqref="P2:P459">
     <cfRule type="cellIs" dxfId="64" priority="31" operator="greaterThan">
       <formula>14.56</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q148">
+  <conditionalFormatting sqref="Q2:Q147">
     <cfRule type="cellIs" dxfId="63" priority="34" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R157">
+  <conditionalFormatting sqref="R1:R156">
     <cfRule type="cellIs" dxfId="62" priority="26" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
@@ -40823,27 +40766,27 @@
       <formula>LEN(TRIM(X2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE149">
+  <conditionalFormatting sqref="AE2:AE148">
     <cfRule type="cellIs" dxfId="60" priority="29" operator="lessThan">
       <formula>10.56</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG460">
+  <conditionalFormatting sqref="AG2:AG459">
     <cfRule type="cellIs" dxfId="59" priority="35" operator="greaterThan">
       <formula>4.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AJ460">
+  <conditionalFormatting sqref="AH2:AJ459">
     <cfRule type="cellIs" dxfId="58" priority="33" operator="greaterThan">
       <formula>8.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK2:AK460">
+  <conditionalFormatting sqref="AK2:AK459">
     <cfRule type="cellIs" dxfId="57" priority="36" operator="greaterThan">
       <formula>13.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL460">
+  <conditionalFormatting sqref="AL2:AL459">
     <cfRule type="containsText" dxfId="56" priority="8" operator="containsText" text="Rec">
       <formula>NOT(ISERROR(SEARCH("Rec",AL2)))</formula>
     </cfRule>
@@ -40854,7 +40797,7 @@
       <formula>NOT(ISERROR(SEARCH("Pos",AL2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN169">
+  <conditionalFormatting sqref="AN2:AN168">
     <cfRule type="endsWith" dxfId="53" priority="13" operator="endsWith" text="4">
       <formula>RIGHT(AN2,LEN("4"))="4"</formula>
     </cfRule>
@@ -40886,7 +40829,7 @@
       <formula>RIGHT(AN2,LEN("5"))="5"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AP2:AP463">
+  <conditionalFormatting sqref="AP2:AP462">
     <cfRule type="containsText" dxfId="43" priority="1" operator="containsText" text="2">
       <formula>NOT(ISERROR(SEARCH("2",AP2)))</formula>
     </cfRule>
@@ -40897,7 +40840,7 @@
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AY2:BG81 AY82 AY83:BG85 AY86:AZ86 AY87:BG97 BA82:BG82 BB86:BG86">
+  <conditionalFormatting sqref="AY2:BG81 AY82 BA82:BG82 AY83:BG85 AY86:AZ86 BB86:BG86 AY87:BG97">
     <cfRule type="cellIs" dxfId="40" priority="32" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -40908,59 +40851,59 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BB175"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" customWidth="1"/>
-    <col min="12" max="12" width="4.140625" customWidth="1"/>
-    <col min="13" max="14" width="6.5703125" customWidth="1"/>
-    <col min="15" max="15" width="7.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="4.88671875" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" customWidth="1"/>
+    <col min="12" max="12" width="4.109375" customWidth="1"/>
+    <col min="13" max="14" width="6.5546875" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.140625" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="5.5703125" customWidth="1"/>
-    <col min="22" max="22" width="6.140625" customWidth="1"/>
-    <col min="23" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="8.28515625" customWidth="1"/>
-    <col min="26" max="26" width="5.42578125" customWidth="1"/>
-    <col min="27" max="27" width="5.140625" customWidth="1"/>
-    <col min="28" max="28" width="4.5703125" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" customWidth="1"/>
-    <col min="30" max="30" width="6.5703125" customWidth="1"/>
-    <col min="31" max="31" width="5.7109375" customWidth="1"/>
-    <col min="32" max="32" width="6.28515625" customWidth="1"/>
-    <col min="33" max="36" width="4.85546875" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
+    <col min="21" max="21" width="5.5546875" customWidth="1"/>
+    <col min="22" max="22" width="6.109375" customWidth="1"/>
+    <col min="23" max="24" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="8.33203125" customWidth="1"/>
+    <col min="26" max="26" width="5.44140625" customWidth="1"/>
+    <col min="27" max="27" width="5.109375" customWidth="1"/>
+    <col min="28" max="28" width="4.5546875" customWidth="1"/>
+    <col min="29" max="29" width="4.88671875" customWidth="1"/>
+    <col min="30" max="30" width="6.5546875" customWidth="1"/>
+    <col min="31" max="31" width="5.6640625" customWidth="1"/>
+    <col min="32" max="32" width="6.33203125" customWidth="1"/>
+    <col min="33" max="36" width="4.88671875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
-    <col min="38" max="38" width="5.7109375" customWidth="1"/>
-    <col min="39" max="39" width="13.7109375" customWidth="1"/>
-    <col min="40" max="40" width="4.5703125" customWidth="1"/>
-    <col min="41" max="41" width="5.42578125" customWidth="1"/>
-    <col min="42" max="44" width="10.85546875" customWidth="1"/>
+    <col min="38" max="38" width="5.6640625" customWidth="1"/>
+    <col min="39" max="39" width="13.6640625" customWidth="1"/>
+    <col min="40" max="40" width="4.5546875" customWidth="1"/>
+    <col min="41" max="41" width="5.44140625" customWidth="1"/>
+    <col min="42" max="44" width="10.88671875" customWidth="1"/>
     <col min="45" max="45" width="6" customWidth="1"/>
-    <col min="46" max="46" width="6.140625" customWidth="1"/>
+    <col min="46" max="46" width="6.109375" customWidth="1"/>
     <col min="47" max="47" width="4" customWidth="1"/>
-    <col min="48" max="48" width="4.140625" customWidth="1"/>
-    <col min="49" max="50" width="5.28515625" customWidth="1"/>
-    <col min="51" max="51" width="6.7109375" customWidth="1"/>
-    <col min="52" max="52" width="3.85546875" customWidth="1"/>
+    <col min="48" max="48" width="4.109375" customWidth="1"/>
+    <col min="49" max="50" width="5.33203125" customWidth="1"/>
+    <col min="51" max="51" width="6.6640625" customWidth="1"/>
+    <col min="52" max="52" width="3.88671875" customWidth="1"/>
     <col min="53" max="53" width="4" customWidth="1"/>
-    <col min="54" max="54" width="4.7109375" customWidth="1"/>
+    <col min="54" max="54" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="92.45" customHeight="1">
+    <row r="1" spans="1:54" ht="92.4" customHeight="1">
       <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
@@ -41234,11 +41177,11 @@
       <c r="AN2" s="47"/>
       <c r="AO2" s="47"/>
       <c r="AP2" s="17">
-        <f t="shared" ref="AP2:AP33" si="9">IF(AK2&gt;22.9,IF(Z2&lt;101,IF(Z2&lt;35,IF(Z2&lt;8,3,2),1),0),0)</f>
+        <f>IF(AK2&gt;23,IF(Z2&lt;101,IF(Z2&lt;35,IF(Z2&lt;8,3,2),1),0),0)</f>
         <v>1</v>
       </c>
       <c r="AQ2" s="16">
-        <f t="shared" ref="AQ2:AQ33" si="10">IF(AP2&gt;0,IF(AB2&gt;10,(AB2/Z2),10/Z2),0)</f>
+        <f t="shared" ref="AQ2:AQ33" si="9">IF(AP2&gt;0,IF(AB2&gt;10,(AB2/Z2),10/Z2),0)</f>
         <v>0.66970265202250201</v>
       </c>
       <c r="AR2" s="47"/>
@@ -41379,11 +41322,11 @@
       <c r="AN3" s="47"/>
       <c r="AO3" s="47"/>
       <c r="AP3" s="17">
+        <f t="shared" ref="AP3:AP66" si="10">IF(AK3&gt;23,IF(Z3&lt;101,IF(Z3&lt;35,IF(Z3&lt;8,3,2),1),0),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AQ3" s="16">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="AQ3" s="16">
-        <f t="shared" si="10"/>
         <v>11.267605633802818</v>
       </c>
       <c r="AR3" s="47"/>
@@ -41524,11 +41467,11 @@
       <c r="AN4" s="47"/>
       <c r="AO4" s="47"/>
       <c r="AP4" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AQ4" s="16">
-        <f t="shared" si="10"/>
         <v>1.2533140515786936</v>
       </c>
       <c r="AR4" s="47"/>
@@ -41669,11 +41612,11 @@
       <c r="AN5" s="47"/>
       <c r="AO5" s="47"/>
       <c r="AP5" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AQ5" s="16">
-        <f t="shared" si="10"/>
         <v>0.51948051948051943</v>
       </c>
       <c r="AR5" s="47"/>
@@ -41814,11 +41757,11 @@
       <c r="AN6" s="47"/>
       <c r="AO6" s="47"/>
       <c r="AP6" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ6" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AQ6" s="16">
-        <f t="shared" si="10"/>
         <v>0.48261178140525191</v>
       </c>
       <c r="AR6" s="47"/>
@@ -41959,11 +41902,11 @@
       <c r="AN7" s="47"/>
       <c r="AO7" s="47"/>
       <c r="AP7" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AQ7" s="16">
-        <f t="shared" si="10"/>
         <v>0.83627578517004275</v>
       </c>
       <c r="AR7" s="47"/>
@@ -42104,11 +42047,11 @@
       <c r="AN8" s="47"/>
       <c r="AO8" s="47"/>
       <c r="AP8" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AQ8" s="16">
-        <f t="shared" si="10"/>
         <v>0.71413997143440122</v>
       </c>
       <c r="AR8" s="47"/>
@@ -42249,11 +42192,11 @@
       <c r="AN9" s="47"/>
       <c r="AO9" s="47"/>
       <c r="AP9" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ9" s="16">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="AQ9" s="16">
-        <f t="shared" si="10"/>
         <v>1.9859813084112148</v>
       </c>
       <c r="AR9" s="47"/>
@@ -42394,11 +42337,11 @@
       <c r="AN10" s="47"/>
       <c r="AO10" s="47"/>
       <c r="AP10" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AQ10" s="16">
-        <f t="shared" si="10"/>
         <v>0.43941411451398138</v>
       </c>
       <c r="AR10" s="47"/>
@@ -42539,11 +42482,11 @@
       <c r="AN11" s="47"/>
       <c r="AO11" s="47"/>
       <c r="AP11" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ11" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AQ11" s="16">
-        <f t="shared" si="10"/>
         <v>1.790977102697801</v>
       </c>
       <c r="AR11" s="47"/>
@@ -42684,11 +42627,11 @@
       <c r="AN12" s="47"/>
       <c r="AO12" s="47"/>
       <c r="AP12" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ12" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AQ12" s="16">
-        <f t="shared" si="10"/>
         <v>0.10734220695577501</v>
       </c>
       <c r="AR12" s="47"/>
@@ -42829,11 +42772,11 @@
       <c r="AN13" s="47"/>
       <c r="AO13" s="47"/>
       <c r="AP13" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="16">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR13" s="47"/>
@@ -42974,11 +42917,11 @@
       <c r="AN14" s="47"/>
       <c r="AO14" s="47"/>
       <c r="AP14" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="16">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR14" s="47"/>
@@ -43119,11 +43062,11 @@
       <c r="AN15" s="47"/>
       <c r="AO15" s="47"/>
       <c r="AP15" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ15" s="16">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="AQ15" s="16">
-        <f t="shared" si="10"/>
         <v>1.5931372549019607</v>
       </c>
       <c r="AR15" s="47"/>
@@ -43264,11 +43207,11 @@
       <c r="AN16" s="47"/>
       <c r="AO16" s="47"/>
       <c r="AP16" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ16" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="AQ16" s="16">
-        <f t="shared" si="10"/>
         <v>1.2005889681730659</v>
       </c>
       <c r="AR16" s="47"/>
@@ -43409,11 +43352,11 @@
       <c r="AN17" s="47"/>
       <c r="AO17" s="47"/>
       <c r="AP17" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ17" s="16">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="AQ17" s="16">
-        <f t="shared" si="10"/>
         <v>3.7997587454764781</v>
       </c>
       <c r="AR17" s="47"/>
@@ -43554,11 +43497,11 @@
       <c r="AN18" s="47"/>
       <c r="AO18" s="47"/>
       <c r="AP18" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ18" s="16">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="AQ18" s="16">
-        <f t="shared" si="10"/>
         <v>14.516129032258064</v>
       </c>
       <c r="AR18" s="47"/>
@@ -43699,11 +43642,11 @@
       <c r="AN19" s="47"/>
       <c r="AO19" s="47"/>
       <c r="AP19" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="16">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR19" s="47"/>
@@ -43844,11 +43787,11 @@
       <c r="AN20" s="47"/>
       <c r="AO20" s="47"/>
       <c r="AP20" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="16">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR20" s="47"/>
@@ -43989,11 +43932,11 @@
       <c r="AN21" s="47"/>
       <c r="AO21" s="47"/>
       <c r="AP21" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ21" s="16">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="AQ21" s="16">
-        <f t="shared" si="10"/>
         <v>2.7100271002710028</v>
       </c>
       <c r="AR21" s="47"/>
@@ -44134,11 +44077,11 @@
       <c r="AN22" s="47"/>
       <c r="AO22" s="47"/>
       <c r="AP22" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="16">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR22" s="47"/>
@@ -44273,11 +44216,11 @@
       <c r="AN23" s="47"/>
       <c r="AO23" s="47"/>
       <c r="AP23" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="16">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR23" s="47"/>
@@ -44412,11 +44355,11 @@
       <c r="AN24" s="47"/>
       <c r="AO24" s="47"/>
       <c r="AP24" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="16">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ24" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR24" s="47"/>
@@ -44551,11 +44494,11 @@
       <c r="AN25" s="47"/>
       <c r="AO25" s="47"/>
       <c r="AP25" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="16">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ25" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR25" s="47"/>
@@ -44690,11 +44633,11 @@
       <c r="AN26" s="47"/>
       <c r="AO26" s="47"/>
       <c r="AP26" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ26" s="16">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="AQ26" s="16">
-        <f t="shared" si="10"/>
         <v>0.55463117027176922</v>
       </c>
       <c r="AR26" s="47"/>
@@ -44829,11 +44772,11 @@
       <c r="AN27" s="47"/>
       <c r="AO27" s="47"/>
       <c r="AP27" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ27" s="16">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="AQ27" s="16">
-        <f t="shared" si="10"/>
         <v>2.3696682464454977</v>
       </c>
       <c r="AR27" s="47"/>
@@ -44968,11 +44911,11 @@
       <c r="AN28" s="47"/>
       <c r="AO28" s="47"/>
       <c r="AP28" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ28" s="16">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="AQ28" s="16">
-        <f t="shared" si="10"/>
         <v>0.30021014710297206</v>
       </c>
       <c r="AR28" s="47"/>
@@ -45109,11 +45052,11 @@
       <c r="AN29" s="47"/>
       <c r="AO29" s="47"/>
       <c r="AP29" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ29" s="16">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="AQ29" s="16">
-        <f t="shared" si="10"/>
         <v>5.0761421319796955</v>
       </c>
       <c r="AR29" s="47"/>
@@ -45250,11 +45193,11 @@
       <c r="AN30" s="47"/>
       <c r="AO30" s="47"/>
       <c r="AP30" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="16">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ30" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR30" s="47"/>
@@ -45389,11 +45332,11 @@
       <c r="AN31" s="47"/>
       <c r="AO31" s="47"/>
       <c r="AP31" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ31" s="16">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="AQ31" s="16">
-        <f t="shared" si="10"/>
         <v>3.6363636363636362</v>
       </c>
       <c r="AR31" s="47"/>
@@ -45528,11 +45471,11 @@
       <c r="AN32" s="47"/>
       <c r="AO32" s="47"/>
       <c r="AP32" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ32" s="16">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="AQ32" s="16">
-        <f t="shared" si="10"/>
         <v>6.8027210884353746</v>
       </c>
       <c r="AR32" s="47"/>
@@ -45669,11 +45612,11 @@
       <c r="AN33" s="47"/>
       <c r="AO33" s="47"/>
       <c r="AP33" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ33" s="16">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="AQ33" s="16">
-        <f t="shared" si="10"/>
         <v>5.7471264367816088</v>
       </c>
       <c r="AR33" s="47"/>
@@ -45812,11 +45755,11 @@
       <c r="AN34" s="47"/>
       <c r="AO34" s="47"/>
       <c r="AP34" s="17">
-        <f t="shared" ref="AP34:AP65" si="20">IF(AK34&gt;22.9,IF(Z34&lt;101,IF(Z34&lt;35,IF(Z34&lt;8,3,2),1),0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ34" s="16">
-        <f t="shared" ref="AQ34:AQ65" si="21">IF(AP34&gt;0,IF(AB34&gt;10,(AB34/Z34),10/Z34),0)</f>
+        <f t="shared" ref="AQ34:AQ65" si="20">IF(AP34&gt;0,IF(AB34&gt;10,(AB34/Z34),10/Z34),0)</f>
         <v>0</v>
       </c>
       <c r="AR34" s="47"/>
@@ -45951,11 +45894,11 @@
       <c r="AN35" s="47"/>
       <c r="AO35" s="47"/>
       <c r="AP35" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AQ35" s="16">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AR35" s="47"/>
@@ -46090,11 +46033,11 @@
       <c r="AN36" s="47"/>
       <c r="AO36" s="47"/>
       <c r="AP36" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AQ36" s="16">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AR36" s="47"/>
@@ -46229,11 +46172,11 @@
       <c r="AN37" s="47"/>
       <c r="AO37" s="47"/>
       <c r="AP37" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="16">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AR37" s="47"/>
@@ -46368,11 +46311,11 @@
       <c r="AN38" s="47"/>
       <c r="AO38" s="47"/>
       <c r="AP38" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ38" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ38" s="16">
-        <f t="shared" si="21"/>
         <v>1.3280212483399734</v>
       </c>
       <c r="AR38" s="47"/>
@@ -46507,11 +46450,11 @@
       <c r="AN39" s="47"/>
       <c r="AO39" s="47"/>
       <c r="AP39" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="16">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AR39" s="47"/>
@@ -46646,11 +46589,11 @@
       <c r="AN40" s="47"/>
       <c r="AO40" s="47"/>
       <c r="AP40" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ40" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AQ40" s="16">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AR40" s="47"/>
@@ -46785,11 +46728,11 @@
       <c r="AN41" s="47"/>
       <c r="AO41" s="47"/>
       <c r="AP41" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ41" s="16">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="AQ41" s="16">
-        <f t="shared" si="21"/>
         <v>0.60316662478009553</v>
       </c>
       <c r="AR41" s="47"/>
@@ -46930,11 +46873,11 @@
       <c r="AN42" s="47"/>
       <c r="AO42" s="47"/>
       <c r="AP42" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="16">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AR42" s="47"/>
@@ -47071,11 +47014,11 @@
       <c r="AN43" s="47"/>
       <c r="AO43" s="47"/>
       <c r="AP43" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ43" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ43" s="16">
-        <f t="shared" si="21"/>
         <v>5.2356020942408383</v>
       </c>
       <c r="AR43" s="47"/>
@@ -47216,11 +47159,11 @@
       <c r="AN44" s="47"/>
       <c r="AO44" s="47"/>
       <c r="AP44" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AQ44" s="16">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AR44" s="47"/>
@@ -47355,11 +47298,11 @@
       <c r="AN45" s="47"/>
       <c r="AO45" s="47"/>
       <c r="AP45" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AQ45" s="16">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AR45" s="47"/>
@@ -47494,11 +47437,11 @@
       <c r="AN46" s="47"/>
       <c r="AO46" s="47"/>
       <c r="AP46" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ46" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ46" s="16">
-        <f t="shared" si="21"/>
         <v>1.3227513227513228</v>
       </c>
       <c r="AR46" s="47"/>
@@ -47637,11 +47580,11 @@
       <c r="AN47" s="47"/>
       <c r="AO47" s="47"/>
       <c r="AP47" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ47" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ47" s="16">
-        <f t="shared" si="21"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="AR47" s="47"/>
@@ -47782,11 +47725,11 @@
       <c r="AN48" s="47"/>
       <c r="AO48" s="47"/>
       <c r="AP48" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ48" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ48" s="16">
-        <f t="shared" si="21"/>
         <v>7.8740157480314963</v>
       </c>
       <c r="AR48" s="47"/>
@@ -47921,11 +47864,11 @@
       <c r="AN49" s="47"/>
       <c r="AO49" s="47"/>
       <c r="AP49" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ49" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ49" s="16">
-        <f t="shared" si="21"/>
         <v>9.0909090909090899</v>
       </c>
       <c r="AR49" s="47"/>
@@ -48060,11 +48003,11 @@
       <c r="AN50" s="47"/>
       <c r="AO50" s="47"/>
       <c r="AP50" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ50" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ50" s="16">
-        <f t="shared" si="21"/>
         <v>8.7719298245614041</v>
       </c>
       <c r="AR50" s="47"/>
@@ -48199,11 +48142,11 @@
       <c r="AN51" s="47"/>
       <c r="AO51" s="47"/>
       <c r="AP51" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ51" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ51" s="16">
-        <f t="shared" si="21"/>
         <v>0.45269352648257133</v>
       </c>
       <c r="AR51" s="47"/>
@@ -48338,11 +48281,11 @@
       <c r="AN52" s="47"/>
       <c r="AO52" s="47"/>
       <c r="AP52" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ52" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ52" s="16">
-        <f t="shared" si="21"/>
         <v>5.2</v>
       </c>
       <c r="AR52" s="47"/>
@@ -48477,11 +48420,11 @@
       <c r="AN53" s="47"/>
       <c r="AO53" s="47"/>
       <c r="AP53" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ53" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ53" s="16">
-        <f t="shared" si="21"/>
         <v>11.363636363636363</v>
       </c>
       <c r="AR53" s="47"/>
@@ -48616,11 +48559,11 @@
       <c r="AN54" s="47"/>
       <c r="AO54" s="47"/>
       <c r="AP54" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ54" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ54" s="16">
-        <f t="shared" si="21"/>
         <v>0.875</v>
       </c>
       <c r="AR54" s="47"/>
@@ -48755,11 +48698,11 @@
       <c r="AN55" s="47"/>
       <c r="AO55" s="47"/>
       <c r="AP55" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ55" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ55" s="16">
-        <f t="shared" si="21"/>
         <v>0.625</v>
       </c>
       <c r="AR55" s="47"/>
@@ -48898,11 +48841,11 @@
         <v>26</v>
       </c>
       <c r="AP56" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ56" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ56" s="16">
-        <f t="shared" si="21"/>
         <v>1.2666666666666666</v>
       </c>
       <c r="AR56" s="47"/>
@@ -49037,11 +48980,11 @@
         <v>8</v>
       </c>
       <c r="AP57" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ57" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ57" s="16">
-        <f t="shared" si="21"/>
         <v>1.75</v>
       </c>
       <c r="AR57" s="47"/>
@@ -49174,11 +49117,11 @@
         <v>8</v>
       </c>
       <c r="AP58" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ58" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ58" s="16">
-        <f t="shared" si="21"/>
         <v>1.9</v>
       </c>
       <c r="AR58" s="47"/>
@@ -49313,11 +49256,11 @@
         <v>8</v>
       </c>
       <c r="AP59" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ59" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ59" s="16">
-        <f t="shared" si="21"/>
         <v>0.95</v>
       </c>
       <c r="AR59" s="47"/>
@@ -49450,11 +49393,11 @@
         <v>11</v>
       </c>
       <c r="AP60" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ60" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ60" s="16">
-        <f t="shared" si="21"/>
         <v>3.6231884057971016</v>
       </c>
       <c r="AR60" s="47"/>
@@ -49587,11 +49530,11 @@
         <v>17</v>
       </c>
       <c r="AP61" s="17">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AQ61" s="16">
         <f t="shared" si="20"/>
-        <v>3</v>
-      </c>
-      <c r="AQ61" s="16">
-        <f t="shared" si="21"/>
         <v>5.602888086642599</v>
       </c>
       <c r="AR61" s="47"/>
@@ -49722,11 +49665,11 @@
         <v>19</v>
       </c>
       <c r="AP62" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ62" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AQ62" s="16">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AR62" s="47"/>
@@ -49857,11 +49800,11 @@
         <v>26</v>
       </c>
       <c r="AP63" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ63" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ63" s="16">
-        <f t="shared" si="21"/>
         <v>0.52521008403361347</v>
       </c>
       <c r="AR63" s="47"/>
@@ -50006,11 +49949,11 @@
         <v>15</v>
       </c>
       <c r="AP64" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AQ64" s="16">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="AQ64" s="16">
-        <f t="shared" si="21"/>
         <v>1.6204172574437918</v>
       </c>
       <c r="AR64" s="101"/>
@@ -50155,11 +50098,11 @@
         <v>18</v>
       </c>
       <c r="AP65" s="17">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AQ65" s="16">
         <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="AQ65" s="16">
-        <f t="shared" si="21"/>
         <v>1.0482180293501049</v>
       </c>
       <c r="AR65" s="101"/>
@@ -50194,7 +50137,7 @@
         <v>660.43</v>
       </c>
       <c r="G66" s="47">
-        <f t="shared" ref="G66:G97" si="22">100*(F66-E66)/F66</f>
+        <f t="shared" ref="G66:G67" si="21">100*(F66-E66)/F66</f>
         <v>79.978196023802667</v>
       </c>
       <c r="H66" s="101">
@@ -50222,7 +50165,7 @@
         <v>2514.66</v>
       </c>
       <c r="P66" s="47">
-        <f t="shared" ref="P66:P97" si="23">O66/I66</f>
+        <f t="shared" ref="P66:P67" si="22">O66/I66</f>
         <v>414.96039603960395</v>
       </c>
       <c r="Q66" s="101">
@@ -50256,14 +50199,14 @@
         <v>2.4300000000000002</v>
       </c>
       <c r="AA66" s="51">
-        <f t="shared" ref="AA66:AA97" si="24">IF(X66&lt;33,IF(Y66&gt;(1.1*X66),0,1),1)+IF(Y66&gt;(4*X66),-1,0)</f>
+        <f t="shared" ref="AA66:AA97" si="23">IF(X66&lt;33,IF(Y66&gt;(1.1*X66),0,1),1)+IF(Y66&gt;(4*X66),-1,0)</f>
         <v>1</v>
       </c>
       <c r="AB66" s="101">
         <v>0</v>
       </c>
       <c r="AC66" s="52">
-        <f t="shared" ref="AC66:AC97" si="25">IF(AB66&gt;9,1,0)+AB66/3</f>
+        <f t="shared" ref="AC66:AC97" si="24">IF(AB66&gt;9,1,0)+AB66/3</f>
         <v>0</v>
       </c>
       <c r="AD66" s="101">
@@ -50276,21 +50219,21 @@
         <v>56.58</v>
       </c>
       <c r="AG66" s="49">
-        <f t="shared" ref="AG66:AG97" si="26">IF(G66&lt;0,0,1.2)+IF(G66&lt;14,0,0.9)+IF(P66&lt;0,0.7,0)+IF(P66&lt;6.5,1,0)+IF(P66&lt;23,1,0)+IF(R66&gt;88,0,1)+IF(S66=5,0,S66)+IF(AD66&lt;20,0,1)+IF(AE66&lt;14,0,1)+IF(AF66&lt;26,0,1)</f>
+        <f t="shared" ref="AG66:AG97" si="25">IF(G66&lt;0,0,1.2)+IF(G66&lt;14,0,0.9)+IF(P66&lt;0,0.7,0)+IF(P66&lt;6.5,1,0)+IF(P66&lt;23,1,0)+IF(R66&gt;88,0,1)+IF(S66=5,0,S66)+IF(AD66&lt;20,0,1)+IF(AE66&lt;14,0,1)+IF(AF66&lt;26,0,1)</f>
         <v>4.0999999999999996</v>
       </c>
       <c r="AH66" s="49">
-        <f t="shared" ref="AH66:AH97" si="27">AG66+IF(AG66&gt;6,1,0)+IF(X66&lt;17,0,1)+IF(Y66&lt;11,0,1)+IF(Z66&lt;1.35,0,1)+AC66+AA66</f>
+        <f t="shared" ref="AH66:AH97" si="26">AG66+IF(AG66&gt;6,1,0)+IF(X66&lt;17,0,1)+IF(Y66&lt;11,0,1)+IF(Z66&lt;1.35,0,1)+AC66+AA66</f>
         <v>6.1</v>
       </c>
       <c r="AI66" s="49"/>
       <c r="AJ66" s="49"/>
       <c r="AK66" s="49">
-        <f t="shared" ref="AK66:AK97" si="28">AG66*3+AH66</f>
+        <f t="shared" ref="AK66:AK97" si="27">AG66*3+AH66</f>
         <v>18.399999999999999</v>
       </c>
       <c r="AL66" s="2" t="str">
-        <f t="shared" ref="AL66:AL97" si="29">D66</f>
+        <f t="shared" ref="AL66:AL97" si="28">D66</f>
         <v>Neg</v>
       </c>
       <c r="AM66" s="2" t="str">
@@ -50304,11 +50247,11 @@
         <v>24</v>
       </c>
       <c r="AP66" s="17">
-        <f t="shared" ref="AP66:AP97" si="30">IF(AK66&gt;22.9,IF(Z66&lt;101,IF(Z66&lt;35,IF(Z66&lt;8,3,2),1),0),0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ66" s="16">
-        <f t="shared" ref="AQ66:AQ97" si="31">IF(AP66&gt;0,IF(AB66&gt;10,(AB66/Z66),10/Z66),0)</f>
+        <f t="shared" ref="AQ66:AQ97" si="29">IF(AP66&gt;0,IF(AB66&gt;10,(AB66/Z66),10/Z66),0)</f>
         <v>0</v>
       </c>
       <c r="AR66" s="101"/>
@@ -50343,7 +50286,7 @@
         <v>1748.3</v>
       </c>
       <c r="G67" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>84.773780243665271</v>
       </c>
       <c r="H67" s="101">
@@ -50371,7 +50314,7 @@
         <v>2816.2</v>
       </c>
       <c r="P67" s="47">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>12.766092475067996</v>
       </c>
       <c r="Q67" s="101">
@@ -50405,14 +50348,14 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AA67" s="51">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="AB67" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="52">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="AB67" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC67" s="52">
-        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AD67" s="101">
@@ -50425,21 +50368,21 @@
         <v>25.15</v>
       </c>
       <c r="AG67" s="49">
+        <f t="shared" si="25"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AH67" s="49">
         <f t="shared" si="26"/>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AH67" s="49">
-        <f t="shared" si="27"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="AI67" s="49"/>
       <c r="AJ67" s="49"/>
       <c r="AK67" s="49">
+        <f t="shared" si="27"/>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="AL67" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>17.399999999999999</v>
-      </c>
-      <c r="AL67" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Neg</v>
       </c>
       <c r="AM67" s="2" t="str">
@@ -50453,11 +50396,11 @@
         <v>13</v>
       </c>
       <c r="AP67" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="AP67:AP130" si="30">IF(AK67&gt;23,IF(Z67&lt;101,IF(Z67&lt;35,IF(Z67&lt;8,3,2),1),0),0)</f>
         <v>0</v>
       </c>
       <c r="AQ67" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AR67" s="101"/>
@@ -50552,14 +50495,14 @@
         <v>0.71</v>
       </c>
       <c r="AA68" s="51">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="AB68" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="52">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="AB68" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC68" s="52">
-        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AD68" s="101">
@@ -50572,21 +50515,21 @@
         <v>34.58</v>
       </c>
       <c r="AG68" s="49">
+        <f t="shared" si="25"/>
+        <v>4</v>
+      </c>
+      <c r="AH68" s="49">
         <f t="shared" si="26"/>
-        <v>4</v>
-      </c>
-      <c r="AH68" s="49">
-        <f t="shared" si="27"/>
         <v>5</v>
       </c>
       <c r="AI68" s="49"/>
       <c r="AJ68" s="49"/>
       <c r="AK68" s="49">
+        <f t="shared" si="27"/>
+        <v>17</v>
+      </c>
+      <c r="AL68" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>17</v>
-      </c>
-      <c r="AL68" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Neg</v>
       </c>
       <c r="AM68" s="2" t="str">
@@ -50604,7 +50547,7 @@
         <v>0</v>
       </c>
       <c r="AQ68" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AR68" s="101"/>
@@ -50699,14 +50642,14 @@
         <v>2</v>
       </c>
       <c r="AA69" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB69" s="101">
         <v>5.0599999999999996</v>
       </c>
       <c r="AC69" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1.6866666666666665</v>
       </c>
       <c r="AD69" s="101">
@@ -50719,21 +50662,21 @@
         <v>71.55</v>
       </c>
       <c r="AG69" s="49">
+        <f t="shared" si="25"/>
+        <v>8.1</v>
+      </c>
+      <c r="AH69" s="49">
         <f t="shared" si="26"/>
-        <v>8.1</v>
-      </c>
-      <c r="AH69" s="49">
-        <f t="shared" si="27"/>
         <v>12.786666666666665</v>
       </c>
       <c r="AI69" s="49"/>
       <c r="AJ69" s="49"/>
       <c r="AK69" s="49">
+        <f t="shared" si="27"/>
+        <v>37.086666666666659</v>
+      </c>
+      <c r="AL69" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>37.086666666666659</v>
-      </c>
-      <c r="AL69" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Pos</v>
       </c>
       <c r="AM69" s="2" t="s">
@@ -50750,7 +50693,7 @@
         <v>3</v>
       </c>
       <c r="AQ69" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>5</v>
       </c>
       <c r="AR69" s="101">
@@ -50849,14 +50792,14 @@
         <v>75</v>
       </c>
       <c r="AA70" s="51">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="AB70" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="52">
         <f t="shared" si="24"/>
-        <v>-1</v>
-      </c>
-      <c r="AB70" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC70" s="52">
-        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AD70" s="101">
@@ -50869,21 +50812,21 @@
         <v>10.82</v>
       </c>
       <c r="AG70" s="49">
+        <f t="shared" si="25"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AH70" s="49">
         <f t="shared" si="26"/>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="AH70" s="49">
-        <f t="shared" si="27"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="AI70" s="49"/>
       <c r="AJ70" s="49"/>
       <c r="AK70" s="49">
+        <f t="shared" si="27"/>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="AL70" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>17.399999999999999</v>
-      </c>
-      <c r="AL70" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Neg</v>
       </c>
       <c r="AM70" s="107" t="s">
@@ -50900,7 +50843,7 @@
         <v>0</v>
       </c>
       <c r="AQ70" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AR70" s="101"/>
@@ -50997,14 +50940,14 @@
         <v>0.05</v>
       </c>
       <c r="AA71" s="51">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="AB71" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="52">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="AB71" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC71" s="52">
-        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AD71" s="101">
@@ -51017,21 +50960,21 @@
         <v>40.020000000000003</v>
       </c>
       <c r="AG71" s="49">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="AH71" s="49">
         <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="AH71" s="49">
-        <f t="shared" si="27"/>
         <v>2</v>
       </c>
       <c r="AI71" s="49"/>
       <c r="AJ71" s="49"/>
       <c r="AK71" s="49">
+        <f t="shared" si="27"/>
+        <v>5</v>
+      </c>
+      <c r="AL71" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>5</v>
-      </c>
-      <c r="AL71" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Neg</v>
       </c>
       <c r="AM71" s="2" t="s">
@@ -51048,7 +50991,7 @@
         <v>0</v>
       </c>
       <c r="AQ71" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AR71" s="101"/>
@@ -51145,14 +51088,14 @@
         <v>1.22</v>
       </c>
       <c r="AA72" s="51">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AB72" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="52">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AB72" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC72" s="52">
-        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AD72" s="101">
@@ -51165,21 +51108,21 @@
         <v>-451.54</v>
       </c>
       <c r="AG72" s="49">
+        <f t="shared" si="25"/>
+        <v>6.2</v>
+      </c>
+      <c r="AH72" s="49">
         <f t="shared" si="26"/>
-        <v>6.2</v>
-      </c>
-      <c r="AH72" s="49">
-        <f t="shared" si="27"/>
         <v>7.2</v>
       </c>
       <c r="AI72" s="49"/>
       <c r="AJ72" s="49"/>
       <c r="AK72" s="49">
+        <f t="shared" si="27"/>
+        <v>25.8</v>
+      </c>
+      <c r="AL72" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>25.8</v>
-      </c>
-      <c r="AL72" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Pos</v>
       </c>
       <c r="AM72" s="107" t="s">
@@ -51196,7 +51139,7 @@
         <v>3</v>
       </c>
       <c r="AQ72" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>8.1967213114754092</v>
       </c>
       <c r="AR72" s="101"/>
@@ -51293,14 +51236,14 @@
         <v>2</v>
       </c>
       <c r="AA73" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB73" s="101">
         <v>2</v>
       </c>
       <c r="AC73" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AD73" s="101">
@@ -51313,21 +51256,21 @@
         <v>159.41</v>
       </c>
       <c r="AG73" s="49">
+        <f t="shared" si="25"/>
+        <v>5</v>
+      </c>
+      <c r="AH73" s="49">
         <f t="shared" si="26"/>
-        <v>5</v>
-      </c>
-      <c r="AH73" s="49">
-        <f t="shared" si="27"/>
         <v>9.6666666666666661</v>
       </c>
       <c r="AI73" s="49"/>
       <c r="AJ73" s="49"/>
       <c r="AK73" s="49">
+        <f t="shared" si="27"/>
+        <v>24.666666666666664</v>
+      </c>
+      <c r="AL73" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>24.666666666666664</v>
-      </c>
-      <c r="AL73" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Neg</v>
       </c>
       <c r="AM73" s="2" t="s">
@@ -51344,7 +51287,7 @@
         <v>3</v>
       </c>
       <c r="AQ73" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>5</v>
       </c>
       <c r="AR73" s="101"/>
@@ -51441,14 +51384,14 @@
         <v>0.5</v>
       </c>
       <c r="AA74" s="51">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="AB74" s="101">
+        <v>1</v>
+      </c>
+      <c r="AC74" s="52">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="AB74" s="101">
-        <v>1</v>
-      </c>
-      <c r="AC74" s="52">
-        <f t="shared" si="25"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AD74" s="101">
@@ -51461,21 +51404,21 @@
         <v>144.22</v>
       </c>
       <c r="AG74" s="49">
+        <f t="shared" si="25"/>
+        <v>7.1</v>
+      </c>
+      <c r="AH74" s="49">
         <f t="shared" si="26"/>
-        <v>7.1</v>
-      </c>
-      <c r="AH74" s="49">
-        <f t="shared" si="27"/>
         <v>9.4333333333333336</v>
       </c>
       <c r="AI74" s="49"/>
       <c r="AJ74" s="49"/>
       <c r="AK74" s="49">
+        <f t="shared" si="27"/>
+        <v>30.733333333333331</v>
+      </c>
+      <c r="AL74" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>30.733333333333331</v>
-      </c>
-      <c r="AL74" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Pos</v>
       </c>
       <c r="AM74" s="2" t="s">
@@ -51492,7 +51435,7 @@
         <v>3</v>
       </c>
       <c r="AQ74" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>20</v>
       </c>
       <c r="AR74" s="101"/>
@@ -51589,14 +51532,14 @@
         <v>1</v>
       </c>
       <c r="AA75" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB75" s="101">
         <v>2</v>
       </c>
       <c r="AC75" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AD75" s="101">
@@ -51609,21 +51552,21 @@
         <v>35.340000000000003</v>
       </c>
       <c r="AG75" s="49">
+        <f t="shared" si="25"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AH75" s="49">
         <f t="shared" si="26"/>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="AH75" s="49">
-        <f t="shared" si="27"/>
         <v>8.7666666666666657</v>
       </c>
       <c r="AI75" s="49"/>
       <c r="AJ75" s="49"/>
       <c r="AK75" s="49">
+        <f t="shared" si="27"/>
+        <v>24.066666666666663</v>
+      </c>
+      <c r="AL75" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>24.066666666666663</v>
-      </c>
-      <c r="AL75" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Neg</v>
       </c>
       <c r="AM75" s="2" t="s">
@@ -51640,7 +51583,7 @@
         <v>3</v>
       </c>
       <c r="AQ75" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>10</v>
       </c>
       <c r="AR75" s="101"/>
@@ -51735,14 +51678,14 @@
         <v>2</v>
       </c>
       <c r="AA76" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB76" s="101">
         <v>0.5</v>
       </c>
       <c r="AC76" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.16666666666666666</v>
       </c>
       <c r="AD76" s="101">
@@ -51755,21 +51698,21 @@
         <v>56.41</v>
       </c>
       <c r="AG76" s="49">
+        <f t="shared" si="25"/>
+        <v>5.2</v>
+      </c>
+      <c r="AH76" s="49">
         <f t="shared" si="26"/>
-        <v>5.2</v>
-      </c>
-      <c r="AH76" s="49">
-        <f t="shared" si="27"/>
         <v>8.3666666666666671</v>
       </c>
       <c r="AI76" s="49"/>
       <c r="AJ76" s="49"/>
       <c r="AK76" s="49">
+        <f t="shared" si="27"/>
+        <v>23.966666666666669</v>
+      </c>
+      <c r="AL76" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>23.966666666666669</v>
-      </c>
-      <c r="AL76" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Neg</v>
       </c>
       <c r="AM76" s="2" t="s">
@@ -51786,7 +51729,7 @@
         <v>3</v>
       </c>
       <c r="AQ76" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>5</v>
       </c>
       <c r="AR76" s="101"/>
@@ -51881,41 +51824,41 @@
         <v>2</v>
       </c>
       <c r="AA77" s="51">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="AB77" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="52">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="AB77" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC77" s="52">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="101">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="101">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="101">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="49">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AD77" s="101">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="101">
-        <v>0</v>
-      </c>
-      <c r="AF77" s="101">
-        <v>0</v>
-      </c>
-      <c r="AG77" s="49">
+        <v>4.2</v>
+      </c>
+      <c r="AH77" s="49">
         <f t="shared" si="26"/>
-        <v>4.2</v>
-      </c>
-      <c r="AH77" s="49">
-        <f t="shared" si="27"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="AI77" s="49"/>
       <c r="AJ77" s="49"/>
       <c r="AK77" s="49">
+        <f t="shared" si="27"/>
+        <v>20.8</v>
+      </c>
+      <c r="AL77" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>20.8</v>
-      </c>
-      <c r="AL77" s="2" t="str">
-        <f t="shared" si="29"/>
         <v>Pos</v>
       </c>
       <c r="AM77" s="2" t="s">
@@ -51932,7 +51875,7 @@
         <v>0</v>
       </c>
       <c r="AQ77" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AR77" s="101"/>
@@ -52025,14 +51968,14 @@
         <v>0.42</v>
       </c>
       <c r="AA78" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AB78" s="101">
         <v>0.62</v>
       </c>
       <c r="AC78" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.20666666666666667</v>
       </c>
       <c r="AD78" s="101">
@@ -52045,21 +51988,21 @@
         <v>21.48</v>
       </c>
       <c r="AG78" s="49">
+        <f t="shared" si="25"/>
+        <v>5.55</v>
+      </c>
+      <c r="AH78" s="49">
         <f t="shared" si="26"/>
-        <v>5.55</v>
-      </c>
-      <c r="AH78" s="49">
-        <f t="shared" si="27"/>
         <v>5.7566666666666668</v>
       </c>
       <c r="AI78" s="49"/>
       <c r="AJ78" s="49"/>
       <c r="AK78" s="49">
+        <f t="shared" si="27"/>
+        <v>22.406666666666666</v>
+      </c>
+      <c r="AL78" s="2">
         <f t="shared" si="28"/>
-        <v>22.406666666666666</v>
-      </c>
-      <c r="AL78" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM78" s="2" t="s">
@@ -52076,7 +52019,7 @@
         <v>0</v>
       </c>
       <c r="AQ78" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AR78" s="101"/>
@@ -52169,14 +52112,14 @@
         <v>0.25</v>
       </c>
       <c r="AA79" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB79" s="101">
         <v>0.57999999999999996</v>
       </c>
       <c r="AC79" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.19333333333333333</v>
       </c>
       <c r="AD79" s="101">
@@ -52189,28 +52132,28 @@
         <v>28.29</v>
       </c>
       <c r="AG79" s="49">
+        <f t="shared" si="25"/>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="AH79" s="49">
         <f t="shared" si="26"/>
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="AH79" s="49">
-        <f t="shared" si="27"/>
         <v>9.3933333333333326</v>
       </c>
       <c r="AI79" s="49"/>
       <c r="AJ79" s="49"/>
       <c r="AK79" s="49">
+        <f t="shared" si="27"/>
+        <v>30.993333333333332</v>
+      </c>
+      <c r="AL79" s="2">
         <f t="shared" si="28"/>
-        <v>30.993333333333332</v>
-      </c>
-      <c r="AL79" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM79" s="2" t="s">
         <v>357</v>
       </c>
       <c r="AN79" s="101">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO79" s="101">
         <v>23</v>
@@ -52220,7 +52163,7 @@
         <v>3</v>
       </c>
       <c r="AQ79" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>40</v>
       </c>
       <c r="AR79" s="101"/>
@@ -52313,14 +52256,14 @@
         <v>0.02</v>
       </c>
       <c r="AA80" s="51">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="AB80" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="52">
         <f t="shared" si="24"/>
-        <v>-1</v>
-      </c>
-      <c r="AB80" s="101">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="52">
-        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AD80" s="101">
@@ -52333,21 +52276,21 @@
         <v>25.37</v>
       </c>
       <c r="AG80" s="49">
+        <f t="shared" si="25"/>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="AH80" s="49">
         <f t="shared" si="26"/>
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="AH80" s="49">
-        <f t="shared" si="27"/>
         <v>3.6500000000000004</v>
       </c>
       <c r="AI80" s="49"/>
       <c r="AJ80" s="49"/>
       <c r="AK80" s="49">
+        <f t="shared" si="27"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="AL80" s="2">
         <f t="shared" si="28"/>
-        <v>17.600000000000001</v>
-      </c>
-      <c r="AL80" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM80" s="2" t="s">
@@ -52364,7 +52307,7 @@
         <v>0</v>
       </c>
       <c r="AQ80" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AR80" s="101"/>
@@ -52457,14 +52400,14 @@
         <v>0.23</v>
       </c>
       <c r="AA81" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1</v>
       </c>
       <c r="AB81" s="101">
         <v>3.3</v>
       </c>
       <c r="AC81" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1.0999999999999999</v>
       </c>
       <c r="AD81" s="101">
@@ -52477,21 +52420,21 @@
         <v>21.73</v>
       </c>
       <c r="AG81" s="49">
+        <f t="shared" si="25"/>
+        <v>2.1</v>
+      </c>
+      <c r="AH81" s="49">
         <f t="shared" si="26"/>
-        <v>2.1</v>
-      </c>
-      <c r="AH81" s="49">
-        <f t="shared" si="27"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="AI81" s="49"/>
       <c r="AJ81" s="49"/>
       <c r="AK81" s="49">
+        <f t="shared" si="27"/>
+        <v>8.5</v>
+      </c>
+      <c r="AL81" s="2">
         <f t="shared" si="28"/>
-        <v>8.5</v>
-      </c>
-      <c r="AL81" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM81" s="2" t="s">
@@ -52508,7 +52451,7 @@
         <v>0</v>
       </c>
       <c r="AQ81" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AR81" s="101"/>
@@ -52601,14 +52544,14 @@
         <v>0.2</v>
       </c>
       <c r="AA82" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-1</v>
       </c>
       <c r="AB82" s="101">
         <v>1.27</v>
       </c>
       <c r="AC82" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.42333333333333334</v>
       </c>
       <c r="AD82" s="101">
@@ -52621,21 +52564,21 @@
         <v>18.97</v>
       </c>
       <c r="AG82" s="49">
+        <f t="shared" si="25"/>
+        <v>5.55</v>
+      </c>
+      <c r="AH82" s="49">
         <f t="shared" si="26"/>
-        <v>5.55</v>
-      </c>
-      <c r="AH82" s="49">
-        <f t="shared" si="27"/>
         <v>4.9733333333333327</v>
       </c>
       <c r="AI82" s="49"/>
       <c r="AJ82" s="49"/>
       <c r="AK82" s="49">
+        <f t="shared" si="27"/>
+        <v>21.623333333333331</v>
+      </c>
+      <c r="AL82" s="2">
         <f t="shared" si="28"/>
-        <v>21.623333333333331</v>
-      </c>
-      <c r="AL82" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM82" s="2" t="s">
@@ -52652,7 +52595,7 @@
         <v>0</v>
       </c>
       <c r="AQ82" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AR82" s="101"/>
@@ -52675,7 +52618,7 @@
       <c r="E83" s="101"/>
       <c r="F83" s="101"/>
       <c r="G83" s="47" t="e">
-        <f t="shared" ref="G83:G114" si="32">100*(F83-E83)/F83</f>
+        <f t="shared" ref="G83:G114" si="31">100*(F83-E83)/F83</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H83" s="101"/>
@@ -52687,7 +52630,7 @@
       <c r="N83" s="101"/>
       <c r="O83" s="101"/>
       <c r="P83" s="47" t="e">
-        <f t="shared" ref="P83:P114" si="33">O83/I83</f>
+        <f t="shared" ref="P83:P114" si="32">O83/I83</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q83" s="101"/>
@@ -52703,37 +52646,37 @@
       <c r="Y83" s="101"/>
       <c r="Z83" s="101"/>
       <c r="AA83" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB83" s="101"/>
       <c r="AC83" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD83" s="101"/>
       <c r="AE83" s="101"/>
       <c r="AF83" s="101"/>
       <c r="AG83" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH83" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH83" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI83" s="49"/>
       <c r="AJ83" s="49"/>
       <c r="AK83" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL83" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL83" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM83" s="2">
-        <f t="shared" ref="AM83:AM114" si="34">B83</f>
+        <f t="shared" ref="AM83:AM114" si="33">B83</f>
         <v>0</v>
       </c>
       <c r="AN83" s="101"/>
@@ -52743,7 +52686,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ83" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR83" s="101"/>
@@ -52766,7 +52709,7 @@
       <c r="E84" s="101"/>
       <c r="F84" s="101"/>
       <c r="G84" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H84" s="101"/>
@@ -52778,7 +52721,7 @@
       <c r="N84" s="101"/>
       <c r="O84" s="101"/>
       <c r="P84" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q84" s="101"/>
@@ -52794,37 +52737,37 @@
       <c r="Y84" s="101"/>
       <c r="Z84" s="101"/>
       <c r="AA84" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB84" s="101"/>
       <c r="AC84" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD84" s="101"/>
       <c r="AE84" s="101"/>
       <c r="AF84" s="101"/>
       <c r="AG84" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH84" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH84" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI84" s="49"/>
       <c r="AJ84" s="49"/>
       <c r="AK84" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL84" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL84" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM84" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN84" s="101"/>
@@ -52834,7 +52777,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ84" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR84" s="101"/>
@@ -52857,7 +52800,7 @@
       <c r="E85" s="101"/>
       <c r="F85" s="101"/>
       <c r="G85" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H85" s="101"/>
@@ -52869,7 +52812,7 @@
       <c r="N85" s="101"/>
       <c r="O85" s="101"/>
       <c r="P85" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q85" s="101"/>
@@ -52885,37 +52828,37 @@
       <c r="Y85" s="101"/>
       <c r="Z85" s="101"/>
       <c r="AA85" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB85" s="101"/>
       <c r="AC85" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD85" s="101"/>
       <c r="AE85" s="101"/>
       <c r="AF85" s="101"/>
       <c r="AG85" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH85" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH85" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI85" s="49"/>
       <c r="AJ85" s="49"/>
       <c r="AK85" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL85" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL85" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM85" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN85" s="101"/>
@@ -52925,7 +52868,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ85" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR85" s="101"/>
@@ -52948,7 +52891,7 @@
       <c r="E86" s="101"/>
       <c r="F86" s="101"/>
       <c r="G86" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H86" s="101"/>
@@ -52960,7 +52903,7 @@
       <c r="N86" s="101"/>
       <c r="O86" s="101"/>
       <c r="P86" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q86" s="101"/>
@@ -52976,37 +52919,37 @@
       <c r="Y86" s="101"/>
       <c r="Z86" s="101"/>
       <c r="AA86" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB86" s="101"/>
       <c r="AC86" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD86" s="101"/>
       <c r="AE86" s="101"/>
       <c r="AF86" s="101"/>
       <c r="AG86" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH86" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH86" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI86" s="49"/>
       <c r="AJ86" s="49"/>
       <c r="AK86" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL86" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL86" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM86" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN86" s="101"/>
@@ -53016,7 +52959,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ86" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR86" s="101"/>
@@ -53039,7 +52982,7 @@
       <c r="E87" s="101"/>
       <c r="F87" s="101"/>
       <c r="G87" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H87" s="101"/>
@@ -53051,7 +52994,7 @@
       <c r="N87" s="101"/>
       <c r="O87" s="101"/>
       <c r="P87" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q87" s="101"/>
@@ -53067,37 +53010,37 @@
       <c r="Y87" s="101"/>
       <c r="Z87" s="101"/>
       <c r="AA87" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB87" s="101"/>
       <c r="AC87" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD87" s="101"/>
       <c r="AE87" s="101"/>
       <c r="AF87" s="101"/>
       <c r="AG87" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH87" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH87" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI87" s="49"/>
       <c r="AJ87" s="49"/>
       <c r="AK87" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL87" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL87" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM87" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN87" s="101"/>
@@ -53107,7 +53050,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ87" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR87" s="101"/>
@@ -53130,7 +53073,7 @@
       <c r="E88" s="101"/>
       <c r="F88" s="101"/>
       <c r="G88" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H88" s="101"/>
@@ -53142,7 +53085,7 @@
       <c r="N88" s="101"/>
       <c r="O88" s="101"/>
       <c r="P88" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q88" s="101"/>
@@ -53158,37 +53101,37 @@
       <c r="Y88" s="101"/>
       <c r="Z88" s="101"/>
       <c r="AA88" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB88" s="101"/>
       <c r="AC88" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD88" s="101"/>
       <c r="AE88" s="101"/>
       <c r="AF88" s="101"/>
       <c r="AG88" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH88" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH88" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI88" s="49"/>
       <c r="AJ88" s="49"/>
       <c r="AK88" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL88" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL88" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM88" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN88" s="101"/>
@@ -53198,7 +53141,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ88" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR88" s="101"/>
@@ -53221,7 +53164,7 @@
       <c r="E89" s="101"/>
       <c r="F89" s="101"/>
       <c r="G89" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H89" s="101"/>
@@ -53233,7 +53176,7 @@
       <c r="N89" s="101"/>
       <c r="O89" s="101"/>
       <c r="P89" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q89" s="101"/>
@@ -53249,37 +53192,37 @@
       <c r="Y89" s="101"/>
       <c r="Z89" s="101"/>
       <c r="AA89" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB89" s="101"/>
       <c r="AC89" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD89" s="101"/>
       <c r="AE89" s="101"/>
       <c r="AF89" s="101"/>
       <c r="AG89" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH89" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH89" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI89" s="49"/>
       <c r="AJ89" s="49"/>
       <c r="AK89" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL89" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL89" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM89" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN89" s="101"/>
@@ -53289,7 +53232,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ89" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR89" s="101"/>
@@ -53312,7 +53255,7 @@
       <c r="E90" s="101"/>
       <c r="F90" s="101"/>
       <c r="G90" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H90" s="101"/>
@@ -53324,7 +53267,7 @@
       <c r="N90" s="101"/>
       <c r="O90" s="101"/>
       <c r="P90" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q90" s="101"/>
@@ -53340,37 +53283,37 @@
       <c r="Y90" s="101"/>
       <c r="Z90" s="101"/>
       <c r="AA90" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB90" s="101"/>
       <c r="AC90" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD90" s="101"/>
       <c r="AE90" s="101"/>
       <c r="AF90" s="101"/>
       <c r="AG90" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH90" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH90" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI90" s="49"/>
       <c r="AJ90" s="49"/>
       <c r="AK90" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL90" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL90" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM90" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN90" s="101"/>
@@ -53380,7 +53323,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ90" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR90" s="101"/>
@@ -53403,7 +53346,7 @@
       <c r="E91" s="101"/>
       <c r="F91" s="101"/>
       <c r="G91" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H91" s="101"/>
@@ -53415,7 +53358,7 @@
       <c r="N91" s="101"/>
       <c r="O91" s="101"/>
       <c r="P91" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q91" s="101"/>
@@ -53431,37 +53374,37 @@
       <c r="Y91" s="101"/>
       <c r="Z91" s="101"/>
       <c r="AA91" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB91" s="101"/>
       <c r="AC91" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD91" s="101"/>
       <c r="AE91" s="101"/>
       <c r="AF91" s="101"/>
       <c r="AG91" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH91" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH91" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI91" s="49"/>
       <c r="AJ91" s="49"/>
       <c r="AK91" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL91" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL91" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM91" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN91" s="101"/>
@@ -53471,7 +53414,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ91" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR91" s="101"/>
@@ -53494,7 +53437,7 @@
       <c r="E92" s="101"/>
       <c r="F92" s="101"/>
       <c r="G92" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H92" s="101"/>
@@ -53506,7 +53449,7 @@
       <c r="N92" s="101"/>
       <c r="O92" s="101"/>
       <c r="P92" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q92" s="101"/>
@@ -53522,37 +53465,37 @@
       <c r="Y92" s="101"/>
       <c r="Z92" s="101"/>
       <c r="AA92" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB92" s="101"/>
       <c r="AC92" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD92" s="101"/>
       <c r="AE92" s="101"/>
       <c r="AF92" s="101"/>
       <c r="AG92" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH92" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH92" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI92" s="49"/>
       <c r="AJ92" s="49"/>
       <c r="AK92" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL92" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL92" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM92" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN92" s="101"/>
@@ -53562,7 +53505,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ92" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR92" s="101"/>
@@ -53585,7 +53528,7 @@
       <c r="E93" s="101"/>
       <c r="F93" s="101"/>
       <c r="G93" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H93" s="101"/>
@@ -53597,7 +53540,7 @@
       <c r="N93" s="101"/>
       <c r="O93" s="101"/>
       <c r="P93" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q93" s="101"/>
@@ -53613,37 +53556,37 @@
       <c r="Y93" s="101"/>
       <c r="Z93" s="101"/>
       <c r="AA93" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB93" s="101"/>
       <c r="AC93" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD93" s="101"/>
       <c r="AE93" s="101"/>
       <c r="AF93" s="101"/>
       <c r="AG93" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH93" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH93" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI93" s="49"/>
       <c r="AJ93" s="49"/>
       <c r="AK93" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL93" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL93" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM93" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN93" s="101"/>
@@ -53653,7 +53596,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ93" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR93" s="101"/>
@@ -53676,7 +53619,7 @@
       <c r="E94" s="101"/>
       <c r="F94" s="101"/>
       <c r="G94" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H94" s="101"/>
@@ -53688,7 +53631,7 @@
       <c r="N94" s="101"/>
       <c r="O94" s="101"/>
       <c r="P94" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q94" s="101"/>
@@ -53704,37 +53647,37 @@
       <c r="Y94" s="101"/>
       <c r="Z94" s="101"/>
       <c r="AA94" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB94" s="101"/>
       <c r="AC94" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD94" s="101"/>
       <c r="AE94" s="101"/>
       <c r="AF94" s="101"/>
       <c r="AG94" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH94" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH94" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI94" s="49"/>
       <c r="AJ94" s="49"/>
       <c r="AK94" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL94" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL94" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM94" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN94" s="101"/>
@@ -53744,7 +53687,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ94" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR94" s="101"/>
@@ -53767,7 +53710,7 @@
       <c r="E95" s="101"/>
       <c r="F95" s="101"/>
       <c r="G95" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H95" s="101"/>
@@ -53779,7 +53722,7 @@
       <c r="N95" s="101"/>
       <c r="O95" s="101"/>
       <c r="P95" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q95" s="101"/>
@@ -53795,37 +53738,37 @@
       <c r="Y95" s="101"/>
       <c r="Z95" s="101"/>
       <c r="AA95" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB95" s="101"/>
       <c r="AC95" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD95" s="101"/>
       <c r="AE95" s="101"/>
       <c r="AF95" s="101"/>
       <c r="AG95" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH95" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH95" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI95" s="49"/>
       <c r="AJ95" s="49"/>
       <c r="AK95" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL95" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL95" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM95" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN95" s="101"/>
@@ -53835,7 +53778,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ95" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR95" s="101"/>
@@ -53858,7 +53801,7 @@
       <c r="E96" s="101"/>
       <c r="F96" s="101"/>
       <c r="G96" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H96" s="101"/>
@@ -53870,7 +53813,7 @@
       <c r="N96" s="101"/>
       <c r="O96" s="101"/>
       <c r="P96" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q96" s="101"/>
@@ -53886,37 +53829,37 @@
       <c r="Y96" s="101"/>
       <c r="Z96" s="101"/>
       <c r="AA96" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB96" s="101"/>
       <c r="AC96" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD96" s="101"/>
       <c r="AE96" s="101"/>
       <c r="AF96" s="101"/>
       <c r="AG96" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH96" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH96" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI96" s="49"/>
       <c r="AJ96" s="49"/>
       <c r="AK96" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL96" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL96" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM96" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN96" s="101"/>
@@ -53926,7 +53869,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ96" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR96" s="101"/>
@@ -53949,7 +53892,7 @@
       <c r="E97" s="101"/>
       <c r="F97" s="101"/>
       <c r="G97" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H97" s="101"/>
@@ -53961,7 +53904,7 @@
       <c r="N97" s="101"/>
       <c r="O97" s="101"/>
       <c r="P97" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q97" s="101"/>
@@ -53977,37 +53920,37 @@
       <c r="Y97" s="101"/>
       <c r="Z97" s="101"/>
       <c r="AA97" s="51">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="AB97" s="101"/>
       <c r="AC97" s="52">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD97" s="101"/>
       <c r="AE97" s="101"/>
       <c r="AF97" s="101"/>
       <c r="AG97" s="49" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH97" s="49" t="e">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH97" s="49" t="e">
-        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI97" s="49"/>
       <c r="AJ97" s="49"/>
       <c r="AK97" s="49" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL97" s="2">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL97" s="2">
-        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM97" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN97" s="101"/>
@@ -54017,7 +53960,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ97" s="16" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR97" s="101"/>
@@ -54040,7 +53983,7 @@
       <c r="E98" s="101"/>
       <c r="F98" s="101"/>
       <c r="G98" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H98" s="101"/>
@@ -54052,7 +53995,7 @@
       <c r="N98" s="101"/>
       <c r="O98" s="101"/>
       <c r="P98" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q98" s="101"/>
@@ -54068,47 +54011,47 @@
       <c r="Y98" s="101"/>
       <c r="Z98" s="101"/>
       <c r="AA98" s="51">
-        <f t="shared" ref="AA98:AA129" si="35">IF(X98&lt;33,IF(Y98&gt;(1.1*X98),0,1),1)+IF(Y98&gt;(4*X98),-1,0)</f>
+        <f t="shared" ref="AA98:AA129" si="34">IF(X98&lt;33,IF(Y98&gt;(1.1*X98),0,1),1)+IF(Y98&gt;(4*X98),-1,0)</f>
         <v>1</v>
       </c>
       <c r="AB98" s="101"/>
       <c r="AC98" s="52">
-        <f t="shared" ref="AC98:AC129" si="36">IF(AB98&gt;9,1,0)+AB98/3</f>
+        <f t="shared" ref="AC98:AC129" si="35">IF(AB98&gt;9,1,0)+AB98/3</f>
         <v>0</v>
       </c>
       <c r="AD98" s="101"/>
       <c r="AE98" s="101"/>
       <c r="AF98" s="101"/>
       <c r="AG98" s="49" t="e">
-        <f t="shared" ref="AG98:AG129" si="37">IF(G98&lt;0,0,1.2)+IF(G98&lt;14,0,0.9)+IF(P98&lt;0,0.7,0)+IF(P98&lt;6.5,1,0)+IF(P98&lt;23,1,0)+IF(R98&gt;88,0,1)+IF(S98=5,0,S98)+IF(AD98&lt;20,0,1)+IF(AE98&lt;14,0,1)+IF(AF98&lt;26,0,1)</f>
+        <f t="shared" ref="AG98:AG129" si="36">IF(G98&lt;0,0,1.2)+IF(G98&lt;14,0,0.9)+IF(P98&lt;0,0.7,0)+IF(P98&lt;6.5,1,0)+IF(P98&lt;23,1,0)+IF(R98&gt;88,0,1)+IF(S98=5,0,S98)+IF(AD98&lt;20,0,1)+IF(AE98&lt;14,0,1)+IF(AF98&lt;26,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH98" s="49" t="e">
-        <f t="shared" ref="AH98:AH129" si="38">AG98+IF(AG98&gt;6,1,0)+IF(X98&lt;17,0,1)+IF(Y98&lt;11,0,1)+IF(Z98&lt;1.35,0,1)+AC98+AA98</f>
+        <f t="shared" ref="AH98:AH129" si="37">AG98+IF(AG98&gt;6,1,0)+IF(X98&lt;17,0,1)+IF(Y98&lt;11,0,1)+IF(Z98&lt;1.35,0,1)+AC98+AA98</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI98" s="49"/>
       <c r="AJ98" s="49"/>
       <c r="AK98" s="49" t="e">
-        <f t="shared" ref="AK98:AK129" si="39">AG98*3+AH98</f>
+        <f t="shared" ref="AK98:AK129" si="38">AG98*3+AH98</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL98" s="2">
-        <f t="shared" ref="AL98:AL129" si="40">D98</f>
+        <f t="shared" ref="AL98:AL129" si="39">D98</f>
         <v>0</v>
       </c>
       <c r="AM98" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN98" s="101"/>
       <c r="AO98" s="101"/>
       <c r="AP98" s="17" t="e">
-        <f t="shared" ref="AP98:AP129" si="41">IF(AK98&gt;22.9,IF(Z98&lt;101,IF(Z98&lt;35,IF(Z98&lt;8,3,2),1),0),0)</f>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ98" s="16" t="e">
-        <f t="shared" ref="AQ98:AQ129" si="42">IF(AP98&gt;0,IF(AB98&gt;10,(AB98/Z98),10/Z98),0)</f>
+        <f t="shared" ref="AQ98:AQ129" si="40">IF(AP98&gt;0,IF(AB98&gt;10,(AB98/Z98),10/Z98),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR98" s="101"/>
@@ -54131,7 +54074,7 @@
       <c r="E99" s="101"/>
       <c r="F99" s="101"/>
       <c r="G99" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H99" s="101"/>
@@ -54143,7 +54086,7 @@
       <c r="N99" s="101"/>
       <c r="O99" s="101"/>
       <c r="P99" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q99" s="101"/>
@@ -54159,47 +54102,47 @@
       <c r="Y99" s="101"/>
       <c r="Z99" s="101"/>
       <c r="AA99" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB99" s="101"/>
       <c r="AC99" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD99" s="101"/>
       <c r="AE99" s="101"/>
       <c r="AF99" s="101"/>
       <c r="AG99" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH99" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH99" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI99" s="49"/>
       <c r="AJ99" s="49"/>
       <c r="AK99" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL99" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL99" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM99" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN99" s="101"/>
       <c r="AO99" s="101"/>
       <c r="AP99" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ99" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR99" s="101"/>
@@ -54222,7 +54165,7 @@
       <c r="E100" s="101"/>
       <c r="F100" s="101"/>
       <c r="G100" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H100" s="101"/>
@@ -54234,7 +54177,7 @@
       <c r="N100" s="101"/>
       <c r="O100" s="101"/>
       <c r="P100" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q100" s="101"/>
@@ -54250,47 +54193,47 @@
       <c r="Y100" s="101"/>
       <c r="Z100" s="101"/>
       <c r="AA100" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB100" s="101"/>
       <c r="AC100" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD100" s="101"/>
       <c r="AE100" s="101"/>
       <c r="AF100" s="101"/>
       <c r="AG100" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH100" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH100" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI100" s="49"/>
       <c r="AJ100" s="49"/>
       <c r="AK100" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL100" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL100" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM100" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN100" s="101"/>
       <c r="AO100" s="101"/>
       <c r="AP100" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ100" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR100" s="101"/>
@@ -54313,7 +54256,7 @@
       <c r="E101" s="101"/>
       <c r="F101" s="101"/>
       <c r="G101" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H101" s="101"/>
@@ -54325,7 +54268,7 @@
       <c r="N101" s="101"/>
       <c r="O101" s="101"/>
       <c r="P101" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q101" s="101"/>
@@ -54341,47 +54284,47 @@
       <c r="Y101" s="101"/>
       <c r="Z101" s="101"/>
       <c r="AA101" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB101" s="101"/>
       <c r="AC101" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD101" s="101"/>
       <c r="AE101" s="101"/>
       <c r="AF101" s="101"/>
       <c r="AG101" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH101" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH101" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI101" s="49"/>
       <c r="AJ101" s="49"/>
       <c r="AK101" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL101" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL101" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM101" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN101" s="101"/>
       <c r="AO101" s="101"/>
       <c r="AP101" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ101" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR101" s="101"/>
@@ -54404,7 +54347,7 @@
       <c r="E102" s="101"/>
       <c r="F102" s="101"/>
       <c r="G102" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H102" s="101"/>
@@ -54416,7 +54359,7 @@
       <c r="N102" s="101"/>
       <c r="O102" s="101"/>
       <c r="P102" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q102" s="101"/>
@@ -54432,47 +54375,47 @@
       <c r="Y102" s="101"/>
       <c r="Z102" s="101"/>
       <c r="AA102" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB102" s="101"/>
       <c r="AC102" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD102" s="101"/>
       <c r="AE102" s="101"/>
       <c r="AF102" s="101"/>
       <c r="AG102" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH102" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH102" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI102" s="49"/>
       <c r="AJ102" s="49"/>
       <c r="AK102" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL102" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL102" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM102" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN102" s="101"/>
       <c r="AO102" s="101"/>
       <c r="AP102" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ102" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR102" s="101"/>
@@ -54495,7 +54438,7 @@
       <c r="E103" s="101"/>
       <c r="F103" s="101"/>
       <c r="G103" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H103" s="101"/>
@@ -54507,7 +54450,7 @@
       <c r="N103" s="101"/>
       <c r="O103" s="101"/>
       <c r="P103" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q103" s="101"/>
@@ -54523,47 +54466,47 @@
       <c r="Y103" s="101"/>
       <c r="Z103" s="101"/>
       <c r="AA103" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB103" s="101"/>
       <c r="AC103" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD103" s="101"/>
       <c r="AE103" s="101"/>
       <c r="AF103" s="101"/>
       <c r="AG103" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH103" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH103" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI103" s="49"/>
       <c r="AJ103" s="49"/>
       <c r="AK103" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL103" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL103" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM103" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN103" s="101"/>
       <c r="AO103" s="101"/>
       <c r="AP103" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ103" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR103" s="101"/>
@@ -54586,7 +54529,7 @@
       <c r="E104" s="101"/>
       <c r="F104" s="101"/>
       <c r="G104" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H104" s="101"/>
@@ -54598,7 +54541,7 @@
       <c r="N104" s="101"/>
       <c r="O104" s="101"/>
       <c r="P104" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q104" s="101"/>
@@ -54614,47 +54557,47 @@
       <c r="Y104" s="101"/>
       <c r="Z104" s="101"/>
       <c r="AA104" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB104" s="101"/>
       <c r="AC104" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD104" s="101"/>
       <c r="AE104" s="101"/>
       <c r="AF104" s="101"/>
       <c r="AG104" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH104" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH104" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI104" s="49"/>
       <c r="AJ104" s="49"/>
       <c r="AK104" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL104" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL104" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM104" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN104" s="101"/>
       <c r="AO104" s="101"/>
       <c r="AP104" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ104" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR104" s="101"/>
@@ -54677,7 +54620,7 @@
       <c r="E105" s="101"/>
       <c r="F105" s="101"/>
       <c r="G105" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H105" s="101"/>
@@ -54689,7 +54632,7 @@
       <c r="N105" s="101"/>
       <c r="O105" s="101"/>
       <c r="P105" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q105" s="101"/>
@@ -54705,47 +54648,47 @@
       <c r="Y105" s="101"/>
       <c r="Z105" s="101"/>
       <c r="AA105" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB105" s="101"/>
       <c r="AC105" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD105" s="101"/>
       <c r="AE105" s="101"/>
       <c r="AF105" s="101"/>
       <c r="AG105" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH105" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH105" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI105" s="49"/>
       <c r="AJ105" s="49"/>
       <c r="AK105" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL105" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL105" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM105" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN105" s="101"/>
       <c r="AO105" s="101"/>
       <c r="AP105" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ105" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR105" s="101"/>
@@ -54768,7 +54711,7 @@
       <c r="E106" s="101"/>
       <c r="F106" s="101"/>
       <c r="G106" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H106" s="101"/>
@@ -54780,7 +54723,7 @@
       <c r="N106" s="101"/>
       <c r="O106" s="101"/>
       <c r="P106" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q106" s="101"/>
@@ -54796,47 +54739,47 @@
       <c r="Y106" s="101"/>
       <c r="Z106" s="101"/>
       <c r="AA106" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB106" s="101"/>
       <c r="AC106" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD106" s="101"/>
       <c r="AE106" s="101"/>
       <c r="AF106" s="101"/>
       <c r="AG106" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH106" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH106" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI106" s="49"/>
       <c r="AJ106" s="49"/>
       <c r="AK106" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL106" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL106" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM106" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN106" s="101"/>
       <c r="AO106" s="101"/>
       <c r="AP106" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ106" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR106" s="101"/>
@@ -54859,7 +54802,7 @@
       <c r="E107" s="101"/>
       <c r="F107" s="101"/>
       <c r="G107" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H107" s="101"/>
@@ -54871,7 +54814,7 @@
       <c r="N107" s="101"/>
       <c r="O107" s="101"/>
       <c r="P107" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q107" s="101"/>
@@ -54887,47 +54830,47 @@
       <c r="Y107" s="101"/>
       <c r="Z107" s="101"/>
       <c r="AA107" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB107" s="101"/>
       <c r="AC107" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD107" s="101"/>
       <c r="AE107" s="101"/>
       <c r="AF107" s="101"/>
       <c r="AG107" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH107" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH107" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI107" s="49"/>
       <c r="AJ107" s="49"/>
       <c r="AK107" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL107" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL107" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM107" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN107" s="101"/>
       <c r="AO107" s="101"/>
       <c r="AP107" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ107" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR107" s="101"/>
@@ -54950,7 +54893,7 @@
       <c r="E108" s="101"/>
       <c r="F108" s="101"/>
       <c r="G108" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H108" s="101"/>
@@ -54962,7 +54905,7 @@
       <c r="N108" s="101"/>
       <c r="O108" s="101"/>
       <c r="P108" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q108" s="101"/>
@@ -54978,47 +54921,47 @@
       <c r="Y108" s="101"/>
       <c r="Z108" s="101"/>
       <c r="AA108" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB108" s="101"/>
       <c r="AC108" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD108" s="101"/>
       <c r="AE108" s="101"/>
       <c r="AF108" s="101"/>
       <c r="AG108" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH108" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH108" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI108" s="49"/>
       <c r="AJ108" s="49"/>
       <c r="AK108" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL108" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL108" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM108" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN108" s="101"/>
       <c r="AO108" s="101"/>
       <c r="AP108" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ108" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR108" s="101"/>
@@ -55041,7 +54984,7 @@
       <c r="E109" s="101"/>
       <c r="F109" s="101"/>
       <c r="G109" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H109" s="101"/>
@@ -55053,7 +54996,7 @@
       <c r="N109" s="101"/>
       <c r="O109" s="101"/>
       <c r="P109" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q109" s="101"/>
@@ -55069,47 +55012,47 @@
       <c r="Y109" s="101"/>
       <c r="Z109" s="101"/>
       <c r="AA109" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB109" s="101"/>
       <c r="AC109" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD109" s="101"/>
       <c r="AE109" s="101"/>
       <c r="AF109" s="101"/>
       <c r="AG109" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH109" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH109" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI109" s="49"/>
       <c r="AJ109" s="49"/>
       <c r="AK109" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL109" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL109" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM109" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN109" s="101"/>
       <c r="AO109" s="101"/>
       <c r="AP109" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ109" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR109" s="101"/>
@@ -55132,7 +55075,7 @@
       <c r="E110" s="101"/>
       <c r="F110" s="101"/>
       <c r="G110" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H110" s="101"/>
@@ -55144,7 +55087,7 @@
       <c r="N110" s="101"/>
       <c r="O110" s="101"/>
       <c r="P110" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q110" s="101"/>
@@ -55160,47 +55103,47 @@
       <c r="Y110" s="101"/>
       <c r="Z110" s="101"/>
       <c r="AA110" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB110" s="101"/>
       <c r="AC110" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD110" s="101"/>
       <c r="AE110" s="101"/>
       <c r="AF110" s="101"/>
       <c r="AG110" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH110" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH110" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI110" s="49"/>
       <c r="AJ110" s="49"/>
       <c r="AK110" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL110" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL110" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM110" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN110" s="101"/>
       <c r="AO110" s="101"/>
       <c r="AP110" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ110" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR110" s="101"/>
@@ -55223,7 +55166,7 @@
       <c r="E111" s="101"/>
       <c r="F111" s="101"/>
       <c r="G111" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H111" s="101"/>
@@ -55235,7 +55178,7 @@
       <c r="N111" s="101"/>
       <c r="O111" s="101"/>
       <c r="P111" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q111" s="101"/>
@@ -55251,47 +55194,47 @@
       <c r="Y111" s="101"/>
       <c r="Z111" s="101"/>
       <c r="AA111" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB111" s="101"/>
       <c r="AC111" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD111" s="101"/>
       <c r="AE111" s="101"/>
       <c r="AF111" s="101"/>
       <c r="AG111" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH111" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH111" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI111" s="49"/>
       <c r="AJ111" s="49"/>
       <c r="AK111" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL111" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL111" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM111" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN111" s="101"/>
       <c r="AO111" s="101"/>
       <c r="AP111" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ111" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR111" s="101"/>
@@ -55314,7 +55257,7 @@
       <c r="E112" s="101"/>
       <c r="F112" s="101"/>
       <c r="G112" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H112" s="101"/>
@@ -55326,7 +55269,7 @@
       <c r="N112" s="101"/>
       <c r="O112" s="101"/>
       <c r="P112" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q112" s="101"/>
@@ -55342,47 +55285,47 @@
       <c r="Y112" s="101"/>
       <c r="Z112" s="101"/>
       <c r="AA112" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB112" s="101"/>
       <c r="AC112" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD112" s="101"/>
       <c r="AE112" s="101"/>
       <c r="AF112" s="101"/>
       <c r="AG112" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH112" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH112" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI112" s="49"/>
       <c r="AJ112" s="49"/>
       <c r="AK112" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL112" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL112" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM112" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN112" s="101"/>
       <c r="AO112" s="101"/>
       <c r="AP112" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ112" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR112" s="101"/>
@@ -55405,7 +55348,7 @@
       <c r="E113" s="101"/>
       <c r="F113" s="101"/>
       <c r="G113" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H113" s="101"/>
@@ -55417,7 +55360,7 @@
       <c r="N113" s="101"/>
       <c r="O113" s="101"/>
       <c r="P113" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q113" s="101"/>
@@ -55433,47 +55376,47 @@
       <c r="Y113" s="101"/>
       <c r="Z113" s="101"/>
       <c r="AA113" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB113" s="101"/>
       <c r="AC113" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD113" s="101"/>
       <c r="AE113" s="101"/>
       <c r="AF113" s="101"/>
       <c r="AG113" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH113" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH113" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI113" s="49"/>
       <c r="AJ113" s="49"/>
       <c r="AK113" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL113" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL113" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM113" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN113" s="101"/>
       <c r="AO113" s="101"/>
       <c r="AP113" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ113" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR113" s="101"/>
@@ -55496,7 +55439,7 @@
       <c r="E114" s="101"/>
       <c r="F114" s="101"/>
       <c r="G114" s="47" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H114" s="101"/>
@@ -55508,7 +55451,7 @@
       <c r="N114" s="101"/>
       <c r="O114" s="101"/>
       <c r="P114" s="47" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q114" s="101"/>
@@ -55524,47 +55467,47 @@
       <c r="Y114" s="101"/>
       <c r="Z114" s="101"/>
       <c r="AA114" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB114" s="101"/>
       <c r="AC114" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD114" s="101"/>
       <c r="AE114" s="101"/>
       <c r="AF114" s="101"/>
       <c r="AG114" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH114" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH114" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI114" s="49"/>
       <c r="AJ114" s="49"/>
       <c r="AK114" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL114" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL114" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM114" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN114" s="101"/>
       <c r="AO114" s="101"/>
       <c r="AP114" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ114" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR114" s="101"/>
@@ -55587,7 +55530,7 @@
       <c r="E115" s="101"/>
       <c r="F115" s="101"/>
       <c r="G115" s="47" t="e">
-        <f t="shared" ref="G115:G146" si="43">100*(F115-E115)/F115</f>
+        <f t="shared" ref="G115:G146" si="41">100*(F115-E115)/F115</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H115" s="101"/>
@@ -55599,7 +55542,7 @@
       <c r="N115" s="101"/>
       <c r="O115" s="101"/>
       <c r="P115" s="47" t="e">
-        <f t="shared" ref="P115:P146" si="44">O115/I115</f>
+        <f t="shared" ref="P115:P146" si="42">O115/I115</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q115" s="101"/>
@@ -55615,47 +55558,47 @@
       <c r="Y115" s="101"/>
       <c r="Z115" s="101"/>
       <c r="AA115" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB115" s="101"/>
       <c r="AC115" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD115" s="101"/>
       <c r="AE115" s="101"/>
       <c r="AF115" s="101"/>
       <c r="AG115" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH115" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH115" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI115" s="49"/>
       <c r="AJ115" s="49"/>
       <c r="AK115" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL115" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL115" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM115" s="2">
-        <f t="shared" ref="AM115:AM146" si="45">B115</f>
+        <f t="shared" ref="AM115:AM146" si="43">B115</f>
         <v>0</v>
       </c>
       <c r="AN115" s="101"/>
       <c r="AO115" s="101"/>
       <c r="AP115" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ115" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR115" s="101"/>
@@ -55678,7 +55621,7 @@
       <c r="E116" s="101"/>
       <c r="F116" s="101"/>
       <c r="G116" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H116" s="101"/>
@@ -55690,7 +55633,7 @@
       <c r="N116" s="101"/>
       <c r="O116" s="101"/>
       <c r="P116" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q116" s="101"/>
@@ -55706,47 +55649,47 @@
       <c r="Y116" s="101"/>
       <c r="Z116" s="101"/>
       <c r="AA116" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB116" s="101"/>
       <c r="AC116" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD116" s="101"/>
       <c r="AE116" s="101"/>
       <c r="AF116" s="101"/>
       <c r="AG116" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH116" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH116" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI116" s="49"/>
       <c r="AJ116" s="49"/>
       <c r="AK116" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL116" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL116" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM116" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN116" s="101"/>
       <c r="AO116" s="101"/>
       <c r="AP116" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ116" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR116" s="101"/>
@@ -55769,7 +55712,7 @@
       <c r="E117" s="101"/>
       <c r="F117" s="101"/>
       <c r="G117" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H117" s="101"/>
@@ -55781,7 +55724,7 @@
       <c r="N117" s="101"/>
       <c r="O117" s="101"/>
       <c r="P117" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q117" s="101"/>
@@ -55797,47 +55740,47 @@
       <c r="Y117" s="101"/>
       <c r="Z117" s="101"/>
       <c r="AA117" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB117" s="101"/>
       <c r="AC117" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD117" s="101"/>
       <c r="AE117" s="101"/>
       <c r="AF117" s="101"/>
       <c r="AG117" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH117" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH117" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI117" s="49"/>
       <c r="AJ117" s="49"/>
       <c r="AK117" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL117" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL117" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM117" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN117" s="101"/>
       <c r="AO117" s="101"/>
       <c r="AP117" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ117" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR117" s="101"/>
@@ -55860,7 +55803,7 @@
       <c r="E118" s="101"/>
       <c r="F118" s="101"/>
       <c r="G118" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H118" s="101"/>
@@ -55872,7 +55815,7 @@
       <c r="N118" s="101"/>
       <c r="O118" s="101"/>
       <c r="P118" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q118" s="101"/>
@@ -55888,47 +55831,47 @@
       <c r="Y118" s="101"/>
       <c r="Z118" s="101"/>
       <c r="AA118" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB118" s="101"/>
       <c r="AC118" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD118" s="101"/>
       <c r="AE118" s="101"/>
       <c r="AF118" s="101"/>
       <c r="AG118" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH118" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH118" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI118" s="49"/>
       <c r="AJ118" s="49"/>
       <c r="AK118" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL118" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL118" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM118" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN118" s="101"/>
       <c r="AO118" s="101"/>
       <c r="AP118" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ118" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR118" s="101"/>
@@ -55951,7 +55894,7 @@
       <c r="E119" s="101"/>
       <c r="F119" s="101"/>
       <c r="G119" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H119" s="101"/>
@@ -55963,7 +55906,7 @@
       <c r="N119" s="101"/>
       <c r="O119" s="101"/>
       <c r="P119" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q119" s="101"/>
@@ -55979,47 +55922,47 @@
       <c r="Y119" s="101"/>
       <c r="Z119" s="101"/>
       <c r="AA119" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB119" s="101"/>
       <c r="AC119" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD119" s="101"/>
       <c r="AE119" s="101"/>
       <c r="AF119" s="101"/>
       <c r="AG119" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH119" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH119" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI119" s="49"/>
       <c r="AJ119" s="49"/>
       <c r="AK119" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL119" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL119" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM119" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN119" s="101"/>
       <c r="AO119" s="101"/>
       <c r="AP119" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ119" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR119" s="101"/>
@@ -56042,7 +55985,7 @@
       <c r="E120" s="101"/>
       <c r="F120" s="101"/>
       <c r="G120" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H120" s="101"/>
@@ -56054,7 +55997,7 @@
       <c r="N120" s="101"/>
       <c r="O120" s="101"/>
       <c r="P120" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q120" s="101"/>
@@ -56070,47 +56013,47 @@
       <c r="Y120" s="101"/>
       <c r="Z120" s="101"/>
       <c r="AA120" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB120" s="101"/>
       <c r="AC120" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD120" s="101"/>
       <c r="AE120" s="101"/>
       <c r="AF120" s="101"/>
       <c r="AG120" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH120" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH120" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI120" s="49"/>
       <c r="AJ120" s="49"/>
       <c r="AK120" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL120" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL120" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM120" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN120" s="101"/>
       <c r="AO120" s="101"/>
       <c r="AP120" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ120" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR120" s="101"/>
@@ -56133,7 +56076,7 @@
       <c r="E121" s="101"/>
       <c r="F121" s="101"/>
       <c r="G121" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H121" s="101"/>
@@ -56145,7 +56088,7 @@
       <c r="N121" s="101"/>
       <c r="O121" s="101"/>
       <c r="P121" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q121" s="101"/>
@@ -56161,47 +56104,47 @@
       <c r="Y121" s="101"/>
       <c r="Z121" s="101"/>
       <c r="AA121" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB121" s="101"/>
       <c r="AC121" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD121" s="101"/>
       <c r="AE121" s="101"/>
       <c r="AF121" s="101"/>
       <c r="AG121" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH121" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH121" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI121" s="49"/>
       <c r="AJ121" s="49"/>
       <c r="AK121" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL121" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL121" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM121" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN121" s="101"/>
       <c r="AO121" s="101"/>
       <c r="AP121" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ121" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR121" s="101"/>
@@ -56224,7 +56167,7 @@
       <c r="E122" s="101"/>
       <c r="F122" s="101"/>
       <c r="G122" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H122" s="101"/>
@@ -56236,7 +56179,7 @@
       <c r="N122" s="101"/>
       <c r="O122" s="101"/>
       <c r="P122" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q122" s="101"/>
@@ -56252,47 +56195,47 @@
       <c r="Y122" s="101"/>
       <c r="Z122" s="101"/>
       <c r="AA122" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB122" s="101"/>
       <c r="AC122" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD122" s="101"/>
       <c r="AE122" s="101"/>
       <c r="AF122" s="101"/>
       <c r="AG122" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH122" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH122" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI122" s="49"/>
       <c r="AJ122" s="49"/>
       <c r="AK122" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL122" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL122" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM122" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN122" s="101"/>
       <c r="AO122" s="101"/>
       <c r="AP122" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ122" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR122" s="101"/>
@@ -56315,7 +56258,7 @@
       <c r="E123" s="101"/>
       <c r="F123" s="101"/>
       <c r="G123" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H123" s="101"/>
@@ -56327,7 +56270,7 @@
       <c r="N123" s="101"/>
       <c r="O123" s="101"/>
       <c r="P123" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q123" s="101"/>
@@ -56343,47 +56286,47 @@
       <c r="Y123" s="101"/>
       <c r="Z123" s="101"/>
       <c r="AA123" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB123" s="101"/>
       <c r="AC123" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD123" s="101"/>
       <c r="AE123" s="101"/>
       <c r="AF123" s="101"/>
       <c r="AG123" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH123" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH123" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI123" s="49"/>
       <c r="AJ123" s="49"/>
       <c r="AK123" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL123" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL123" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM123" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN123" s="101"/>
       <c r="AO123" s="101"/>
       <c r="AP123" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ123" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR123" s="101"/>
@@ -56406,7 +56349,7 @@
       <c r="E124" s="101"/>
       <c r="F124" s="101"/>
       <c r="G124" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H124" s="101"/>
@@ -56418,7 +56361,7 @@
       <c r="N124" s="101"/>
       <c r="O124" s="101"/>
       <c r="P124" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q124" s="101"/>
@@ -56434,47 +56377,47 @@
       <c r="Y124" s="101"/>
       <c r="Z124" s="101"/>
       <c r="AA124" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB124" s="101"/>
       <c r="AC124" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD124" s="101"/>
       <c r="AE124" s="101"/>
       <c r="AF124" s="101"/>
       <c r="AG124" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH124" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH124" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI124" s="49"/>
       <c r="AJ124" s="49"/>
       <c r="AK124" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL124" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL124" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM124" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN124" s="101"/>
       <c r="AO124" s="101"/>
       <c r="AP124" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ124" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR124" s="101"/>
@@ -56497,7 +56440,7 @@
       <c r="E125" s="101"/>
       <c r="F125" s="101"/>
       <c r="G125" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H125" s="101"/>
@@ -56509,7 +56452,7 @@
       <c r="N125" s="101"/>
       <c r="O125" s="101"/>
       <c r="P125" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q125" s="101"/>
@@ -56525,47 +56468,47 @@
       <c r="Y125" s="101"/>
       <c r="Z125" s="101"/>
       <c r="AA125" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB125" s="101"/>
       <c r="AC125" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD125" s="101"/>
       <c r="AE125" s="101"/>
       <c r="AF125" s="101"/>
       <c r="AG125" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH125" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH125" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI125" s="49"/>
       <c r="AJ125" s="49"/>
       <c r="AK125" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL125" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL125" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM125" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN125" s="101"/>
       <c r="AO125" s="101"/>
       <c r="AP125" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ125" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR125" s="101"/>
@@ -56588,7 +56531,7 @@
       <c r="E126" s="101"/>
       <c r="F126" s="101"/>
       <c r="G126" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H126" s="101"/>
@@ -56600,7 +56543,7 @@
       <c r="N126" s="101"/>
       <c r="O126" s="101"/>
       <c r="P126" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q126" s="101"/>
@@ -56616,47 +56559,47 @@
       <c r="Y126" s="101"/>
       <c r="Z126" s="101"/>
       <c r="AA126" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB126" s="101"/>
       <c r="AC126" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD126" s="101"/>
       <c r="AE126" s="101"/>
       <c r="AF126" s="101"/>
       <c r="AG126" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH126" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH126" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI126" s="49"/>
       <c r="AJ126" s="49"/>
       <c r="AK126" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL126" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL126" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM126" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN126" s="101"/>
       <c r="AO126" s="101"/>
       <c r="AP126" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ126" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR126" s="101"/>
@@ -56679,7 +56622,7 @@
       <c r="E127" s="101"/>
       <c r="F127" s="101"/>
       <c r="G127" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H127" s="101"/>
@@ -56691,7 +56634,7 @@
       <c r="N127" s="101"/>
       <c r="O127" s="101"/>
       <c r="P127" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q127" s="101"/>
@@ -56707,47 +56650,47 @@
       <c r="Y127" s="101"/>
       <c r="Z127" s="101"/>
       <c r="AA127" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB127" s="101"/>
       <c r="AC127" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD127" s="101"/>
       <c r="AE127" s="101"/>
       <c r="AF127" s="101"/>
       <c r="AG127" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH127" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH127" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI127" s="49"/>
       <c r="AJ127" s="49"/>
       <c r="AK127" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL127" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL127" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM127" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN127" s="101"/>
       <c r="AO127" s="101"/>
       <c r="AP127" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ127" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR127" s="101"/>
@@ -56770,7 +56713,7 @@
       <c r="E128" s="101"/>
       <c r="F128" s="101"/>
       <c r="G128" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H128" s="101"/>
@@ -56782,7 +56725,7 @@
       <c r="N128" s="101"/>
       <c r="O128" s="101"/>
       <c r="P128" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q128" s="101"/>
@@ -56798,47 +56741,47 @@
       <c r="Y128" s="101"/>
       <c r="Z128" s="101"/>
       <c r="AA128" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB128" s="101"/>
       <c r="AC128" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD128" s="101"/>
       <c r="AE128" s="101"/>
       <c r="AF128" s="101"/>
       <c r="AG128" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH128" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH128" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI128" s="49"/>
       <c r="AJ128" s="49"/>
       <c r="AK128" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL128" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL128" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM128" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN128" s="101"/>
       <c r="AO128" s="101"/>
       <c r="AP128" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ128" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR128" s="101"/>
@@ -56861,7 +56804,7 @@
       <c r="E129" s="101"/>
       <c r="F129" s="101"/>
       <c r="G129" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H129" s="101"/>
@@ -56873,7 +56816,7 @@
       <c r="N129" s="101"/>
       <c r="O129" s="101"/>
       <c r="P129" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q129" s="101"/>
@@ -56889,47 +56832,47 @@
       <c r="Y129" s="101"/>
       <c r="Z129" s="101"/>
       <c r="AA129" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AB129" s="101"/>
       <c r="AC129" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD129" s="101"/>
       <c r="AE129" s="101"/>
       <c r="AF129" s="101"/>
       <c r="AG129" s="49" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH129" s="49" t="e">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH129" s="49" t="e">
-        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI129" s="49"/>
       <c r="AJ129" s="49"/>
       <c r="AK129" s="49" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL129" s="2">
         <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL129" s="2">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AM129" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN129" s="101"/>
       <c r="AO129" s="101"/>
       <c r="AP129" s="17" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ129" s="16" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR129" s="101"/>
@@ -56952,7 +56895,7 @@
       <c r="E130" s="101"/>
       <c r="F130" s="101"/>
       <c r="G130" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H130" s="101"/>
@@ -56964,7 +56907,7 @@
       <c r="N130" s="101"/>
       <c r="O130" s="101"/>
       <c r="P130" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q130" s="101"/>
@@ -56980,47 +56923,47 @@
       <c r="Y130" s="101"/>
       <c r="Z130" s="101"/>
       <c r="AA130" s="51">
-        <f t="shared" ref="AA130:AA161" si="46">IF(X130&lt;33,IF(Y130&gt;(1.1*X130),0,1),1)+IF(Y130&gt;(4*X130),-1,0)</f>
+        <f t="shared" ref="AA130:AA161" si="44">IF(X130&lt;33,IF(Y130&gt;(1.1*X130),0,1),1)+IF(Y130&gt;(4*X130),-1,0)</f>
         <v>1</v>
       </c>
       <c r="AB130" s="101"/>
       <c r="AC130" s="52">
-        <f t="shared" ref="AC130:AC161" si="47">IF(AB130&gt;9,1,0)+AB130/3</f>
+        <f t="shared" ref="AC130:AC161" si="45">IF(AB130&gt;9,1,0)+AB130/3</f>
         <v>0</v>
       </c>
       <c r="AD130" s="101"/>
       <c r="AE130" s="101"/>
       <c r="AF130" s="101"/>
       <c r="AG130" s="49" t="e">
-        <f t="shared" ref="AG130:AG161" si="48">IF(G130&lt;0,0,1.2)+IF(G130&lt;14,0,0.9)+IF(P130&lt;0,0.7,0)+IF(P130&lt;6.5,1,0)+IF(P130&lt;23,1,0)+IF(R130&gt;88,0,1)+IF(S130=5,0,S130)+IF(AD130&lt;20,0,1)+IF(AE130&lt;14,0,1)+IF(AF130&lt;26,0,1)</f>
+        <f t="shared" ref="AG130:AG161" si="46">IF(G130&lt;0,0,1.2)+IF(G130&lt;14,0,0.9)+IF(P130&lt;0,0.7,0)+IF(P130&lt;6.5,1,0)+IF(P130&lt;23,1,0)+IF(R130&gt;88,0,1)+IF(S130=5,0,S130)+IF(AD130&lt;20,0,1)+IF(AE130&lt;14,0,1)+IF(AF130&lt;26,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH130" s="49" t="e">
-        <f t="shared" ref="AH130:AH161" si="49">AG130+IF(AG130&gt;6,1,0)+IF(X130&lt;17,0,1)+IF(Y130&lt;11,0,1)+IF(Z130&lt;1.35,0,1)+AC130+AA130</f>
+        <f t="shared" ref="AH130:AH161" si="47">AG130+IF(AG130&gt;6,1,0)+IF(X130&lt;17,0,1)+IF(Y130&lt;11,0,1)+IF(Z130&lt;1.35,0,1)+AC130+AA130</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI130" s="49"/>
       <c r="AJ130" s="49"/>
       <c r="AK130" s="49" t="e">
-        <f t="shared" ref="AK130:AK161" si="50">AG130*3+AH130</f>
+        <f t="shared" ref="AK130:AK161" si="48">AG130*3+AH130</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL130" s="2">
-        <f t="shared" ref="AL130:AL161" si="51">D130</f>
+        <f t="shared" ref="AL130:AL161" si="49">D130</f>
         <v>0</v>
       </c>
       <c r="AM130" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN130" s="101"/>
       <c r="AO130" s="101"/>
       <c r="AP130" s="17" t="e">
-        <f t="shared" ref="AP130:AP159" si="52">IF(AK130&gt;22.9,IF(Z130&lt;101,IF(Z130&lt;35,IF(Z130&lt;8,3,2),1),0),0)</f>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ130" s="16" t="e">
-        <f t="shared" ref="AQ130:AQ161" si="53">IF(AP130&gt;0,IF(AB130&gt;10,(AB130/Z130),10/Z130),0)</f>
+        <f t="shared" ref="AQ130:AQ161" si="50">IF(AP130&gt;0,IF(AB130&gt;10,(AB130/Z130),10/Z130),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR130" s="101"/>
@@ -57043,7 +56986,7 @@
       <c r="E131" s="101"/>
       <c r="F131" s="101"/>
       <c r="G131" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H131" s="101"/>
@@ -57055,7 +56998,7 @@
       <c r="N131" s="101"/>
       <c r="O131" s="101"/>
       <c r="P131" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q131" s="101"/>
@@ -57071,47 +57014,47 @@
       <c r="Y131" s="101"/>
       <c r="Z131" s="101"/>
       <c r="AA131" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB131" s="101"/>
       <c r="AC131" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD131" s="101"/>
       <c r="AE131" s="101"/>
       <c r="AF131" s="101"/>
       <c r="AG131" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH131" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI131" s="49"/>
       <c r="AJ131" s="49"/>
       <c r="AK131" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL131" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM131" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN131" s="101"/>
       <c r="AO131" s="101"/>
       <c r="AP131" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="AP131:AP163" si="51">IF(AK131&gt;23,IF(Z131&lt;101,IF(Z131&lt;35,IF(Z131&lt;8,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ131" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR131" s="101"/>
@@ -57134,7 +57077,7 @@
       <c r="E132" s="101"/>
       <c r="F132" s="101"/>
       <c r="G132" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H132" s="101"/>
@@ -57146,7 +57089,7 @@
       <c r="N132" s="101"/>
       <c r="O132" s="101"/>
       <c r="P132" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q132" s="101"/>
@@ -57162,47 +57105,47 @@
       <c r="Y132" s="101"/>
       <c r="Z132" s="101"/>
       <c r="AA132" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB132" s="101"/>
       <c r="AC132" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD132" s="101"/>
       <c r="AE132" s="101"/>
       <c r="AF132" s="101"/>
       <c r="AG132" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH132" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI132" s="49"/>
       <c r="AJ132" s="49"/>
       <c r="AK132" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL132" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM132" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN132" s="101"/>
       <c r="AO132" s="101"/>
       <c r="AP132" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ132" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR132" s="101"/>
@@ -57225,7 +57168,7 @@
       <c r="E133" s="101"/>
       <c r="F133" s="101"/>
       <c r="G133" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H133" s="101"/>
@@ -57237,7 +57180,7 @@
       <c r="N133" s="101"/>
       <c r="O133" s="101"/>
       <c r="P133" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q133" s="101"/>
@@ -57253,47 +57196,47 @@
       <c r="Y133" s="101"/>
       <c r="Z133" s="101"/>
       <c r="AA133" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB133" s="101"/>
       <c r="AC133" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD133" s="101"/>
       <c r="AE133" s="101"/>
       <c r="AF133" s="101"/>
       <c r="AG133" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH133" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI133" s="49"/>
       <c r="AJ133" s="49"/>
       <c r="AK133" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL133" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM133" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN133" s="101"/>
       <c r="AO133" s="101"/>
       <c r="AP133" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ133" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR133" s="101"/>
@@ -57316,7 +57259,7 @@
       <c r="E134" s="101"/>
       <c r="F134" s="101"/>
       <c r="G134" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H134" s="101"/>
@@ -57328,7 +57271,7 @@
       <c r="N134" s="101"/>
       <c r="O134" s="101"/>
       <c r="P134" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q134" s="101"/>
@@ -57344,47 +57287,47 @@
       <c r="Y134" s="101"/>
       <c r="Z134" s="101"/>
       <c r="AA134" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB134" s="101"/>
       <c r="AC134" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD134" s="101"/>
       <c r="AE134" s="101"/>
       <c r="AF134" s="101"/>
       <c r="AG134" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH134" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI134" s="49"/>
       <c r="AJ134" s="49"/>
       <c r="AK134" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL134" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM134" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN134" s="101"/>
       <c r="AO134" s="101"/>
       <c r="AP134" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ134" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR134" s="101"/>
@@ -57407,7 +57350,7 @@
       <c r="E135" s="101"/>
       <c r="F135" s="101"/>
       <c r="G135" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H135" s="101"/>
@@ -57419,7 +57362,7 @@
       <c r="N135" s="101"/>
       <c r="O135" s="101"/>
       <c r="P135" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q135" s="101"/>
@@ -57435,47 +57378,47 @@
       <c r="Y135" s="101"/>
       <c r="Z135" s="101"/>
       <c r="AA135" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB135" s="101"/>
       <c r="AC135" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD135" s="101"/>
       <c r="AE135" s="101"/>
       <c r="AF135" s="101"/>
       <c r="AG135" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH135" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI135" s="49"/>
       <c r="AJ135" s="49"/>
       <c r="AK135" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL135" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM135" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN135" s="101"/>
       <c r="AO135" s="101"/>
       <c r="AP135" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ135" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR135" s="101"/>
@@ -57498,7 +57441,7 @@
       <c r="E136" s="101"/>
       <c r="F136" s="101"/>
       <c r="G136" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H136" s="101"/>
@@ -57510,7 +57453,7 @@
       <c r="N136" s="101"/>
       <c r="O136" s="101"/>
       <c r="P136" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q136" s="101"/>
@@ -57526,47 +57469,47 @@
       <c r="Y136" s="101"/>
       <c r="Z136" s="101"/>
       <c r="AA136" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB136" s="101"/>
       <c r="AC136" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD136" s="101"/>
       <c r="AE136" s="101"/>
       <c r="AF136" s="101"/>
       <c r="AG136" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH136" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI136" s="49"/>
       <c r="AJ136" s="49"/>
       <c r="AK136" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL136" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM136" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN136" s="101"/>
       <c r="AO136" s="101"/>
       <c r="AP136" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ136" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR136" s="101"/>
@@ -57589,7 +57532,7 @@
       <c r="E137" s="101"/>
       <c r="F137" s="101"/>
       <c r="G137" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H137" s="101"/>
@@ -57601,7 +57544,7 @@
       <c r="N137" s="101"/>
       <c r="O137" s="101"/>
       <c r="P137" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q137" s="101"/>
@@ -57617,47 +57560,47 @@
       <c r="Y137" s="101"/>
       <c r="Z137" s="101"/>
       <c r="AA137" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB137" s="101"/>
       <c r="AC137" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD137" s="101"/>
       <c r="AE137" s="101"/>
       <c r="AF137" s="101"/>
       <c r="AG137" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH137" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI137" s="49"/>
       <c r="AJ137" s="49"/>
       <c r="AK137" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL137" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM137" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN137" s="101"/>
       <c r="AO137" s="101"/>
       <c r="AP137" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ137" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR137" s="101"/>
@@ -57680,7 +57623,7 @@
       <c r="E138" s="101"/>
       <c r="F138" s="101"/>
       <c r="G138" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H138" s="101"/>
@@ -57692,7 +57635,7 @@
       <c r="N138" s="101"/>
       <c r="O138" s="101"/>
       <c r="P138" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q138" s="101"/>
@@ -57708,47 +57651,47 @@
       <c r="Y138" s="101"/>
       <c r="Z138" s="101"/>
       <c r="AA138" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB138" s="101"/>
       <c r="AC138" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD138" s="101"/>
       <c r="AE138" s="101"/>
       <c r="AF138" s="101"/>
       <c r="AG138" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH138" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI138" s="49"/>
       <c r="AJ138" s="49"/>
       <c r="AK138" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL138" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM138" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN138" s="101"/>
       <c r="AO138" s="101"/>
       <c r="AP138" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ138" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR138" s="101"/>
@@ -57771,7 +57714,7 @@
       <c r="E139" s="101"/>
       <c r="F139" s="101"/>
       <c r="G139" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H139" s="101"/>
@@ -57783,7 +57726,7 @@
       <c r="N139" s="101"/>
       <c r="O139" s="101"/>
       <c r="P139" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q139" s="101"/>
@@ -57799,47 +57742,47 @@
       <c r="Y139" s="101"/>
       <c r="Z139" s="101"/>
       <c r="AA139" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB139" s="101"/>
       <c r="AC139" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD139" s="101"/>
       <c r="AE139" s="101"/>
       <c r="AF139" s="101"/>
       <c r="AG139" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH139" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI139" s="49"/>
       <c r="AJ139" s="49"/>
       <c r="AK139" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL139" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM139" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN139" s="101"/>
       <c r="AO139" s="101"/>
       <c r="AP139" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ139" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR139" s="101"/>
@@ -57862,7 +57805,7 @@
       <c r="E140" s="101"/>
       <c r="F140" s="101"/>
       <c r="G140" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H140" s="101"/>
@@ -57874,7 +57817,7 @@
       <c r="N140" s="101"/>
       <c r="O140" s="101"/>
       <c r="P140" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q140" s="101"/>
@@ -57890,47 +57833,47 @@
       <c r="Y140" s="101"/>
       <c r="Z140" s="101"/>
       <c r="AA140" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB140" s="101"/>
       <c r="AC140" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD140" s="101"/>
       <c r="AE140" s="101"/>
       <c r="AF140" s="101"/>
       <c r="AG140" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH140" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI140" s="49"/>
       <c r="AJ140" s="49"/>
       <c r="AK140" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL140" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM140" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN140" s="101"/>
       <c r="AO140" s="101"/>
       <c r="AP140" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ140" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR140" s="101"/>
@@ -57953,7 +57896,7 @@
       <c r="E141" s="101"/>
       <c r="F141" s="101"/>
       <c r="G141" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H141" s="101"/>
@@ -57965,7 +57908,7 @@
       <c r="N141" s="101"/>
       <c r="O141" s="101"/>
       <c r="P141" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q141" s="101"/>
@@ -57981,47 +57924,47 @@
       <c r="Y141" s="101"/>
       <c r="Z141" s="101"/>
       <c r="AA141" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB141" s="101"/>
       <c r="AC141" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD141" s="101"/>
       <c r="AE141" s="101"/>
       <c r="AF141" s="101"/>
       <c r="AG141" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH141" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI141" s="49"/>
       <c r="AJ141" s="49"/>
       <c r="AK141" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL141" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM141" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN141" s="101"/>
       <c r="AO141" s="101"/>
       <c r="AP141" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ141" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR141" s="101"/>
@@ -58044,7 +57987,7 @@
       <c r="E142" s="101"/>
       <c r="F142" s="101"/>
       <c r="G142" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H142" s="101"/>
@@ -58056,7 +57999,7 @@
       <c r="N142" s="101"/>
       <c r="O142" s="101"/>
       <c r="P142" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q142" s="101"/>
@@ -58072,47 +58015,47 @@
       <c r="Y142" s="101"/>
       <c r="Z142" s="101"/>
       <c r="AA142" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB142" s="101"/>
       <c r="AC142" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD142" s="101"/>
       <c r="AE142" s="101"/>
       <c r="AF142" s="101"/>
       <c r="AG142" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH142" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI142" s="49"/>
       <c r="AJ142" s="49"/>
       <c r="AK142" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL142" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM142" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN142" s="101"/>
       <c r="AO142" s="101"/>
       <c r="AP142" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ142" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR142" s="101"/>
@@ -58135,7 +58078,7 @@
       <c r="E143" s="101"/>
       <c r="F143" s="101"/>
       <c r="G143" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H143" s="101"/>
@@ -58147,7 +58090,7 @@
       <c r="N143" s="101"/>
       <c r="O143" s="101"/>
       <c r="P143" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q143" s="101"/>
@@ -58163,47 +58106,47 @@
       <c r="Y143" s="101"/>
       <c r="Z143" s="101"/>
       <c r="AA143" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB143" s="101"/>
       <c r="AC143" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD143" s="101"/>
       <c r="AE143" s="101"/>
       <c r="AF143" s="101"/>
       <c r="AG143" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH143" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI143" s="49"/>
       <c r="AJ143" s="49"/>
       <c r="AK143" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL143" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM143" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN143" s="101"/>
       <c r="AO143" s="101"/>
       <c r="AP143" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ143" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR143" s="101"/>
@@ -58226,7 +58169,7 @@
       <c r="E144" s="101"/>
       <c r="F144" s="101"/>
       <c r="G144" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H144" s="101"/>
@@ -58238,7 +58181,7 @@
       <c r="N144" s="101"/>
       <c r="O144" s="101"/>
       <c r="P144" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q144" s="101"/>
@@ -58254,47 +58197,47 @@
       <c r="Y144" s="101"/>
       <c r="Z144" s="101"/>
       <c r="AA144" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB144" s="101"/>
       <c r="AC144" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD144" s="101"/>
       <c r="AE144" s="101"/>
       <c r="AF144" s="101"/>
       <c r="AG144" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH144" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI144" s="49"/>
       <c r="AJ144" s="49"/>
       <c r="AK144" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL144" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM144" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN144" s="101"/>
       <c r="AO144" s="101"/>
       <c r="AP144" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ144" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR144" s="101"/>
@@ -58317,7 +58260,7 @@
       <c r="E145" s="101"/>
       <c r="F145" s="101"/>
       <c r="G145" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H145" s="101"/>
@@ -58329,7 +58272,7 @@
       <c r="N145" s="101"/>
       <c r="O145" s="101"/>
       <c r="P145" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q145" s="101"/>
@@ -58345,47 +58288,47 @@
       <c r="Y145" s="101"/>
       <c r="Z145" s="101"/>
       <c r="AA145" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB145" s="101"/>
       <c r="AC145" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD145" s="101"/>
       <c r="AE145" s="101"/>
       <c r="AF145" s="101"/>
       <c r="AG145" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH145" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI145" s="49"/>
       <c r="AJ145" s="49"/>
       <c r="AK145" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL145" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM145" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN145" s="101"/>
       <c r="AO145" s="101"/>
       <c r="AP145" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ145" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR145" s="101"/>
@@ -58408,7 +58351,7 @@
       <c r="E146" s="101"/>
       <c r="F146" s="101"/>
       <c r="G146" s="47" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H146" s="101"/>
@@ -58420,7 +58363,7 @@
       <c r="N146" s="101"/>
       <c r="O146" s="101"/>
       <c r="P146" s="47" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q146" s="101"/>
@@ -58436,47 +58379,47 @@
       <c r="Y146" s="101"/>
       <c r="Z146" s="101"/>
       <c r="AA146" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB146" s="101"/>
       <c r="AC146" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD146" s="101"/>
       <c r="AE146" s="101"/>
       <c r="AF146" s="101"/>
       <c r="AG146" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH146" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI146" s="49"/>
       <c r="AJ146" s="49"/>
       <c r="AK146" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL146" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM146" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AN146" s="101"/>
       <c r="AO146" s="101"/>
       <c r="AP146" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ146" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR146" s="101"/>
@@ -58499,7 +58442,7 @@
       <c r="E147" s="101"/>
       <c r="F147" s="101"/>
       <c r="G147" s="47" t="e">
-        <f t="shared" ref="G147:G178" si="54">100*(F147-E147)/F147</f>
+        <f t="shared" ref="G147:G175" si="52">100*(F147-E147)/F147</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H147" s="101"/>
@@ -58511,7 +58454,7 @@
       <c r="N147" s="101"/>
       <c r="O147" s="101"/>
       <c r="P147" s="47" t="e">
-        <f t="shared" ref="P147:P178" si="55">O147/I147</f>
+        <f t="shared" ref="P147:P175" si="53">O147/I147</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q147" s="101"/>
@@ -58527,47 +58470,47 @@
       <c r="Y147" s="101"/>
       <c r="Z147" s="101"/>
       <c r="AA147" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB147" s="101"/>
       <c r="AC147" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD147" s="101"/>
       <c r="AE147" s="101"/>
       <c r="AF147" s="101"/>
       <c r="AG147" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH147" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI147" s="49"/>
       <c r="AJ147" s="49"/>
       <c r="AK147" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL147" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM147" s="2">
-        <f t="shared" ref="AM147:AM167" si="56">B147</f>
+        <f t="shared" ref="AM147:AM167" si="54">B147</f>
         <v>0</v>
       </c>
       <c r="AN147" s="101"/>
       <c r="AO147" s="101"/>
       <c r="AP147" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ147" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR147" s="101"/>
@@ -58590,7 +58533,7 @@
       <c r="E148" s="101"/>
       <c r="F148" s="101"/>
       <c r="G148" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H148" s="101"/>
@@ -58602,7 +58545,7 @@
       <c r="N148" s="101"/>
       <c r="O148" s="101"/>
       <c r="P148" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q148" s="101"/>
@@ -58618,47 +58561,47 @@
       <c r="Y148" s="101"/>
       <c r="Z148" s="101"/>
       <c r="AA148" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB148" s="101"/>
       <c r="AC148" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD148" s="101"/>
       <c r="AE148" s="101"/>
       <c r="AF148" s="101"/>
       <c r="AG148" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH148" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI148" s="49"/>
       <c r="AJ148" s="49"/>
       <c r="AK148" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL148" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM148" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN148" s="101"/>
       <c r="AO148" s="101"/>
       <c r="AP148" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ148" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR148" s="101"/>
@@ -58681,7 +58624,7 @@
       <c r="E149" s="101"/>
       <c r="F149" s="101"/>
       <c r="G149" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H149" s="101"/>
@@ -58693,7 +58636,7 @@
       <c r="N149" s="101"/>
       <c r="O149" s="101"/>
       <c r="P149" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q149" s="101"/>
@@ -58709,47 +58652,47 @@
       <c r="Y149" s="101"/>
       <c r="Z149" s="101"/>
       <c r="AA149" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB149" s="101"/>
       <c r="AC149" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD149" s="101"/>
       <c r="AE149" s="101"/>
       <c r="AF149" s="101"/>
       <c r="AG149" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH149" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI149" s="49"/>
       <c r="AJ149" s="49"/>
       <c r="AK149" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL149" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM149" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN149" s="101"/>
       <c r="AO149" s="101"/>
       <c r="AP149" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ149" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR149" s="101"/>
@@ -58772,7 +58715,7 @@
       <c r="E150" s="101"/>
       <c r="F150" s="101"/>
       <c r="G150" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H150" s="101"/>
@@ -58784,7 +58727,7 @@
       <c r="N150" s="101"/>
       <c r="O150" s="101"/>
       <c r="P150" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q150" s="101"/>
@@ -58800,47 +58743,47 @@
       <c r="Y150" s="101"/>
       <c r="Z150" s="101"/>
       <c r="AA150" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB150" s="101"/>
       <c r="AC150" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD150" s="101"/>
       <c r="AE150" s="101"/>
       <c r="AF150" s="101"/>
       <c r="AG150" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH150" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI150" s="49"/>
       <c r="AJ150" s="49"/>
       <c r="AK150" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL150" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM150" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN150" s="101"/>
       <c r="AO150" s="101"/>
       <c r="AP150" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ150" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR150" s="101"/>
@@ -58863,7 +58806,7 @@
       <c r="E151" s="101"/>
       <c r="F151" s="101"/>
       <c r="G151" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H151" s="101"/>
@@ -58875,7 +58818,7 @@
       <c r="N151" s="101"/>
       <c r="O151" s="101"/>
       <c r="P151" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q151" s="101"/>
@@ -58891,47 +58834,47 @@
       <c r="Y151" s="101"/>
       <c r="Z151" s="101"/>
       <c r="AA151" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB151" s="101"/>
       <c r="AC151" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD151" s="101"/>
       <c r="AE151" s="101"/>
       <c r="AF151" s="101"/>
       <c r="AG151" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH151" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI151" s="49"/>
       <c r="AJ151" s="49"/>
       <c r="AK151" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL151" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM151" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN151" s="101"/>
       <c r="AO151" s="101"/>
       <c r="AP151" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ151" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR151" s="101"/>
@@ -58954,7 +58897,7 @@
       <c r="E152" s="101"/>
       <c r="F152" s="101"/>
       <c r="G152" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H152" s="101"/>
@@ -58966,7 +58909,7 @@
       <c r="N152" s="101"/>
       <c r="O152" s="101"/>
       <c r="P152" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q152" s="101"/>
@@ -58982,47 +58925,47 @@
       <c r="Y152" s="101"/>
       <c r="Z152" s="101"/>
       <c r="AA152" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB152" s="101"/>
       <c r="AC152" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD152" s="101"/>
       <c r="AE152" s="101"/>
       <c r="AF152" s="101"/>
       <c r="AG152" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH152" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI152" s="49"/>
       <c r="AJ152" s="49"/>
       <c r="AK152" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL152" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM152" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN152" s="101"/>
       <c r="AO152" s="101"/>
       <c r="AP152" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ152" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR152" s="101"/>
@@ -59045,7 +58988,7 @@
       <c r="E153" s="101"/>
       <c r="F153" s="101"/>
       <c r="G153" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H153" s="101"/>
@@ -59057,7 +59000,7 @@
       <c r="N153" s="101"/>
       <c r="O153" s="101"/>
       <c r="P153" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q153" s="101"/>
@@ -59073,47 +59016,47 @@
       <c r="Y153" s="101"/>
       <c r="Z153" s="101"/>
       <c r="AA153" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB153" s="101"/>
       <c r="AC153" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD153" s="101"/>
       <c r="AE153" s="101"/>
       <c r="AF153" s="101"/>
       <c r="AG153" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH153" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI153" s="49"/>
       <c r="AJ153" s="49"/>
       <c r="AK153" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL153" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM153" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN153" s="101"/>
       <c r="AO153" s="101"/>
       <c r="AP153" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ153" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR153" s="101"/>
@@ -59136,7 +59079,7 @@
       <c r="E154" s="101"/>
       <c r="F154" s="101"/>
       <c r="G154" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H154" s="101"/>
@@ -59148,7 +59091,7 @@
       <c r="N154" s="101"/>
       <c r="O154" s="101"/>
       <c r="P154" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q154" s="101"/>
@@ -59164,47 +59107,47 @@
       <c r="Y154" s="101"/>
       <c r="Z154" s="101"/>
       <c r="AA154" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB154" s="101"/>
       <c r="AC154" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD154" s="101"/>
       <c r="AE154" s="101"/>
       <c r="AF154" s="101"/>
       <c r="AG154" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH154" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI154" s="49"/>
       <c r="AJ154" s="49"/>
       <c r="AK154" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL154" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM154" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN154" s="101"/>
       <c r="AO154" s="101"/>
       <c r="AP154" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ154" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR154" s="101"/>
@@ -59227,7 +59170,7 @@
       <c r="E155" s="101"/>
       <c r="F155" s="101"/>
       <c r="G155" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H155" s="101"/>
@@ -59239,7 +59182,7 @@
       <c r="N155" s="101"/>
       <c r="O155" s="101"/>
       <c r="P155" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q155" s="101"/>
@@ -59255,47 +59198,47 @@
       <c r="Y155" s="101"/>
       <c r="Z155" s="101"/>
       <c r="AA155" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB155" s="101"/>
       <c r="AC155" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD155" s="101"/>
       <c r="AE155" s="101"/>
       <c r="AF155" s="101"/>
       <c r="AG155" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH155" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI155" s="49"/>
       <c r="AJ155" s="49"/>
       <c r="AK155" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL155" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM155" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN155" s="101"/>
       <c r="AO155" s="101"/>
       <c r="AP155" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ155" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR155" s="101"/>
@@ -59318,7 +59261,7 @@
       <c r="E156" s="101"/>
       <c r="F156" s="101"/>
       <c r="G156" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H156" s="101"/>
@@ -59330,7 +59273,7 @@
       <c r="N156" s="101"/>
       <c r="O156" s="101"/>
       <c r="P156" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q156" s="101"/>
@@ -59346,47 +59289,47 @@
       <c r="Y156" s="101"/>
       <c r="Z156" s="101"/>
       <c r="AA156" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB156" s="101"/>
       <c r="AC156" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD156" s="101"/>
       <c r="AE156" s="101"/>
       <c r="AF156" s="101"/>
       <c r="AG156" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH156" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI156" s="49"/>
       <c r="AJ156" s="49"/>
       <c r="AK156" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL156" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM156" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN156" s="101"/>
       <c r="AO156" s="101"/>
       <c r="AP156" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ156" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR156" s="101"/>
@@ -59409,7 +59352,7 @@
       <c r="E157" s="101"/>
       <c r="F157" s="101"/>
       <c r="G157" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H157" s="101"/>
@@ -59421,7 +59364,7 @@
       <c r="N157" s="101"/>
       <c r="O157" s="101"/>
       <c r="P157" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q157" s="101"/>
@@ -59437,47 +59380,47 @@
       <c r="Y157" s="101"/>
       <c r="Z157" s="101"/>
       <c r="AA157" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB157" s="101"/>
       <c r="AC157" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD157" s="101"/>
       <c r="AE157" s="101"/>
       <c r="AF157" s="101"/>
       <c r="AG157" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH157" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI157" s="49"/>
       <c r="AJ157" s="49"/>
       <c r="AK157" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL157" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM157" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN157" s="101"/>
       <c r="AO157" s="101"/>
       <c r="AP157" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ157" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR157" s="101"/>
@@ -59500,7 +59443,7 @@
       <c r="E158" s="101"/>
       <c r="F158" s="101"/>
       <c r="G158" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H158" s="101"/>
@@ -59512,7 +59455,7 @@
       <c r="N158" s="101"/>
       <c r="O158" s="101"/>
       <c r="P158" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q158" s="101"/>
@@ -59528,47 +59471,47 @@
       <c r="Y158" s="101"/>
       <c r="Z158" s="101"/>
       <c r="AA158" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB158" s="101"/>
       <c r="AC158" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD158" s="101"/>
       <c r="AE158" s="101"/>
       <c r="AF158" s="101"/>
       <c r="AG158" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH158" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI158" s="49"/>
       <c r="AJ158" s="49"/>
       <c r="AK158" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL158" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM158" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN158" s="101"/>
       <c r="AO158" s="101"/>
       <c r="AP158" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ158" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR158" s="101"/>
@@ -59591,7 +59534,7 @@
       <c r="E159" s="101"/>
       <c r="F159" s="101"/>
       <c r="G159" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H159" s="101"/>
@@ -59603,7 +59546,7 @@
       <c r="N159" s="101"/>
       <c r="O159" s="101"/>
       <c r="P159" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q159" s="101"/>
@@ -59619,47 +59562,47 @@
       <c r="Y159" s="101"/>
       <c r="Z159" s="101"/>
       <c r="AA159" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB159" s="101"/>
       <c r="AC159" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD159" s="101"/>
       <c r="AE159" s="101"/>
       <c r="AF159" s="101"/>
       <c r="AG159" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH159" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI159" s="49"/>
       <c r="AJ159" s="49"/>
       <c r="AK159" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL159" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM159" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN159" s="101"/>
       <c r="AO159" s="101"/>
       <c r="AP159" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ159" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR159" s="101"/>
@@ -59682,7 +59625,7 @@
       <c r="E160" s="101"/>
       <c r="F160" s="101"/>
       <c r="G160" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H160" s="101"/>
@@ -59694,7 +59637,7 @@
       <c r="N160" s="101"/>
       <c r="O160" s="101"/>
       <c r="P160" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q160" s="101"/>
@@ -59710,47 +59653,47 @@
       <c r="Y160" s="101"/>
       <c r="Z160" s="101"/>
       <c r="AA160" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB160" s="101"/>
       <c r="AC160" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD160" s="101"/>
       <c r="AE160" s="101"/>
       <c r="AF160" s="101"/>
       <c r="AG160" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH160" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI160" s="49"/>
       <c r="AJ160" s="49"/>
       <c r="AK160" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL160" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM160" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN160" s="101"/>
       <c r="AO160" s="101"/>
       <c r="AP160" s="17" t="e">
-        <f>IF(AK160&gt;13.8,IF(Z160&lt;101,IF(Z160&lt;35,IF(Z160&lt;8,3,2),1),0),0)</f>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ160" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR160" s="101"/>
@@ -59773,7 +59716,7 @@
       <c r="E161" s="101"/>
       <c r="F161" s="101"/>
       <c r="G161" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H161" s="101"/>
@@ -59785,7 +59728,7 @@
       <c r="N161" s="101"/>
       <c r="O161" s="101"/>
       <c r="P161" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q161" s="101"/>
@@ -59801,47 +59744,47 @@
       <c r="Y161" s="101"/>
       <c r="Z161" s="101"/>
       <c r="AA161" s="51">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="AB161" s="101"/>
       <c r="AC161" s="52">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AD161" s="101"/>
       <c r="AE161" s="101"/>
       <c r="AF161" s="101"/>
       <c r="AG161" s="49" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH161" s="49" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI161" s="49"/>
       <c r="AJ161" s="49"/>
       <c r="AK161" s="49" t="e">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL161" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AM161" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN161" s="101"/>
       <c r="AO161" s="101"/>
       <c r="AP161" s="17" t="e">
-        <f>IF(AK161&gt;13.8,IF(Z161&lt;101,IF(Z161&lt;35,IF(Z161&lt;8,3,2),1),0),0)</f>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ161" s="16" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR161" s="101"/>
@@ -59864,7 +59807,7 @@
       <c r="E162" s="101"/>
       <c r="F162" s="101"/>
       <c r="G162" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H162" s="101"/>
@@ -59876,7 +59819,7 @@
       <c r="N162" s="101"/>
       <c r="O162" s="101"/>
       <c r="P162" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q162" s="101"/>
@@ -59892,47 +59835,47 @@
       <c r="Y162" s="101"/>
       <c r="Z162" s="101"/>
       <c r="AA162" s="51">
-        <f t="shared" ref="AA162:AA169" si="57">IF(X162&lt;33,IF(Y162&gt;(1.1*X162),0,1),1)+IF(Y162&gt;(4*X162),-1,0)</f>
+        <f t="shared" ref="AA162:AA169" si="55">IF(X162&lt;33,IF(Y162&gt;(1.1*X162),0,1),1)+IF(Y162&gt;(4*X162),-1,0)</f>
         <v>1</v>
       </c>
       <c r="AB162" s="101"/>
       <c r="AC162" s="52">
-        <f t="shared" ref="AC162:AC193" si="58">IF(AB162&gt;9,1,0)+AB162/3</f>
+        <f t="shared" ref="AC162:AC165" si="56">IF(AB162&gt;9,1,0)+AB162/3</f>
         <v>0</v>
       </c>
       <c r="AD162" s="101"/>
       <c r="AE162" s="101"/>
       <c r="AF162" s="101"/>
       <c r="AG162" s="49" t="e">
-        <f t="shared" ref="AG162:AG193" si="59">IF(G162&lt;0,0,1.2)+IF(G162&lt;14,0,0.9)+IF(P162&lt;0,0.7,0)+IF(P162&lt;6.5,1,0)+IF(P162&lt;23,1,0)+IF(R162&gt;88,0,1)+IF(S162=5,0,S162)+IF(AD162&lt;20,0,1)+IF(AE162&lt;14,0,1)+IF(AF162&lt;26,0,1)</f>
+        <f t="shared" ref="AG162:AG169" si="57">IF(G162&lt;0,0,1.2)+IF(G162&lt;14,0,0.9)+IF(P162&lt;0,0.7,0)+IF(P162&lt;6.5,1,0)+IF(P162&lt;23,1,0)+IF(R162&gt;88,0,1)+IF(S162=5,0,S162)+IF(AD162&lt;20,0,1)+IF(AE162&lt;14,0,1)+IF(AF162&lt;26,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH162" s="49" t="e">
-        <f t="shared" ref="AH162:AH193" si="60">AG162+IF(AG162&gt;6,1,0)+IF(X162&lt;17,0,1)+IF(Y162&lt;11,0,1)+IF(Z162&lt;1.35,0,1)+AC162+AA162</f>
+        <f t="shared" ref="AH162:AH169" si="58">AG162+IF(AG162&gt;6,1,0)+IF(X162&lt;17,0,1)+IF(Y162&lt;11,0,1)+IF(Z162&lt;1.35,0,1)+AC162+AA162</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI162" s="49"/>
       <c r="AJ162" s="49"/>
       <c r="AK162" s="49" t="e">
-        <f t="shared" ref="AK162:AK169" si="61">AG162*3+AH162</f>
+        <f t="shared" ref="AK162:AK169" si="59">AG162*3+AH162</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL162" s="2">
-        <f t="shared" ref="AL162:AL167" si="62">D162</f>
+        <f t="shared" ref="AL162:AL167" si="60">D162</f>
         <v>0</v>
       </c>
       <c r="AM162" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN162" s="101"/>
       <c r="AO162" s="101"/>
       <c r="AP162" s="17" t="e">
-        <f>IF(AK162&gt;13.8,IF(Z162&lt;101,IF(Z162&lt;35,IF(Z162&lt;8,3,2),1),0),0)</f>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ162" s="16" t="e">
-        <f t="shared" ref="AQ162:AQ193" si="63">IF(AP162&gt;0,IF(AB162&gt;10,(AB162/Z162),10/Z162),0)</f>
+        <f t="shared" ref="AQ162:AQ166" si="61">IF(AP162&gt;0,IF(AB162&gt;10,(AB162/Z162),10/Z162),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR162" s="101"/>
@@ -59955,7 +59898,7 @@
       <c r="E163" s="101"/>
       <c r="F163" s="101"/>
       <c r="G163" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H163" s="101"/>
@@ -59967,7 +59910,7 @@
       <c r="N163" s="101"/>
       <c r="O163" s="101"/>
       <c r="P163" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q163" s="101"/>
@@ -59983,47 +59926,47 @@
       <c r="Y163" s="101"/>
       <c r="Z163" s="101"/>
       <c r="AA163" s="51">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="AB163" s="101"/>
       <c r="AC163" s="52">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AD163" s="101"/>
       <c r="AE163" s="101"/>
       <c r="AF163" s="101"/>
       <c r="AG163" s="49" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH163" s="49" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI163" s="49"/>
       <c r="AJ163" s="49"/>
       <c r="AK163" s="49" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL163" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AM163" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN163" s="101"/>
       <c r="AO163" s="101"/>
       <c r="AP163" s="17" t="e">
-        <f>IF(AK163&gt;13.8,IF(Z163&lt;101,IF(Z163&lt;35,IF(Z163&lt;8,3,2),1),0),0)</f>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ163" s="16" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR163" s="101"/>
@@ -60046,7 +59989,7 @@
       <c r="E164" s="101"/>
       <c r="F164" s="101"/>
       <c r="G164" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H164" s="101"/>
@@ -60058,7 +60001,7 @@
       <c r="N164" s="101"/>
       <c r="O164" s="101"/>
       <c r="P164" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q164" s="101"/>
@@ -60074,37 +60017,37 @@
       <c r="Y164" s="101"/>
       <c r="Z164" s="101"/>
       <c r="AA164" s="51">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="AB164" s="101"/>
       <c r="AC164" s="52">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AD164" s="101"/>
       <c r="AE164" s="101"/>
       <c r="AF164" s="101"/>
       <c r="AG164" s="49" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH164" s="49" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI164" s="49"/>
       <c r="AJ164" s="49"/>
       <c r="AK164" s="49" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL164" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AM164" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN164" s="101"/>
@@ -60114,7 +60057,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ164" s="16" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR164" s="101"/>
@@ -60137,7 +60080,7 @@
       <c r="E165" s="101"/>
       <c r="F165" s="101"/>
       <c r="G165" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H165" s="101"/>
@@ -60149,7 +60092,7 @@
       <c r="N165" s="101"/>
       <c r="O165" s="101"/>
       <c r="P165" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q165" s="101"/>
@@ -60165,37 +60108,37 @@
       <c r="Y165" s="101"/>
       <c r="Z165" s="101"/>
       <c r="AA165" s="51">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="AB165" s="101"/>
       <c r="AC165" s="52">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AD165" s="101"/>
       <c r="AE165" s="101"/>
       <c r="AF165" s="101"/>
       <c r="AG165" s="49" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH165" s="49" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI165" s="49"/>
       <c r="AJ165" s="49"/>
       <c r="AK165" s="49" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL165" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AM165" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN165" s="101"/>
@@ -60205,7 +60148,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ165" s="16" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR165" s="101"/>
@@ -60228,7 +60171,7 @@
       <c r="E166" s="101"/>
       <c r="F166" s="101"/>
       <c r="G166" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H166" s="101"/>
@@ -60240,7 +60183,7 @@
       <c r="N166" s="101"/>
       <c r="O166" s="101"/>
       <c r="P166" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q166" s="101"/>
@@ -60256,7 +60199,7 @@
       <c r="Y166" s="101"/>
       <c r="Z166" s="101"/>
       <c r="AA166" s="51">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="AB166" s="101"/>
@@ -60265,25 +60208,25 @@
       <c r="AE166" s="101"/>
       <c r="AF166" s="101"/>
       <c r="AG166" s="49" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH166" s="49" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI166" s="49"/>
       <c r="AJ166" s="49"/>
       <c r="AK166" s="49" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL166" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AM166" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN166" s="101"/>
@@ -60293,7 +60236,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ166" s="16" t="e">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AR166" s="101"/>
@@ -60316,7 +60259,7 @@
       <c r="E167" s="101"/>
       <c r="F167" s="101"/>
       <c r="G167" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H167" s="101"/>
@@ -60328,7 +60271,7 @@
       <c r="N167" s="101"/>
       <c r="O167" s="101"/>
       <c r="P167" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q167" s="101"/>
@@ -60344,7 +60287,7 @@
       <c r="Y167" s="101"/>
       <c r="Z167" s="101"/>
       <c r="AA167" s="51">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="AB167" s="101"/>
@@ -60353,25 +60296,25 @@
       <c r="AE167" s="101"/>
       <c r="AF167" s="101"/>
       <c r="AG167" s="49" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH167" s="49" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI167" s="49"/>
       <c r="AJ167" s="49"/>
       <c r="AK167" s="49" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL167" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AM167" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AN167" s="101"/>
@@ -60398,7 +60341,7 @@
       <c r="E168" s="101"/>
       <c r="F168" s="101"/>
       <c r="G168" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H168" s="101"/>
@@ -60410,7 +60353,7 @@
       <c r="N168" s="101"/>
       <c r="O168" s="101"/>
       <c r="P168" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q168" s="101"/>
@@ -60426,7 +60369,7 @@
       <c r="Y168" s="101"/>
       <c r="Z168" s="101"/>
       <c r="AA168" s="51">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="AB168" s="101"/>
@@ -60435,17 +60378,17 @@
       <c r="AE168" s="101"/>
       <c r="AF168" s="101"/>
       <c r="AG168" s="49" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH168" s="49" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI168" s="49"/>
       <c r="AJ168" s="49"/>
       <c r="AK168" s="49" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL168" s="101"/>
@@ -60474,7 +60417,7 @@
       <c r="E169" s="101"/>
       <c r="F169" s="101"/>
       <c r="G169" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H169" s="101"/>
@@ -60486,7 +60429,7 @@
       <c r="N169" s="101"/>
       <c r="O169" s="101"/>
       <c r="P169" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q169" s="101"/>
@@ -60502,7 +60445,7 @@
       <c r="Y169" s="101"/>
       <c r="Z169" s="101"/>
       <c r="AA169" s="51">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="AB169" s="101"/>
@@ -60511,17 +60454,17 @@
       <c r="AE169" s="101"/>
       <c r="AF169" s="101"/>
       <c r="AG169" s="49" t="e">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH169" s="49" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI169" s="49"/>
       <c r="AJ169" s="49"/>
       <c r="AK169" s="49" t="e">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL169" s="101"/>
@@ -60550,7 +60493,7 @@
       <c r="E170" s="101"/>
       <c r="F170" s="101"/>
       <c r="G170" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H170" s="101"/>
@@ -60562,7 +60505,7 @@
       <c r="N170" s="101"/>
       <c r="O170" s="101"/>
       <c r="P170" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q170" s="101"/>
@@ -60612,7 +60555,7 @@
       <c r="E171" s="101"/>
       <c r="F171" s="101"/>
       <c r="G171" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H171" s="101"/>
@@ -60624,7 +60567,7 @@
       <c r="N171" s="101"/>
       <c r="O171" s="101"/>
       <c r="P171" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q171" s="101"/>
@@ -60674,7 +60617,7 @@
       <c r="E172" s="101"/>
       <c r="F172" s="101"/>
       <c r="G172" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H172" s="101"/>
@@ -60686,7 +60629,7 @@
       <c r="N172" s="101"/>
       <c r="O172" s="101"/>
       <c r="P172" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q172" s="101"/>
@@ -60736,7 +60679,7 @@
       <c r="E173" s="101"/>
       <c r="F173" s="101"/>
       <c r="G173" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H173" s="101"/>
@@ -60748,7 +60691,7 @@
       <c r="N173" s="101"/>
       <c r="O173" s="101"/>
       <c r="P173" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q173" s="101"/>
@@ -60798,7 +60741,7 @@
       <c r="E174" s="101"/>
       <c r="F174" s="101"/>
       <c r="G174" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H174" s="101"/>
@@ -60810,7 +60753,7 @@
       <c r="N174" s="101"/>
       <c r="O174" s="101"/>
       <c r="P174" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q174" s="101"/>
@@ -60860,7 +60803,7 @@
       <c r="E175" s="101"/>
       <c r="F175" s="101"/>
       <c r="G175" s="47" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H175" s="101"/>
@@ -60872,7 +60815,7 @@
       <c r="N175" s="101"/>
       <c r="O175" s="101"/>
       <c r="P175" s="47" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q175" s="101"/>
@@ -61000,52 +60943,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:DA484"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" customWidth="1"/>
-    <col min="25" max="25" width="5.5703125" customWidth="1"/>
-    <col min="26" max="26" width="3.42578125" customWidth="1"/>
-    <col min="27" max="27" width="5.85546875" customWidth="1"/>
-    <col min="28" max="28" width="7.28515625" customWidth="1"/>
-    <col min="29" max="29" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="7.140625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="5.5703125" customWidth="1"/>
-    <col min="34" max="34" width="6.28515625" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" customWidth="1"/>
-    <col min="36" max="36" width="4.42578125" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" customWidth="1"/>
+    <col min="20" max="20" width="5.33203125" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.33203125" customWidth="1"/>
+    <col min="25" max="25" width="5.5546875" customWidth="1"/>
+    <col min="26" max="26" width="3.44140625" customWidth="1"/>
+    <col min="27" max="27" width="5.88671875" customWidth="1"/>
+    <col min="28" max="28" width="7.33203125" customWidth="1"/>
+    <col min="29" max="29" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.109375" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="5.5546875" customWidth="1"/>
+    <col min="34" max="34" width="6.33203125" customWidth="1"/>
+    <col min="35" max="35" width="8.88671875" customWidth="1"/>
+    <col min="36" max="36" width="4.44140625" customWidth="1"/>
     <col min="38" max="42" width="13" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="1.5703125" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="1.5546875" hidden="1" customWidth="1"/>
     <col min="53" max="54" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104" ht="92.45" customHeight="1">
+    <row r="1" spans="1:104" ht="92.4" customHeight="1">
       <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
@@ -69847,7 +69790,7 @@
         <v>15.6</v>
       </c>
       <c r="G66" s="70">
-        <f t="shared" ref="G66:G97" si="18">100*(F66-E66)/F66</f>
+        <f t="shared" ref="G66:G89" si="18">100*(F66-E66)/F66</f>
         <v>82.371794871794876</v>
       </c>
       <c r="H66" s="75">
@@ -69869,7 +69812,7 @@
         <v>120.99</v>
       </c>
       <c r="P66" s="70">
-        <f t="shared" ref="P66:P97" si="19">O66/I66</f>
+        <f t="shared" ref="P66:P89" si="19">O66/I66</f>
         <v>16.003968253968253</v>
       </c>
       <c r="Q66" s="75">
@@ -69902,7 +69845,7 @@
         <v>4</v>
       </c>
       <c r="AC66" s="70">
-        <f t="shared" ref="AC66:AC97" si="21">IF(AB66&gt;6.2,1,0)+AB66/5</f>
+        <f t="shared" ref="AC66:AC89" si="21">IF(AB66&gt;6.2,1,0)+AB66/5</f>
         <v>0.8</v>
       </c>
       <c r="AD66" s="71">
@@ -69919,11 +69862,11 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="AH66" s="70">
-        <f t="shared" ref="AH66:AH97" si="23">AG66+IF(X66&lt;1.35,0,1)+IF(Y66&lt;1.35,0,1)+AC66+AA66</f>
+        <f t="shared" ref="AH66:AH89" si="23">AG66+IF(X66&lt;1.35,0,1)+IF(Y66&lt;1.35,0,1)+AC66+AA66</f>
         <v>8.8999999999999986</v>
       </c>
       <c r="AI66" s="70">
-        <f t="shared" ref="AI66:AI97" si="24">AG66+AH66*1.4</f>
+        <f t="shared" ref="AI66:AI89" si="24">AG66+AH66*1.4</f>
         <v>17.559999999999995</v>
       </c>
       <c r="AJ66" s="71" t="str">

--- a/General.xlsx
+++ b/General.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2433D8-CCCC-4524-B945-17184C55D533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4F2470-F81B-459E-9AFF-0341F19AA42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23129,24 +23129,24 @@
         <v>1</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y137">
         <v>1.05</v>
       </c>
       <c r="Z137">
-        <v>0.91</v>
+        <v>3</v>
       </c>
       <c r="AA137" s="2">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="AB137">
-        <v>0.23499999999999999</v>
+        <v>25</v>
       </c>
       <c r="AC137" s="16">
         <f t="shared" si="39"/>
-        <v>1.9583333333333331E-2</v>
+        <v>3.0833333333333335</v>
       </c>
       <c r="AD137">
         <v>5.44</v>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="AH137" s="16">
         <f t="shared" si="34"/>
-        <v>4.7195833333333335</v>
+        <v>8.0833333333333339</v>
       </c>
       <c r="AI137" s="16"/>
       <c r="AJ137" s="16">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="AK137" s="16">
         <f t="shared" si="35"/>
-        <v>10.359583333333333</v>
+        <v>13.723333333333333</v>
       </c>
       <c r="AL137" s="15">
         <f t="shared" si="36"/>

--- a/General.xlsx
+++ b/General.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CapitalFund1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4F2470-F81B-459E-9AFF-0341F19AA42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="IPOSME" sheetId="1" r:id="rId1"/>
     <sheet name="IPOMB" sheetId="2" r:id="rId2"/>
     <sheet name="IPOSME (2)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -133,9 +132,6 @@
   </si>
   <si>
     <t>Company Name 2</t>
-  </si>
-  <si>
-    <t>ClosingDate</t>
   </si>
   <si>
     <t>BOADate</t>
@@ -1121,11 +1117,14 @@
   <si>
     <t>0: NA, 1: RII, 2: NIIA, 3: NIIB</t>
   </si>
+  <si>
+    <t>ClosingDate (40)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -2534,83 +2533,83 @@
     </dxf>
   </dxfs>
   <tableStyles count="19" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="108"/>
       <tableStyleElement type="firstRowStripe" dxfId="107"/>
       <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="SME IPO v1-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="105"/>
       <tableStyleElement type="firstRowStripe" dxfId="104"/>
       <tableStyleElement type="secondRowStripe" dxfId="103"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="102"/>
       <tableStyleElement type="secondRowStripe" dxfId="101"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="100"/>
       <tableStyleElement type="secondRowStripe" dxfId="99"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="98"/>
       <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
+    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="96"/>
       <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
+    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="94"/>
       <tableStyleElement type="secondRowStripe" dxfId="93"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
+    <tableStyle name="SME IPO v2-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="92"/>
       <tableStyleElement type="firstRowStripe" dxfId="91"/>
       <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
+    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="89"/>
       <tableStyleElement type="secondRowStripe" dxfId="88"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
+    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="87"/>
       <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
+    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="85"/>
       <tableStyleElement type="secondRowStripe" dxfId="84"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
+    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="83"/>
       <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
+    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="81"/>
       <tableStyleElement type="secondRowStripe" dxfId="80"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
+    <tableStyle name="SME IPO v3-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="79"/>
       <tableStyleElement type="firstRowStripe" dxfId="78"/>
       <tableStyleElement type="secondRowStripe" dxfId="77"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
+    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="76"/>
       <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
+    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="74"/>
       <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF10000000}">
+    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="72"/>
       <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF11000000}">
+    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="70"/>
       <tableStyleElement type="secondRowStripe" dxfId="69"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF12000000}">
+    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="68"/>
       <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
@@ -2823,52 +2822,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:DF470"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
-    <col min="4" max="4" width="3.88671875" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="6.6640625" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="6.6640625" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" style="108" customWidth="1"/>
-    <col min="20" max="20" width="5.33203125" customWidth="1"/>
-    <col min="21" max="21" width="4.6640625" customWidth="1"/>
-    <col min="22" max="22" width="4.33203125" customWidth="1"/>
-    <col min="23" max="23" width="6.6640625" customWidth="1"/>
-    <col min="24" max="24" width="7.33203125" customWidth="1"/>
-    <col min="25" max="25" width="10.33203125" customWidth="1"/>
-    <col min="26" max="26" width="8.5546875" customWidth="1"/>
-    <col min="27" max="27" width="5.88671875" customWidth="1"/>
-    <col min="28" max="28" width="7.33203125" customWidth="1"/>
-    <col min="29" max="29" width="5.88671875" customWidth="1"/>
-    <col min="30" max="30" width="6.6640625" customWidth="1"/>
-    <col min="31" max="31" width="7.6640625" customWidth="1"/>
-    <col min="32" max="32" width="8.44140625" customWidth="1"/>
-    <col min="33" max="33" width="7.33203125" customWidth="1"/>
-    <col min="34" max="36" width="6.33203125" customWidth="1"/>
-    <col min="37" max="37" width="8.88671875" customWidth="1"/>
-    <col min="38" max="38" width="4.44140625" customWidth="1"/>
-    <col min="39" max="39" width="20.109375" customWidth="1"/>
-    <col min="40" max="40" width="6.5546875" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" style="108" customWidth="1"/>
+    <col min="20" max="20" width="5.28515625" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" customWidth="1"/>
+    <col min="25" max="25" width="10.28515625" customWidth="1"/>
+    <col min="26" max="26" width="8.5703125" customWidth="1"/>
+    <col min="27" max="27" width="5.85546875" customWidth="1"/>
+    <col min="28" max="28" width="7.28515625" customWidth="1"/>
+    <col min="29" max="29" width="5.85546875" customWidth="1"/>
+    <col min="30" max="30" width="6.7109375" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" customWidth="1"/>
+    <col min="32" max="32" width="8.42578125" customWidth="1"/>
+    <col min="33" max="33" width="7.28515625" customWidth="1"/>
+    <col min="34" max="36" width="6.28515625" customWidth="1"/>
+    <col min="37" max="37" width="8.85546875" customWidth="1"/>
+    <col min="38" max="38" width="4.42578125" customWidth="1"/>
+    <col min="39" max="39" width="20.140625" customWidth="1"/>
+    <col min="40" max="40" width="6.5703125" customWidth="1"/>
     <col min="42" max="48" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" ht="92.4" customHeight="1">
+    <row r="1" spans="1:59" ht="92.45" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2983,73 +2982,73 @@
         <v>36</v>
       </c>
       <c r="AN1" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="AO1" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="AO1" s="39" t="s">
+      <c r="AP1" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="AP1" s="39" t="s">
+      <c r="AQ1" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="AQ1" s="39" t="s">
+      <c r="AR1" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="AR1" s="39" t="s">
+      <c r="AS1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="AS1" s="12" t="s">
+      <c r="AT1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AT1" s="12" t="s">
+      <c r="AU1" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="AU1" s="12" t="s">
-        <v>44</v>
       </c>
       <c r="AV1" s="12"/>
       <c r="AW1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AX1" s="12" t="s">
+      <c r="AY1" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="AY1" s="12" t="s">
+      <c r="AZ1" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="AZ1" s="39" t="s">
+      <c r="BA1" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="BA1" s="39" t="s">
+      <c r="BB1" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="BB1" s="39" t="s">
+      <c r="BC1" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="BC1" s="39" t="s">
+      <c r="BD1" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="BD1" s="72" t="s">
+      <c r="BE1" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="BE1" s="39" t="s">
+      <c r="BF1" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="BF1" s="39" t="s">
+      <c r="BG1" s="39" t="s">
         <v>54</v>
-      </c>
-      <c r="BG1" s="39" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:59">
       <c r="B2" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="15">
         <v>2025</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" s="16">
         <v>31.7</v>
@@ -3217,13 +3216,13 @@
     </row>
     <row r="3" spans="1:59">
       <c r="B3" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" s="15">
         <v>2025</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" s="16">
         <v>0</v>
@@ -3375,13 +3374,13 @@
     </row>
     <row r="4" spans="1:59">
       <c r="B4" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="15">
         <v>2025</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="16">
         <v>30.68</v>
@@ -3533,13 +3532,13 @@
     </row>
     <row r="5" spans="1:59">
       <c r="B5" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="15">
         <v>2025</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="16">
         <v>17.36</v>
@@ -3691,13 +3690,13 @@
     </row>
     <row r="6" spans="1:59">
       <c r="B6" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="15">
         <v>2025</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" s="16">
         <v>0.23</v>
@@ -3857,13 +3856,13 @@
     </row>
     <row r="7" spans="1:59">
       <c r="B7" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="15">
         <v>2025</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="16">
         <v>0.05</v>
@@ -4015,13 +4014,13 @@
     </row>
     <row r="8" spans="1:59">
       <c r="B8" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="15">
         <v>2025</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" s="16">
         <v>50.23</v>
@@ -4181,13 +4180,13 @@
     </row>
     <row r="9" spans="1:59">
       <c r="B9" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="15">
         <v>2025</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="16">
         <v>10.71</v>
@@ -4339,13 +4338,13 @@
     </row>
     <row r="10" spans="1:59">
       <c r="B10" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="15">
         <v>2025</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="16">
         <v>0.22</v>
@@ -4497,13 +4496,13 @@
     </row>
     <row r="11" spans="1:59">
       <c r="B11" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="15">
         <v>2024</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="16">
         <v>0.19</v>
@@ -4655,13 +4654,13 @@
     </row>
     <row r="12" spans="1:59">
       <c r="B12" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" s="15">
         <v>2024</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="16">
         <v>6.43</v>
@@ -4813,13 +4812,13 @@
     </row>
     <row r="13" spans="1:59">
       <c r="B13" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="15">
         <v>2024</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="16">
         <v>1.05</v>
@@ -4981,13 +4980,13 @@
     </row>
     <row r="14" spans="1:59">
       <c r="B14" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" s="15">
         <v>2024</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="16">
         <v>7.08</v>
@@ -5139,13 +5138,13 @@
     </row>
     <row r="15" spans="1:59">
       <c r="B15" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="15">
         <v>2024</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="16">
         <v>25.62</v>
@@ -5307,13 +5306,13 @@
     </row>
     <row r="16" spans="1:59">
       <c r="B16" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" s="15">
         <v>2024</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="16">
         <v>0</v>
@@ -5465,13 +5464,13 @@
     </row>
     <row r="17" spans="2:109">
       <c r="B17" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" s="15">
         <v>2024</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" s="16">
         <v>0.42</v>
@@ -5623,13 +5622,13 @@
     </row>
     <row r="18" spans="2:109">
       <c r="B18" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="15">
         <v>2024</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" s="16">
         <v>29</v>
@@ -5789,13 +5788,13 @@
     </row>
     <row r="19" spans="2:109">
       <c r="B19" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19" s="15">
         <v>2024</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" s="16">
         <v>6.89</v>
@@ -5947,13 +5946,13 @@
     </row>
     <row r="20" spans="2:109">
       <c r="B20" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="15">
         <v>2023</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" s="15">
         <v>22.99</v>
@@ -6089,13 +6088,13 @@
     </row>
     <row r="21" spans="2:109">
       <c r="B21" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21" s="15">
         <v>2023</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="15">
         <v>41.78</v>
@@ -6119,7 +6118,7 @@
       </c>
       <c r="L21" s="15"/>
       <c r="M21" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N21" s="15"/>
       <c r="O21" s="15">
@@ -6229,13 +6228,13 @@
     </row>
     <row r="22" spans="2:109">
       <c r="B22" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" s="15">
         <v>2023</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" s="15">
         <v>40.83</v>
@@ -6373,13 +6372,13 @@
     </row>
     <row r="23" spans="2:109">
       <c r="B23" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C23" s="15">
         <v>2025</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="16">
         <v>12.99</v>
@@ -6531,13 +6530,13 @@
     </row>
     <row r="24" spans="2:109">
       <c r="B24" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="15">
         <v>2025</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" s="16">
         <v>20.22</v>
@@ -6689,13 +6688,13 @@
     </row>
     <row r="25" spans="2:109">
       <c r="B25" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C25" s="15">
         <v>2025</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="16">
         <v>3.34</v>
@@ -6847,13 +6846,13 @@
     </row>
     <row r="26" spans="2:109">
       <c r="B26" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C26" s="15">
         <v>2025</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="16">
         <v>49.21</v>
@@ -7013,13 +7012,13 @@
     </row>
     <row r="27" spans="2:109">
       <c r="B27" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C27" s="15">
         <v>2025</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" s="16">
         <v>3.67</v>
@@ -7171,13 +7170,13 @@
     </row>
     <row r="28" spans="2:109">
       <c r="B28" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="15">
         <v>2025</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" s="16">
         <v>67.11</v>
@@ -7329,13 +7328,13 @@
     </row>
     <row r="29" spans="2:109">
       <c r="B29" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C29" s="15">
         <v>2025</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" s="16">
         <v>8.3699999999999992</v>
@@ -7485,18 +7484,18 @@
         <v>-10.3448275862069</v>
       </c>
       <c r="DE29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="2:109">
       <c r="B30" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" s="15">
         <v>2025</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" s="16">
         <v>1.07</v>
@@ -7648,13 +7647,13 @@
     </row>
     <row r="31" spans="2:109">
       <c r="B31" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" s="15">
         <v>2025</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" s="16">
         <v>12.21</v>
@@ -7804,13 +7803,13 @@
     </row>
     <row r="32" spans="2:109">
       <c r="B32" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C32" s="15">
         <v>2024</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32" s="16">
         <v>17.25</v>
@@ -7962,13 +7961,13 @@
     </row>
     <row r="33" spans="2:110">
       <c r="B33" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C33" s="15">
         <v>2024</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E33" s="16">
         <v>14.19</v>
@@ -8118,18 +8117,18 @@
         <v>-64.444444444444443</v>
       </c>
       <c r="DF33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="2:110">
       <c r="B34" s="22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C34" s="15">
         <v>2024</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" s="16">
         <v>4.6100000000000003</v>
@@ -8153,7 +8152,7 @@
       </c>
       <c r="L34" s="16"/>
       <c r="M34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N34" s="16"/>
       <c r="O34" s="16">
@@ -8205,7 +8204,7 @@
         <v>-11</v>
       </c>
       <c r="AF34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG34" s="118">
         <f t="shared" si="3"/>
@@ -8281,13 +8280,13 @@
     </row>
     <row r="35" spans="2:110">
       <c r="B35" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" s="15">
         <v>2024</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E35" s="16">
         <v>0</v>
@@ -8363,7 +8362,7 @@
         <v>-6</v>
       </c>
       <c r="AF35" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG35" s="118">
         <f t="shared" si="3"/>
@@ -8439,13 +8438,13 @@
     </row>
     <row r="36" spans="2:110">
       <c r="B36" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" s="15">
         <v>2024</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" s="16">
         <v>91.56</v>
@@ -8495,7 +8494,7 @@
       </c>
       <c r="W36" s="16"/>
       <c r="X36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y36" s="16">
         <v>3.9</v>
@@ -8521,7 +8520,7 @@
         <v>-29</v>
       </c>
       <c r="AF36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG36" s="118">
         <f t="shared" si="3"/>
@@ -8597,13 +8596,13 @@
     </row>
     <row r="37" spans="2:110">
       <c r="B37" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C37" s="15">
         <v>2024</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E37" s="16">
         <v>2.5299999999999998</v>
@@ -8763,13 +8762,13 @@
     </row>
     <row r="38" spans="2:110">
       <c r="B38" s="22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C38" s="15">
         <v>2024</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" s="16">
         <v>20.57</v>
@@ -8921,13 +8920,13 @@
     </row>
     <row r="39" spans="2:110">
       <c r="B39" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" s="15">
         <v>2024</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="16">
         <v>10.29</v>
@@ -9079,13 +9078,13 @@
     </row>
     <row r="40" spans="2:110">
       <c r="B40" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C40" s="15">
         <v>2024</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E40" s="16">
         <v>7.7</v>
@@ -9237,13 +9236,13 @@
     </row>
     <row r="41" spans="2:110">
       <c r="B41" s="22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" s="15">
         <v>2023</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="15">
         <v>8.94</v>
@@ -9381,13 +9380,13 @@
     </row>
     <row r="42" spans="2:110">
       <c r="B42" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C42" s="15">
         <v>2023</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E42" s="15">
         <v>3.98</v>
@@ -9525,13 +9524,13 @@
     </row>
     <row r="43" spans="2:110">
       <c r="B43" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C43" s="15">
         <v>2023</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E43" s="15">
         <v>1.96</v>
@@ -9669,13 +9668,13 @@
     </row>
     <row r="44" spans="2:110">
       <c r="B44" s="101" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C44" s="15">
         <v>2025</v>
       </c>
       <c r="D44" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="16">
         <v>9.74</v>
@@ -9833,13 +9832,13 @@
     </row>
     <row r="45" spans="2:110">
       <c r="B45" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C45" s="15">
         <v>2025</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E45" s="16">
         <v>27.99</v>
@@ -9983,13 +9982,13 @@
     </row>
     <row r="46" spans="2:110">
       <c r="B46" s="101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C46" s="15">
         <v>2025</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E46" s="16">
         <v>20.55</v>
@@ -10133,13 +10132,13 @@
     </row>
     <row r="47" spans="2:110">
       <c r="B47" s="101" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C47" s="15">
         <v>2025</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E47" s="16">
         <v>30.45</v>
@@ -10283,13 +10282,13 @@
     </row>
     <row r="48" spans="2:110">
       <c r="B48" s="101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C48" s="101">
         <v>2025</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E48" s="101">
         <v>27.92</v>
@@ -10433,13 +10432,13 @@
     </row>
     <row r="49" spans="2:59">
       <c r="B49" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C49" s="101">
         <v>2025</v>
       </c>
       <c r="D49" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E49" s="101">
         <v>18.5</v>
@@ -10597,13 +10596,13 @@
     </row>
     <row r="50" spans="2:59">
       <c r="B50" s="101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C50" s="101">
         <v>2025</v>
       </c>
       <c r="D50" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E50" s="101">
         <v>15.6</v>
@@ -10747,13 +10746,13 @@
     </row>
     <row r="51" spans="2:59">
       <c r="B51" s="101" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C51" s="101">
         <v>2025</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E51" s="101">
         <v>8.18</v>
@@ -10897,13 +10896,13 @@
     </row>
     <row r="52" spans="2:59">
       <c r="B52" s="101" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C52" s="101">
         <v>2025</v>
       </c>
       <c r="D52" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E52" s="101">
         <v>58.11</v>
@@ -11049,13 +11048,13 @@
     </row>
     <row r="53" spans="2:59">
       <c r="B53" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C53" s="101">
         <v>2025</v>
       </c>
       <c r="D53" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E53" s="101">
         <v>0</v>
@@ -11068,7 +11067,7 @@
         <v>100</v>
       </c>
       <c r="H53" s="101" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I53" s="101">
         <v>13.93</v>
@@ -11079,7 +11078,7 @@
       </c>
       <c r="L53" s="101"/>
       <c r="M53" s="101" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N53" s="101"/>
       <c r="O53" s="101">
@@ -11199,13 +11198,13 @@
     </row>
     <row r="54" spans="2:59">
       <c r="B54" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C54" s="15">
         <v>2025</v>
       </c>
       <c r="D54" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E54" s="15">
         <v>20.38</v>
@@ -11351,13 +11350,13 @@
     </row>
     <row r="55" spans="2:59">
       <c r="B55" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C55" s="15">
         <v>2025</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E55" s="15">
         <v>6.07</v>
@@ -11491,13 +11490,13 @@
     </row>
     <row r="56" spans="2:59">
       <c r="B56" s="101" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C56" s="101">
         <v>2025</v>
       </c>
       <c r="D56" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E56" s="101">
         <v>59.61</v>
@@ -11631,13 +11630,13 @@
     </row>
     <row r="57" spans="2:59">
       <c r="B57" s="101" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C57" s="101">
         <v>2025</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E57" s="101">
         <v>59.31</v>
@@ -11771,13 +11770,13 @@
     </row>
     <row r="58" spans="2:59">
       <c r="B58" s="101" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C58" s="101">
         <v>2025</v>
       </c>
       <c r="D58" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E58" s="101">
         <v>14.66</v>
@@ -11911,13 +11910,13 @@
     </row>
     <row r="59" spans="2:59">
       <c r="B59" s="101" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C59" s="101">
         <v>2025</v>
       </c>
       <c r="D59" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E59" s="101">
         <v>31.63</v>
@@ -11937,7 +11936,7 @@
       </c>
       <c r="J59" s="101"/>
       <c r="K59" s="101" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L59" s="101"/>
       <c r="M59" s="101">
@@ -12051,13 +12050,13 @@
     </row>
     <row r="60" spans="2:59">
       <c r="B60" s="101" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C60" s="101">
         <v>2025</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E60" s="101">
         <v>0.02</v>
@@ -12191,13 +12190,13 @@
     </row>
     <row r="61" spans="2:59">
       <c r="B61" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C61" s="15">
         <v>2025</v>
       </c>
       <c r="D61" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E61" s="15">
         <v>0</v>
@@ -12333,13 +12332,13 @@
     </row>
     <row r="62" spans="2:59">
       <c r="B62" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C62" s="15">
         <v>2025</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E62" s="15">
         <v>85.59</v>
@@ -12374,7 +12373,7 @@
         <v>24.011925042589436</v>
       </c>
       <c r="Q62" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R62" s="16">
         <v>10.75</v>
@@ -12475,13 +12474,13 @@
     </row>
     <row r="63" spans="2:59">
       <c r="B63" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C63" s="15">
         <v>2025</v>
       </c>
       <c r="D63" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E63" s="101">
         <v>3.54</v>
@@ -12629,13 +12628,13 @@
     </row>
     <row r="64" spans="2:59">
       <c r="B64" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C64" s="101">
         <v>2025</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E64" s="101">
         <v>6.75</v>
@@ -12771,13 +12770,13 @@
     </row>
     <row r="65" spans="2:59">
       <c r="B65" s="101" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C65" s="101">
         <v>2025</v>
       </c>
       <c r="D65" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E65" s="101">
         <v>0</v>
@@ -12927,13 +12926,13 @@
     </row>
     <row r="66" spans="2:59">
       <c r="B66" s="101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C66" s="101">
         <v>2025</v>
       </c>
       <c r="D66" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E66" s="101">
         <v>35.619999999999997</v>
@@ -13083,13 +13082,13 @@
     </row>
     <row r="67" spans="2:59">
       <c r="B67" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C67" s="101">
         <v>2025</v>
       </c>
       <c r="D67" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E67" s="15">
         <v>0.04</v>
@@ -13225,13 +13224,13 @@
     </row>
     <row r="68" spans="2:59">
       <c r="B68" s="101" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C68" s="101">
         <v>2025</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E68" s="101">
         <v>50.98</v>
@@ -13367,13 +13366,13 @@
     </row>
     <row r="69" spans="2:59">
       <c r="B69" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C69" s="101">
         <v>2025</v>
       </c>
       <c r="D69" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E69" s="101">
         <v>1.49</v>
@@ -13509,13 +13508,13 @@
     </row>
     <row r="70" spans="2:59">
       <c r="B70" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C70" s="101">
         <v>2025</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E70" s="15">
         <v>4.09</v>
@@ -13651,13 +13650,13 @@
     </row>
     <row r="71" spans="2:59">
       <c r="B71" s="101" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C71" s="101">
         <v>2025</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E71" s="101">
         <v>32.159999999999997</v>
@@ -13805,13 +13804,13 @@
     </row>
     <row r="72" spans="2:59">
       <c r="B72" s="101" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C72" s="101">
         <v>2025</v>
       </c>
       <c r="D72" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E72" s="101">
         <v>0</v>
@@ -13947,13 +13946,13 @@
     </row>
     <row r="73" spans="2:59">
       <c r="B73" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C73" s="101">
         <v>2025</v>
       </c>
       <c r="D73" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E73" s="101">
         <v>18.09</v>
@@ -14103,13 +14102,13 @@
     </row>
     <row r="74" spans="2:59">
       <c r="B74" s="101" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C74" s="101">
         <v>2025</v>
       </c>
       <c r="D74" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E74" s="26">
         <v>44.03</v>
@@ -14245,13 +14244,13 @@
     </row>
     <row r="75" spans="2:59">
       <c r="B75" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C75" s="101">
         <v>2025</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" s="15">
         <v>10.79</v>
@@ -14387,13 +14386,13 @@
     </row>
     <row r="76" spans="2:59">
       <c r="B76" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C76" s="101">
         <v>2025</v>
       </c>
       <c r="D76" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E76">
         <v>7.99</v>
@@ -14540,13 +14539,13 @@
     </row>
     <row r="77" spans="2:59">
       <c r="B77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C77" s="101">
         <v>2025</v>
       </c>
       <c r="D77" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E77">
         <v>11.9</v>
@@ -14559,13 +14558,13 @@
         <v>-23.958333333333339</v>
       </c>
       <c r="H77" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I77">
         <v>4.2699999999999996</v>
       </c>
       <c r="K77" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M77">
         <v>7.1</v>
@@ -14679,13 +14678,13 @@
     </row>
     <row r="78" spans="2:59">
       <c r="B78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C78" s="101">
         <v>2025</v>
       </c>
       <c r="D78" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G78" s="16" t="e">
         <f t="shared" si="16"/>
@@ -14797,13 +14796,13 @@
     </row>
     <row r="79" spans="2:59">
       <c r="B79" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C79" s="101">
         <v>2025</v>
       </c>
       <c r="D79" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E79">
         <v>38.659999999999997</v>
@@ -14841,7 +14840,7 @@
         <v>26.07</v>
       </c>
       <c r="R79" s="110" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S79" s="118">
         <v>0</v>
@@ -14955,13 +14954,13 @@
     </row>
     <row r="80" spans="2:59">
       <c r="B80" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C80" s="101">
         <v>2025</v>
       </c>
       <c r="D80" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E80">
         <v>14.57</v>
@@ -15111,13 +15110,13 @@
     </row>
     <row r="81" spans="2:59">
       <c r="B81" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C81" s="101">
         <v>2025</v>
       </c>
       <c r="D81" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E81">
         <v>62.57</v>
@@ -15250,13 +15249,13 @@
     </row>
     <row r="82" spans="2:59">
       <c r="B82" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C82" s="101">
         <v>2025</v>
       </c>
       <c r="D82" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E82">
         <v>2.75</v>
@@ -15403,13 +15402,13 @@
     </row>
     <row r="83" spans="2:59">
       <c r="B83" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C83" s="101">
         <v>2025</v>
       </c>
       <c r="D83" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E83">
         <v>0.09</v>
@@ -15542,13 +15541,13 @@
     </row>
     <row r="84" spans="2:59">
       <c r="B84" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C84" s="101">
         <v>2025</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E84">
         <v>57.99</v>
@@ -15681,13 +15680,13 @@
     </row>
     <row r="85" spans="2:59">
       <c r="B85" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C85" s="101">
         <v>2025</v>
       </c>
       <c r="D85" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E85">
         <v>1.1499999999999999</v>
@@ -15820,13 +15819,13 @@
     </row>
     <row r="86" spans="2:59">
       <c r="B86" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C86" s="101">
         <v>2025</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E86">
         <v>0.94</v>
@@ -15973,13 +15972,13 @@
     </row>
     <row r="87" spans="2:59">
       <c r="B87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C87" s="101">
         <v>2025</v>
       </c>
       <c r="D87" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E87">
         <v>18.690000000000001</v>
@@ -16093,7 +16092,7 @@
       </c>
       <c r="AR87" s="16"/>
       <c r="AS87" s="27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AT87" s="27"/>
       <c r="AU87" s="28"/>
@@ -16112,13 +16111,13 @@
     </row>
     <row r="88" spans="2:59">
       <c r="B88" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C88" s="101">
         <v>2025</v>
       </c>
       <c r="D88" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E88" s="7">
         <v>47.24</v>
@@ -16254,13 +16253,13 @@
     </row>
     <row r="89" spans="2:59">
       <c r="B89" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C89" s="101">
         <v>2025</v>
       </c>
       <c r="D89" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E89" s="26">
         <v>44.11</v>
@@ -16396,13 +16395,13 @@
     </row>
     <row r="90" spans="2:59">
       <c r="B90" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C90" s="101">
         <v>2025</v>
       </c>
       <c r="D90" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E90">
         <v>12.25</v>
@@ -16538,13 +16537,13 @@
     </row>
     <row r="91" spans="2:59">
       <c r="B91" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C91" s="101">
         <v>2025</v>
       </c>
       <c r="D91" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E91" s="1">
         <v>17.38</v>
@@ -16680,13 +16679,13 @@
     </row>
     <row r="92" spans="2:59">
       <c r="B92" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C92" s="101">
         <v>2025</v>
       </c>
       <c r="D92" s="101" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E92" s="6">
         <v>10.66</v>
@@ -16838,13 +16837,13 @@
     </row>
     <row r="93" spans="2:59">
       <c r="B93" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C93" s="101">
         <v>2025</v>
       </c>
       <c r="D93" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E93" s="6">
         <v>0.5</v>
@@ -16996,13 +16995,13 @@
     </row>
     <row r="94" spans="2:59">
       <c r="B94" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C94" s="101">
         <v>2025</v>
       </c>
       <c r="D94" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E94" s="37">
         <v>31.75</v>
@@ -17140,13 +17139,13 @@
     </row>
     <row r="95" spans="2:59">
       <c r="B95" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C95" s="101">
         <v>2025</v>
       </c>
       <c r="D95" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E95" s="9">
         <v>109</v>
@@ -17281,13 +17280,13 @@
     </row>
     <row r="96" spans="2:59">
       <c r="B96" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C96" s="101">
         <v>2025</v>
       </c>
       <c r="D96" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E96" s="37">
         <v>21.29</v>
@@ -17425,13 +17424,13 @@
     </row>
     <row r="97" spans="1:59">
       <c r="B97" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C97" s="101">
         <v>2025</v>
       </c>
       <c r="D97" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E97" s="6">
         <v>66.180000000000007</v>
@@ -17583,13 +17582,13 @@
     </row>
     <row r="98" spans="1:59">
       <c r="B98" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C98" s="101">
         <v>2025</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E98" s="37">
         <v>22.09</v>
@@ -17721,16 +17720,16 @@
     </row>
     <row r="99" spans="1:59">
       <c r="A99" t="s">
+        <v>159</v>
+      </c>
+      <c r="B99" t="s">
         <v>160</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>161</v>
       </c>
-      <c r="C99" t="s">
-        <v>162</v>
-      </c>
       <c r="D99" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E99">
         <v>46.71</v>
@@ -17863,16 +17862,16 @@
     </row>
     <row r="100" spans="1:59">
       <c r="A100" t="s">
+        <v>162</v>
+      </c>
+      <c r="B100" t="s">
         <v>163</v>
       </c>
-      <c r="B100" t="s">
-        <v>164</v>
-      </c>
       <c r="C100" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D100" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E100">
         <v>9.2899999999999991</v>
@@ -18005,16 +18004,16 @@
     </row>
     <row r="101" spans="1:59">
       <c r="A101" t="s">
+        <v>164</v>
+      </c>
+      <c r="B101" t="s">
         <v>165</v>
       </c>
-      <c r="B101" t="s">
-        <v>166</v>
-      </c>
       <c r="C101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D101" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E101">
         <v>66.180000000000007</v>
@@ -18147,16 +18146,16 @@
     </row>
     <row r="102" spans="1:59">
       <c r="A102" t="s">
+        <v>166</v>
+      </c>
+      <c r="B102" t="s">
         <v>167</v>
-      </c>
-      <c r="B102" t="s">
-        <v>168</v>
       </c>
       <c r="C102">
         <v>2026</v>
       </c>
       <c r="D102" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E102">
         <v>11.56</v>
@@ -18289,16 +18288,16 @@
     </row>
     <row r="103" spans="1:59">
       <c r="A103" t="s">
+        <v>168</v>
+      </c>
+      <c r="B103" t="s">
         <v>169</v>
       </c>
-      <c r="B103" t="s">
-        <v>170</v>
-      </c>
       <c r="C103" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D103" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E103">
         <v>5.69</v>
@@ -18431,16 +18430,16 @@
     </row>
     <row r="104" spans="1:59">
       <c r="A104" t="s">
+        <v>170</v>
+      </c>
+      <c r="B104" t="s">
         <v>171</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
+        <v>161</v>
+      </c>
+      <c r="D104" s="101" t="s">
         <v>172</v>
-      </c>
-      <c r="C104" t="s">
-        <v>162</v>
-      </c>
-      <c r="D104" s="101" t="s">
-        <v>173</v>
       </c>
       <c r="E104">
         <v>24.73</v>
@@ -18573,16 +18572,16 @@
     </row>
     <row r="105" spans="1:59">
       <c r="A105" t="s">
+        <v>173</v>
+      </c>
+      <c r="B105" t="s">
         <v>174</v>
       </c>
-      <c r="B105" t="s">
-        <v>175</v>
-      </c>
       <c r="C105" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D105" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E105">
         <v>35.76</v>
@@ -18736,16 +18735,16 @@
     </row>
     <row r="106" spans="1:59">
       <c r="A106" t="s">
+        <v>175</v>
+      </c>
+      <c r="B106" t="s">
         <v>176</v>
       </c>
-      <c r="B106" t="s">
-        <v>177</v>
-      </c>
       <c r="C106" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D106" s="101" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E106">
         <v>1.59</v>
@@ -18881,16 +18880,16 @@
     </row>
     <row r="107" spans="1:59">
       <c r="A107" t="s">
+        <v>177</v>
+      </c>
+      <c r="B107" t="s">
         <v>178</v>
       </c>
-      <c r="B107" t="s">
-        <v>179</v>
-      </c>
       <c r="C107" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D107" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E107">
         <v>4.6900000000000004</v>
@@ -19023,16 +19022,16 @@
     </row>
     <row r="108" spans="1:59">
       <c r="A108" t="s">
+        <v>179</v>
+      </c>
+      <c r="B108" t="s">
         <v>180</v>
       </c>
-      <c r="B108" t="s">
-        <v>181</v>
-      </c>
       <c r="C108" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D108" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E108">
         <v>36.82</v>
@@ -19165,16 +19164,16 @@
     </row>
     <row r="109" spans="1:59">
       <c r="A109" t="s">
+        <v>181</v>
+      </c>
+      <c r="B109" t="s">
         <v>182</v>
       </c>
-      <c r="B109" t="s">
-        <v>183</v>
-      </c>
       <c r="C109" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D109" s="101" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E109">
         <v>13.34</v>
@@ -19307,16 +19306,16 @@
     </row>
     <row r="110" spans="1:59">
       <c r="A110" t="s">
+        <v>183</v>
+      </c>
+      <c r="B110" t="s">
         <v>184</v>
       </c>
-      <c r="B110" t="s">
-        <v>185</v>
-      </c>
       <c r="C110" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D110" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E110">
         <v>31.2</v>
@@ -19449,16 +19448,16 @@
     </row>
     <row r="111" spans="1:59">
       <c r="A111" t="s">
+        <v>185</v>
+      </c>
+      <c r="B111" t="s">
         <v>186</v>
       </c>
-      <c r="B111" t="s">
-        <v>187</v>
-      </c>
       <c r="C111" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D111" s="101" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E111">
         <v>33.58</v>
@@ -19591,16 +19590,16 @@
     </row>
     <row r="112" spans="1:59">
       <c r="A112" t="s">
+        <v>187</v>
+      </c>
+      <c r="B112" t="s">
         <v>188</v>
       </c>
-      <c r="B112" t="s">
-        <v>189</v>
-      </c>
       <c r="C112" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D112" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E112">
         <v>13.92</v>
@@ -19733,16 +19732,16 @@
     </row>
     <row r="113" spans="1:46">
       <c r="A113" t="s">
+        <v>189</v>
+      </c>
+      <c r="B113" t="s">
         <v>190</v>
       </c>
-      <c r="B113" t="s">
-        <v>191</v>
-      </c>
       <c r="C113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D113" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E113">
         <v>13.15</v>
@@ -19875,16 +19874,16 @@
     </row>
     <row r="114" spans="1:46">
       <c r="A114" t="s">
+        <v>191</v>
+      </c>
+      <c r="B114" t="s">
         <v>192</v>
       </c>
-      <c r="B114" t="s">
-        <v>193</v>
-      </c>
       <c r="C114" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D114" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E114">
         <v>22.74</v>
@@ -20017,16 +20016,16 @@
     </row>
     <row r="115" spans="1:46">
       <c r="A115" t="s">
+        <v>193</v>
+      </c>
+      <c r="B115" t="s">
         <v>194</v>
       </c>
-      <c r="B115" t="s">
-        <v>195</v>
-      </c>
       <c r="C115" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D115" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E115">
         <v>32.56</v>
@@ -20159,16 +20158,16 @@
     </row>
     <row r="116" spans="1:46">
       <c r="A116" t="s">
+        <v>195</v>
+      </c>
+      <c r="B116" t="s">
         <v>196</v>
       </c>
-      <c r="B116" t="s">
-        <v>197</v>
-      </c>
       <c r="C116" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D116" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E116">
         <v>3.86</v>
@@ -20301,16 +20300,16 @@
     </row>
     <row r="117" spans="1:46">
       <c r="A117" t="s">
+        <v>197</v>
+      </c>
+      <c r="B117" t="s">
         <v>198</v>
       </c>
-      <c r="B117" t="s">
-        <v>199</v>
-      </c>
       <c r="C117" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D117" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -20443,16 +20442,16 @@
     </row>
     <row r="118" spans="1:46">
       <c r="A118" t="s">
+        <v>199</v>
+      </c>
+      <c r="B118" t="s">
         <v>200</v>
       </c>
-      <c r="B118" t="s">
-        <v>201</v>
-      </c>
       <c r="C118" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D118" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E118">
         <v>11.87</v>
@@ -20561,7 +20560,7 @@
         <v>Pos</v>
       </c>
       <c r="AM118" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AN118">
         <v>6</v>
@@ -20582,16 +20581,16 @@
     </row>
     <row r="119" spans="1:46">
       <c r="A119" t="s">
+        <v>201</v>
+      </c>
+      <c r="B119" t="s">
         <v>202</v>
       </c>
-      <c r="B119" t="s">
-        <v>203</v>
-      </c>
       <c r="C119" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D119" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E119">
         <v>9.34</v>
@@ -20700,7 +20699,7 @@
         <v>Pos</v>
       </c>
       <c r="AM119" s="100" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AN119">
         <v>6</v>
@@ -20721,16 +20720,16 @@
     </row>
     <row r="120" spans="1:46">
       <c r="A120" t="s">
+        <v>203</v>
+      </c>
+      <c r="B120" t="s">
         <v>204</v>
       </c>
-      <c r="B120" t="s">
-        <v>205</v>
-      </c>
       <c r="C120" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D120" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -20839,7 +20838,7 @@
         <v>Neg</v>
       </c>
       <c r="AM120" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AN120">
         <v>10</v>
@@ -20860,16 +20859,16 @@
     </row>
     <row r="121" spans="1:46">
       <c r="A121" t="s">
+        <v>205</v>
+      </c>
+      <c r="B121" t="s">
         <v>206</v>
       </c>
-      <c r="B121" t="s">
-        <v>207</v>
-      </c>
       <c r="C121" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D121" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E121">
         <v>7.69</v>
@@ -20978,7 +20977,7 @@
         <v>Neg</v>
       </c>
       <c r="AM121" s="100" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN121">
         <v>10</v>
@@ -20999,16 +20998,16 @@
     </row>
     <row r="122" spans="1:46">
       <c r="A122" t="s">
+        <v>207</v>
+      </c>
+      <c r="B122" t="s">
         <v>208</v>
       </c>
-      <c r="B122" t="s">
-        <v>209</v>
-      </c>
       <c r="C122" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D122" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E122">
         <v>21.37</v>
@@ -21117,7 +21116,7 @@
         <v>Pos</v>
       </c>
       <c r="AM122" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AN122">
         <v>16</v>
@@ -21138,16 +21137,16 @@
     </row>
     <row r="123" spans="1:46">
       <c r="A123" t="s">
+        <v>209</v>
+      </c>
+      <c r="B123" t="s">
         <v>210</v>
       </c>
-      <c r="B123" t="s">
-        <v>211</v>
-      </c>
       <c r="C123" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D123" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E123">
         <v>27.61</v>
@@ -21256,7 +21255,7 @@
         <v>Pos</v>
       </c>
       <c r="AM123" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AN123">
         <v>18</v>
@@ -21277,16 +21276,16 @@
     </row>
     <row r="124" spans="1:46">
       <c r="A124" t="s">
+        <v>211</v>
+      </c>
+      <c r="B124" t="s">
         <v>212</v>
       </c>
-      <c r="B124" t="s">
-        <v>213</v>
-      </c>
       <c r="C124" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D124" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E124">
         <v>43.85</v>
@@ -21395,7 +21394,7 @@
         <v>Neg</v>
       </c>
       <c r="AM124" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AN124">
         <v>20</v>
@@ -21415,16 +21414,16 @@
     </row>
     <row r="125" spans="1:46">
       <c r="A125" t="s">
+        <v>213</v>
+      </c>
+      <c r="B125" t="s">
         <v>214</v>
       </c>
-      <c r="B125" t="s">
-        <v>215</v>
-      </c>
       <c r="C125" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D125" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E125">
         <v>62.44</v>
@@ -21533,7 +21532,7 @@
         <v>Neg</v>
       </c>
       <c r="AM125" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN125">
         <v>24</v>
@@ -21553,16 +21552,16 @@
     </row>
     <row r="126" spans="1:46">
       <c r="A126" t="s">
+        <v>215</v>
+      </c>
+      <c r="B126" t="s">
         <v>216</v>
       </c>
-      <c r="B126" t="s">
-        <v>217</v>
-      </c>
       <c r="C126" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D126" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E126">
         <v>28.67</v>
@@ -21671,7 +21670,7 @@
         <v>Neg</v>
       </c>
       <c r="AM126" s="100" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AN126">
         <v>3</v>
@@ -21691,16 +21690,16 @@
     </row>
     <row r="127" spans="1:46">
       <c r="A127" t="s">
+        <v>217</v>
+      </c>
+      <c r="B127" t="s">
         <v>218</v>
       </c>
-      <c r="B127" t="s">
-        <v>219</v>
-      </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D127" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E127">
         <v>0.11</v>
@@ -21809,7 +21808,7 @@
         <v>Neg</v>
       </c>
       <c r="AM127" s="100" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AN127">
         <v>25</v>
@@ -21829,16 +21828,16 @@
     </row>
     <row r="128" spans="1:46">
       <c r="A128" t="s">
+        <v>219</v>
+      </c>
+      <c r="B128" t="s">
         <v>220</v>
       </c>
-      <c r="B128" t="s">
-        <v>221</v>
-      </c>
       <c r="C128" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D128" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E128">
         <v>11.81</v>
@@ -21947,7 +21946,7 @@
         <v>Pos</v>
       </c>
       <c r="AM128" s="100" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AN128">
         <v>3</v>
@@ -21968,16 +21967,16 @@
     </row>
     <row r="129" spans="1:44">
       <c r="A129" t="s">
+        <v>221</v>
+      </c>
+      <c r="B129" t="s">
         <v>222</v>
       </c>
-      <c r="B129" t="s">
-        <v>223</v>
-      </c>
       <c r="C129" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D129" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E129">
         <v>22.8</v>
@@ -22086,7 +22085,7 @@
         <v>Neg</v>
       </c>
       <c r="AM129" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AN129">
         <v>27</v>
@@ -22106,16 +22105,16 @@
     </row>
     <row r="130" spans="1:44">
       <c r="A130" t="s">
+        <v>223</v>
+      </c>
+      <c r="B130" t="s">
         <v>224</v>
       </c>
-      <c r="B130" t="s">
-        <v>225</v>
-      </c>
       <c r="C130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D130" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E130">
         <v>20.55</v>
@@ -22224,7 +22223,7 @@
         <v>Neg</v>
       </c>
       <c r="AM130" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AN130">
         <v>2</v>
@@ -22244,16 +22243,16 @@
     </row>
     <row r="131" spans="1:44">
       <c r="A131" t="s">
+        <v>225</v>
+      </c>
+      <c r="B131" t="s">
         <v>226</v>
       </c>
-      <c r="B131" t="s">
-        <v>227</v>
-      </c>
       <c r="C131" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D131" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E131">
         <v>0.49</v>
@@ -22362,7 +22361,7 @@
         <v>Pos</v>
       </c>
       <c r="AM131" s="100" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AN131">
         <v>4</v>
@@ -22382,16 +22381,16 @@
     </row>
     <row r="132" spans="1:44">
       <c r="A132" t="s">
+        <v>227</v>
+      </c>
+      <c r="B132" t="s">
         <v>228</v>
       </c>
-      <c r="B132" t="s">
-        <v>229</v>
-      </c>
       <c r="C132" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D132" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E132">
         <v>12.19</v>
@@ -22500,7 +22499,7 @@
         <v>Pos</v>
       </c>
       <c r="AM132" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AN132">
         <v>9</v>
@@ -22520,16 +22519,16 @@
     </row>
     <row r="133" spans="1:44">
       <c r="A133" t="s">
+        <v>229</v>
+      </c>
+      <c r="B133" t="s">
         <v>230</v>
       </c>
-      <c r="B133" t="s">
-        <v>231</v>
-      </c>
       <c r="C133" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D133" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E133">
         <v>17.25</v>
@@ -22638,7 +22637,7 @@
         <v>Pos</v>
       </c>
       <c r="AM133" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN133">
         <v>10</v>
@@ -22658,13 +22657,13 @@
     </row>
     <row r="134" spans="1:44">
       <c r="A134" t="s">
+        <v>231</v>
+      </c>
+      <c r="B134" t="s">
         <v>232</v>
       </c>
-      <c r="B134" t="s">
-        <v>233</v>
-      </c>
       <c r="C134" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E134">
         <v>2.84</v>
@@ -22773,7 +22772,7 @@
         <v>0</v>
       </c>
       <c r="AM134" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AN134">
         <v>13</v>
@@ -22793,13 +22792,13 @@
     </row>
     <row r="135" spans="1:44">
       <c r="A135" t="s">
+        <v>233</v>
+      </c>
+      <c r="B135" t="s">
         <v>234</v>
       </c>
-      <c r="B135" t="s">
-        <v>235</v>
-      </c>
       <c r="C135" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -22908,7 +22907,7 @@
         <v>0</v>
       </c>
       <c r="AM135" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AN135">
         <v>20</v>
@@ -22928,13 +22927,13 @@
     </row>
     <row r="136" spans="1:44">
       <c r="A136" t="s">
+        <v>235</v>
+      </c>
+      <c r="B136" t="s">
         <v>236</v>
       </c>
-      <c r="B136" t="s">
-        <v>237</v>
-      </c>
       <c r="C136" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E136">
         <v>5.05</v>
@@ -23043,7 +23042,7 @@
         <v>0</v>
       </c>
       <c r="AM136" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AN136">
         <v>20</v>
@@ -23063,13 +23062,13 @@
     </row>
     <row r="137" spans="1:44">
       <c r="A137" t="s">
+        <v>237</v>
+      </c>
+      <c r="B137" t="s">
         <v>238</v>
       </c>
-      <c r="B137" t="s">
-        <v>239</v>
-      </c>
       <c r="C137" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E137">
         <v>4.93</v>
@@ -23178,7 +23177,7 @@
         <v>0</v>
       </c>
       <c r="AM137" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AN137">
         <v>27</v>
@@ -23198,13 +23197,13 @@
     </row>
     <row r="138" spans="1:44">
       <c r="A138" t="s">
+        <v>239</v>
+      </c>
+      <c r="B138" t="s">
         <v>240</v>
       </c>
-      <c r="B138" t="s">
-        <v>241</v>
-      </c>
       <c r="C138" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E138">
         <v>4.2300000000000004</v>
@@ -23313,10 +23312,10 @@
         <v>0</v>
       </c>
       <c r="AM138" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AN138">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AO138" s="17">
         <v>31</v>
@@ -40851,59 +40850,59 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BB175"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" customWidth="1"/>
-    <col min="4" max="4" width="4.33203125" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="4.88671875" customWidth="1"/>
-    <col min="11" max="11" width="6.109375" customWidth="1"/>
-    <col min="12" max="12" width="4.109375" customWidth="1"/>
-    <col min="13" max="14" width="6.5546875" customWidth="1"/>
-    <col min="15" max="15" width="7.5546875" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" customWidth="1"/>
+    <col min="12" max="12" width="4.140625" customWidth="1"/>
+    <col min="13" max="14" width="6.5703125" customWidth="1"/>
+    <col min="15" max="15" width="7.5703125" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.109375" customWidth="1"/>
+    <col min="18" max="18" width="6.140625" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="5.5546875" customWidth="1"/>
-    <col min="22" max="22" width="6.109375" customWidth="1"/>
-    <col min="23" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="8.33203125" customWidth="1"/>
-    <col min="26" max="26" width="5.44140625" customWidth="1"/>
-    <col min="27" max="27" width="5.109375" customWidth="1"/>
-    <col min="28" max="28" width="4.5546875" customWidth="1"/>
-    <col min="29" max="29" width="4.88671875" customWidth="1"/>
-    <col min="30" max="30" width="6.5546875" customWidth="1"/>
-    <col min="31" max="31" width="5.6640625" customWidth="1"/>
-    <col min="32" max="32" width="6.33203125" customWidth="1"/>
-    <col min="33" max="36" width="4.88671875" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="5.5703125" customWidth="1"/>
+    <col min="22" max="22" width="6.140625" customWidth="1"/>
+    <col min="23" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="8.28515625" customWidth="1"/>
+    <col min="26" max="26" width="5.42578125" customWidth="1"/>
+    <col min="27" max="27" width="5.140625" customWidth="1"/>
+    <col min="28" max="28" width="4.5703125" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" customWidth="1"/>
+    <col min="30" max="30" width="6.5703125" customWidth="1"/>
+    <col min="31" max="31" width="5.7109375" customWidth="1"/>
+    <col min="32" max="32" width="6.28515625" customWidth="1"/>
+    <col min="33" max="36" width="4.85546875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
-    <col min="38" max="38" width="5.6640625" customWidth="1"/>
-    <col min="39" max="39" width="13.6640625" customWidth="1"/>
-    <col min="40" max="40" width="4.5546875" customWidth="1"/>
-    <col min="41" max="41" width="5.44140625" customWidth="1"/>
-    <col min="42" max="44" width="10.88671875" customWidth="1"/>
+    <col min="38" max="38" width="5.7109375" customWidth="1"/>
+    <col min="39" max="39" width="13.7109375" customWidth="1"/>
+    <col min="40" max="40" width="4.5703125" customWidth="1"/>
+    <col min="41" max="41" width="5.42578125" customWidth="1"/>
+    <col min="42" max="44" width="10.85546875" customWidth="1"/>
     <col min="45" max="45" width="6" customWidth="1"/>
-    <col min="46" max="46" width="6.109375" customWidth="1"/>
+    <col min="46" max="46" width="6.140625" customWidth="1"/>
     <col min="47" max="47" width="4" customWidth="1"/>
-    <col min="48" max="48" width="4.109375" customWidth="1"/>
-    <col min="49" max="50" width="5.33203125" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" customWidth="1"/>
-    <col min="52" max="52" width="3.88671875" customWidth="1"/>
+    <col min="48" max="48" width="4.140625" customWidth="1"/>
+    <col min="49" max="50" width="5.28515625" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" customWidth="1"/>
+    <col min="52" max="52" width="3.85546875" customWidth="1"/>
     <col min="53" max="53" width="4" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" customWidth="1"/>
+    <col min="54" max="54" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="92.4" customHeight="1">
+    <row r="1" spans="1:54" ht="92.45" customHeight="1">
       <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
@@ -40914,7 +40913,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>4</v>
@@ -40923,13 +40922,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1" s="40" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J1" s="42" t="s">
         <v>9</v>
@@ -40944,19 +40943,19 @@
         <v>12</v>
       </c>
       <c r="N1" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O1" s="42" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q1" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="Q1" s="40" t="s">
+      <c r="R1" s="40" t="s">
         <v>247</v>
-      </c>
-      <c r="R1" s="40" t="s">
-        <v>248</v>
       </c>
       <c r="S1" s="40" t="s">
         <v>18</v>
@@ -40974,13 +40973,13 @@
         <v>22</v>
       </c>
       <c r="X1" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="Y1" s="64" t="s">
         <v>249</v>
       </c>
-      <c r="Y1" s="64" t="s">
+      <c r="Z1" s="64" t="s">
         <v>250</v>
-      </c>
-      <c r="Z1" s="64" t="s">
-        <v>251</v>
       </c>
       <c r="AA1" s="66" t="s">
         <v>26</v>
@@ -40992,87 +40991,87 @@
         <v>28</v>
       </c>
       <c r="AD1" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE1" s="40" t="s">
         <v>252</v>
       </c>
-      <c r="AE1" s="40" t="s">
+      <c r="AF1" s="40" t="s">
         <v>253</v>
       </c>
-      <c r="AF1" s="40" t="s">
+      <c r="AG1" s="69" t="s">
         <v>254</v>
       </c>
-      <c r="AG1" s="69" t="s">
+      <c r="AH1" s="69" t="s">
         <v>255</v>
-      </c>
-      <c r="AH1" s="69" t="s">
-        <v>256</v>
       </c>
       <c r="AI1" s="69"/>
       <c r="AJ1" s="69"/>
       <c r="AK1" s="69" t="s">
+        <v>256</v>
+      </c>
+      <c r="AL1" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="AM1" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN1" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="AL1" s="44" t="s">
-        <v>242</v>
-      </c>
-      <c r="AM1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN1" s="39" t="s">
+      <c r="AO1" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="AO1" s="39" t="s">
+      <c r="AP1" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ1" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AR1" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS1" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="AT1" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AU1" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="AV1" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW1" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX1" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="AY1" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="AP1" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="AQ1" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="AR1" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AS1" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="AT1" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="AU1" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="AV1" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="AW1" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="AX1" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="AY1" s="45" t="s">
-        <v>260</v>
-      </c>
       <c r="AZ1" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA1" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" s="45" t="s">
+      <c r="BB1" s="45" t="s">
         <v>54</v>
-      </c>
-      <c r="BB1" s="45" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:54">
       <c r="A2" s="101"/>
       <c r="B2" s="46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C2" s="47">
         <v>2025</v>
       </c>
       <c r="D2" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" s="47">
         <v>495.77</v>
@@ -41211,13 +41210,13 @@
     <row r="3" spans="1:54">
       <c r="A3" s="101"/>
       <c r="B3" s="46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C3" s="47">
         <v>2025</v>
       </c>
       <c r="D3" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" s="47">
         <v>427.8</v>
@@ -41356,13 +41355,13 @@
     <row r="4" spans="1:54">
       <c r="A4" s="101"/>
       <c r="B4" s="46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C4" s="47">
         <v>2025</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="47">
         <v>119.91</v>
@@ -41501,13 +41500,13 @@
     <row r="5" spans="1:54">
       <c r="A5" s="101"/>
       <c r="B5" s="53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C5" s="54">
         <v>2025</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="54">
         <v>507.05</v>
@@ -41646,13 +41645,13 @@
     <row r="6" spans="1:54">
       <c r="A6" s="101"/>
       <c r="B6" s="53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C6" s="54">
         <v>2025</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" s="54">
         <v>71.8</v>
@@ -41791,13 +41790,13 @@
     <row r="7" spans="1:54">
       <c r="A7" s="101"/>
       <c r="B7" s="53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C7" s="54">
         <v>2025</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="54">
         <v>412.84</v>
@@ -41936,13 +41935,13 @@
     <row r="8" spans="1:54">
       <c r="A8" s="101"/>
       <c r="B8" s="53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C8" s="54">
         <v>2025</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" s="54">
         <v>39</v>
@@ -42081,13 +42080,13 @@
     <row r="9" spans="1:54">
       <c r="A9" s="101"/>
       <c r="B9" s="53" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C9" s="54">
         <v>2025</v>
       </c>
       <c r="D9" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="54">
         <v>181.43</v>
@@ -42226,13 +42225,13 @@
     <row r="10" spans="1:54">
       <c r="A10" s="101"/>
       <c r="B10" s="53" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C10" s="54">
         <v>2025</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="54">
         <v>42</v>
@@ -42371,13 +42370,13 @@
     <row r="11" spans="1:54">
       <c r="A11" s="101"/>
       <c r="B11" s="53" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C11" s="47">
         <v>2024</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="54">
         <v>75.03</v>
@@ -42516,13 +42515,13 @@
     <row r="12" spans="1:54">
       <c r="A12" s="101"/>
       <c r="B12" s="53" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C12" s="47">
         <v>2024</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="54">
         <v>200.8</v>
@@ -42661,13 +42660,13 @@
     <row r="13" spans="1:54">
       <c r="A13" s="101"/>
       <c r="B13" s="53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C13" s="47">
         <v>2024</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="54">
         <v>11.5</v>
@@ -42806,13 +42805,13 @@
     <row r="14" spans="1:54">
       <c r="A14" s="101"/>
       <c r="B14" s="53" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C14" s="47">
         <v>2024</v>
       </c>
       <c r="D14" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="54">
         <v>211.7</v>
@@ -42951,13 +42950,13 @@
     <row r="15" spans="1:54">
       <c r="A15" s="101"/>
       <c r="B15" s="53" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C15" s="47">
         <v>2024</v>
       </c>
       <c r="D15" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="54">
         <v>305.58</v>
@@ -43096,13 +43095,13 @@
     <row r="16" spans="1:54">
       <c r="A16" s="101"/>
       <c r="B16" s="53" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C16" s="54">
         <v>2024</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="54">
         <v>63.04</v>
@@ -43241,13 +43240,13 @@
     <row r="17" spans="1:54">
       <c r="A17" s="101"/>
       <c r="B17" s="53" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C17" s="54">
         <v>2024</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" s="54">
         <v>396.5</v>
@@ -43386,13 +43385,13 @@
     <row r="18" spans="1:54">
       <c r="A18" s="101"/>
       <c r="B18" s="53" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C18" s="54">
         <v>2024</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" s="54">
         <v>1392.24</v>
@@ -43531,13 +43530,13 @@
     <row r="19" spans="1:54">
       <c r="A19" s="101"/>
       <c r="B19" s="53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C19" s="54">
         <v>2024</v>
       </c>
       <c r="D19" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" s="54">
         <v>68.010000000000005</v>
@@ -43676,13 +43675,13 @@
     <row r="20" spans="1:54">
       <c r="A20" s="101"/>
       <c r="B20" s="57" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C20" s="54">
         <v>2025</v>
       </c>
       <c r="D20" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" s="54">
         <v>6166.54</v>
@@ -43821,13 +43820,13 @@
     <row r="21" spans="1:54">
       <c r="A21" s="101"/>
       <c r="B21" s="57" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="54">
         <v>2025</v>
       </c>
       <c r="D21" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="54">
         <v>397.77</v>
@@ -43966,13 +43965,13 @@
     <row r="22" spans="1:54">
       <c r="A22" s="101"/>
       <c r="B22" s="59" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="54">
         <v>2024</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="54">
         <v>213</v>
@@ -44105,13 +44104,13 @@
     <row r="23" spans="1:54">
       <c r="A23" s="101"/>
       <c r="B23" s="59" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C23" s="54">
         <v>2024</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="54">
         <v>8536.35</v>
@@ -44244,13 +44243,13 @@
     <row r="24" spans="1:54">
       <c r="A24" s="101"/>
       <c r="B24" s="59" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C24" s="54">
         <v>2024</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" s="54">
         <v>2253.44</v>
@@ -44383,13 +44382,13 @@
     <row r="25" spans="1:54">
       <c r="A25" s="101"/>
       <c r="B25" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C25" s="54">
         <v>2024</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="54">
         <v>652</v>
@@ -44522,13 +44521,13 @@
     <row r="26" spans="1:54">
       <c r="A26" s="101"/>
       <c r="B26" s="59" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C26" s="54">
         <v>2024</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="54">
         <v>100</v>
@@ -44661,13 +44660,13 @@
     <row r="27" spans="1:54">
       <c r="A27" s="101"/>
       <c r="B27" s="59" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C27" s="54">
         <v>2024</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" s="54">
         <v>108</v>
@@ -44800,13 +44799,13 @@
     <row r="28" spans="1:54">
       <c r="A28" s="101"/>
       <c r="B28" s="59" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C28" s="54">
         <v>2024</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" s="54">
         <v>4.51</v>
@@ -44941,13 +44940,13 @@
     <row r="29" spans="1:54">
       <c r="A29" s="101"/>
       <c r="B29" s="59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C29" s="54">
         <v>2024</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" s="54">
         <v>472.25</v>
@@ -45082,13 +45081,13 @@
     <row r="30" spans="1:54">
       <c r="A30" s="101"/>
       <c r="B30" s="59" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C30" s="54">
         <v>2024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" s="54">
         <v>492.45</v>
@@ -45221,13 +45220,13 @@
     <row r="31" spans="1:54">
       <c r="A31" s="101"/>
       <c r="B31" s="61" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C31" s="47">
         <v>2025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" s="47">
         <v>26.95</v>
@@ -45360,13 +45359,13 @@
     <row r="32" spans="1:54">
       <c r="A32" s="101"/>
       <c r="B32" s="59" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C32" s="54">
         <v>2025</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32" s="54">
         <v>21.67</v>
@@ -45501,13 +45500,13 @@
     <row r="33" spans="1:54">
       <c r="A33" s="101"/>
       <c r="B33" s="59" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C33" s="54">
         <v>2025</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E33" s="54">
         <v>318.52999999999997</v>
@@ -45644,13 +45643,13 @@
     <row r="34" spans="1:54">
       <c r="A34" s="101"/>
       <c r="B34" s="59" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C34" s="54">
         <v>2025</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" s="54">
         <v>428.39</v>
@@ -45783,13 +45782,13 @@
     <row r="35" spans="1:54">
       <c r="A35" s="101"/>
       <c r="B35" s="59" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C35" s="54">
         <v>2025</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E35" s="54">
         <v>50</v>
@@ -45922,13 +45921,13 @@
     <row r="36" spans="1:54">
       <c r="A36" s="101"/>
       <c r="B36" s="59" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C36" s="54">
         <v>2025</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" s="54">
         <v>1137.06</v>
@@ -46061,13 +46060,13 @@
     <row r="37" spans="1:54">
       <c r="A37" s="101"/>
       <c r="B37" s="59" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C37" s="54">
         <v>2025</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E37" s="54">
         <v>781.2</v>
@@ -46200,13 +46199,13 @@
     <row r="38" spans="1:54">
       <c r="A38" s="101"/>
       <c r="B38" s="59" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C38" s="54">
         <v>2025</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38" s="54">
         <v>343.96</v>
@@ -46339,13 +46338,13 @@
     <row r="39" spans="1:54">
       <c r="A39" s="101"/>
       <c r="B39" s="59" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C39" s="54">
         <v>2025</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="54">
         <v>273.98</v>
@@ -46478,13 +46477,13 @@
     <row r="40" spans="1:54">
       <c r="A40" s="101"/>
       <c r="B40" s="62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C40" s="58">
         <v>2024</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E40" s="54">
         <v>0</v>
@@ -46617,13 +46616,13 @@
     <row r="41" spans="1:54">
       <c r="A41" s="101"/>
       <c r="B41" s="62" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C41" s="54">
         <v>2024</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="54">
         <v>1530</v>
@@ -46762,13 +46761,13 @@
     <row r="42" spans="1:54">
       <c r="A42" s="101"/>
       <c r="B42" s="62" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C42" s="54">
         <v>2025</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E42" s="54">
         <v>92.12</v>
@@ -46903,13 +46902,13 @@
     <row r="43" spans="1:54">
       <c r="A43" s="101"/>
       <c r="B43" s="63" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C43" s="54">
         <v>2025</v>
       </c>
       <c r="D43" s="63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" s="54">
         <v>0</v>
@@ -47048,13 +47047,13 @@
     <row r="44" spans="1:54">
       <c r="A44" s="101"/>
       <c r="B44" s="63" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C44" s="54">
         <v>2025</v>
       </c>
       <c r="D44" s="63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="54">
         <v>0</v>
@@ -47187,13 +47186,13 @@
     <row r="45" spans="1:54">
       <c r="A45" s="101"/>
       <c r="B45" s="63" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C45" s="54">
         <v>2025</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E45" s="54">
         <v>0</v>
@@ -47326,13 +47325,13 @@
     <row r="46" spans="1:54">
       <c r="A46" s="101"/>
       <c r="B46" s="63" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C46" s="54">
         <v>2025</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E46" s="54">
         <v>346</v>
@@ -47467,13 +47466,13 @@
     <row r="47" spans="1:54">
       <c r="A47" s="101"/>
       <c r="B47" s="63" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C47" s="54">
         <v>2025</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E47" s="54">
         <v>351.99</v>
@@ -47517,7 +47516,7 @@
         <v>-1</v>
       </c>
       <c r="T47" s="54" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="U47" s="54"/>
       <c r="V47" s="54">
@@ -47614,13 +47613,13 @@
     <row r="48" spans="1:54">
       <c r="A48" s="101"/>
       <c r="B48" s="63" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C48" s="54">
         <v>2025</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E48" s="54">
         <v>829.48</v>
@@ -47753,13 +47752,13 @@
     <row r="49" spans="1:54">
       <c r="A49" s="101"/>
       <c r="B49" s="63" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C49" s="54">
         <v>2025</v>
       </c>
       <c r="D49" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E49" s="54">
         <v>1949.69</v>
@@ -47892,13 +47891,13 @@
     <row r="50" spans="1:54">
       <c r="A50" s="101"/>
       <c r="B50" s="63" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C50" s="54">
         <v>2025</v>
       </c>
       <c r="D50" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E50" s="54">
         <v>0.33</v>
@@ -48031,13 +48030,13 @@
     <row r="51" spans="1:54">
       <c r="A51" s="101"/>
       <c r="B51" s="63" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C51" s="54">
         <v>2025</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E51" s="54">
         <v>2.9</v>
@@ -48170,13 +48169,13 @@
     <row r="52" spans="1:54">
       <c r="A52" s="101"/>
       <c r="B52" s="63" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C52" s="54">
         <v>2025</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E52" s="54">
         <v>0</v>
@@ -48309,13 +48308,13 @@
     <row r="53" spans="1:54">
       <c r="A53" s="101"/>
       <c r="B53" s="63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C53" s="54">
         <v>2025</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E53" s="54">
         <v>346.22</v>
@@ -48448,13 +48447,13 @@
     <row r="54" spans="1:54">
       <c r="A54" s="101"/>
       <c r="B54" s="63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C54" s="54">
         <v>2025</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E54" s="54">
         <v>100.09</v>
@@ -48587,13 +48586,13 @@
     <row r="55" spans="1:54">
       <c r="A55" s="101"/>
       <c r="B55" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C55" s="47">
         <v>2025</v>
       </c>
       <c r="D55" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E55" s="47">
         <v>76.73</v>
@@ -48726,13 +48725,13 @@
     <row r="56" spans="1:54">
       <c r="A56" s="101"/>
       <c r="B56" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C56" s="47">
         <v>2025</v>
       </c>
       <c r="D56" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E56" s="54">
         <v>135.25</v>
@@ -48865,13 +48864,13 @@
     <row r="57" spans="1:54">
       <c r="A57" s="101"/>
       <c r="B57" s="102" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C57" s="47">
         <v>2025</v>
       </c>
       <c r="D57" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E57" s="47">
         <v>437.04</v>
@@ -49002,13 +49001,13 @@
     <row r="58" spans="1:54">
       <c r="A58" s="101"/>
       <c r="B58" s="102" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C58" s="47">
         <v>2025</v>
       </c>
       <c r="D58" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E58" s="47">
         <v>0</v>
@@ -49138,16 +49137,16 @@
     </row>
     <row r="59" spans="1:54">
       <c r="A59" s="101" t="s">
+        <v>318</v>
+      </c>
+      <c r="B59" s="104" t="s">
         <v>319</v>
-      </c>
-      <c r="B59" s="104" t="s">
-        <v>320</v>
       </c>
       <c r="C59" s="47">
         <v>2025</v>
       </c>
       <c r="D59" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E59" s="54">
         <v>146.38</v>
@@ -49277,16 +49276,16 @@
     </row>
     <row r="60" spans="1:54">
       <c r="A60" s="101" t="s">
+        <v>320</v>
+      </c>
+      <c r="B60" s="104" t="s">
         <v>321</v>
-      </c>
-      <c r="B60" s="104" t="s">
-        <v>322</v>
       </c>
       <c r="C60" s="47">
         <v>2025</v>
       </c>
       <c r="D60" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E60" s="54">
         <v>0</v>
@@ -49415,13 +49414,13 @@
     <row r="61" spans="1:54">
       <c r="A61" s="101"/>
       <c r="B61" s="104" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C61" s="47">
         <v>2025</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E61" s="54">
         <v>0</v>
@@ -49552,13 +49551,13 @@
     <row r="62" spans="1:54">
       <c r="A62" s="101"/>
       <c r="B62" s="104" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C62" s="47">
         <v>2025</v>
       </c>
       <c r="D62" s="106" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E62" s="54">
         <v>360.05</v>
@@ -49687,13 +49686,13 @@
     <row r="63" spans="1:54">
       <c r="A63" s="101"/>
       <c r="B63" s="104" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C63" s="58">
         <v>2025</v>
       </c>
       <c r="D63" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E63" s="54">
         <v>3.88</v>
@@ -49821,16 +49820,16 @@
     </row>
     <row r="64" spans="1:54">
       <c r="A64" s="101" t="s">
+        <v>325</v>
+      </c>
+      <c r="B64" s="101" t="s">
         <v>326</v>
       </c>
-      <c r="B64" s="101" t="s">
-        <v>327</v>
-      </c>
       <c r="C64" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D64" s="48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E64" s="101">
         <v>0</v>
@@ -49970,16 +49969,16 @@
     </row>
     <row r="65" spans="1:54">
       <c r="A65" s="101" t="s">
+        <v>327</v>
+      </c>
+      <c r="B65" s="101" t="s">
         <v>328</v>
       </c>
-      <c r="B65" s="101" t="s">
-        <v>329</v>
-      </c>
       <c r="C65" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D65" s="48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E65" s="101">
         <v>0</v>
@@ -50119,16 +50118,16 @@
     </row>
     <row r="66" spans="1:54">
       <c r="A66" s="101" t="s">
+        <v>329</v>
+      </c>
+      <c r="B66" s="101" t="s">
         <v>330</v>
       </c>
-      <c r="B66" s="101" t="s">
-        <v>331</v>
-      </c>
       <c r="C66" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D66" s="48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E66" s="101">
         <v>132.22999999999999</v>
@@ -50268,16 +50267,16 @@
     </row>
     <row r="67" spans="1:54">
       <c r="A67" s="101" t="s">
+        <v>331</v>
+      </c>
+      <c r="B67" s="101" t="s">
         <v>332</v>
       </c>
-      <c r="B67" s="101" t="s">
-        <v>333</v>
-      </c>
       <c r="C67" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D67" s="48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E67" s="101">
         <v>266.2</v>
@@ -50417,16 +50416,16 @@
     </row>
     <row r="68" spans="1:54">
       <c r="A68" s="101" t="s">
+        <v>333</v>
+      </c>
+      <c r="B68" s="101" t="s">
         <v>334</v>
       </c>
-      <c r="B68" s="101" t="s">
-        <v>335</v>
-      </c>
       <c r="C68" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D68" s="48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E68" s="101">
         <v>4526.33</v>
@@ -50564,16 +50563,16 @@
     </row>
     <row r="69" spans="1:54">
       <c r="A69" s="101" t="s">
+        <v>335</v>
+      </c>
+      <c r="B69" s="101" t="s">
         <v>336</v>
       </c>
-      <c r="B69" s="101" t="s">
-        <v>337</v>
-      </c>
       <c r="C69" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D69" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E69" s="101">
         <v>18.93</v>
@@ -50680,7 +50679,7 @@
         <v>Pos</v>
       </c>
       <c r="AM69" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AN69" s="101">
         <v>24</v>
@@ -50714,16 +50713,16 @@
     </row>
     <row r="70" spans="1:54">
       <c r="A70" s="101" t="s">
+        <v>337</v>
+      </c>
+      <c r="B70" s="101" t="s">
         <v>338</v>
       </c>
-      <c r="B70" s="101" t="s">
-        <v>339</v>
-      </c>
       <c r="C70" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D70" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E70" s="101">
         <v>62.48</v>
@@ -50830,7 +50829,7 @@
         <v>Neg</v>
       </c>
       <c r="AM70" s="107" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AN70" s="101">
         <v>25</v>
@@ -50862,16 +50861,16 @@
     </row>
     <row r="71" spans="1:54">
       <c r="A71" s="101" t="s">
+        <v>339</v>
+      </c>
+      <c r="B71" s="101" t="s">
         <v>340</v>
       </c>
-      <c r="B71" s="101" t="s">
-        <v>341</v>
-      </c>
       <c r="C71" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D71" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E71" s="101">
         <v>7973.7</v>
@@ -50978,7 +50977,7 @@
         <v>Neg</v>
       </c>
       <c r="AM71" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AN71" s="101">
         <v>25</v>
@@ -51010,16 +51009,16 @@
     </row>
     <row r="72" spans="1:54">
       <c r="A72" s="101" t="s">
+        <v>341</v>
+      </c>
+      <c r="B72" s="101" t="s">
         <v>342</v>
       </c>
-      <c r="B72" s="101" t="s">
-        <v>343</v>
-      </c>
       <c r="C72" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D72" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E72" s="101">
         <v>90.65</v>
@@ -51126,7 +51125,7 @@
         <v>Pos</v>
       </c>
       <c r="AM72" s="107" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN72" s="101">
         <v>26</v>
@@ -51158,16 +51157,16 @@
     </row>
     <row r="73" spans="1:54">
       <c r="A73" s="101" t="s">
+        <v>343</v>
+      </c>
+      <c r="B73" s="101" t="s">
         <v>344</v>
       </c>
-      <c r="B73" s="101" t="s">
-        <v>345</v>
-      </c>
       <c r="C73" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D73" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E73" s="101">
         <v>330.63</v>
@@ -51274,7 +51273,7 @@
         <v>Neg</v>
       </c>
       <c r="AM73" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AN73" s="101">
         <v>27</v>
@@ -51306,16 +51305,16 @@
     </row>
     <row r="74" spans="1:54">
       <c r="A74" s="101" t="s">
+        <v>345</v>
+      </c>
+      <c r="B74" s="101" t="s">
         <v>346</v>
       </c>
-      <c r="B74" s="101" t="s">
-        <v>347</v>
-      </c>
       <c r="C74" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D74" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E74" s="101">
         <v>49.62</v>
@@ -51422,7 +51421,7 @@
         <v>Pos</v>
       </c>
       <c r="AM74" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AN74" s="101">
         <v>6</v>
@@ -51454,16 +51453,16 @@
     </row>
     <row r="75" spans="1:54">
       <c r="A75" s="101" t="s">
+        <v>347</v>
+      </c>
+      <c r="B75" s="101" t="s">
         <v>348</v>
       </c>
-      <c r="B75" s="101" t="s">
-        <v>349</v>
-      </c>
       <c r="C75" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D75" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" s="101">
         <v>99.75</v>
@@ -51570,7 +51569,7 @@
         <v>Neg</v>
       </c>
       <c r="AM75" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN75" s="101">
         <v>11</v>
@@ -51600,16 +51599,16 @@
     </row>
     <row r="76" spans="1:54">
       <c r="A76" s="101" t="s">
+        <v>349</v>
+      </c>
+      <c r="B76" s="101" t="s">
         <v>350</v>
       </c>
-      <c r="B76" s="101" t="s">
-        <v>351</v>
-      </c>
       <c r="C76" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D76" s="101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E76" s="101">
         <v>79.05</v>
@@ -51716,7 +51715,7 @@
         <v>Neg</v>
       </c>
       <c r="AM76" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AN76" s="101">
         <v>12</v>
@@ -51746,16 +51745,16 @@
     </row>
     <row r="77" spans="1:54">
       <c r="A77" s="101" t="s">
+        <v>351</v>
+      </c>
+      <c r="B77" s="101" t="s">
         <v>352</v>
       </c>
-      <c r="B77" s="101" t="s">
-        <v>353</v>
-      </c>
       <c r="C77" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D77" s="101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E77" s="101">
         <v>0</v>
@@ -51862,7 +51861,7 @@
         <v>Pos</v>
       </c>
       <c r="AM77" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AN77" s="101">
         <v>13</v>
@@ -51892,13 +51891,13 @@
     </row>
     <row r="78" spans="1:54">
       <c r="A78" s="101" t="s">
+        <v>353</v>
+      </c>
+      <c r="B78" s="101" t="s">
         <v>354</v>
       </c>
-      <c r="B78" s="101" t="s">
-        <v>355</v>
-      </c>
       <c r="C78" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D78" s="101"/>
       <c r="E78" s="101">
@@ -52006,7 +52005,7 @@
         <v>0</v>
       </c>
       <c r="AM78" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AN78" s="101">
         <v>18</v>
@@ -52036,13 +52035,13 @@
     </row>
     <row r="79" spans="1:54">
       <c r="A79" s="101" t="s">
+        <v>355</v>
+      </c>
+      <c r="B79" s="101" t="s">
         <v>356</v>
       </c>
-      <c r="B79" s="101" t="s">
-        <v>357</v>
-      </c>
       <c r="C79" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D79" s="101"/>
       <c r="E79" s="101">
@@ -52150,13 +52149,13 @@
         <v>0</v>
       </c>
       <c r="AM79" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN79" s="101">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO79" s="101">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP79" s="17">
         <f t="shared" si="30"/>
@@ -52180,13 +52179,13 @@
     </row>
     <row r="80" spans="1:54">
       <c r="A80" s="101" t="s">
+        <v>357</v>
+      </c>
+      <c r="B80" s="101" t="s">
         <v>358</v>
       </c>
-      <c r="B80" s="101" t="s">
-        <v>359</v>
-      </c>
       <c r="C80" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D80" s="101"/>
       <c r="E80" s="101">
@@ -52294,7 +52293,7 @@
         <v>0</v>
       </c>
       <c r="AM80" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AN80" s="101">
         <v>27</v>
@@ -52324,13 +52323,13 @@
     </row>
     <row r="81" spans="1:54">
       <c r="A81" s="101" t="s">
+        <v>359</v>
+      </c>
+      <c r="B81" s="101" t="s">
         <v>360</v>
       </c>
-      <c r="B81" s="101" t="s">
-        <v>361</v>
-      </c>
       <c r="C81" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D81" s="101"/>
       <c r="E81" s="101">
@@ -52438,7 +52437,7 @@
         <v>0</v>
       </c>
       <c r="AM81" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AN81" s="101">
         <v>27</v>
@@ -52468,13 +52467,13 @@
     </row>
     <row r="82" spans="1:54">
       <c r="A82" s="101" t="s">
+        <v>361</v>
+      </c>
+      <c r="B82" s="101" t="s">
         <v>362</v>
       </c>
-      <c r="B82" s="101" t="s">
-        <v>363</v>
-      </c>
       <c r="C82" s="101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D82" s="101"/>
       <c r="E82" s="101">
@@ -52582,7 +52581,7 @@
         <v>0</v>
       </c>
       <c r="AM82" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN82" s="101">
         <v>27</v>
@@ -60943,52 +60942,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:DA484"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
-    <col min="4" max="4" width="3.88671875" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="6.6640625" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="6.6640625" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" customWidth="1"/>
-    <col min="20" max="20" width="5.33203125" customWidth="1"/>
-    <col min="21" max="21" width="4.6640625" customWidth="1"/>
-    <col min="22" max="22" width="4.33203125" customWidth="1"/>
-    <col min="23" max="23" width="6.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.33203125" customWidth="1"/>
-    <col min="25" max="25" width="5.5546875" customWidth="1"/>
-    <col min="26" max="26" width="3.44140625" customWidth="1"/>
-    <col min="27" max="27" width="5.88671875" customWidth="1"/>
-    <col min="28" max="28" width="7.33203125" customWidth="1"/>
-    <col min="29" max="29" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="6.6640625" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="7.109375" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="5.5546875" customWidth="1"/>
-    <col min="34" max="34" width="6.33203125" customWidth="1"/>
-    <col min="35" max="35" width="8.88671875" customWidth="1"/>
-    <col min="36" max="36" width="4.44140625" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" customWidth="1"/>
+    <col min="20" max="20" width="5.28515625" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.28515625" customWidth="1"/>
+    <col min="25" max="25" width="5.5703125" customWidth="1"/>
+    <col min="26" max="26" width="3.42578125" customWidth="1"/>
+    <col min="27" max="27" width="5.85546875" customWidth="1"/>
+    <col min="28" max="28" width="7.28515625" customWidth="1"/>
+    <col min="29" max="29" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="6.7109375" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="5.5703125" customWidth="1"/>
+    <col min="34" max="34" width="6.28515625" customWidth="1"/>
+    <col min="35" max="35" width="8.85546875" customWidth="1"/>
+    <col min="36" max="36" width="4.42578125" customWidth="1"/>
     <col min="38" max="42" width="13" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="1.5546875" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="1.5703125" hidden="1" customWidth="1"/>
     <col min="53" max="54" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104" ht="92.4" customHeight="1">
+    <row r="1" spans="1:104" ht="92.45" customHeight="1">
       <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
@@ -61044,7 +61043,7 @@
         <v>17</v>
       </c>
       <c r="S1" s="72" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="T1" s="72" t="s">
         <v>19</v>
@@ -61101,67 +61100,67 @@
         <v>36</v>
       </c>
       <c r="AL1" s="72" t="s">
+        <v>257</v>
+      </c>
+      <c r="AM1" s="72" t="s">
         <v>258</v>
       </c>
-      <c r="AM1" s="72" t="s">
-        <v>259</v>
-      </c>
       <c r="AN1" s="72" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO1" s="72" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP1" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="AP1" s="72" t="s">
+      <c r="AQ1" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="AQ1" s="72" t="s">
+      <c r="AR1" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="AR1" s="72" t="s">
+      <c r="AS1" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="AS1" s="72" t="s">
+      <c r="AT1" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="AT1" s="72" t="s">
+      <c r="AU1" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="AU1" s="72" t="s">
+      <c r="AV1" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="AV1" s="72" t="s">
+      <c r="AW1" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="AW1" s="72" t="s">
+      <c r="AX1" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="AX1" s="72" t="s">
+      <c r="AY1" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="AY1" s="72" t="s">
+      <c r="AZ1" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="AZ1" s="72" t="s">
+      <c r="BA1" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" s="72" t="s">
+      <c r="BB1" s="72" t="s">
         <v>54</v>
-      </c>
-      <c r="BB1" s="72" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:104">
       <c r="A2" s="75"/>
       <c r="B2" s="77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" s="71">
         <v>2024</v>
       </c>
       <c r="D2" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="70">
         <v>2.5299999999999998</v>
@@ -61200,7 +61199,7 @@
       </c>
       <c r="R2" s="70"/>
       <c r="S2" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T2" s="78"/>
       <c r="U2" s="78"/>
@@ -61304,13 +61303,13 @@
     <row r="3" spans="1:104" hidden="1">
       <c r="A3" s="75"/>
       <c r="B3" s="79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="71">
         <v>2024</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" s="70">
         <v>6.89</v>
@@ -61445,13 +61444,13 @@
     <row r="4" spans="1:104" hidden="1">
       <c r="A4" s="75"/>
       <c r="B4" s="80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="71">
         <v>2023</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="71">
         <v>22.99</v>
@@ -61490,7 +61489,7 @@
       </c>
       <c r="R4" s="71"/>
       <c r="S4" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T4" s="78"/>
       <c r="U4" s="78"/>
@@ -61570,13 +61569,13 @@
     <row r="5" spans="1:104" hidden="1">
       <c r="A5" s="75"/>
       <c r="B5" s="80" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" s="71">
         <v>2023</v>
       </c>
       <c r="D5" s="71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="71">
         <v>41.78</v>
@@ -61600,7 +61599,7 @@
       </c>
       <c r="L5" s="71"/>
       <c r="M5" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N5" s="71"/>
       <c r="O5" s="71">
@@ -61615,7 +61614,7 @@
       </c>
       <c r="R5" s="71"/>
       <c r="S5" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T5" s="78"/>
       <c r="U5" s="78"/>
@@ -61693,13 +61692,13 @@
     <row r="6" spans="1:104" hidden="1">
       <c r="A6" s="75"/>
       <c r="B6" s="81" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="71">
         <v>2023</v>
       </c>
       <c r="D6" s="71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" s="71">
         <v>40.83</v>
@@ -61738,7 +61737,7 @@
       </c>
       <c r="R6" s="71"/>
       <c r="S6" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T6" s="78"/>
       <c r="U6" s="78"/>
@@ -61820,13 +61819,13 @@
     <row r="7" spans="1:104" hidden="1">
       <c r="A7" s="75"/>
       <c r="B7" s="82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="71">
         <v>2025</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="70">
         <v>12.99</v>
@@ -61963,13 +61962,13 @@
     <row r="8" spans="1:104" hidden="1">
       <c r="A8" s="75"/>
       <c r="B8" s="82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" s="71">
         <v>2025</v>
       </c>
       <c r="D8" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="70">
         <v>20.22</v>
@@ -62106,13 +62105,13 @@
     <row r="9" spans="1:104" hidden="1">
       <c r="A9" s="75"/>
       <c r="B9" s="83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" s="71">
         <v>2025</v>
       </c>
       <c r="D9" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="70">
         <v>3.34</v>
@@ -62249,13 +62248,13 @@
     <row r="10" spans="1:104">
       <c r="A10" s="75"/>
       <c r="B10" s="75" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C10" s="75">
         <v>2025</v>
       </c>
       <c r="D10" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="75">
         <v>14.57</v>
@@ -62388,13 +62387,13 @@
     <row r="11" spans="1:104" hidden="1">
       <c r="A11" s="75"/>
       <c r="B11" s="77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" s="71">
         <v>2025</v>
       </c>
       <c r="D11" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="70">
         <v>3.67</v>
@@ -62433,7 +62432,7 @@
       </c>
       <c r="R11" s="70"/>
       <c r="S11" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T11" s="78"/>
       <c r="U11" s="78"/>
@@ -62529,13 +62528,13 @@
     <row r="12" spans="1:104" hidden="1">
       <c r="A12" s="75"/>
       <c r="B12" s="77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" s="71">
         <v>2025</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="70">
         <v>67.11</v>
@@ -62670,13 +62669,13 @@
     <row r="13" spans="1:104" hidden="1">
       <c r="A13" s="75"/>
       <c r="B13" s="77" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" s="71">
         <v>2025</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="70">
         <v>8.3699999999999992</v>
@@ -62715,7 +62714,7 @@
       </c>
       <c r="R13" s="70"/>
       <c r="S13" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T13" s="78"/>
       <c r="U13" s="78"/>
@@ -62808,19 +62807,19 @@
         <v>-10.3448275862069</v>
       </c>
       <c r="CZ13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:104" hidden="1">
       <c r="A14" s="75"/>
       <c r="B14" s="77" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="71">
         <v>2025</v>
       </c>
       <c r="D14" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="70">
         <v>1.07</v>
@@ -62859,7 +62858,7 @@
       </c>
       <c r="R14" s="70"/>
       <c r="S14" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T14" s="78"/>
       <c r="U14" s="78"/>
@@ -62955,13 +62954,13 @@
     <row r="15" spans="1:104" hidden="1">
       <c r="A15" s="75"/>
       <c r="B15" s="77" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="71">
         <v>2025</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="70">
         <v>12.21</v>
@@ -63094,13 +63093,13 @@
     <row r="16" spans="1:104" hidden="1">
       <c r="A16" s="75"/>
       <c r="B16" s="77" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="71">
         <v>2024</v>
       </c>
       <c r="D16" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="70">
         <v>17.25</v>
@@ -63235,13 +63234,13 @@
     <row r="17" spans="1:105" hidden="1">
       <c r="A17" s="75"/>
       <c r="B17" s="83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C17" s="71">
         <v>2024</v>
       </c>
       <c r="D17" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="70">
         <v>14.19</v>
@@ -63371,19 +63370,19 @@
         <v>-64.444444444444443</v>
       </c>
       <c r="DA17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:105" hidden="1">
       <c r="A18" s="75"/>
       <c r="B18" s="77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C18" s="71">
         <v>2024</v>
       </c>
       <c r="D18" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="70">
         <v>4.6100000000000003</v>
@@ -63407,7 +63406,7 @@
       </c>
       <c r="L18" s="70"/>
       <c r="M18" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N18" s="70"/>
       <c r="O18" s="70">
@@ -63422,7 +63421,7 @@
       </c>
       <c r="R18" s="70"/>
       <c r="S18" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T18" s="78"/>
       <c r="U18" s="78"/>
@@ -63457,7 +63456,7 @@
         <v>-11</v>
       </c>
       <c r="AF18" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG18" s="71">
         <f t="shared" si="4"/>
@@ -63518,13 +63517,13 @@
     <row r="19" spans="1:105" hidden="1">
       <c r="A19" s="75"/>
       <c r="B19" s="77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" s="71">
         <v>2024</v>
       </c>
       <c r="D19" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="70">
         <v>0</v>
@@ -63565,7 +63564,7 @@
         <v>46.47</v>
       </c>
       <c r="S19" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T19" s="78"/>
       <c r="U19" s="78"/>
@@ -63600,7 +63599,7 @@
         <v>-6</v>
       </c>
       <c r="AF19" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG19" s="71">
         <f t="shared" si="4"/>
@@ -63661,13 +63660,13 @@
     <row r="20" spans="1:105" hidden="1">
       <c r="A20" s="75"/>
       <c r="B20" s="77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C20" s="71">
         <v>2024</v>
       </c>
       <c r="D20" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="70">
         <v>91.56</v>
@@ -63706,7 +63705,7 @@
       </c>
       <c r="R20" s="70"/>
       <c r="S20" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T20" s="78"/>
       <c r="U20" s="78"/>
@@ -63715,7 +63714,7 @@
       </c>
       <c r="W20" s="70"/>
       <c r="X20" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y20" s="70">
         <v>3.9</v>
@@ -63741,7 +63740,7 @@
         <v>-29</v>
       </c>
       <c r="AF20" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG20" s="71">
         <f t="shared" si="4"/>
@@ -63802,13 +63801,13 @@
     <row r="21" spans="1:105">
       <c r="A21" s="75"/>
       <c r="B21" s="75" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C21" s="75">
         <v>2025</v>
       </c>
       <c r="D21" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="75">
         <v>0</v>
@@ -63947,13 +63946,13 @@
     <row r="22" spans="1:105" hidden="1">
       <c r="A22" s="75"/>
       <c r="B22" s="77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C22" s="71">
         <v>2024</v>
       </c>
       <c r="D22" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="70">
         <v>20.57</v>
@@ -63992,7 +63991,7 @@
       </c>
       <c r="R22" s="70"/>
       <c r="S22" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T22" s="78"/>
       <c r="U22" s="78"/>
@@ -64088,13 +64087,13 @@
     <row r="23" spans="1:105" hidden="1">
       <c r="A23" s="75"/>
       <c r="B23" s="77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C23" s="71">
         <v>2024</v>
       </c>
       <c r="D23" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="70">
         <v>10.29</v>
@@ -64229,13 +64228,13 @@
     <row r="24" spans="1:105" hidden="1">
       <c r="A24" s="75"/>
       <c r="B24" s="77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C24" s="71">
         <v>2024</v>
       </c>
       <c r="D24" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" s="70">
         <v>7.7</v>
@@ -64274,7 +64273,7 @@
       </c>
       <c r="R24" s="70"/>
       <c r="S24" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T24" s="78"/>
       <c r="U24" s="78"/>
@@ -64370,13 +64369,13 @@
     <row r="25" spans="1:105" hidden="1">
       <c r="A25" s="75"/>
       <c r="B25" s="77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" s="71">
         <v>2023</v>
       </c>
       <c r="D25" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="71">
         <v>8.94</v>
@@ -64497,13 +64496,13 @@
     <row r="26" spans="1:105" hidden="1">
       <c r="A26" s="75"/>
       <c r="B26" s="77" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C26" s="71">
         <v>2023</v>
       </c>
       <c r="D26" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="71">
         <v>3.98</v>
@@ -64624,13 +64623,13 @@
     <row r="27" spans="1:105" hidden="1">
       <c r="A27" s="75"/>
       <c r="B27" s="77" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C27" s="71">
         <v>2023</v>
       </c>
       <c r="D27" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" s="71">
         <v>1.96</v>
@@ -64669,7 +64668,7 @@
       </c>
       <c r="R27" s="71"/>
       <c r="S27" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T27" s="78"/>
       <c r="U27" s="78"/>
@@ -64751,13 +64750,13 @@
     <row r="28" spans="1:105">
       <c r="A28" s="75"/>
       <c r="B28" s="73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C28" s="75">
         <v>2025</v>
       </c>
       <c r="D28" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" s="73">
         <v>0.5</v>
@@ -64894,13 +64893,13 @@
     <row r="29" spans="1:105" hidden="1">
       <c r="A29" s="75"/>
       <c r="B29" s="88" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" s="71">
         <v>2025</v>
       </c>
       <c r="D29" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" s="70">
         <v>27.99</v>
@@ -64939,7 +64938,7 @@
       </c>
       <c r="R29" s="70"/>
       <c r="S29" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T29" s="78"/>
       <c r="U29" s="78"/>
@@ -65029,13 +65028,13 @@
     <row r="30" spans="1:105" hidden="1">
       <c r="A30" s="75"/>
       <c r="B30" s="75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C30" s="71">
         <v>2025</v>
       </c>
       <c r="D30" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" s="70">
         <v>20.55</v>
@@ -65164,13 +65163,13 @@
     <row r="31" spans="1:105" hidden="1">
       <c r="A31" s="75"/>
       <c r="B31" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" s="71">
         <v>2025</v>
       </c>
       <c r="D31" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" s="70">
         <v>30.45</v>
@@ -65299,13 +65298,13 @@
     <row r="32" spans="1:105" hidden="1">
       <c r="A32" s="75"/>
       <c r="B32" s="75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C32" s="75">
         <v>2025</v>
       </c>
       <c r="D32" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32" s="75">
         <v>27.92</v>
@@ -65344,7 +65343,7 @@
       </c>
       <c r="R32" s="75"/>
       <c r="S32" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T32" s="89"/>
       <c r="U32" s="89"/>
@@ -65434,13 +65433,13 @@
     <row r="33" spans="1:54">
       <c r="A33" s="75"/>
       <c r="B33" s="75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33" s="71">
         <v>2025</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E33" s="70">
         <v>9.74</v>
@@ -65583,13 +65582,13 @@
     <row r="34" spans="1:54" hidden="1">
       <c r="A34" s="75"/>
       <c r="B34" s="75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C34" s="75">
         <v>2025</v>
       </c>
       <c r="D34" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E34" s="75">
         <v>15.6</v>
@@ -65628,7 +65627,7 @@
       </c>
       <c r="R34" s="75"/>
       <c r="S34" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T34" s="89"/>
       <c r="U34" s="89"/>
@@ -65718,13 +65717,13 @@
     <row r="35" spans="1:54" hidden="1">
       <c r="A35" s="75"/>
       <c r="B35" s="75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C35" s="75">
         <v>2025</v>
       </c>
       <c r="D35" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E35" s="75">
         <v>8.18</v>
@@ -65763,7 +65762,7 @@
       </c>
       <c r="R35" s="75"/>
       <c r="S35" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T35" s="89"/>
       <c r="U35" s="89"/>
@@ -65853,13 +65852,13 @@
     <row r="36" spans="1:54" hidden="1">
       <c r="A36" s="75"/>
       <c r="B36" s="75" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C36" s="75">
         <v>2025</v>
       </c>
       <c r="D36" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" s="75">
         <v>58.11</v>
@@ -65898,7 +65897,7 @@
       </c>
       <c r="R36" s="75"/>
       <c r="S36" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T36" s="89"/>
       <c r="U36" s="89"/>
@@ -65988,13 +65987,13 @@
     <row r="37" spans="1:54" hidden="1">
       <c r="A37" s="75"/>
       <c r="B37" s="88" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C37" s="75">
         <v>2025</v>
       </c>
       <c r="D37" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E37" s="75">
         <v>0</v>
@@ -66007,7 +66006,7 @@
         <v>100</v>
       </c>
       <c r="H37" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I37" s="75">
         <v>13.93</v>
@@ -66018,7 +66017,7 @@
       </c>
       <c r="L37" s="75"/>
       <c r="M37" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N37" s="75"/>
       <c r="O37" s="75">
@@ -66033,7 +66032,7 @@
       </c>
       <c r="R37" s="75"/>
       <c r="S37" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T37" s="89"/>
       <c r="U37" s="89"/>
@@ -66123,13 +66122,13 @@
     <row r="38" spans="1:54" hidden="1">
       <c r="A38" s="75"/>
       <c r="B38" s="71" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C38" s="71">
         <v>2025</v>
       </c>
       <c r="D38" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E38" s="71">
         <v>20.38</v>
@@ -66168,7 +66167,7 @@
       </c>
       <c r="R38" s="71"/>
       <c r="S38" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T38" s="78"/>
       <c r="U38" s="78"/>
@@ -66260,13 +66259,13 @@
     <row r="39" spans="1:54" hidden="1">
       <c r="A39" s="75"/>
       <c r="B39" s="71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C39" s="71">
         <v>2025</v>
       </c>
       <c r="D39" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="71">
         <v>6.07</v>
@@ -66305,7 +66304,7 @@
       </c>
       <c r="R39" s="75"/>
       <c r="S39" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T39" s="78"/>
       <c r="U39" s="78"/>
@@ -66387,13 +66386,13 @@
     <row r="40" spans="1:54" hidden="1">
       <c r="A40" s="75"/>
       <c r="B40" s="75" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C40" s="75">
         <v>2025</v>
       </c>
       <c r="D40" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E40" s="75">
         <v>59.61</v>
@@ -66432,7 +66431,7 @@
       </c>
       <c r="R40" s="75"/>
       <c r="S40" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T40" s="78"/>
       <c r="U40" s="78"/>
@@ -66514,13 +66513,13 @@
     <row r="41" spans="1:54" hidden="1">
       <c r="A41" s="75"/>
       <c r="B41" s="75" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C41" s="75">
         <v>2025</v>
       </c>
       <c r="D41" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="75">
         <v>59.31</v>
@@ -66641,13 +66640,13 @@
     <row r="42" spans="1:54" hidden="1">
       <c r="A42" s="75"/>
       <c r="B42" s="75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C42" s="75">
         <v>2025</v>
       </c>
       <c r="D42" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E42" s="75">
         <v>14.66</v>
@@ -66686,7 +66685,7 @@
       </c>
       <c r="R42" s="75"/>
       <c r="S42" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T42" s="78"/>
       <c r="U42" s="78"/>
@@ -66768,13 +66767,13 @@
     <row r="43" spans="1:54" hidden="1">
       <c r="A43" s="75"/>
       <c r="B43" s="75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C43" s="75">
         <v>2025</v>
       </c>
       <c r="D43" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" s="75">
         <v>31.63</v>
@@ -66794,7 +66793,7 @@
       </c>
       <c r="J43" s="75"/>
       <c r="K43" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L43" s="75"/>
       <c r="M43" s="75">
@@ -66813,7 +66812,7 @@
       </c>
       <c r="R43" s="75"/>
       <c r="S43" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T43" s="78"/>
       <c r="U43" s="78"/>
@@ -66895,13 +66894,13 @@
     <row r="44" spans="1:54" hidden="1">
       <c r="A44" s="75"/>
       <c r="B44" s="75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C44" s="75">
         <v>2025</v>
       </c>
       <c r="D44" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E44" s="75">
         <v>0.02</v>
@@ -66940,7 +66939,7 @@
       </c>
       <c r="R44" s="75"/>
       <c r="S44" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T44" s="78"/>
       <c r="U44" s="78"/>
@@ -67022,13 +67021,13 @@
     <row r="45" spans="1:54" hidden="1">
       <c r="A45" s="75"/>
       <c r="B45" s="71" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C45" s="71">
         <v>2025</v>
       </c>
       <c r="D45" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E45" s="71">
         <v>0</v>
@@ -67067,7 +67066,7 @@
       </c>
       <c r="R45" s="71"/>
       <c r="S45" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T45" s="78"/>
       <c r="U45" s="78"/>
@@ -67149,13 +67148,13 @@
     <row r="46" spans="1:54" hidden="1">
       <c r="A46" s="75"/>
       <c r="B46" s="71" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C46" s="71">
         <v>2025</v>
       </c>
       <c r="D46" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E46" s="71">
         <v>85.59</v>
@@ -67190,7 +67189,7 @@
         <v>24.011925042589436</v>
       </c>
       <c r="Q46" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R46" s="71"/>
       <c r="S46" s="71">
@@ -67276,13 +67275,13 @@
     <row r="47" spans="1:54" hidden="1">
       <c r="A47" s="75"/>
       <c r="B47" s="71" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C47" s="71">
         <v>2025</v>
       </c>
       <c r="D47" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E47" s="75">
         <v>3.54</v>
@@ -67403,13 +67402,13 @@
     <row r="48" spans="1:54" hidden="1">
       <c r="A48" s="75"/>
       <c r="B48" s="71" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C48" s="75">
         <v>2025</v>
       </c>
       <c r="D48" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E48" s="75">
         <v>6.75</v>
@@ -67530,13 +67529,13 @@
     <row r="49" spans="1:54">
       <c r="A49" s="75"/>
       <c r="B49" s="73" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C49" s="75">
         <v>2025</v>
       </c>
       <c r="D49" s="75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E49" s="73">
         <v>10.66</v>
@@ -67675,13 +67674,13 @@
     <row r="50" spans="1:54">
       <c r="A50" s="75"/>
       <c r="B50" s="75" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C50" s="75">
         <v>2025</v>
       </c>
       <c r="D50" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E50" s="75">
         <v>0.94</v>
@@ -67818,13 +67817,13 @@
     <row r="51" spans="1:54" hidden="1">
       <c r="A51" s="75"/>
       <c r="B51" s="71" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C51" s="75">
         <v>2025</v>
       </c>
       <c r="D51" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E51" s="71">
         <v>0.04</v>
@@ -67945,13 +67944,13 @@
     <row r="52" spans="1:54" hidden="1">
       <c r="A52" s="75"/>
       <c r="B52" s="75" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C52" s="75">
         <v>2025</v>
       </c>
       <c r="D52" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E52" s="75">
         <v>50.98</v>
@@ -68072,13 +68071,13 @@
     <row r="53" spans="1:54" hidden="1">
       <c r="A53" s="75"/>
       <c r="B53" s="71" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C53" s="75">
         <v>2025</v>
       </c>
       <c r="D53" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E53" s="75">
         <v>1.49</v>
@@ -68117,7 +68116,7 @@
       </c>
       <c r="R53" s="71"/>
       <c r="S53" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T53" s="78"/>
       <c r="U53" s="78"/>
@@ -68199,13 +68198,13 @@
     <row r="54" spans="1:54" hidden="1">
       <c r="A54" s="75"/>
       <c r="B54" s="71" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="75">
         <v>2025</v>
       </c>
       <c r="D54" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E54" s="71">
         <v>4.09</v>
@@ -68244,7 +68243,7 @@
       </c>
       <c r="R54" s="71"/>
       <c r="S54" s="71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T54" s="78"/>
       <c r="U54" s="78"/>
@@ -68328,13 +68327,13 @@
     <row r="55" spans="1:54">
       <c r="A55" s="75"/>
       <c r="B55" s="91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C55" s="75">
         <v>2025</v>
       </c>
       <c r="D55" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E55" s="75">
         <v>18.09</v>
@@ -68471,13 +68470,13 @@
     <row r="56" spans="1:54" hidden="1">
       <c r="A56" s="75"/>
       <c r="B56" s="75" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C56" s="75">
         <v>2025</v>
       </c>
       <c r="D56" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E56" s="75">
         <v>0</v>
@@ -68516,7 +68515,7 @@
       </c>
       <c r="R56" s="75"/>
       <c r="S56" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T56" s="78"/>
       <c r="U56" s="78"/>
@@ -68598,13 +68597,13 @@
     <row r="57" spans="1:54">
       <c r="A57" s="75"/>
       <c r="B57" s="75" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C57" s="75">
         <v>2025</v>
       </c>
       <c r="D57" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E57" s="75">
         <v>7.99</v>
@@ -68737,13 +68736,13 @@
     <row r="58" spans="1:54" hidden="1">
       <c r="A58" s="75"/>
       <c r="B58" s="75" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" s="75">
         <v>2025</v>
       </c>
       <c r="D58" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E58" s="71">
         <v>44.03</v>
@@ -68864,13 +68863,13 @@
     <row r="59" spans="1:54" hidden="1">
       <c r="A59" s="75"/>
       <c r="B59" s="71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C59" s="75">
         <v>2025</v>
       </c>
       <c r="D59" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E59" s="71">
         <v>10.79</v>
@@ -68989,13 +68988,13 @@
     <row r="60" spans="1:54">
       <c r="A60" s="75"/>
       <c r="B60" s="79" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C60" s="71">
         <v>2024</v>
       </c>
       <c r="D60" s="71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E60" s="70">
         <v>29</v>
@@ -69034,7 +69033,7 @@
       </c>
       <c r="R60" s="70"/>
       <c r="S60" s="70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T60" s="78"/>
       <c r="U60" s="78"/>
@@ -69138,13 +69137,13 @@
     <row r="61" spans="1:54" hidden="1">
       <c r="A61" s="75"/>
       <c r="B61" s="75" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C61" s="75">
         <v>2025</v>
       </c>
       <c r="D61" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E61" s="75">
         <v>11.9</v>
@@ -69157,14 +69156,14 @@
         <v>-23.958333333333339</v>
       </c>
       <c r="H61" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I61" s="75">
         <v>4.2699999999999996</v>
       </c>
       <c r="J61" s="75"/>
       <c r="K61" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L61" s="75"/>
       <c r="M61" s="75">
@@ -69265,13 +69264,13 @@
     <row r="62" spans="1:54" hidden="1">
       <c r="A62" s="75"/>
       <c r="B62" s="75" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C62" s="75">
         <v>2025</v>
       </c>
       <c r="D62" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E62" s="75"/>
       <c r="F62" s="75"/>
@@ -69368,13 +69367,13 @@
     <row r="63" spans="1:54">
       <c r="A63" s="75"/>
       <c r="B63" s="75" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="75">
         <v>2025</v>
       </c>
       <c r="D63" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E63" s="75">
         <v>32.159999999999997</v>
@@ -69509,13 +69508,13 @@
     <row r="64" spans="1:54">
       <c r="A64" s="75"/>
       <c r="B64" s="73" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C64" s="75">
         <v>2025</v>
       </c>
       <c r="D64" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E64" s="73">
         <v>66.180000000000007</v>
@@ -69650,13 +69649,13 @@
     <row r="65" spans="1:54" hidden="1">
       <c r="A65" s="75"/>
       <c r="B65" s="75" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C65" s="75">
         <v>2025</v>
       </c>
       <c r="D65" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E65" s="75">
         <v>62.57</v>
@@ -69775,13 +69774,13 @@
     <row r="66" spans="1:54" hidden="1">
       <c r="A66" s="75"/>
       <c r="B66" s="75" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C66" s="75">
         <v>2025</v>
       </c>
       <c r="D66" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E66" s="75">
         <v>2.75</v>
@@ -69902,13 +69901,13 @@
     <row r="67" spans="1:54" hidden="1">
       <c r="A67" s="75"/>
       <c r="B67" s="91" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C67" s="75">
         <v>2025</v>
       </c>
       <c r="D67" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E67" s="75">
         <v>0.09</v>
@@ -70029,13 +70028,13 @@
     <row r="68" spans="1:54" hidden="1">
       <c r="A68" s="75"/>
       <c r="B68" s="75" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C68" s="75">
         <v>2025</v>
       </c>
       <c r="D68" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E68" s="75">
         <v>57.99</v>
@@ -70156,13 +70155,13 @@
     <row r="69" spans="1:54" hidden="1">
       <c r="A69" s="75"/>
       <c r="B69" s="75" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C69" s="75">
         <v>2025</v>
       </c>
       <c r="D69" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E69" s="75">
         <v>1.1499999999999999</v>
@@ -70283,13 +70282,13 @@
     <row r="70" spans="1:54">
       <c r="A70" s="75"/>
       <c r="B70" s="88" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C70" s="75">
         <v>2025</v>
       </c>
       <c r="D70" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E70" s="75">
         <v>18.5</v>
@@ -70328,7 +70327,7 @@
       </c>
       <c r="R70" s="75"/>
       <c r="S70" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T70" s="89"/>
       <c r="U70" s="89"/>
@@ -70430,13 +70429,13 @@
     <row r="71" spans="1:54" hidden="1">
       <c r="A71" s="75"/>
       <c r="B71" s="75" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C71" s="75">
         <v>2025</v>
       </c>
       <c r="D71" s="75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E71" s="75">
         <v>18.690000000000001</v>
@@ -70538,7 +70537,7 @@
       </c>
       <c r="AN71" s="78"/>
       <c r="AO71" s="78" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AP71" s="78"/>
       <c r="AQ71" s="71"/>
@@ -70557,13 +70556,13 @@
     <row r="72" spans="1:54" hidden="1">
       <c r="A72" s="75"/>
       <c r="B72" s="75" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C72" s="75">
         <v>2025</v>
       </c>
       <c r="D72" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E72" s="73">
         <v>47.24</v>
@@ -70684,13 +70683,13 @@
     <row r="73" spans="1:54" hidden="1">
       <c r="A73" s="75"/>
       <c r="B73" s="71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C73" s="75">
         <v>2025</v>
       </c>
       <c r="D73" s="75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E73" s="71">
         <v>44.11</v>
@@ -70811,13 +70810,13 @@
     <row r="74" spans="1:54" hidden="1">
       <c r="A74" s="75"/>
       <c r="B74" s="75" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C74" s="75">
         <v>2025</v>
       </c>
       <c r="D74" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E74" s="75">
         <v>12.25</v>
@@ -70938,13 +70937,13 @@
     <row r="75" spans="1:54" hidden="1">
       <c r="A75" s="75"/>
       <c r="B75" s="71" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C75" s="75">
         <v>2025</v>
       </c>
       <c r="D75" s="75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E75" s="71">
         <v>17.38</v>
@@ -71064,16 +71063,16 @@
     </row>
     <row r="76" spans="1:54">
       <c r="A76" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="B76" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="B76" s="75" t="s">
-        <v>175</v>
-      </c>
       <c r="C76" s="75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D76" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E76" s="75">
         <v>35.76</v>
@@ -71224,13 +71223,13 @@
     <row r="77" spans="1:54">
       <c r="A77" s="75"/>
       <c r="B77" s="75" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C77" s="75">
         <v>2025</v>
       </c>
       <c r="D77" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E77" s="75">
         <v>38.659999999999997</v>
@@ -71365,13 +71364,13 @@
     <row r="78" spans="1:54" hidden="1">
       <c r="A78" s="75"/>
       <c r="B78" s="73" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C78" s="75">
         <v>2025</v>
       </c>
       <c r="D78" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E78" s="85">
         <v>31.75</v>
@@ -71496,13 +71495,13 @@
     <row r="79" spans="1:54" hidden="1">
       <c r="A79" s="75"/>
       <c r="B79" s="94" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C79" s="75">
         <v>2025</v>
       </c>
       <c r="D79" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E79" s="94">
         <v>109</v>
@@ -71627,13 +71626,13 @@
     <row r="80" spans="1:54" hidden="1">
       <c r="A80" s="75"/>
       <c r="B80" s="73" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C80" s="75">
         <v>2025</v>
       </c>
       <c r="D80" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E80" s="85">
         <v>21.29</v>
@@ -71758,13 +71757,13 @@
     <row r="81" spans="1:54">
       <c r="A81" s="75"/>
       <c r="B81" s="75" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C81" s="75">
         <v>2025</v>
       </c>
       <c r="D81" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E81" s="75">
         <v>35.619999999999997</v>
@@ -71903,13 +71902,13 @@
     <row r="82" spans="1:54" hidden="1">
       <c r="A82" s="75"/>
       <c r="B82" s="73" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C82" s="75">
         <v>2025</v>
       </c>
       <c r="D82" s="73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E82" s="85">
         <v>22.09</v>
@@ -72027,16 +72026,16 @@
     </row>
     <row r="83" spans="1:54" hidden="1">
       <c r="A83" s="75" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="B83" s="75" t="s">
+      <c r="C83" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="C83" s="75" t="s">
-        <v>162</v>
-      </c>
       <c r="D83" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E83" s="75">
         <v>46.71</v>
@@ -72168,16 +72167,16 @@
     </row>
     <row r="84" spans="1:54" hidden="1">
       <c r="A84" s="75" t="s">
+        <v>162</v>
+      </c>
+      <c r="B84" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="B84" s="75" t="s">
-        <v>164</v>
-      </c>
       <c r="C84" s="75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D84" s="75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E84" s="75">
         <v>9.2899999999999991</v>
@@ -72309,16 +72308,16 @@
     </row>
     <row r="85" spans="1:54" hidden="1">
       <c r="A85" s="75" t="s">
+        <v>164</v>
+      </c>
+      <c r="B85" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="B85" s="75" t="s">
-        <v>166</v>
-      </c>
       <c r="C85" s="75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D85" s="75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E85" s="75">
         <v>66.180000000000007</v>
@@ -72450,16 +72449,16 @@
     </row>
     <row r="86" spans="1:54" hidden="1">
       <c r="A86" s="75" t="s">
+        <v>166</v>
+      </c>
+      <c r="B86" s="75" t="s">
         <v>167</v>
-      </c>
-      <c r="B86" s="75" t="s">
-        <v>168</v>
       </c>
       <c r="C86" s="75">
         <v>2026</v>
       </c>
       <c r="D86" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E86" s="75">
         <v>11.56</v>
@@ -72591,16 +72590,16 @@
     </row>
     <row r="87" spans="1:54" hidden="1">
       <c r="A87" s="75" t="s">
+        <v>168</v>
+      </c>
+      <c r="B87" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="B87" s="75" t="s">
-        <v>170</v>
-      </c>
       <c r="C87" s="75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D87" s="75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E87" s="75">
         <v>5.69</v>
@@ -72732,16 +72731,16 @@
     </row>
     <row r="88" spans="1:54" hidden="1">
       <c r="A88" s="75" t="s">
+        <v>170</v>
+      </c>
+      <c r="B88" s="75" t="s">
         <v>171</v>
       </c>
-      <c r="B88" s="75" t="s">
+      <c r="C88" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="D88" s="75" t="s">
         <v>172</v>
-      </c>
-      <c r="C88" s="75" t="s">
-        <v>162</v>
-      </c>
-      <c r="D88" s="75" t="s">
-        <v>173</v>
       </c>
       <c r="E88" s="75">
         <v>24.73</v>
@@ -72874,13 +72873,13 @@
     <row r="89" spans="1:54">
       <c r="A89" s="75"/>
       <c r="B89" s="83" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C89" s="71">
         <v>2025</v>
       </c>
       <c r="D89" s="71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E89" s="70">
         <v>49.21</v>

--- a/General.xlsx
+++ b/General.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBFB0A2-C19D-4CB8-911A-45020C436975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638CAB55-7BD8-405B-ADB9-1CEBAF65C1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IPOSME" sheetId="1" r:id="rId1"/>
@@ -2830,7 +2830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DF468"/>
+  <dimension ref="A1:DF466"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
@@ -23270,7 +23270,7 @@
         <v>1</v>
       </c>
       <c r="X138">
-        <v>2</v>
+        <v>0.04</v>
       </c>
       <c r="Y138">
         <v>11.77</v>
@@ -23283,11 +23283,11 @@
         <v>-1.7</v>
       </c>
       <c r="AB138">
-        <v>25</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="AC138" s="16">
         <f t="shared" si="39"/>
-        <v>3.0833333333333335</v>
+        <v>1.9583333333333331E-2</v>
       </c>
       <c r="AD138">
         <v>5.44</v>
@@ -23304,7 +23304,7 @@
       </c>
       <c r="AH138" s="16">
         <f t="shared" si="34"/>
-        <v>8.0833333333333339</v>
+        <v>4.0195833333333333</v>
       </c>
       <c r="AI138" s="16"/>
       <c r="AJ138" s="16">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="AK138" s="16">
         <f t="shared" si="35"/>
-        <v>13.723333333333333</v>
+        <v>9.6595833333333339</v>
       </c>
       <c r="AL138" s="15">
         <f t="shared" si="36"/>
@@ -23322,10 +23322,10 @@
         <v>241</v>
       </c>
       <c r="AN138">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO138" s="17">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AP138" s="17">
         <f t="shared" si="37"/>
@@ -23405,13 +23405,13 @@
         <v>1</v>
       </c>
       <c r="X139">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Y139">
-        <v>2</v>
+        <v>0.36</v>
       </c>
       <c r="Z139">
-        <v>2</v>
+        <v>0.01</v>
       </c>
       <c r="AA139" s="2">
         <f t="shared" si="32"/>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="AH139" s="16">
         <f t="shared" si="34"/>
-        <v>9.1195833333333329</v>
+        <v>7.1195833333333329</v>
       </c>
       <c r="AI139" s="16"/>
       <c r="AJ139" s="16">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="AK139" s="16">
         <f t="shared" si="35"/>
-        <v>16.439583333333331</v>
+        <v>14.439583333333331</v>
       </c>
       <c r="AL139" s="15">
         <f t="shared" si="36"/>
@@ -23457,7 +23457,7 @@
         <v>243</v>
       </c>
       <c r="AN139">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AO139" s="17">
         <v>31</v>
@@ -23468,7 +23468,7 @@
       </c>
       <c r="AQ139" s="17">
         <f t="shared" si="38"/>
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AR139" s="17"/>
     </row>
@@ -30456,7 +30456,7 @@
         <v>0</v>
       </c>
       <c r="AG258" s="118" t="e">
-        <f t="shared" ref="AG258:AG323" si="57">IF(G258&lt;52,0,0.7)+IF(G258&lt;34,0,0.7)+IF(G258&lt;1,0,0.7)+IF(P258&gt;14.56,0,1)+IF(R258&lt;9,0.5,0)+IF(R258&lt;33.8,0.5,0)+IF(R258&lt;50,0.5,0)+IF(R258&lt;80,0.5,0)+IF(S258=5,0,S258)+IF(V258&gt;0,1,0)+IF(AE258&lt;10.56,0,1)-IF(AE258&lt;3,1,0)-IF(AE258&lt;1,1,0)</f>
+        <f t="shared" ref="AG258:AG321" si="57">IF(G258&lt;52,0,0.7)+IF(G258&lt;34,0,0.7)+IF(G258&lt;1,0,0.7)+IF(P258&gt;14.56,0,1)+IF(R258&lt;9,0.5,0)+IF(R258&lt;33.8,0.5,0)+IF(R258&lt;50,0.5,0)+IF(R258&lt;80,0.5,0)+IF(S258=5,0,S258)+IF(V258&gt;0,1,0)+IF(AE258&lt;10.56,0,1)-IF(AE258&lt;3,1,0)-IF(AE258&lt;1,1,0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH258" s="16" t="e">
@@ -31667,11 +31667,6 @@
         <f t="shared" si="61"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ278" s="17" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AR278" s="17"/>
     </row>
     <row r="279" spans="7:44">
       <c r="G279" s="16" t="e">
@@ -31726,11 +31721,6 @@
         <f t="shared" si="61"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AQ279" s="17" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AR279" s="17"/>
     </row>
     <row r="280" spans="7:44">
       <c r="G280" s="16" t="e">
@@ -34021,12 +34011,12 @@
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
-      <c r="AG322" s="118" t="e">
-        <f t="shared" si="57"/>
+      <c r="AG322" s="15" t="e">
+        <f t="shared" ref="AG322:AG353" si="69">IF(G322&lt;52,0,0.7)+IF(G322&lt;34,0,0.7)+IF(G322&lt;1,0,0.7)+IF(P322&gt;14.56,0,1)+IF(R322&lt;9,0.5,0)+IF(R322&lt;33.8,0.5,0)+IF(R322&lt;50,0.5,0)+IF(R322&lt;80,0.5,0)+IF(V322&gt;0,1,0)+IF(AE322&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH322" s="16" t="e">
-        <f t="shared" ref="AH322:AH385" si="69">AG322+IF(X322&lt;1.35,0,1)+IF(Y322&lt;1.35,0,1)+AC322+AA322</f>
+        <f t="shared" ref="AH322:AH385" si="70">AG322+IF(X322&lt;1.35,0,1)+IF(Y322&lt;1.35,0,1)+AC322+AA322</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI322" s="16"/>
@@ -34034,11 +34024,11 @@
         <v>1</v>
       </c>
       <c r="AK322" s="16" t="e">
-        <f t="shared" ref="AK322:AK385" si="70">(1.2*AG322+AH322)*AJ322</f>
+        <f t="shared" ref="AK322:AK385" si="71">(1.2*AG322+AH322)*AJ322</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL322" s="15">
-        <f t="shared" ref="AL322:AL385" si="71">D322</f>
+        <f t="shared" ref="AL322:AL385" si="72">D322</f>
         <v>0</v>
       </c>
       <c r="AM322" s="15">
@@ -34050,7 +34040,7 @@
         <v>1</v>
       </c>
       <c r="AP322" s="17" t="e">
-        <f t="shared" ref="AP322:AP385" si="72">IF(AK322&gt;13.8,IF(Z322&lt;101,IF(Z322&lt;35,IF(Z322&lt;8,3,2),1),0),0)</f>
+        <f t="shared" ref="AP322:AP385" si="73">IF(AK322&gt;13.8,IF(Z322&lt;101,IF(Z322&lt;35,IF(Z322&lt;8,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34072,15 +34062,15 @@
         <v>1</v>
       </c>
       <c r="AC323" s="16">
-        <f t="shared" ref="AC323:AC386" si="73">IF(AB323&gt;4,1,0)+AB323/12</f>
-        <v>0</v>
-      </c>
-      <c r="AG323" s="118" t="e">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="AC323:AC386" si="74">IF(AB323&gt;4,1,0)+AB323/12</f>
+        <v>0</v>
+      </c>
+      <c r="AG323" s="15" t="e">
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH323" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI323" s="16"/>
@@ -34088,11 +34078,11 @@
         <v>1</v>
       </c>
       <c r="AK323" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL323" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM323" s="15">
@@ -34104,7 +34094,7 @@
         <v>1</v>
       </c>
       <c r="AP323" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34126,15 +34116,15 @@
         <v>1</v>
       </c>
       <c r="AC324" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG324" s="15" t="e">
-        <f t="shared" ref="AG324:AG355" si="74">IF(G324&lt;52,0,0.7)+IF(G324&lt;34,0,0.7)+IF(G324&lt;1,0,0.7)+IF(P324&gt;14.56,0,1)+IF(R324&lt;9,0.5,0)+IF(R324&lt;33.8,0.5,0)+IF(R324&lt;50,0.5,0)+IF(R324&lt;80,0.5,0)+IF(V324&gt;0,1,0)+IF(AE324&lt;10.56,0,1)</f>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH324" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI324" s="16"/>
@@ -34142,11 +34132,11 @@
         <v>1</v>
       </c>
       <c r="AK324" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL324" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM324" s="15">
@@ -34158,7 +34148,7 @@
         <v>1</v>
       </c>
       <c r="AP324" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34180,15 +34170,15 @@
         <v>1</v>
       </c>
       <c r="AC325" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG325" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH325" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI325" s="16"/>
@@ -34196,11 +34186,11 @@
         <v>1</v>
       </c>
       <c r="AK325" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL325" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM325" s="15">
@@ -34212,7 +34202,7 @@
         <v>1</v>
       </c>
       <c r="AP325" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34234,15 +34224,15 @@
         <v>1</v>
       </c>
       <c r="AC326" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG326" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH326" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI326" s="16"/>
@@ -34250,11 +34240,11 @@
         <v>1</v>
       </c>
       <c r="AK326" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL326" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM326" s="15">
@@ -34266,7 +34256,7 @@
         <v>1</v>
       </c>
       <c r="AP326" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34288,15 +34278,15 @@
         <v>1</v>
       </c>
       <c r="AC327" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG327" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH327" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI327" s="16"/>
@@ -34304,11 +34294,11 @@
         <v>1</v>
       </c>
       <c r="AK327" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL327" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM327" s="15">
@@ -34320,7 +34310,7 @@
         <v>1</v>
       </c>
       <c r="AP327" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34342,15 +34332,15 @@
         <v>1</v>
       </c>
       <c r="AC328" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG328" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH328" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI328" s="16"/>
@@ -34358,11 +34348,11 @@
         <v>1</v>
       </c>
       <c r="AK328" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL328" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM328" s="15">
@@ -34374,7 +34364,7 @@
         <v>1</v>
       </c>
       <c r="AP328" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34396,15 +34386,15 @@
         <v>1</v>
       </c>
       <c r="AC329" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG329" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH329" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI329" s="16"/>
@@ -34412,11 +34402,11 @@
         <v>1</v>
       </c>
       <c r="AK329" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL329" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM329" s="15">
@@ -34428,7 +34418,7 @@
         <v>1</v>
       </c>
       <c r="AP329" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34450,15 +34440,15 @@
         <v>1</v>
       </c>
       <c r="AC330" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG330" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH330" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI330" s="16"/>
@@ -34466,11 +34456,11 @@
         <v>1</v>
       </c>
       <c r="AK330" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL330" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM330" s="15">
@@ -34482,7 +34472,7 @@
         <v>1</v>
       </c>
       <c r="AP330" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34504,15 +34494,15 @@
         <v>1</v>
       </c>
       <c r="AC331" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG331" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH331" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI331" s="16"/>
@@ -34520,11 +34510,11 @@
         <v>1</v>
       </c>
       <c r="AK331" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL331" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM331" s="15">
@@ -34536,7 +34526,7 @@
         <v>1</v>
       </c>
       <c r="AP331" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34558,15 +34548,15 @@
         <v>1</v>
       </c>
       <c r="AC332" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG332" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH332" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI332" s="16"/>
@@ -34574,11 +34564,11 @@
         <v>1</v>
       </c>
       <c r="AK332" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL332" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM332" s="15">
@@ -34590,7 +34580,7 @@
         <v>1</v>
       </c>
       <c r="AP332" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34612,15 +34602,15 @@
         <v>1</v>
       </c>
       <c r="AC333" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG333" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH333" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI333" s="16"/>
@@ -34628,11 +34618,11 @@
         <v>1</v>
       </c>
       <c r="AK333" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL333" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM333" s="15">
@@ -34644,7 +34634,7 @@
         <v>1</v>
       </c>
       <c r="AP333" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34666,15 +34656,15 @@
         <v>1</v>
       </c>
       <c r="AC334" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG334" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH334" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI334" s="16"/>
@@ -34682,11 +34672,11 @@
         <v>1</v>
       </c>
       <c r="AK334" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL334" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM334" s="15">
@@ -34698,7 +34688,7 @@
         <v>1</v>
       </c>
       <c r="AP334" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34720,15 +34710,15 @@
         <v>1</v>
       </c>
       <c r="AC335" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" ref="AC335:AC359" si="79">IF(AB335&gt;9,1,0)+AB335/3</f>
         <v>0</v>
       </c>
       <c r="AG335" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH335" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI335" s="16"/>
@@ -34736,11 +34726,11 @@
         <v>1</v>
       </c>
       <c r="AK335" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL335" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM335" s="15">
@@ -34752,7 +34742,7 @@
         <v>1</v>
       </c>
       <c r="AP335" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34774,15 +34764,15 @@
         <v>1</v>
       </c>
       <c r="AC336" s="16">
-        <f t="shared" si="73"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG336" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH336" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI336" s="16"/>
@@ -34790,11 +34780,11 @@
         <v>1</v>
       </c>
       <c r="AK336" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL336" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM336" s="15">
@@ -34806,7 +34796,7 @@
         <v>1</v>
       </c>
       <c r="AP336" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34828,15 +34818,15 @@
         <v>1</v>
       </c>
       <c r="AC337" s="16">
-        <f t="shared" ref="AC337:AC361" si="79">IF(AB337&gt;9,1,0)+AB337/3</f>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG337" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH337" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI337" s="16"/>
@@ -34844,11 +34834,11 @@
         <v>1</v>
       </c>
       <c r="AK337" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL337" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM337" s="15">
@@ -34860,7 +34850,7 @@
         <v>1</v>
       </c>
       <c r="AP337" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34886,11 +34876,11 @@
         <v>0</v>
       </c>
       <c r="AG338" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH338" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI338" s="16"/>
@@ -34898,11 +34888,11 @@
         <v>1</v>
       </c>
       <c r="AK338" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL338" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM338" s="15">
@@ -34914,7 +34904,7 @@
         <v>1</v>
       </c>
       <c r="AP338" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34940,11 +34930,11 @@
         <v>0</v>
       </c>
       <c r="AG339" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH339" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI339" s="16"/>
@@ -34952,11 +34942,11 @@
         <v>1</v>
       </c>
       <c r="AK339" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL339" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM339" s="15">
@@ -34968,7 +34958,7 @@
         <v>1</v>
       </c>
       <c r="AP339" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -34994,11 +34984,11 @@
         <v>0</v>
       </c>
       <c r="AG340" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH340" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI340" s="16"/>
@@ -35006,11 +34996,11 @@
         <v>1</v>
       </c>
       <c r="AK340" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL340" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM340" s="15">
@@ -35022,7 +35012,7 @@
         <v>1</v>
       </c>
       <c r="AP340" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35048,11 +35038,11 @@
         <v>0</v>
       </c>
       <c r="AG341" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH341" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI341" s="16"/>
@@ -35060,11 +35050,11 @@
         <v>1</v>
       </c>
       <c r="AK341" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL341" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM341" s="15">
@@ -35076,7 +35066,7 @@
         <v>1</v>
       </c>
       <c r="AP341" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35102,11 +35092,11 @@
         <v>0</v>
       </c>
       <c r="AG342" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH342" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI342" s="16"/>
@@ -35114,11 +35104,11 @@
         <v>1</v>
       </c>
       <c r="AK342" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL342" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM342" s="15">
@@ -35130,7 +35120,7 @@
         <v>1</v>
       </c>
       <c r="AP342" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35156,11 +35146,11 @@
         <v>0</v>
       </c>
       <c r="AG343" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH343" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI343" s="16"/>
@@ -35168,11 +35158,11 @@
         <v>1</v>
       </c>
       <c r="AK343" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL343" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM343" s="15">
@@ -35184,7 +35174,7 @@
         <v>1</v>
       </c>
       <c r="AP343" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35210,11 +35200,11 @@
         <v>0</v>
       </c>
       <c r="AG344" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH344" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI344" s="16"/>
@@ -35222,11 +35212,11 @@
         <v>1</v>
       </c>
       <c r="AK344" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL344" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM344" s="15">
@@ -35238,7 +35228,7 @@
         <v>1</v>
       </c>
       <c r="AP344" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35264,11 +35254,11 @@
         <v>0</v>
       </c>
       <c r="AG345" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH345" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI345" s="16"/>
@@ -35276,11 +35266,11 @@
         <v>1</v>
       </c>
       <c r="AK345" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL345" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM345" s="15">
@@ -35292,7 +35282,7 @@
         <v>1</v>
       </c>
       <c r="AP345" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35318,11 +35308,11 @@
         <v>0</v>
       </c>
       <c r="AG346" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH346" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI346" s="16"/>
@@ -35330,11 +35320,11 @@
         <v>1</v>
       </c>
       <c r="AK346" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" ref="AK346:AK377" si="80">(2*AG346+AH346)*AJ346</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL346" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM346" s="15">
@@ -35346,7 +35336,7 @@
         <v>1</v>
       </c>
       <c r="AP346" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35372,11 +35362,11 @@
         <v>0</v>
       </c>
       <c r="AG347" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH347" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI347" s="16"/>
@@ -35384,23 +35374,19 @@
         <v>1</v>
       </c>
       <c r="AK347" s="16" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="80"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL347" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM347" s="15">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="AO347" s="17">
-        <f t="shared" si="78"/>
-        <v>1</v>
-      </c>
       <c r="AP347" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35426,35 +35412,29 @@
         <v>0</v>
       </c>
       <c r="AG348" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH348" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI348" s="16"/>
-      <c r="AJ348" s="16">
-        <v>1</v>
-      </c>
+      <c r="AJ348" s="16"/>
       <c r="AK348" s="16" t="e">
-        <f t="shared" ref="AK348:AK379" si="80">(2*AG348+AH348)*AJ348</f>
+        <f t="shared" si="80"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL348" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM348" s="15">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="AO348" s="17">
-        <f t="shared" si="78"/>
-        <v>1</v>
-      </c>
       <c r="AP348" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35480,23 +35460,21 @@
         <v>0</v>
       </c>
       <c r="AG349" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH349" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI349" s="16"/>
-      <c r="AJ349" s="16">
-        <v>1</v>
-      </c>
+      <c r="AJ349" s="16"/>
       <c r="AK349" s="16" t="e">
         <f t="shared" si="80"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL349" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM349" s="15">
@@ -35504,7 +35482,7 @@
         <v>0</v>
       </c>
       <c r="AP349" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35530,11 +35508,11 @@
         <v>0</v>
       </c>
       <c r="AG350" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH350" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI350" s="16"/>
@@ -35544,7 +35522,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL350" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM350" s="15">
@@ -35552,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="AP350" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35578,11 +35556,11 @@
         <v>0</v>
       </c>
       <c r="AG351" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH351" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI351" s="16"/>
@@ -35592,7 +35570,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL351" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM351" s="15">
@@ -35600,7 +35578,7 @@
         <v>0</v>
       </c>
       <c r="AP351" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35626,11 +35604,11 @@
         <v>0</v>
       </c>
       <c r="AG352" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH352" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI352" s="16"/>
@@ -35640,7 +35618,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL352" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM352" s="15">
@@ -35648,7 +35626,7 @@
         <v>0</v>
       </c>
       <c r="AP352" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35674,11 +35652,11 @@
         <v>0</v>
       </c>
       <c r="AG353" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH353" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI353" s="16"/>
@@ -35688,7 +35666,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL353" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM353" s="15">
@@ -35696,7 +35674,7 @@
         <v>0</v>
       </c>
       <c r="AP353" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35722,11 +35700,11 @@
         <v>0</v>
       </c>
       <c r="AG354" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" ref="AG354:AG385" si="81">IF(G354&lt;52,0,0.7)+IF(G354&lt;34,0,0.7)+IF(G354&lt;1,0,0.7)+IF(P354&gt;14.56,0,1)+IF(R354&lt;9,0.5,0)+IF(R354&lt;33.8,0.5,0)+IF(R354&lt;50,0.5,0)+IF(R354&lt;80,0.5,0)+IF(V354&gt;0,1,0)+IF(AE354&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH354" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI354" s="16"/>
@@ -35736,7 +35714,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL354" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM354" s="15">
@@ -35744,7 +35722,7 @@
         <v>0</v>
       </c>
       <c r="AP354" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35770,11 +35748,11 @@
         <v>0</v>
       </c>
       <c r="AG355" s="15" t="e">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH355" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI355" s="16"/>
@@ -35784,7 +35762,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL355" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM355" s="15">
@@ -35792,7 +35770,7 @@
         <v>0</v>
       </c>
       <c r="AP355" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35818,11 +35796,11 @@
         <v>0</v>
       </c>
       <c r="AG356" s="15" t="e">
-        <f t="shared" ref="AG356:AG387" si="81">IF(G356&lt;52,0,0.7)+IF(G356&lt;34,0,0.7)+IF(G356&lt;1,0,0.7)+IF(P356&gt;14.56,0,1)+IF(R356&lt;9,0.5,0)+IF(R356&lt;33.8,0.5,0)+IF(R356&lt;50,0.5,0)+IF(R356&lt;80,0.5,0)+IF(V356&gt;0,1,0)+IF(AE356&lt;10.56,0,1)</f>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH356" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI356" s="16"/>
@@ -35832,7 +35810,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL356" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM356" s="15">
@@ -35840,7 +35818,7 @@
         <v>0</v>
       </c>
       <c r="AP356" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35870,7 +35848,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH357" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI357" s="16"/>
@@ -35880,7 +35858,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL357" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM357" s="15">
@@ -35888,7 +35866,7 @@
         <v>0</v>
       </c>
       <c r="AP357" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35918,7 +35896,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH358" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI358" s="16"/>
@@ -35928,7 +35906,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL358" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM358" s="15">
@@ -35936,7 +35914,7 @@
         <v>0</v>
       </c>
       <c r="AP358" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -35966,7 +35944,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH359" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI359" s="16"/>
@@ -35976,7 +35954,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL359" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM359" s="15">
@@ -35984,7 +35962,7 @@
         <v>0</v>
       </c>
       <c r="AP359" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36006,7 +35984,7 @@
         <v>1</v>
       </c>
       <c r="AC360" s="16">
-        <f t="shared" si="79"/>
+        <f t="shared" ref="AC360:AC391" si="82">IF(U361&gt;9,1,0)+U361/3</f>
         <v>0</v>
       </c>
       <c r="AG360" s="15" t="e">
@@ -36014,7 +35992,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH360" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI360" s="16"/>
@@ -36024,7 +36002,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL360" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM360" s="15">
@@ -36032,7 +36010,7 @@
         <v>0</v>
       </c>
       <c r="AP360" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36054,7 +36032,7 @@
         <v>1</v>
       </c>
       <c r="AC361" s="16">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="AG361" s="15" t="e">
@@ -36062,7 +36040,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH361" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI361" s="16"/>
@@ -36072,7 +36050,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL361" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM361" s="15">
@@ -36080,7 +36058,7 @@
         <v>0</v>
       </c>
       <c r="AP361" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36102,7 +36080,7 @@
         <v>1</v>
       </c>
       <c r="AC362" s="16">
-        <f t="shared" ref="AC362:AC393" si="82">IF(U363&gt;9,1,0)+U363/3</f>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="AG362" s="15" t="e">
@@ -36110,7 +36088,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH362" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI362" s="16"/>
@@ -36120,7 +36098,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL362" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM362" s="15">
@@ -36128,7 +36106,7 @@
         <v>0</v>
       </c>
       <c r="AP362" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36158,7 +36136,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH363" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI363" s="16"/>
@@ -36168,7 +36146,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL363" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM363" s="15">
@@ -36176,7 +36154,7 @@
         <v>0</v>
       </c>
       <c r="AP363" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36206,7 +36184,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH364" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI364" s="16"/>
@@ -36216,7 +36194,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL364" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM364" s="15">
@@ -36224,7 +36202,7 @@
         <v>0</v>
       </c>
       <c r="AP364" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36254,7 +36232,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH365" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI365" s="16"/>
@@ -36264,7 +36242,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL365" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM365" s="15">
@@ -36272,7 +36250,7 @@
         <v>0</v>
       </c>
       <c r="AP365" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36302,7 +36280,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH366" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI366" s="16"/>
@@ -36312,7 +36290,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL366" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM366" s="15">
@@ -36320,7 +36298,7 @@
         <v>0</v>
       </c>
       <c r="AP366" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36350,7 +36328,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH367" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI367" s="16"/>
@@ -36360,7 +36338,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL367" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM367" s="15">
@@ -36368,7 +36346,7 @@
         <v>0</v>
       </c>
       <c r="AP367" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36398,7 +36376,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH368" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI368" s="16"/>
@@ -36408,7 +36386,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL368" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM368" s="15">
@@ -36416,7 +36394,7 @@
         <v>0</v>
       </c>
       <c r="AP368" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36446,7 +36424,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH369" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI369" s="16"/>
@@ -36456,7 +36434,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL369" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM369" s="15">
@@ -36464,7 +36442,7 @@
         <v>0</v>
       </c>
       <c r="AP369" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36494,7 +36472,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH370" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI370" s="16"/>
@@ -36504,7 +36482,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL370" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM370" s="15">
@@ -36512,7 +36490,7 @@
         <v>0</v>
       </c>
       <c r="AP370" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36542,7 +36520,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH371" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI371" s="16"/>
@@ -36552,7 +36530,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL371" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM371" s="15">
@@ -36560,7 +36538,7 @@
         <v>0</v>
       </c>
       <c r="AP371" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36590,7 +36568,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH372" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI372" s="16"/>
@@ -36600,7 +36578,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL372" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM372" s="15">
@@ -36608,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="AP372" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36638,7 +36616,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH373" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI373" s="16"/>
@@ -36648,7 +36626,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL373" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM373" s="15">
@@ -36656,7 +36634,7 @@
         <v>0</v>
       </c>
       <c r="AP373" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36686,7 +36664,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH374" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI374" s="16"/>
@@ -36696,7 +36674,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL374" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM374" s="15">
@@ -36704,7 +36682,7 @@
         <v>0</v>
       </c>
       <c r="AP374" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36734,7 +36712,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH375" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI375" s="16"/>
@@ -36744,7 +36722,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL375" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM375" s="15">
@@ -36752,7 +36730,7 @@
         <v>0</v>
       </c>
       <c r="AP375" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36782,7 +36760,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH376" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI376" s="16"/>
@@ -36792,7 +36770,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL376" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM376" s="15">
@@ -36800,7 +36778,7 @@
         <v>0</v>
       </c>
       <c r="AP376" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36830,7 +36808,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH377" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI377" s="16"/>
@@ -36840,7 +36818,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL377" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM377" s="15">
@@ -36848,7 +36826,7 @@
         <v>0</v>
       </c>
       <c r="AP377" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36878,17 +36856,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH378" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI378" s="16"/>
       <c r="AJ378" s="16"/>
       <c r="AK378" s="16" t="e">
-        <f t="shared" si="80"/>
+        <f t="shared" ref="AK378:AK409" si="83">(2*AG378+AH378)*AJ378</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL378" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM378" s="15">
@@ -36896,7 +36874,7 @@
         <v>0</v>
       </c>
       <c r="AP378" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36926,17 +36904,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH379" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI379" s="16"/>
       <c r="AJ379" s="16"/>
       <c r="AK379" s="16" t="e">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL379" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM379" s="15">
@@ -36944,7 +36922,7 @@
         <v>0</v>
       </c>
       <c r="AP379" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -36974,17 +36952,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH380" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI380" s="16"/>
       <c r="AJ380" s="16"/>
       <c r="AK380" s="16" t="e">
-        <f t="shared" ref="AK380:AK411" si="83">(2*AG380+AH380)*AJ380</f>
+        <f t="shared" si="83"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL380" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM380" s="15">
@@ -36992,7 +36970,7 @@
         <v>0</v>
       </c>
       <c r="AP380" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37022,7 +37000,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH381" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI381" s="16"/>
@@ -37032,7 +37010,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL381" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM381" s="15">
@@ -37040,7 +37018,7 @@
         <v>0</v>
       </c>
       <c r="AP381" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37070,7 +37048,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH382" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI382" s="16"/>
@@ -37080,7 +37058,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL382" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM382" s="15">
@@ -37088,7 +37066,7 @@
         <v>0</v>
       </c>
       <c r="AP382" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37118,7 +37096,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH383" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI383" s="16"/>
@@ -37128,7 +37106,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL383" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM383" s="15">
@@ -37136,7 +37114,7 @@
         <v>0</v>
       </c>
       <c r="AP383" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37166,7 +37144,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH384" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI384" s="16"/>
@@ -37176,7 +37154,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL384" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM384" s="15">
@@ -37184,7 +37162,7 @@
         <v>0</v>
       </c>
       <c r="AP384" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37214,7 +37192,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH385" s="16" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI385" s="16"/>
@@ -37224,7 +37202,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL385" s="15">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AM385" s="15">
@@ -37232,7 +37210,7 @@
         <v>0</v>
       </c>
       <c r="AP385" s="17" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37258,11 +37236,11 @@
         <v>0</v>
       </c>
       <c r="AG386" s="15" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" ref="AG386:AG417" si="85">IF(G386&lt;52,0,0.7)+IF(G386&lt;34,0,0.7)+IF(G386&lt;1,0,0.7)+IF(P386&gt;14.56,0,1)+IF(R386&lt;9,0.5,0)+IF(R386&lt;33.8,0.5,0)+IF(R386&lt;50,0.5,0)+IF(R386&lt;80,0.5,0)+IF(V386&gt;0,1,0)+IF(AE386&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH386" s="16" t="e">
-        <f t="shared" ref="AH386:AH449" si="85">AG386+IF(X386&lt;1.35,0,1)+IF(Y386&lt;1.35,0,1)+AC386+AA386</f>
+        <f t="shared" ref="AH386:AH449" si="86">AG386+IF(X386&lt;1.35,0,1)+IF(Y386&lt;1.35,0,1)+AC386+AA386</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI386" s="16"/>
@@ -37272,7 +37250,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL386" s="15">
-        <f t="shared" ref="AL386:AL449" si="86">D386</f>
+        <f t="shared" ref="AL386:AL449" si="87">D386</f>
         <v>0</v>
       </c>
       <c r="AM386" s="15">
@@ -37280,7 +37258,7 @@
         <v>0</v>
       </c>
       <c r="AP386" s="17" t="e">
-        <f t="shared" ref="AP386:AP449" si="87">IF(AK386&gt;13.8,IF(Z386&lt;101,IF(Z386&lt;35,IF(Z386&lt;8,3,2),1),0),0)</f>
+        <f t="shared" ref="AP386:AP454" si="88">IF(AK386&gt;13.8,IF(Z386&lt;101,IF(Z386&lt;35,IF(Z386&lt;8,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37306,11 +37284,11 @@
         <v>0</v>
       </c>
       <c r="AG387" s="15" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH387" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI387" s="16"/>
@@ -37320,7 +37298,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL387" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM387" s="15">
@@ -37328,7 +37306,7 @@
         <v>0</v>
       </c>
       <c r="AP387" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37354,11 +37332,11 @@
         <v>0</v>
       </c>
       <c r="AG388" s="15" t="e">
-        <f t="shared" ref="AG388:AG419" si="88">IF(G388&lt;52,0,0.7)+IF(G388&lt;34,0,0.7)+IF(G388&lt;1,0,0.7)+IF(P388&gt;14.56,0,1)+IF(R388&lt;9,0.5,0)+IF(R388&lt;33.8,0.5,0)+IF(R388&lt;50,0.5,0)+IF(R388&lt;80,0.5,0)+IF(V388&gt;0,1,0)+IF(AE388&lt;10.56,0,1)</f>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH388" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI388" s="16"/>
@@ -37368,7 +37346,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL388" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM388" s="15">
@@ -37376,7 +37354,7 @@
         <v>0</v>
       </c>
       <c r="AP388" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37402,11 +37380,11 @@
         <v>0</v>
       </c>
       <c r="AG389" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH389" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI389" s="16"/>
@@ -37416,7 +37394,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL389" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM389" s="15">
@@ -37424,7 +37402,7 @@
         <v>0</v>
       </c>
       <c r="AP389" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37450,11 +37428,11 @@
         <v>0</v>
       </c>
       <c r="AG390" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH390" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI390" s="16"/>
@@ -37464,7 +37442,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL390" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM390" s="15">
@@ -37472,7 +37450,7 @@
         <v>0</v>
       </c>
       <c r="AP390" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37498,11 +37476,11 @@
         <v>0</v>
       </c>
       <c r="AG391" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH391" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI391" s="16"/>
@@ -37512,7 +37490,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL391" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM391" s="15">
@@ -37520,7 +37498,7 @@
         <v>0</v>
       </c>
       <c r="AP391" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37542,15 +37520,15 @@
         <v>1</v>
       </c>
       <c r="AC392" s="16">
-        <f t="shared" si="82"/>
+        <f t="shared" ref="AC392:AC423" si="89">IF(U393&gt;9,1,0)+U393/3</f>
         <v>0</v>
       </c>
       <c r="AG392" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH392" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI392" s="16"/>
@@ -37560,7 +37538,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL392" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM392" s="15">
@@ -37568,7 +37546,7 @@
         <v>0</v>
       </c>
       <c r="AP392" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37590,15 +37568,15 @@
         <v>1</v>
       </c>
       <c r="AC393" s="16">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="AG393" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH393" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI393" s="16"/>
@@ -37608,7 +37586,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL393" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM393" s="15">
@@ -37616,7 +37594,7 @@
         <v>0</v>
       </c>
       <c r="AP393" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37638,15 +37616,15 @@
         <v>1</v>
       </c>
       <c r="AC394" s="16">
-        <f t="shared" ref="AC394:AC425" si="89">IF(U395&gt;9,1,0)+U395/3</f>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="AG394" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH394" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI394" s="16"/>
@@ -37656,7 +37634,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL394" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM394" s="15">
@@ -37664,7 +37642,7 @@
         <v>0</v>
       </c>
       <c r="AP394" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37690,11 +37668,11 @@
         <v>0</v>
       </c>
       <c r="AG395" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH395" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI395" s="16"/>
@@ -37704,7 +37682,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL395" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM395" s="15">
@@ -37712,7 +37690,7 @@
         <v>0</v>
       </c>
       <c r="AP395" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37738,11 +37716,11 @@
         <v>0</v>
       </c>
       <c r="AG396" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH396" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI396" s="16"/>
@@ -37752,15 +37730,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL396" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM396" s="15">
-        <f t="shared" ref="AM396:AM457" si="92">B396</f>
+        <f t="shared" ref="AM396:AM455" si="92">B396</f>
         <v>0</v>
       </c>
       <c r="AP396" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37786,11 +37764,11 @@
         <v>0</v>
       </c>
       <c r="AG397" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH397" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI397" s="16"/>
@@ -37800,7 +37778,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL397" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM397" s="15">
@@ -37808,7 +37786,7 @@
         <v>0</v>
       </c>
       <c r="AP397" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37834,11 +37812,11 @@
         <v>0</v>
       </c>
       <c r="AG398" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH398" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI398" s="16"/>
@@ -37848,7 +37826,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL398" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM398" s="15">
@@ -37856,7 +37834,7 @@
         <v>0</v>
       </c>
       <c r="AP398" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37882,11 +37860,11 @@
         <v>0</v>
       </c>
       <c r="AG399" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH399" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI399" s="16"/>
@@ -37896,7 +37874,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL399" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM399" s="15">
@@ -37904,7 +37882,7 @@
         <v>0</v>
       </c>
       <c r="AP399" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37930,11 +37908,11 @@
         <v>0</v>
       </c>
       <c r="AG400" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH400" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI400" s="16"/>
@@ -37944,7 +37922,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL400" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM400" s="15">
@@ -37952,7 +37930,7 @@
         <v>0</v>
       </c>
       <c r="AP400" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -37978,11 +37956,11 @@
         <v>0</v>
       </c>
       <c r="AG401" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH401" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI401" s="16"/>
@@ -37992,7 +37970,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL401" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM401" s="15">
@@ -38000,7 +37978,7 @@
         <v>0</v>
       </c>
       <c r="AP401" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38026,11 +38004,11 @@
         <v>0</v>
       </c>
       <c r="AG402" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH402" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI402" s="16"/>
@@ -38040,7 +38018,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL402" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM402" s="15">
@@ -38048,7 +38026,7 @@
         <v>0</v>
       </c>
       <c r="AP402" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38074,11 +38052,11 @@
         <v>0</v>
       </c>
       <c r="AG403" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH403" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI403" s="16"/>
@@ -38088,7 +38066,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL403" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM403" s="15">
@@ -38096,7 +38074,7 @@
         <v>0</v>
       </c>
       <c r="AP403" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38122,11 +38100,11 @@
         <v>0</v>
       </c>
       <c r="AG404" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH404" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI404" s="16"/>
@@ -38136,7 +38114,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL404" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM404" s="15">
@@ -38144,7 +38122,7 @@
         <v>0</v>
       </c>
       <c r="AP404" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38170,11 +38148,11 @@
         <v>0</v>
       </c>
       <c r="AG405" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH405" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI405" s="16"/>
@@ -38184,7 +38162,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL405" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM405" s="15">
@@ -38192,7 +38170,7 @@
         <v>0</v>
       </c>
       <c r="AP405" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38218,11 +38196,11 @@
         <v>0</v>
       </c>
       <c r="AG406" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH406" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI406" s="16"/>
@@ -38232,7 +38210,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL406" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM406" s="15">
@@ -38240,7 +38218,7 @@
         <v>0</v>
       </c>
       <c r="AP406" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38266,11 +38244,11 @@
         <v>0</v>
       </c>
       <c r="AG407" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH407" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI407" s="16"/>
@@ -38280,7 +38258,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL407" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM407" s="15">
@@ -38288,7 +38266,7 @@
         <v>0</v>
       </c>
       <c r="AP407" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38314,11 +38292,11 @@
         <v>0</v>
       </c>
       <c r="AG408" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH408" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI408" s="16"/>
@@ -38328,7 +38306,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL408" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM408" s="15">
@@ -38336,7 +38314,7 @@
         <v>0</v>
       </c>
       <c r="AP408" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38362,11 +38340,11 @@
         <v>0</v>
       </c>
       <c r="AG409" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH409" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI409" s="16"/>
@@ -38376,7 +38354,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL409" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM409" s="15">
@@ -38384,7 +38362,7 @@
         <v>0</v>
       </c>
       <c r="AP409" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38410,21 +38388,21 @@
         <v>0</v>
       </c>
       <c r="AG410" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH410" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI410" s="16"/>
       <c r="AJ410" s="16"/>
       <c r="AK410" s="16" t="e">
-        <f t="shared" si="83"/>
+        <f t="shared" ref="AK410:AK441" si="93">(2*AG410+AH410)*AJ410</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL410" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM410" s="15">
@@ -38432,7 +38410,7 @@
         <v>0</v>
       </c>
       <c r="AP410" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38458,21 +38436,21 @@
         <v>0</v>
       </c>
       <c r="AG411" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH411" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI411" s="16"/>
       <c r="AJ411" s="16"/>
       <c r="AK411" s="16" t="e">
-        <f t="shared" si="83"/>
+        <f t="shared" si="93"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL411" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM411" s="15">
@@ -38480,7 +38458,7 @@
         <v>0</v>
       </c>
       <c r="AP411" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38506,21 +38484,21 @@
         <v>0</v>
       </c>
       <c r="AG412" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH412" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI412" s="16"/>
       <c r="AJ412" s="16"/>
       <c r="AK412" s="16" t="e">
-        <f t="shared" ref="AK412:AK443" si="93">(2*AG412+AH412)*AJ412</f>
+        <f t="shared" si="93"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL412" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM412" s="15">
@@ -38528,7 +38506,7 @@
         <v>0</v>
       </c>
       <c r="AP412" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38554,11 +38532,11 @@
         <v>0</v>
       </c>
       <c r="AG413" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH413" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI413" s="16"/>
@@ -38568,7 +38546,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL413" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM413" s="15">
@@ -38576,7 +38554,7 @@
         <v>0</v>
       </c>
       <c r="AP413" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38602,11 +38580,11 @@
         <v>0</v>
       </c>
       <c r="AG414" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH414" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI414" s="16"/>
@@ -38616,7 +38594,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL414" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM414" s="15">
@@ -38624,7 +38602,7 @@
         <v>0</v>
       </c>
       <c r="AP414" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38650,11 +38628,11 @@
         <v>0</v>
       </c>
       <c r="AG415" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH415" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI415" s="16"/>
@@ -38664,7 +38642,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL415" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM415" s="15">
@@ -38672,7 +38650,7 @@
         <v>0</v>
       </c>
       <c r="AP415" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38698,11 +38676,11 @@
         <v>0</v>
       </c>
       <c r="AG416" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH416" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI416" s="16"/>
@@ -38712,7 +38690,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL416" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM416" s="15">
@@ -38720,7 +38698,7 @@
         <v>0</v>
       </c>
       <c r="AP416" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38746,11 +38724,11 @@
         <v>0</v>
       </c>
       <c r="AG417" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="85"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH417" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI417" s="16"/>
@@ -38760,7 +38738,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL417" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM417" s="15">
@@ -38768,7 +38746,7 @@
         <v>0</v>
       </c>
       <c r="AP417" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38794,11 +38772,11 @@
         <v>0</v>
       </c>
       <c r="AG418" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" ref="AG418:AG451" si="94">IF(G418&lt;52,0,0.7)+IF(G418&lt;34,0,0.7)+IF(G418&lt;1,0,0.7)+IF(P418&gt;14.56,0,1)+IF(R418&lt;9,0.5,0)+IF(R418&lt;33.8,0.5,0)+IF(R418&lt;50,0.5,0)+IF(R418&lt;80,0.5,0)+IF(V418&gt;0,1,0)+IF(AE418&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH418" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI418" s="16"/>
@@ -38808,7 +38786,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL418" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM418" s="15">
@@ -38816,7 +38794,7 @@
         <v>0</v>
       </c>
       <c r="AP418" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38842,11 +38820,11 @@
         <v>0</v>
       </c>
       <c r="AG419" s="15" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="94"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH419" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI419" s="16"/>
@@ -38856,7 +38834,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL419" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM419" s="15">
@@ -38864,7 +38842,7 @@
         <v>0</v>
       </c>
       <c r="AP419" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38890,11 +38868,11 @@
         <v>0</v>
       </c>
       <c r="AG420" s="15" t="e">
-        <f t="shared" ref="AG420:AG453" si="94">IF(G420&lt;52,0,0.7)+IF(G420&lt;34,0,0.7)+IF(G420&lt;1,0,0.7)+IF(P420&gt;14.56,0,1)+IF(R420&lt;9,0.5,0)+IF(R420&lt;33.8,0.5,0)+IF(R420&lt;50,0.5,0)+IF(R420&lt;80,0.5,0)+IF(V420&gt;0,1,0)+IF(AE420&lt;10.56,0,1)</f>
+        <f t="shared" si="94"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH420" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI420" s="16"/>
@@ -38904,7 +38882,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL420" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM420" s="15">
@@ -38912,7 +38890,7 @@
         <v>0</v>
       </c>
       <c r="AP420" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38942,7 +38920,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH421" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI421" s="16"/>
@@ -38952,7 +38930,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL421" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM421" s="15">
@@ -38960,7 +38938,7 @@
         <v>0</v>
       </c>
       <c r="AP421" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -38990,7 +38968,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH422" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI422" s="16"/>
@@ -39000,7 +38978,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL422" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM422" s="15">
@@ -39008,7 +38986,7 @@
         <v>0</v>
       </c>
       <c r="AP422" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39038,7 +39016,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH423" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI423" s="16"/>
@@ -39048,7 +39026,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL423" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM423" s="15">
@@ -39056,7 +39034,7 @@
         <v>0</v>
       </c>
       <c r="AP423" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39078,7 +39056,7 @@
         <v>1</v>
       </c>
       <c r="AC424" s="16">
-        <f t="shared" si="89"/>
+        <f t="shared" ref="AC424:AC449" si="95">IF(U425&gt;9,1,0)+U425/3</f>
         <v>0</v>
       </c>
       <c r="AG424" s="15" t="e">
@@ -39086,7 +39064,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH424" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI424" s="16"/>
@@ -39096,7 +39074,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL424" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM424" s="15">
@@ -39104,7 +39082,7 @@
         <v>0</v>
       </c>
       <c r="AP424" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39126,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="AC425" s="16">
-        <f t="shared" si="89"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="AG425" s="15" t="e">
@@ -39134,7 +39112,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH425" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI425" s="16"/>
@@ -39144,7 +39122,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL425" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM425" s="15">
@@ -39152,7 +39130,7 @@
         <v>0</v>
       </c>
       <c r="AP425" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39174,7 +39152,7 @@
         <v>1</v>
       </c>
       <c r="AC426" s="16">
-        <f t="shared" ref="AC426:AC451" si="95">IF(U427&gt;9,1,0)+U427/3</f>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="AG426" s="15" t="e">
@@ -39182,7 +39160,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH426" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI426" s="16"/>
@@ -39192,7 +39170,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL426" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM426" s="15">
@@ -39200,7 +39178,7 @@
         <v>0</v>
       </c>
       <c r="AP426" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39230,7 +39208,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH427" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI427" s="16"/>
@@ -39240,7 +39218,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL427" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM427" s="15">
@@ -39248,7 +39226,7 @@
         <v>0</v>
       </c>
       <c r="AP427" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39278,7 +39256,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH428" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI428" s="16"/>
@@ -39288,7 +39266,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL428" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM428" s="15">
@@ -39296,7 +39274,7 @@
         <v>0</v>
       </c>
       <c r="AP428" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39326,7 +39304,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH429" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI429" s="16"/>
@@ -39336,7 +39314,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL429" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM429" s="15">
@@ -39344,7 +39322,7 @@
         <v>0</v>
       </c>
       <c r="AP429" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39374,7 +39352,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH430" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI430" s="16"/>
@@ -39384,7 +39362,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL430" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM430" s="15">
@@ -39392,7 +39370,7 @@
         <v>0</v>
       </c>
       <c r="AP430" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39422,7 +39400,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH431" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI431" s="16"/>
@@ -39432,7 +39410,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL431" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM431" s="15">
@@ -39440,7 +39418,7 @@
         <v>0</v>
       </c>
       <c r="AP431" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39470,7 +39448,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH432" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI432" s="16"/>
@@ -39480,7 +39458,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL432" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM432" s="15">
@@ -39488,7 +39466,7 @@
         <v>0</v>
       </c>
       <c r="AP432" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39518,7 +39496,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH433" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI433" s="16"/>
@@ -39528,7 +39506,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL433" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM433" s="15">
@@ -39536,7 +39514,7 @@
         <v>0</v>
       </c>
       <c r="AP433" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39566,7 +39544,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH434" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI434" s="16"/>
@@ -39576,7 +39554,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL434" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM434" s="15">
@@ -39584,7 +39562,7 @@
         <v>0</v>
       </c>
       <c r="AP434" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39614,7 +39592,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH435" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI435" s="16"/>
@@ -39624,7 +39602,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL435" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM435" s="15">
@@ -39632,7 +39610,7 @@
         <v>0</v>
       </c>
       <c r="AP435" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39662,7 +39640,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH436" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI436" s="16"/>
@@ -39672,7 +39650,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL436" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM436" s="15">
@@ -39680,7 +39658,7 @@
         <v>0</v>
       </c>
       <c r="AP436" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39710,7 +39688,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH437" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI437" s="16"/>
@@ -39720,7 +39698,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL437" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM437" s="15">
@@ -39728,7 +39706,7 @@
         <v>0</v>
       </c>
       <c r="AP437" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39758,7 +39736,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH438" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI438" s="16"/>
@@ -39768,7 +39746,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL438" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM438" s="15">
@@ -39776,7 +39754,7 @@
         <v>0</v>
       </c>
       <c r="AP438" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39806,7 +39784,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH439" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI439" s="16"/>
@@ -39816,7 +39794,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL439" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM439" s="15">
@@ -39824,7 +39802,7 @@
         <v>0</v>
       </c>
       <c r="AP439" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39854,7 +39832,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH440" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI440" s="16"/>
@@ -39864,7 +39842,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL440" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM440" s="15">
@@ -39872,7 +39850,7 @@
         <v>0</v>
       </c>
       <c r="AP440" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39902,7 +39880,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH441" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI441" s="16"/>
@@ -39912,7 +39890,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL441" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM441" s="15">
@@ -39920,7 +39898,7 @@
         <v>0</v>
       </c>
       <c r="AP441" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39950,17 +39928,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH442" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI442" s="16"/>
       <c r="AJ442" s="16"/>
       <c r="AK442" s="16" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" ref="AK442:AK473" si="96">(2*AG442+AH442)*AJ442</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL442" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM442" s="15">
@@ -39968,7 +39946,7 @@
         <v>0</v>
       </c>
       <c r="AP442" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -39998,17 +39976,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH443" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI443" s="16"/>
       <c r="AJ443" s="16"/>
       <c r="AK443" s="16" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL443" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM443" s="15">
@@ -40016,7 +39994,7 @@
         <v>0</v>
       </c>
       <c r="AP443" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40046,17 +40024,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH444" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI444" s="16"/>
       <c r="AJ444" s="16"/>
       <c r="AK444" s="16" t="e">
-        <f t="shared" ref="AK444:AK475" si="96">(2*AG444+AH444)*AJ444</f>
+        <f t="shared" si="96"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL444" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM444" s="15">
@@ -40064,7 +40042,7 @@
         <v>0</v>
       </c>
       <c r="AP444" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40094,7 +40072,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH445" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI445" s="16"/>
@@ -40104,7 +40082,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL445" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM445" s="15">
@@ -40112,7 +40090,7 @@
         <v>0</v>
       </c>
       <c r="AP445" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40142,7 +40120,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH446" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI446" s="16"/>
@@ -40152,7 +40130,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL446" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM446" s="15">
@@ -40160,7 +40138,7 @@
         <v>0</v>
       </c>
       <c r="AP446" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40190,7 +40168,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH447" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI447" s="16"/>
@@ -40200,7 +40178,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL447" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM447" s="15">
@@ -40208,7 +40186,7 @@
         <v>0</v>
       </c>
       <c r="AP447" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40223,10 +40201,10 @@
       </c>
       <c r="R448" s="111"/>
       <c r="S448" s="118">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA448" s="2">
-        <f t="shared" si="84"/>
+        <f>IF(X448&lt;50,IF(Y448&gt;(2.3*X448),0,1),1)-IF(Z448&gt;Y448,1.5,0)</f>
         <v>1</v>
       </c>
       <c r="AC448" s="16">
@@ -40238,7 +40216,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH448" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI448" s="16"/>
@@ -40248,7 +40226,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL448" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM448" s="15">
@@ -40256,7 +40234,7 @@
         <v>0</v>
       </c>
       <c r="AP448" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40271,10 +40249,10 @@
       </c>
       <c r="R449" s="111"/>
       <c r="S449" s="118">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA449" s="2">
-        <f t="shared" si="84"/>
+        <f>IF(X449&lt;50,IF(Y449&gt;(2.3*X449),0,1),1)-IF(Z449&gt;Y449,1.5,0)</f>
         <v>1</v>
       </c>
       <c r="AC449" s="16">
@@ -40286,7 +40264,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH449" s="16" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI449" s="16"/>
@@ -40296,7 +40274,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AL449" s="15">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AM449" s="15">
@@ -40304,7 +40282,7 @@
         <v>0</v>
       </c>
       <c r="AP449" s="17" t="e">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40318,15 +40296,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R450" s="111"/>
-      <c r="S450" s="118">
-        <v>0</v>
-      </c>
       <c r="AA450" s="2">
-        <f>IF(X450&lt;50,IF(Y450&gt;(2.3*X450),0,1),1)-IF(Z450&gt;Y450,1.5,0)</f>
+        <f t="shared" ref="AA450:AA455" si="97">IF(X450&lt;50,IF(Y450&gt;(2.3*X450),0,1),1)</f>
         <v>1</v>
       </c>
       <c r="AC450" s="16">
-        <f t="shared" si="95"/>
+        <f>IF(AB450&gt;6.2,1,0)+AB450/5</f>
         <v>0</v>
       </c>
       <c r="AG450" s="15" t="e">
@@ -40334,17 +40309,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH450" s="16" t="e">
-        <f t="shared" ref="AH450:AH513" si="97">AG450+IF(X450&lt;1.35,0,1)+IF(Y450&lt;1.35,0,1)+AC450+AA450</f>
+        <f t="shared" ref="AH450:AH513" si="98">AG450+IF(X450&lt;1.35,0,1)+IF(Y450&lt;1.35,0,1)+AC450+AA450</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI450" s="16"/>
       <c r="AJ450" s="16"/>
       <c r="AK450" s="16" t="e">
-        <f t="shared" si="96"/>
+        <f t="shared" ref="AK450:AK455" si="99">AG450+AH450*1.4</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL450" s="15">
-        <f t="shared" ref="AL450:AL457" si="98">D450</f>
+        <f t="shared" ref="AL450:AL455" si="100">D450</f>
         <v>0</v>
       </c>
       <c r="AM450" s="15">
@@ -40352,7 +40327,7 @@
         <v>0</v>
       </c>
       <c r="AP450" s="17" t="e">
-        <f t="shared" ref="AP450:AP456" si="99">IF(AK450&gt;13.8,IF(Z450&lt;101,IF(Z450&lt;35,IF(Z450&lt;8,3,2),1),0),0)</f>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40366,15 +40341,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R451" s="111"/>
-      <c r="S451" s="118">
-        <v>0</v>
-      </c>
       <c r="AA451" s="2">
-        <f>IF(X451&lt;50,IF(Y451&gt;(2.3*X451),0,1),1)-IF(Z451&gt;Y451,1.5,0)</f>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="AC451" s="16">
-        <f t="shared" si="95"/>
+        <f>IF(AB451&gt;6.2,1,0)+AB451/5</f>
         <v>0</v>
       </c>
       <c r="AG451" s="15" t="e">
@@ -40382,17 +40354,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH451" s="16" t="e">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI451" s="16"/>
       <c r="AJ451" s="16"/>
       <c r="AK451" s="16" t="e">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL451" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="AM451" s="15">
@@ -40400,7 +40372,7 @@
         <v>0</v>
       </c>
       <c r="AP451" s="17" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40415,7 +40387,7 @@
       </c>
       <c r="R452" s="111"/>
       <c r="AA452" s="2">
-        <f t="shared" ref="AA452:AA457" si="100">IF(X452&lt;50,IF(Y452&gt;(2.3*X452),0,1),1)</f>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="AC452" s="16">
@@ -40423,21 +40395,21 @@
         <v>0</v>
       </c>
       <c r="AG452" s="15" t="e">
-        <f t="shared" si="94"/>
+        <f>IF(G452&lt;52,0,0.7)+IF(G452&lt;34,0,0.7)+IF(G452&lt;1,0,0.7)+IF(P452&gt;14.56,0,1)+IF(Q452&gt;33.8,0,1)+IF(V452&gt;0,1,0)+IF(AE452&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH452" s="16" t="e">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI452" s="16"/>
       <c r="AJ452" s="16"/>
       <c r="AK452" s="16" t="e">
-        <f t="shared" ref="AK452:AK457" si="101">AG452+AH452*1.4</f>
+        <f t="shared" si="99"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL452" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="AM452" s="15">
@@ -40445,7 +40417,7 @@
         <v>0</v>
       </c>
       <c r="AP452" s="17" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40460,7 +40432,7 @@
       </c>
       <c r="R453" s="111"/>
       <c r="AA453" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="AC453" s="16">
@@ -40468,21 +40440,21 @@
         <v>0</v>
       </c>
       <c r="AG453" s="15" t="e">
-        <f t="shared" si="94"/>
+        <f>IF(G453&lt;52,0,0.7)+IF(G453&lt;34,0,0.7)+IF(G453&lt;1,0,0.7)+IF(P453&gt;14.56,0,1)+IF(Q453&gt;33.8,0,1)+IF(V453&gt;0,1,0)+IF(AE453&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH453" s="16" t="e">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI453" s="16"/>
       <c r="AJ453" s="16"/>
       <c r="AK453" s="16" t="e">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL453" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="AM453" s="15">
@@ -40490,7 +40462,7 @@
         <v>0</v>
       </c>
       <c r="AP453" s="17" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40505,7 +40477,7 @@
       </c>
       <c r="R454" s="111"/>
       <c r="AA454" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="AC454" s="16">
@@ -40517,17 +40489,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH454" s="16" t="e">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI454" s="16"/>
       <c r="AJ454" s="16"/>
       <c r="AK454" s="16" t="e">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL454" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="AM454" s="15">
@@ -40535,7 +40507,7 @@
         <v>0</v>
       </c>
       <c r="AP454" s="17" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="88"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40550,121 +40522,37 @@
       </c>
       <c r="R455" s="111"/>
       <c r="AA455" s="2">
-        <f t="shared" si="100"/>
-        <v>1</v>
-      </c>
-      <c r="AC455" s="16">
-        <f>IF(AB455&gt;6.2,1,0)+AB455/5</f>
-        <v>0</v>
+        <f t="shared" si="97"/>
+        <v>1</v>
       </c>
       <c r="AG455" s="15" t="e">
         <f>IF(G455&lt;52,0,0.7)+IF(G455&lt;34,0,0.7)+IF(G455&lt;1,0,0.7)+IF(P455&gt;14.56,0,1)+IF(Q455&gt;33.8,0,1)+IF(V455&gt;0,1,0)+IF(AE455&lt;10.56,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH455" s="16" t="e">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI455" s="16"/>
       <c r="AJ455" s="16"/>
       <c r="AK455" s="16" t="e">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL455" s="15">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="AM455" s="15">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AP455" s="17" t="e">
-        <f t="shared" si="99"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="456" spans="7:42">
-      <c r="G456" s="16" t="e">
-        <f t="shared" si="90"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P456" s="16" t="e">
-        <f t="shared" si="91"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="R456" s="111"/>
-      <c r="AA456" s="2">
-        <f t="shared" si="100"/>
-        <v>1</v>
-      </c>
-      <c r="AC456" s="16">
-        <f>IF(AB456&gt;6.2,1,0)+AB456/5</f>
-        <v>0</v>
-      </c>
-      <c r="AG456" s="15" t="e">
-        <f>IF(G456&lt;52,0,0.7)+IF(G456&lt;34,0,0.7)+IF(G456&lt;1,0,0.7)+IF(P456&gt;14.56,0,1)+IF(Q456&gt;33.8,0,1)+IF(V456&gt;0,1,0)+IF(AE456&lt;10.56,0,1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH456" s="16" t="e">
-        <f t="shared" si="97"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI456" s="16"/>
-      <c r="AJ456" s="16"/>
-      <c r="AK456" s="16" t="e">
-        <f t="shared" si="101"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL456" s="15">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AM456" s="15">
-        <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="AP456" s="17" t="e">
-        <f t="shared" si="99"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="457" spans="7:42">
-      <c r="G457" s="16" t="e">
-        <f t="shared" si="90"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P457" s="16" t="e">
-        <f t="shared" si="91"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="R457" s="111"/>
-      <c r="AA457" s="2">
-        <f t="shared" si="100"/>
-        <v>1</v>
-      </c>
-      <c r="AG457" s="15" t="e">
-        <f>IF(G457&lt;52,0,0.7)+IF(G457&lt;34,0,0.7)+IF(G457&lt;1,0,0.7)+IF(P457&gt;14.56,0,1)+IF(Q457&gt;33.8,0,1)+IF(V457&gt;0,1,0)+IF(AE457&lt;10.56,0,1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH457" s="16" t="e">
-        <f t="shared" si="97"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI457" s="16"/>
-      <c r="AJ457" s="16"/>
-      <c r="AK457" s="16" t="e">
-        <f t="shared" si="101"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL457" s="15">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AM457" s="15">
-        <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="458" spans="7:42">
       <c r="R458" s="111"/>
@@ -40693,34 +40581,28 @@
     <row r="466" spans="18:18">
       <c r="R466" s="111"/>
     </row>
-    <row r="467" spans="18:18">
-      <c r="R467" s="111"/>
-    </row>
-    <row r="468" spans="18:18">
-      <c r="R468" s="111"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D146">
+  <conditionalFormatting sqref="D2:D144">
     <cfRule type="containsText" dxfId="66" priority="37" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH(("neg"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G457">
+  <conditionalFormatting sqref="G2:G455">
     <cfRule type="cellIs" dxfId="65" priority="30" operator="lessThan">
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P457">
+  <conditionalFormatting sqref="P2:P455">
     <cfRule type="cellIs" dxfId="64" priority="31" operator="greaterThan">
       <formula>14.56</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q145">
+  <conditionalFormatting sqref="Q2:Q143">
     <cfRule type="cellIs" dxfId="63" priority="34" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R154">
+  <conditionalFormatting sqref="R1:R152">
     <cfRule type="cellIs" dxfId="62" priority="26" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
@@ -40730,27 +40612,27 @@
       <formula>LEN(TRIM(X2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE146">
+  <conditionalFormatting sqref="AE2:AE144">
     <cfRule type="cellIs" dxfId="60" priority="29" operator="lessThan">
       <formula>10.56</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG457">
+  <conditionalFormatting sqref="AG2:AG455">
     <cfRule type="cellIs" dxfId="59" priority="35" operator="greaterThan">
       <formula>4.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AJ457">
+  <conditionalFormatting sqref="AH2:AJ455">
     <cfRule type="cellIs" dxfId="58" priority="33" operator="greaterThan">
       <formula>8.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK2:AK457">
+  <conditionalFormatting sqref="AK2:AK455">
     <cfRule type="cellIs" dxfId="57" priority="36" operator="greaterThan">
       <formula>13.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL457">
+  <conditionalFormatting sqref="AL2:AL455">
     <cfRule type="containsText" dxfId="56" priority="8" operator="containsText" text="Rec">
       <formula>NOT(ISERROR(SEARCH("Rec",AL2)))</formula>
     </cfRule>
@@ -40761,7 +40643,7 @@
       <formula>NOT(ISERROR(SEARCH("Pos",AL2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN166">
+  <conditionalFormatting sqref="AN2:AN164">
     <cfRule type="endsWith" dxfId="53" priority="13" operator="endsWith" text="4">
       <formula>RIGHT(AN2,LEN("4"))="4"</formula>
     </cfRule>
@@ -40793,7 +40675,7 @@
       <formula>RIGHT(AN2,LEN("5"))="5"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AP2:AP460">
+  <conditionalFormatting sqref="AP2:AP458">
     <cfRule type="containsText" dxfId="43" priority="1" operator="containsText" text="2">
       <formula>NOT(ISERROR(SEARCH("2",AP2)))</formula>
     </cfRule>
@@ -40810,13 +40692,13 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BB172"/>
+  <dimension ref="A1:BB166"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -52264,7 +52146,7 @@
         <v>27</v>
       </c>
       <c r="AO80" s="101">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AP80" s="17">
         <f t="shared" si="30"/>
@@ -52368,11 +52250,11 @@
         <v>-1</v>
       </c>
       <c r="AB81" s="101">
-        <v>3.3</v>
+        <v>3.77</v>
       </c>
       <c r="AC81" s="52">
         <f t="shared" si="25"/>
-        <v>1.0999999999999999</v>
+        <v>1.2566666666666666</v>
       </c>
       <c r="AD81" s="101">
         <v>100</v>
@@ -52389,13 +52271,13 @@
       </c>
       <c r="AH81" s="49">
         <f t="shared" si="27"/>
-        <v>2.2000000000000002</v>
+        <v>2.3566666666666665</v>
       </c>
       <c r="AI81" s="49"/>
       <c r="AJ81" s="49"/>
       <c r="AK81" s="49">
         <f t="shared" si="28"/>
-        <v>8.5</v>
+        <v>8.6566666666666663</v>
       </c>
       <c r="AL81" s="2">
         <f t="shared" si="29"/>
@@ -52408,7 +52290,7 @@
         <v>27</v>
       </c>
       <c r="AO81" s="101">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AP81" s="17">
         <f t="shared" si="30"/>
@@ -52538,7 +52420,8 @@
       <c r="AI82" s="49"/>
       <c r="AJ82" s="49"/>
       <c r="AK82" s="49">
-        <v>31</v>
+        <f t="shared" si="28"/>
+        <v>21.283333333333331</v>
       </c>
       <c r="AL82" s="2">
         <f t="shared" si="29"/>
@@ -52548,18 +52431,18 @@
         <v>365</v>
       </c>
       <c r="AN82" s="101">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO82" s="101">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AP82" s="17">
         <f t="shared" si="30"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ82" s="16">
         <f t="shared" si="31"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AR82" s="101"/>
       <c r="AS82" s="101"/>
@@ -56886,7 +56769,7 @@
       <c r="Y130" s="101"/>
       <c r="Z130" s="101"/>
       <c r="AA130" s="51">
-        <f t="shared" ref="AA130:AA166" si="46">IF(X130&lt;33,IF(Y130&gt;(1.1*X130),0,1),1)+IF(Y130&gt;(4*X130),-1,0)</f>
+        <f t="shared" ref="AA130:AA160" si="46">IF(X130&lt;33,IF(Y130&gt;(1.1*X130),0,1),1)+IF(Y130&gt;(4*X130),-1,0)</f>
         <v>1</v>
       </c>
       <c r="AB130" s="101"/>
@@ -56908,11 +56791,11 @@
       <c r="AI130" s="49"/>
       <c r="AJ130" s="49"/>
       <c r="AK130" s="49" t="e">
-        <f t="shared" ref="AK130:AK166" si="50">AG130*3+AH130</f>
+        <f t="shared" ref="AK130:AK160" si="50">AG130*3+AH130</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL130" s="2">
-        <f t="shared" ref="AL130:AL164" si="51">D130</f>
+        <f t="shared" ref="AL130:AL158" si="51">D130</f>
         <v>0</v>
       </c>
       <c r="AM130" s="2">
@@ -56922,7 +56805,7 @@
       <c r="AN130" s="101"/>
       <c r="AO130" s="101"/>
       <c r="AP130" s="17" t="e">
-        <f t="shared" ref="AP130:AP160" si="52">IF(AK130&gt;23,IF(Z130&lt;101,IF(Z130&lt;35,IF(Z130&lt;8,3,2),1),0),0)</f>
+        <f t="shared" ref="AP130:AP154" si="52">IF(AK130&gt;23,IF(Z130&lt;101,IF(Z130&lt;35,IF(Z130&lt;8,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ130" s="16" t="e">
@@ -58463,7 +58346,7 @@
         <v>0</v>
       </c>
       <c r="AM147" s="2">
-        <f t="shared" ref="AM147:AM164" si="56">B147</f>
+        <f t="shared" ref="AM147:AM158" si="56">B147</f>
         <v>0</v>
       </c>
       <c r="AN147" s="101"/>
@@ -59197,7 +59080,7 @@
       <c r="AN155" s="101"/>
       <c r="AO155" s="101"/>
       <c r="AP155" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f>IF(AK155&gt;24.5,IF(Z155&lt;50,IF(Z155&lt;6,2,1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ155" s="16" t="e">
@@ -59288,7 +59171,7 @@
       <c r="AN156" s="101"/>
       <c r="AO156" s="101"/>
       <c r="AP156" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f>IF(AK156&gt;24.5,IF(Z156&lt;50,IF(Z156&lt;6,2,1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ156" s="16" t="e">
@@ -59347,10 +59230,7 @@
         <v>1</v>
       </c>
       <c r="AB157" s="101"/>
-      <c r="AC157" s="52">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
+      <c r="AC157" s="101"/>
       <c r="AD157" s="101"/>
       <c r="AE157" s="101"/>
       <c r="AF157" s="101"/>
@@ -59379,7 +59259,7 @@
       <c r="AN157" s="101"/>
       <c r="AO157" s="101"/>
       <c r="AP157" s="17" t="e">
-        <f t="shared" si="52"/>
+        <f>IF(AK157&gt;24.5,IF(Z157&lt;50,IF(Z157&lt;6,2,1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ157" s="16" t="e">
@@ -59438,10 +59318,7 @@
         <v>1</v>
       </c>
       <c r="AB158" s="101"/>
-      <c r="AC158" s="52">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
+      <c r="AC158" s="101"/>
       <c r="AD158" s="101"/>
       <c r="AE158" s="101"/>
       <c r="AF158" s="101"/>
@@ -59469,14 +59346,8 @@
       </c>
       <c r="AN158" s="101"/>
       <c r="AO158" s="101"/>
-      <c r="AP158" s="17" t="e">
-        <f t="shared" si="52"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AQ158" s="16" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AP158" s="101"/>
+      <c r="AQ158" s="101"/>
       <c r="AR158" s="101"/>
       <c r="AS158" s="101"/>
       <c r="AT158" s="101"/>
@@ -59529,10 +59400,7 @@
         <v>1</v>
       </c>
       <c r="AB159" s="101"/>
-      <c r="AC159" s="52">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
+      <c r="AC159" s="101"/>
       <c r="AD159" s="101"/>
       <c r="AE159" s="101"/>
       <c r="AF159" s="101"/>
@@ -59550,24 +59418,12 @@
         <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL159" s="2">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AM159" s="2">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
+      <c r="AL159" s="101"/>
+      <c r="AM159" s="101"/>
       <c r="AN159" s="101"/>
       <c r="AO159" s="101"/>
-      <c r="AP159" s="17" t="e">
-        <f t="shared" si="52"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AQ159" s="16" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AP159" s="101"/>
+      <c r="AQ159" s="101"/>
       <c r="AR159" s="101"/>
       <c r="AS159" s="101"/>
       <c r="AT159" s="101"/>
@@ -59620,10 +59476,7 @@
         <v>1</v>
       </c>
       <c r="AB160" s="101"/>
-      <c r="AC160" s="52">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
+      <c r="AC160" s="101"/>
       <c r="AD160" s="101"/>
       <c r="AE160" s="101"/>
       <c r="AF160" s="101"/>
@@ -59641,24 +59494,12 @@
         <f t="shared" si="50"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL160" s="2">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AM160" s="2">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
+      <c r="AL160" s="101"/>
+      <c r="AM160" s="101"/>
       <c r="AN160" s="101"/>
       <c r="AO160" s="101"/>
-      <c r="AP160" s="17" t="e">
-        <f t="shared" si="52"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AQ160" s="16" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AP160" s="101"/>
+      <c r="AQ160" s="101"/>
       <c r="AR160" s="101"/>
       <c r="AS160" s="101"/>
       <c r="AT160" s="101"/>
@@ -59696,9 +59537,7 @@
       </c>
       <c r="Q161" s="101"/>
       <c r="R161" s="101"/>
-      <c r="S161" s="47">
-        <v>5</v>
-      </c>
+      <c r="S161" s="101"/>
       <c r="T161" s="101"/>
       <c r="U161" s="101"/>
       <c r="V161" s="101"/>
@@ -59706,50 +59545,23 @@
       <c r="X161" s="101"/>
       <c r="Y161" s="101"/>
       <c r="Z161" s="101"/>
-      <c r="AA161" s="51">
-        <f t="shared" si="46"/>
-        <v>1</v>
-      </c>
+      <c r="AA161" s="101"/>
       <c r="AB161" s="101"/>
-      <c r="AC161" s="52">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
+      <c r="AC161" s="101"/>
       <c r="AD161" s="101"/>
       <c r="AE161" s="101"/>
       <c r="AF161" s="101"/>
-      <c r="AG161" s="49" t="e">
-        <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH161" s="49" t="e">
-        <f t="shared" si="49"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI161" s="49"/>
-      <c r="AJ161" s="49"/>
-      <c r="AK161" s="49" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL161" s="2">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AM161" s="2">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
+      <c r="AG161" s="101"/>
+      <c r="AH161" s="101"/>
+      <c r="AI161" s="101"/>
+      <c r="AJ161" s="101"/>
+      <c r="AK161" s="101"/>
+      <c r="AL161" s="101"/>
+      <c r="AM161" s="101"/>
       <c r="AN161" s="101"/>
       <c r="AO161" s="101"/>
-      <c r="AP161" s="17" t="e">
-        <f>IF(AK161&gt;24.5,IF(Z161&lt;50,IF(Z161&lt;6,2,1),0),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AQ161" s="16" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AP161" s="101"/>
+      <c r="AQ161" s="101"/>
       <c r="AR161" s="101"/>
       <c r="AS161" s="101"/>
       <c r="AT161" s="101"/>
@@ -59787,9 +59599,7 @@
       </c>
       <c r="Q162" s="101"/>
       <c r="R162" s="101"/>
-      <c r="S162" s="47">
-        <v>5</v>
-      </c>
+      <c r="S162" s="101"/>
       <c r="T162" s="101"/>
       <c r="U162" s="101"/>
       <c r="V162" s="101"/>
@@ -59797,50 +59607,23 @@
       <c r="X162" s="101"/>
       <c r="Y162" s="101"/>
       <c r="Z162" s="101"/>
-      <c r="AA162" s="51">
-        <f t="shared" si="46"/>
-        <v>1</v>
-      </c>
+      <c r="AA162" s="101"/>
       <c r="AB162" s="101"/>
-      <c r="AC162" s="52">
-        <f t="shared" ref="AC162:AC193" si="57">IF(AB162&gt;9,1,0)+AB162/3</f>
-        <v>0</v>
-      </c>
+      <c r="AC162" s="101"/>
       <c r="AD162" s="101"/>
       <c r="AE162" s="101"/>
       <c r="AF162" s="101"/>
-      <c r="AG162" s="49" t="e">
-        <f t="shared" ref="AG162:AG193" si="58">IF(G162&lt;0,0,1.2)+IF(G162&lt;14,0,0.9)+IF(P162&lt;0,0.7,0)+IF(P162&lt;6.5,1,0)+IF(P162&lt;23,1,0)+IF(R162&gt;88,0,1)+IF(S162=5,0,S162)+IF(AD162&lt;20,0,1)+IF(AE162&lt;14,0,1)+IF(AF162&lt;26,0,1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH162" s="49" t="e">
-        <f t="shared" ref="AH162:AH193" si="59">AG162+IF(AG162&gt;6,1,0)+IF(X162&lt;17,0,1)+IF(Y162&lt;11,0,1)+IF(Z162&lt;1.35,0,1)+AC162+AA162</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI162" s="49"/>
-      <c r="AJ162" s="49"/>
-      <c r="AK162" s="49" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL162" s="2">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AM162" s="2">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
+      <c r="AG162" s="101"/>
+      <c r="AH162" s="101"/>
+      <c r="AI162" s="101"/>
+      <c r="AJ162" s="101"/>
+      <c r="AK162" s="101"/>
+      <c r="AL162" s="101"/>
+      <c r="AM162" s="101"/>
       <c r="AN162" s="101"/>
       <c r="AO162" s="101"/>
-      <c r="AP162" s="17" t="e">
-        <f>IF(AK162&gt;24.5,IF(Z162&lt;50,IF(Z162&lt;6,2,1),0),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AQ162" s="16" t="e">
-        <f t="shared" ref="AQ162:AQ193" si="60">IF(AP162&gt;0,IF(AB162&gt;10,(AB162/Z162),10/Z162),0)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AP162" s="101"/>
+      <c r="AQ162" s="101"/>
       <c r="AR162" s="101"/>
       <c r="AS162" s="101"/>
       <c r="AT162" s="101"/>
@@ -59878,9 +59661,7 @@
       </c>
       <c r="Q163" s="101"/>
       <c r="R163" s="101"/>
-      <c r="S163" s="47">
-        <v>5</v>
-      </c>
+      <c r="S163" s="101"/>
       <c r="T163" s="101"/>
       <c r="U163" s="101"/>
       <c r="V163" s="101"/>
@@ -59888,47 +59669,23 @@
       <c r="X163" s="101"/>
       <c r="Y163" s="101"/>
       <c r="Z163" s="101"/>
-      <c r="AA163" s="51">
-        <f t="shared" si="46"/>
-        <v>1</v>
-      </c>
+      <c r="AA163" s="101"/>
       <c r="AB163" s="101"/>
       <c r="AC163" s="101"/>
       <c r="AD163" s="101"/>
       <c r="AE163" s="101"/>
       <c r="AF163" s="101"/>
-      <c r="AG163" s="49" t="e">
-        <f t="shared" si="58"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH163" s="49" t="e">
-        <f t="shared" si="59"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI163" s="49"/>
-      <c r="AJ163" s="49"/>
-      <c r="AK163" s="49" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL163" s="2">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AM163" s="2">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
+      <c r="AG163" s="101"/>
+      <c r="AH163" s="101"/>
+      <c r="AI163" s="101"/>
+      <c r="AJ163" s="101"/>
+      <c r="AK163" s="101"/>
+      <c r="AL163" s="101"/>
+      <c r="AM163" s="101"/>
       <c r="AN163" s="101"/>
       <c r="AO163" s="101"/>
-      <c r="AP163" s="17" t="e">
-        <f>IF(AK163&gt;24.5,IF(Z163&lt;50,IF(Z163&lt;6,2,1),0),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AQ163" s="16" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AP163" s="101"/>
+      <c r="AQ163" s="101"/>
       <c r="AR163" s="101"/>
       <c r="AS163" s="101"/>
       <c r="AT163" s="101"/>
@@ -59966,9 +59723,7 @@
       </c>
       <c r="Q164" s="101"/>
       <c r="R164" s="101"/>
-      <c r="S164" s="47">
-        <v>5</v>
-      </c>
+      <c r="S164" s="101"/>
       <c r="T164" s="101"/>
       <c r="U164" s="101"/>
       <c r="V164" s="101"/>
@@ -59976,37 +59731,19 @@
       <c r="X164" s="101"/>
       <c r="Y164" s="101"/>
       <c r="Z164" s="101"/>
-      <c r="AA164" s="51">
-        <f t="shared" si="46"/>
-        <v>1</v>
-      </c>
+      <c r="AA164" s="101"/>
       <c r="AB164" s="101"/>
       <c r="AC164" s="101"/>
       <c r="AD164" s="101"/>
       <c r="AE164" s="101"/>
       <c r="AF164" s="101"/>
-      <c r="AG164" s="49" t="e">
-        <f t="shared" si="58"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH164" s="49" t="e">
-        <f t="shared" si="59"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI164" s="49"/>
-      <c r="AJ164" s="49"/>
-      <c r="AK164" s="49" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL164" s="2">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AM164" s="2">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
+      <c r="AG164" s="101"/>
+      <c r="AH164" s="101"/>
+      <c r="AI164" s="101"/>
+      <c r="AJ164" s="101"/>
+      <c r="AK164" s="101"/>
+      <c r="AL164" s="101"/>
+      <c r="AM164" s="101"/>
       <c r="AN164" s="101"/>
       <c r="AO164" s="101"/>
       <c r="AP164" s="101"/>
@@ -60048,9 +59785,7 @@
       </c>
       <c r="Q165" s="101"/>
       <c r="R165" s="101"/>
-      <c r="S165" s="47">
-        <v>5</v>
-      </c>
+      <c r="S165" s="101"/>
       <c r="T165" s="101"/>
       <c r="U165" s="101"/>
       <c r="V165" s="101"/>
@@ -60058,29 +59793,17 @@
       <c r="X165" s="101"/>
       <c r="Y165" s="101"/>
       <c r="Z165" s="101"/>
-      <c r="AA165" s="51">
-        <f t="shared" si="46"/>
-        <v>1</v>
-      </c>
+      <c r="AA165" s="101"/>
       <c r="AB165" s="101"/>
       <c r="AC165" s="101"/>
       <c r="AD165" s="101"/>
       <c r="AE165" s="101"/>
       <c r="AF165" s="101"/>
-      <c r="AG165" s="49" t="e">
-        <f t="shared" si="58"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH165" s="49" t="e">
-        <f t="shared" si="59"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI165" s="49"/>
-      <c r="AJ165" s="49"/>
-      <c r="AK165" s="49" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AG165" s="101"/>
+      <c r="AH165" s="101"/>
+      <c r="AI165" s="101"/>
+      <c r="AJ165" s="101"/>
+      <c r="AK165" s="101"/>
       <c r="AL165" s="101"/>
       <c r="AM165" s="101"/>
       <c r="AN165" s="101"/>
@@ -60124,9 +59847,7 @@
       </c>
       <c r="Q166" s="101"/>
       <c r="R166" s="101"/>
-      <c r="S166" s="47">
-        <v>5</v>
-      </c>
+      <c r="S166" s="101"/>
       <c r="T166" s="101"/>
       <c r="U166" s="101"/>
       <c r="V166" s="101"/>
@@ -60134,29 +59855,17 @@
       <c r="X166" s="101"/>
       <c r="Y166" s="101"/>
       <c r="Z166" s="101"/>
-      <c r="AA166" s="51">
-        <f t="shared" si="46"/>
-        <v>1</v>
-      </c>
+      <c r="AA166" s="101"/>
       <c r="AB166" s="101"/>
       <c r="AC166" s="101"/>
       <c r="AD166" s="101"/>
       <c r="AE166" s="101"/>
       <c r="AF166" s="101"/>
-      <c r="AG166" s="49" t="e">
-        <f t="shared" si="58"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH166" s="49" t="e">
-        <f t="shared" si="59"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI166" s="49"/>
-      <c r="AJ166" s="49"/>
-      <c r="AK166" s="49" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AG166" s="101"/>
+      <c r="AH166" s="101"/>
+      <c r="AI166" s="101"/>
+      <c r="AJ166" s="101"/>
+      <c r="AK166" s="101"/>
       <c r="AL166" s="101"/>
       <c r="AM166" s="101"/>
       <c r="AN166" s="101"/>
@@ -60175,390 +59884,18 @@
       <c r="BA166" s="101"/>
       <c r="BB166" s="101"/>
     </row>
-    <row r="167" spans="1:54">
-      <c r="A167" s="101"/>
-      <c r="B167" s="101"/>
-      <c r="C167" s="101"/>
-      <c r="D167" s="101"/>
-      <c r="E167" s="101"/>
-      <c r="F167" s="101"/>
-      <c r="G167" s="47" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H167" s="101"/>
-      <c r="I167" s="101"/>
-      <c r="J167" s="101"/>
-      <c r="K167" s="101"/>
-      <c r="L167" s="101"/>
-      <c r="M167" s="101"/>
-      <c r="N167" s="101"/>
-      <c r="O167" s="101"/>
-      <c r="P167" s="47" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q167" s="101"/>
-      <c r="R167" s="101"/>
-      <c r="S167" s="101"/>
-      <c r="T167" s="101"/>
-      <c r="U167" s="101"/>
-      <c r="V167" s="101"/>
-      <c r="W167" s="101"/>
-      <c r="X167" s="101"/>
-      <c r="Y167" s="101"/>
-      <c r="Z167" s="101"/>
-      <c r="AA167" s="101"/>
-      <c r="AB167" s="101"/>
-      <c r="AC167" s="101"/>
-      <c r="AD167" s="101"/>
-      <c r="AE167" s="101"/>
-      <c r="AF167" s="101"/>
-      <c r="AG167" s="101"/>
-      <c r="AH167" s="101"/>
-      <c r="AI167" s="101"/>
-      <c r="AJ167" s="101"/>
-      <c r="AK167" s="101"/>
-      <c r="AL167" s="101"/>
-      <c r="AM167" s="101"/>
-      <c r="AN167" s="101"/>
-      <c r="AO167" s="101"/>
-      <c r="AP167" s="101"/>
-      <c r="AQ167" s="101"/>
-      <c r="AR167" s="101"/>
-      <c r="AS167" s="101"/>
-      <c r="AT167" s="101"/>
-      <c r="AU167" s="101"/>
-      <c r="AV167" s="101"/>
-      <c r="AW167" s="101"/>
-      <c r="AX167" s="101"/>
-      <c r="AY167" s="101"/>
-      <c r="AZ167" s="101"/>
-      <c r="BA167" s="101"/>
-      <c r="BB167" s="101"/>
-    </row>
-    <row r="168" spans="1:54">
-      <c r="A168" s="101"/>
-      <c r="B168" s="101"/>
-      <c r="C168" s="101"/>
-      <c r="D168" s="101"/>
-      <c r="E168" s="101"/>
-      <c r="F168" s="101"/>
-      <c r="G168" s="47" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H168" s="101"/>
-      <c r="I168" s="101"/>
-      <c r="J168" s="101"/>
-      <c r="K168" s="101"/>
-      <c r="L168" s="101"/>
-      <c r="M168" s="101"/>
-      <c r="N168" s="101"/>
-      <c r="O168" s="101"/>
-      <c r="P168" s="47" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q168" s="101"/>
-      <c r="R168" s="101"/>
-      <c r="S168" s="101"/>
-      <c r="T168" s="101"/>
-      <c r="U168" s="101"/>
-      <c r="V168" s="101"/>
-      <c r="W168" s="101"/>
-      <c r="X168" s="101"/>
-      <c r="Y168" s="101"/>
-      <c r="Z168" s="101"/>
-      <c r="AA168" s="101"/>
-      <c r="AB168" s="101"/>
-      <c r="AC168" s="101"/>
-      <c r="AD168" s="101"/>
-      <c r="AE168" s="101"/>
-      <c r="AF168" s="101"/>
-      <c r="AG168" s="101"/>
-      <c r="AH168" s="101"/>
-      <c r="AI168" s="101"/>
-      <c r="AJ168" s="101"/>
-      <c r="AK168" s="101"/>
-      <c r="AL168" s="101"/>
-      <c r="AM168" s="101"/>
-      <c r="AN168" s="101"/>
-      <c r="AO168" s="101"/>
-      <c r="AP168" s="101"/>
-      <c r="AQ168" s="101"/>
-      <c r="AR168" s="101"/>
-      <c r="AS168" s="101"/>
-      <c r="AT168" s="101"/>
-      <c r="AU168" s="101"/>
-      <c r="AV168" s="101"/>
-      <c r="AW168" s="101"/>
-      <c r="AX168" s="101"/>
-      <c r="AY168" s="101"/>
-      <c r="AZ168" s="101"/>
-      <c r="BA168" s="101"/>
-      <c r="BB168" s="101"/>
-    </row>
-    <row r="169" spans="1:54">
-      <c r="A169" s="101"/>
-      <c r="B169" s="101"/>
-      <c r="C169" s="101"/>
-      <c r="D169" s="101"/>
-      <c r="E169" s="101"/>
-      <c r="F169" s="101"/>
-      <c r="G169" s="47" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H169" s="101"/>
-      <c r="I169" s="101"/>
-      <c r="J169" s="101"/>
-      <c r="K169" s="101"/>
-      <c r="L169" s="101"/>
-      <c r="M169" s="101"/>
-      <c r="N169" s="101"/>
-      <c r="O169" s="101"/>
-      <c r="P169" s="47" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q169" s="101"/>
-      <c r="R169" s="101"/>
-      <c r="S169" s="101"/>
-      <c r="T169" s="101"/>
-      <c r="U169" s="101"/>
-      <c r="V169" s="101"/>
-      <c r="W169" s="101"/>
-      <c r="X169" s="101"/>
-      <c r="Y169" s="101"/>
-      <c r="Z169" s="101"/>
-      <c r="AA169" s="101"/>
-      <c r="AB169" s="101"/>
-      <c r="AC169" s="101"/>
-      <c r="AD169" s="101"/>
-      <c r="AE169" s="101"/>
-      <c r="AF169" s="101"/>
-      <c r="AG169" s="101"/>
-      <c r="AH169" s="101"/>
-      <c r="AI169" s="101"/>
-      <c r="AJ169" s="101"/>
-      <c r="AK169" s="101"/>
-      <c r="AL169" s="101"/>
-      <c r="AM169" s="101"/>
-      <c r="AN169" s="101"/>
-      <c r="AO169" s="101"/>
-      <c r="AP169" s="101"/>
-      <c r="AQ169" s="101"/>
-      <c r="AR169" s="101"/>
-      <c r="AS169" s="101"/>
-      <c r="AT169" s="101"/>
-      <c r="AU169" s="101"/>
-      <c r="AV169" s="101"/>
-      <c r="AW169" s="101"/>
-      <c r="AX169" s="101"/>
-      <c r="AY169" s="101"/>
-      <c r="AZ169" s="101"/>
-      <c r="BA169" s="101"/>
-      <c r="BB169" s="101"/>
-    </row>
-    <row r="170" spans="1:54">
-      <c r="A170" s="101"/>
-      <c r="B170" s="101"/>
-      <c r="C170" s="101"/>
-      <c r="D170" s="101"/>
-      <c r="E170" s="101"/>
-      <c r="F170" s="101"/>
-      <c r="G170" s="47" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H170" s="101"/>
-      <c r="I170" s="101"/>
-      <c r="J170" s="101"/>
-      <c r="K170" s="101"/>
-      <c r="L170" s="101"/>
-      <c r="M170" s="101"/>
-      <c r="N170" s="101"/>
-      <c r="O170" s="101"/>
-      <c r="P170" s="47" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q170" s="101"/>
-      <c r="R170" s="101"/>
-      <c r="S170" s="101"/>
-      <c r="T170" s="101"/>
-      <c r="U170" s="101"/>
-      <c r="V170" s="101"/>
-      <c r="W170" s="101"/>
-      <c r="X170" s="101"/>
-      <c r="Y170" s="101"/>
-      <c r="Z170" s="101"/>
-      <c r="AA170" s="101"/>
-      <c r="AB170" s="101"/>
-      <c r="AC170" s="101"/>
-      <c r="AD170" s="101"/>
-      <c r="AE170" s="101"/>
-      <c r="AF170" s="101"/>
-      <c r="AG170" s="101"/>
-      <c r="AH170" s="101"/>
-      <c r="AI170" s="101"/>
-      <c r="AJ170" s="101"/>
-      <c r="AK170" s="101"/>
-      <c r="AL170" s="101"/>
-      <c r="AM170" s="101"/>
-      <c r="AN170" s="101"/>
-      <c r="AO170" s="101"/>
-      <c r="AP170" s="101"/>
-      <c r="AQ170" s="101"/>
-      <c r="AR170" s="101"/>
-      <c r="AS170" s="101"/>
-      <c r="AT170" s="101"/>
-      <c r="AU170" s="101"/>
-      <c r="AV170" s="101"/>
-      <c r="AW170" s="101"/>
-      <c r="AX170" s="101"/>
-      <c r="AY170" s="101"/>
-      <c r="AZ170" s="101"/>
-      <c r="BA170" s="101"/>
-      <c r="BB170" s="101"/>
-    </row>
-    <row r="171" spans="1:54">
-      <c r="A171" s="101"/>
-      <c r="B171" s="101"/>
-      <c r="C171" s="101"/>
-      <c r="D171" s="101"/>
-      <c r="E171" s="101"/>
-      <c r="F171" s="101"/>
-      <c r="G171" s="47" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H171" s="101"/>
-      <c r="I171" s="101"/>
-      <c r="J171" s="101"/>
-      <c r="K171" s="101"/>
-      <c r="L171" s="101"/>
-      <c r="M171" s="101"/>
-      <c r="N171" s="101"/>
-      <c r="O171" s="101"/>
-      <c r="P171" s="47" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q171" s="101"/>
-      <c r="R171" s="101"/>
-      <c r="S171" s="101"/>
-      <c r="T171" s="101"/>
-      <c r="U171" s="101"/>
-      <c r="V171" s="101"/>
-      <c r="W171" s="101"/>
-      <c r="X171" s="101"/>
-      <c r="Y171" s="101"/>
-      <c r="Z171" s="101"/>
-      <c r="AA171" s="101"/>
-      <c r="AB171" s="101"/>
-      <c r="AC171" s="101"/>
-      <c r="AD171" s="101"/>
-      <c r="AE171" s="101"/>
-      <c r="AF171" s="101"/>
-      <c r="AG171" s="101"/>
-      <c r="AH171" s="101"/>
-      <c r="AI171" s="101"/>
-      <c r="AJ171" s="101"/>
-      <c r="AK171" s="101"/>
-      <c r="AL171" s="101"/>
-      <c r="AM171" s="101"/>
-      <c r="AN171" s="101"/>
-      <c r="AO171" s="101"/>
-      <c r="AP171" s="101"/>
-      <c r="AQ171" s="101"/>
-      <c r="AR171" s="101"/>
-      <c r="AS171" s="101"/>
-      <c r="AT171" s="101"/>
-      <c r="AU171" s="101"/>
-      <c r="AV171" s="101"/>
-      <c r="AW171" s="101"/>
-      <c r="AX171" s="101"/>
-      <c r="AY171" s="101"/>
-      <c r="AZ171" s="101"/>
-      <c r="BA171" s="101"/>
-      <c r="BB171" s="101"/>
-    </row>
-    <row r="172" spans="1:54">
-      <c r="A172" s="101"/>
-      <c r="B172" s="101"/>
-      <c r="C172" s="101"/>
-      <c r="D172" s="101"/>
-      <c r="E172" s="101"/>
-      <c r="F172" s="101"/>
-      <c r="G172" s="47" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H172" s="101"/>
-      <c r="I172" s="101"/>
-      <c r="J172" s="101"/>
-      <c r="K172" s="101"/>
-      <c r="L172" s="101"/>
-      <c r="M172" s="101"/>
-      <c r="N172" s="101"/>
-      <c r="O172" s="101"/>
-      <c r="P172" s="47" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q172" s="101"/>
-      <c r="R172" s="101"/>
-      <c r="S172" s="101"/>
-      <c r="T172" s="101"/>
-      <c r="U172" s="101"/>
-      <c r="V172" s="101"/>
-      <c r="W172" s="101"/>
-      <c r="X172" s="101"/>
-      <c r="Y172" s="101"/>
-      <c r="Z172" s="101"/>
-      <c r="AA172" s="101"/>
-      <c r="AB172" s="101"/>
-      <c r="AC172" s="101"/>
-      <c r="AD172" s="101"/>
-      <c r="AE172" s="101"/>
-      <c r="AF172" s="101"/>
-      <c r="AG172" s="101"/>
-      <c r="AH172" s="101"/>
-      <c r="AI172" s="101"/>
-      <c r="AJ172" s="101"/>
-      <c r="AK172" s="101"/>
-      <c r="AL172" s="101"/>
-      <c r="AM172" s="101"/>
-      <c r="AN172" s="101"/>
-      <c r="AO172" s="101"/>
-      <c r="AP172" s="101"/>
-      <c r="AQ172" s="101"/>
-      <c r="AR172" s="101"/>
-      <c r="AS172" s="101"/>
-      <c r="AT172" s="101"/>
-      <c r="AU172" s="101"/>
-      <c r="AV172" s="101"/>
-      <c r="AW172" s="101"/>
-      <c r="AX172" s="101"/>
-      <c r="AY172" s="101"/>
-      <c r="AZ172" s="101"/>
-      <c r="BA172" s="101"/>
-      <c r="BB172" s="101"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G172 H56">
+  <conditionalFormatting sqref="G2:G166 H56">
     <cfRule type="cellIs" dxfId="39" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P172 Q60:R60">
+  <conditionalFormatting sqref="P2:P166 Q60:R60">
     <cfRule type="cellIs" dxfId="38" priority="17" operator="greaterThan">
       <formula>23</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R409">
+  <conditionalFormatting sqref="R2:R403">
     <cfRule type="cellIs" dxfId="37" priority="19" operator="greaterThan">
       <formula>88</formula>
     </cfRule>
@@ -60588,7 +59925,7 @@
       <formula>3.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA166">
+  <conditionalFormatting sqref="AA2:AA160">
     <cfRule type="cellIs" dxfId="31" priority="18" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -60598,17 +59935,17 @@
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG1:AJ520">
+  <conditionalFormatting sqref="AG1:AJ514">
     <cfRule type="cellIs" dxfId="29" priority="4" operator="greaterThan">
       <formula>6.1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK1:AK220">
+  <conditionalFormatting sqref="AK1:AK214">
     <cfRule type="cellIs" dxfId="28" priority="20" operator="greaterThan">
       <formula>22.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL466">
+  <conditionalFormatting sqref="AL2:AL460">
     <cfRule type="containsText" dxfId="27" priority="6" operator="containsText" text="Neg">
       <formula>NOT(ISERROR(SEARCH("Neg",AL2)))</formula>
     </cfRule>
@@ -60616,7 +59953,7 @@
       <formula>NOT(ISERROR(SEARCH("Pos",AL2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AP2:AP163">
+  <conditionalFormatting sqref="AP2:AP157">
     <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>3</formula>
     </cfRule>
@@ -60628,7 +59965,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 

--- a/General.xlsx
+++ b/General.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CapitalFund1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638CAB55-7BD8-405B-ADB9-1CEBAF65C1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="IPOSME" sheetId="1" r:id="rId1"/>
     <sheet name="IPOMB" sheetId="2" r:id="rId2"/>
     <sheet name="IPOSME (2)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1131,7 +1130,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -2540,83 +2539,83 @@
     </dxf>
   </dxfs>
   <tableStyles count="19" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="108"/>
       <tableStyleElement type="firstRowStripe" dxfId="107"/>
       <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="SME IPO v1-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="105"/>
       <tableStyleElement type="firstRowStripe" dxfId="104"/>
       <tableStyleElement type="secondRowStripe" dxfId="103"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="102"/>
       <tableStyleElement type="secondRowStripe" dxfId="101"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="100"/>
       <tableStyleElement type="secondRowStripe" dxfId="99"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="98"/>
       <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
+    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="96"/>
       <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
+    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="94"/>
       <tableStyleElement type="secondRowStripe" dxfId="93"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
+    <tableStyle name="SME IPO v2-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="92"/>
       <tableStyleElement type="firstRowStripe" dxfId="91"/>
       <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
+    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="89"/>
       <tableStyleElement type="secondRowStripe" dxfId="88"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
+    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="87"/>
       <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
+    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="85"/>
       <tableStyleElement type="secondRowStripe" dxfId="84"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
+    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="83"/>
       <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
+    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="81"/>
       <tableStyleElement type="secondRowStripe" dxfId="80"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
+    <tableStyle name="SME IPO v3-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="79"/>
       <tableStyleElement type="firstRowStripe" dxfId="78"/>
       <tableStyleElement type="secondRowStripe" dxfId="77"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
+    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="76"/>
       <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
+    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="74"/>
       <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF10000000}">
+    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="72"/>
       <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF11000000}">
+    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="70"/>
       <tableStyleElement type="secondRowStripe" dxfId="69"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF12000000}">
+    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="68"/>
       <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
@@ -2829,52 +2828,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:DF466"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
-    <col min="4" max="4" width="3.88671875" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="6.6640625" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="6.6640625" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" style="108" customWidth="1"/>
-    <col min="20" max="20" width="5.33203125" customWidth="1"/>
-    <col min="21" max="21" width="4.6640625" customWidth="1"/>
-    <col min="22" max="22" width="4.33203125" customWidth="1"/>
-    <col min="23" max="23" width="6.6640625" customWidth="1"/>
-    <col min="24" max="24" width="7.33203125" customWidth="1"/>
-    <col min="25" max="25" width="10.33203125" customWidth="1"/>
-    <col min="26" max="26" width="8.5546875" customWidth="1"/>
-    <col min="27" max="27" width="5.88671875" customWidth="1"/>
-    <col min="28" max="28" width="7.33203125" customWidth="1"/>
-    <col min="29" max="29" width="5.88671875" customWidth="1"/>
-    <col min="30" max="30" width="6.6640625" customWidth="1"/>
-    <col min="31" max="31" width="7.6640625" customWidth="1"/>
-    <col min="32" max="32" width="8.44140625" customWidth="1"/>
-    <col min="33" max="33" width="7.33203125" customWidth="1"/>
-    <col min="34" max="36" width="6.33203125" customWidth="1"/>
-    <col min="37" max="37" width="8.88671875" customWidth="1"/>
-    <col min="38" max="38" width="4.44140625" customWidth="1"/>
-    <col min="39" max="39" width="20.109375" customWidth="1"/>
-    <col min="40" max="40" width="6.5546875" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" style="108" customWidth="1"/>
+    <col min="20" max="20" width="5.28515625" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" customWidth="1"/>
+    <col min="25" max="25" width="10.28515625" customWidth="1"/>
+    <col min="26" max="26" width="8.5703125" customWidth="1"/>
+    <col min="27" max="27" width="5.85546875" customWidth="1"/>
+    <col min="28" max="28" width="7.28515625" customWidth="1"/>
+    <col min="29" max="29" width="5.85546875" customWidth="1"/>
+    <col min="30" max="30" width="6.7109375" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" customWidth="1"/>
+    <col min="32" max="32" width="8.42578125" customWidth="1"/>
+    <col min="33" max="33" width="7.28515625" customWidth="1"/>
+    <col min="34" max="36" width="6.28515625" customWidth="1"/>
+    <col min="37" max="37" width="8.85546875" customWidth="1"/>
+    <col min="38" max="38" width="4.42578125" customWidth="1"/>
+    <col min="39" max="39" width="20.140625" customWidth="1"/>
+    <col min="40" max="40" width="6.5703125" customWidth="1"/>
     <col min="42" max="48" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" ht="92.4" customHeight="1">
+    <row r="1" spans="1:59" ht="92.45" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -17604,7 +17603,7 @@
         <v>20.73</v>
       </c>
       <c r="G98" s="16">
-        <f t="shared" ref="G98:G129" si="28">100*(F98-E98)/F98</f>
+        <f t="shared" ref="G98:G117" si="28">100*(F98-E98)/F98</f>
         <v>-6.5605402797877446</v>
       </c>
       <c r="H98" s="37">
@@ -17626,7 +17625,7 @@
         <v>78.900000000000006</v>
       </c>
       <c r="P98" s="16">
-        <f t="shared" ref="P98:P129" si="29">O98/I98</f>
+        <f t="shared" ref="P98:P117" si="29">O98/I98</f>
         <v>8.7959866220735794</v>
       </c>
       <c r="Q98" s="9">
@@ -17700,7 +17699,7 @@
         <v>2</v>
       </c>
       <c r="AO98" s="17">
-        <f t="shared" ref="AO98:AO129" si="31">AN98+1</f>
+        <f t="shared" ref="AO98:AO123" si="31">AN98+1</f>
         <v>3</v>
       </c>
       <c r="AP98" s="17">
@@ -23322,7 +23321,7 @@
         <v>241</v>
       </c>
       <c r="AN138">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO138" s="17">
         <v>25</v>
@@ -30488,7 +30487,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ258" s="17" t="e">
-        <f t="shared" ref="AQ258:AQ321" si="62">IF(AP258&gt;0,IF(AB258&gt;10,(AB258/Z258),10/Z258),0)</f>
+        <f t="shared" ref="AQ258:AQ277" si="62">IF(AP258&gt;0,IF(AB258&gt;10,(AB258/Z258),10/Z258),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR258" s="17"/>
@@ -34024,7 +34023,7 @@
         <v>1</v>
       </c>
       <c r="AK322" s="16" t="e">
-        <f t="shared" ref="AK322:AK385" si="71">(1.2*AG322+AH322)*AJ322</f>
+        <f t="shared" ref="AK322:AK345" si="71">(1.2*AG322+AH322)*AJ322</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL322" s="15">
@@ -34062,7 +34061,7 @@
         <v>1</v>
       </c>
       <c r="AC323" s="16">
-        <f t="shared" ref="AC323:AC386" si="74">IF(AB323&gt;4,1,0)+AB323/12</f>
+        <f t="shared" ref="AC323:AC334" si="74">IF(AB323&gt;4,1,0)+AB323/12</f>
         <v>0</v>
       </c>
       <c r="AG323" s="15" t="e">
@@ -34576,7 +34575,7 @@
         <v>0</v>
       </c>
       <c r="AO332" s="17">
-        <f t="shared" ref="AO332:AO395" si="78">AN332+1</f>
+        <f t="shared" ref="AO332:AO346" si="78">AN332+1</f>
         <v>1</v>
       </c>
       <c r="AP332" s="17" t="e">
@@ -37228,7 +37227,7 @@
         <v>5</v>
       </c>
       <c r="AA386" s="2">
-        <f t="shared" ref="AA386:AA449" si="84">IF(X386&lt;50,IF(Y386&gt;(2.3*X386),0,1),1)-IF(Z386&gt;Y386,1.7,0)</f>
+        <f t="shared" ref="AA386:AA447" si="84">IF(X386&lt;50,IF(Y386&gt;(2.3*X386),0,1),1)-IF(Z386&gt;Y386,1.7,0)</f>
         <v>1</v>
       </c>
       <c r="AC386" s="16">
@@ -37696,11 +37695,11 @@
     </row>
     <row r="396" spans="7:42">
       <c r="G396" s="16" t="e">
-        <f t="shared" ref="G396:G459" si="90">100*(F396-E396)/F396</f>
+        <f t="shared" ref="G396:G455" si="90">100*(F396-E396)/F396</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P396" s="16" t="e">
-        <f t="shared" ref="P396:P459" si="91">O396/I396</f>
+        <f t="shared" ref="P396:P455" si="91">O396/I396</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R396" s="111"/>
@@ -39934,7 +39933,7 @@
       <c r="AI442" s="16"/>
       <c r="AJ442" s="16"/>
       <c r="AK442" s="16" t="e">
-        <f t="shared" ref="AK442:AK473" si="96">(2*AG442+AH442)*AJ442</f>
+        <f t="shared" ref="AK442:AK449" si="96">(2*AG442+AH442)*AJ442</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL442" s="15">
@@ -40309,7 +40308,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH450" s="16" t="e">
-        <f t="shared" ref="AH450:AH513" si="98">AG450+IF(X450&lt;1.35,0,1)+IF(Y450&lt;1.35,0,1)+AC450+AA450</f>
+        <f t="shared" ref="AH450:AH455" si="98">AG450+IF(X450&lt;1.35,0,1)+IF(Y450&lt;1.35,0,1)+AC450+AA450</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI450" s="16"/>
@@ -40697,59 +40696,59 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BB166"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" customWidth="1"/>
-    <col min="4" max="4" width="4.33203125" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="4.88671875" customWidth="1"/>
-    <col min="11" max="11" width="6.109375" customWidth="1"/>
-    <col min="12" max="12" width="4.109375" customWidth="1"/>
-    <col min="13" max="14" width="6.5546875" customWidth="1"/>
-    <col min="15" max="15" width="7.5546875" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" customWidth="1"/>
+    <col min="12" max="12" width="4.140625" customWidth="1"/>
+    <col min="13" max="14" width="6.5703125" customWidth="1"/>
+    <col min="15" max="15" width="7.5703125" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.109375" customWidth="1"/>
+    <col min="18" max="18" width="6.140625" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="5.5546875" customWidth="1"/>
-    <col min="22" max="22" width="6.109375" customWidth="1"/>
-    <col min="23" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="8.33203125" customWidth="1"/>
-    <col min="26" max="26" width="5.44140625" customWidth="1"/>
-    <col min="27" max="27" width="5.109375" customWidth="1"/>
-    <col min="28" max="28" width="4.5546875" customWidth="1"/>
-    <col min="29" max="29" width="4.88671875" customWidth="1"/>
-    <col min="30" max="30" width="6.5546875" customWidth="1"/>
-    <col min="31" max="31" width="5.6640625" customWidth="1"/>
-    <col min="32" max="32" width="6.33203125" customWidth="1"/>
-    <col min="33" max="36" width="4.88671875" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="5.5703125" customWidth="1"/>
+    <col min="22" max="22" width="6.140625" customWidth="1"/>
+    <col min="23" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="8.28515625" customWidth="1"/>
+    <col min="26" max="26" width="5.42578125" customWidth="1"/>
+    <col min="27" max="27" width="5.140625" customWidth="1"/>
+    <col min="28" max="28" width="4.5703125" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" customWidth="1"/>
+    <col min="30" max="30" width="6.5703125" customWidth="1"/>
+    <col min="31" max="31" width="5.7109375" customWidth="1"/>
+    <col min="32" max="32" width="6.28515625" customWidth="1"/>
+    <col min="33" max="36" width="4.85546875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
-    <col min="38" max="38" width="5.6640625" customWidth="1"/>
-    <col min="39" max="39" width="13.6640625" customWidth="1"/>
-    <col min="40" max="40" width="4.5546875" customWidth="1"/>
-    <col min="41" max="41" width="5.44140625" customWidth="1"/>
-    <col min="42" max="44" width="10.88671875" customWidth="1"/>
+    <col min="38" max="38" width="5.7109375" customWidth="1"/>
+    <col min="39" max="39" width="13.7109375" customWidth="1"/>
+    <col min="40" max="40" width="4.5703125" customWidth="1"/>
+    <col min="41" max="41" width="5.42578125" customWidth="1"/>
+    <col min="42" max="44" width="10.85546875" customWidth="1"/>
     <col min="45" max="45" width="6" customWidth="1"/>
-    <col min="46" max="46" width="6.109375" customWidth="1"/>
+    <col min="46" max="46" width="6.140625" customWidth="1"/>
     <col min="47" max="47" width="4" customWidth="1"/>
-    <col min="48" max="48" width="4.109375" customWidth="1"/>
-    <col min="49" max="50" width="5.33203125" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" customWidth="1"/>
-    <col min="52" max="52" width="3.88671875" customWidth="1"/>
+    <col min="48" max="48" width="4.140625" customWidth="1"/>
+    <col min="49" max="50" width="5.28515625" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" customWidth="1"/>
+    <col min="52" max="52" width="3.85546875" customWidth="1"/>
     <col min="53" max="53" width="4" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" customWidth="1"/>
+    <col min="54" max="54" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="92.4" customHeight="1">
+    <row r="1" spans="1:54" ht="92.45" customHeight="1">
       <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
@@ -49983,7 +49982,7 @@
         <v>660.43</v>
       </c>
       <c r="G66" s="47">
-        <f t="shared" ref="G66:G97" si="22">100*(F66-E66)/F66</f>
+        <f t="shared" ref="G66:G67" si="22">100*(F66-E66)/F66</f>
         <v>79.978196023802667</v>
       </c>
       <c r="H66" s="101">
@@ -50011,7 +50010,7 @@
         <v>2514.66</v>
       </c>
       <c r="P66" s="47">
-        <f t="shared" ref="P66:P97" si="23">O66/I66</f>
+        <f t="shared" ref="P66:P67" si="23">O66/I66</f>
         <v>414.96039603960395</v>
       </c>
       <c r="Q66" s="101">
@@ -52237,17 +52236,17 @@
         <v>1</v>
       </c>
       <c r="X81" s="101">
-        <v>0.82</v>
+        <v>5</v>
       </c>
       <c r="Y81" s="101">
-        <v>5.52</v>
+        <v>9</v>
       </c>
       <c r="Z81" s="101">
-        <v>0.59</v>
+        <v>1</v>
       </c>
       <c r="AA81" s="51">
         <f t="shared" si="24"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB81" s="101">
         <v>3.77</v>
@@ -52271,13 +52270,13 @@
       </c>
       <c r="AH81" s="49">
         <f t="shared" si="27"/>
-        <v>2.3566666666666665</v>
+        <v>3.3566666666666665</v>
       </c>
       <c r="AI81" s="49"/>
       <c r="AJ81" s="49"/>
       <c r="AK81" s="49">
         <f t="shared" si="28"/>
-        <v>8.6566666666666663</v>
+        <v>9.6566666666666663</v>
       </c>
       <c r="AL81" s="2">
         <f t="shared" si="29"/>
@@ -52381,17 +52380,17 @@
         <v>1</v>
       </c>
       <c r="X82" s="101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82" s="101">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="Z82" s="101">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="AA82" s="51">
         <f t="shared" si="24"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB82" s="101">
         <v>0.25</v>
@@ -52415,13 +52414,13 @@
       </c>
       <c r="AH82" s="49">
         <f t="shared" si="27"/>
-        <v>4.6333333333333329</v>
+        <v>6.6333333333333329</v>
       </c>
       <c r="AI82" s="49"/>
       <c r="AJ82" s="49"/>
       <c r="AK82" s="49">
         <f t="shared" si="28"/>
-        <v>21.283333333333331</v>
+        <v>23.283333333333331</v>
       </c>
       <c r="AL82" s="2">
         <f t="shared" si="29"/>
@@ -52438,11 +52437,11 @@
       </c>
       <c r="AP82" s="17">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ82" s="16">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AR82" s="101"/>
       <c r="AS82" s="101"/>
@@ -56774,18 +56773,18 @@
       </c>
       <c r="AB130" s="101"/>
       <c r="AC130" s="52">
-        <f t="shared" ref="AC130:AC161" si="47">IF(AB130&gt;9,1,0)+AB130/3</f>
+        <f t="shared" ref="AC130:AC156" si="47">IF(AB130&gt;9,1,0)+AB130/3</f>
         <v>0</v>
       </c>
       <c r="AD130" s="101"/>
       <c r="AE130" s="101"/>
       <c r="AF130" s="101"/>
       <c r="AG130" s="49" t="e">
-        <f t="shared" ref="AG130:AG161" si="48">IF(G130&lt;0,0,1.2)+IF(G130&lt;14,0,0.9)+IF(P130&lt;0,0.7,0)+IF(P130&lt;6.5,1,0)+IF(P130&lt;23,1,0)+IF(R130&gt;88,0,1)+IF(S130=5,0,S130)+IF(AD130&lt;20,0,1)+IF(AE130&lt;14,0,1)+IF(AF130&lt;26,0,1)</f>
+        <f t="shared" ref="AG130:AG160" si="48">IF(G130&lt;0,0,1.2)+IF(G130&lt;14,0,0.9)+IF(P130&lt;0,0.7,0)+IF(P130&lt;6.5,1,0)+IF(P130&lt;23,1,0)+IF(R130&gt;88,0,1)+IF(S130=5,0,S130)+IF(AD130&lt;20,0,1)+IF(AE130&lt;14,0,1)+IF(AF130&lt;26,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH130" s="49" t="e">
-        <f t="shared" ref="AH130:AH161" si="49">AG130+IF(AG130&gt;6,1,0)+IF(X130&lt;17,0,1)+IF(Y130&lt;11,0,1)+IF(Z130&lt;1.35,0,1)+AC130+AA130</f>
+        <f t="shared" ref="AH130:AH160" si="49">AG130+IF(AG130&gt;6,1,0)+IF(X130&lt;17,0,1)+IF(Y130&lt;11,0,1)+IF(Z130&lt;1.35,0,1)+AC130+AA130</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI130" s="49"/>
@@ -56809,7 +56808,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AQ130" s="16" t="e">
-        <f t="shared" ref="AQ130:AQ161" si="53">IF(AP130&gt;0,IF(AB130&gt;10,(AB130/Z130),10/Z130),0)</f>
+        <f t="shared" ref="AQ130:AQ157" si="53">IF(AP130&gt;0,IF(AB130&gt;10,(AB130/Z130),10/Z130),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AR130" s="101"/>
@@ -58288,7 +58287,7 @@
       <c r="E147" s="101"/>
       <c r="F147" s="101"/>
       <c r="G147" s="47" t="e">
-        <f t="shared" ref="G147:G178" si="54">100*(F147-E147)/F147</f>
+        <f t="shared" ref="G147:G166" si="54">100*(F147-E147)/F147</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H147" s="101"/>
@@ -58300,7 +58299,7 @@
       <c r="N147" s="101"/>
       <c r="O147" s="101"/>
       <c r="P147" s="47" t="e">
-        <f t="shared" ref="P147:P178" si="55">O147/I147</f>
+        <f t="shared" ref="P147:P166" si="55">O147/I147</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q147" s="101"/>
@@ -59970,52 +59969,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:DA484"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
-    <col min="4" max="4" width="3.88671875" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="6.6640625" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="6.6640625" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" customWidth="1"/>
-    <col min="20" max="20" width="5.33203125" customWidth="1"/>
-    <col min="21" max="21" width="4.6640625" customWidth="1"/>
-    <col min="22" max="22" width="4.33203125" customWidth="1"/>
-    <col min="23" max="23" width="6.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.33203125" customWidth="1"/>
-    <col min="25" max="25" width="5.5546875" customWidth="1"/>
-    <col min="26" max="26" width="3.44140625" customWidth="1"/>
-    <col min="27" max="27" width="5.88671875" customWidth="1"/>
-    <col min="28" max="28" width="7.33203125" customWidth="1"/>
-    <col min="29" max="29" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="6.6640625" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="7.109375" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="5.5546875" customWidth="1"/>
-    <col min="34" max="34" width="6.33203125" customWidth="1"/>
-    <col min="35" max="35" width="8.88671875" customWidth="1"/>
-    <col min="36" max="36" width="4.44140625" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" customWidth="1"/>
+    <col min="20" max="20" width="5.28515625" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.28515625" customWidth="1"/>
+    <col min="25" max="25" width="5.5703125" customWidth="1"/>
+    <col min="26" max="26" width="3.42578125" customWidth="1"/>
+    <col min="27" max="27" width="5.85546875" customWidth="1"/>
+    <col min="28" max="28" width="7.28515625" customWidth="1"/>
+    <col min="29" max="29" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="6.7109375" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="5.5703125" customWidth="1"/>
+    <col min="34" max="34" width="6.28515625" customWidth="1"/>
+    <col min="35" max="35" width="8.85546875" customWidth="1"/>
+    <col min="36" max="36" width="4.42578125" customWidth="1"/>
     <col min="38" max="42" width="13" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="1.5546875" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="1.5703125" hidden="1" customWidth="1"/>
     <col min="53" max="54" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104" ht="92.4" customHeight="1">
+    <row r="1" spans="1:104" ht="92.45" customHeight="1">
       <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
@@ -68817,7 +68816,7 @@
         <v>15.6</v>
       </c>
       <c r="G66" s="70">
-        <f t="shared" ref="G66:G97" si="18">100*(F66-E66)/F66</f>
+        <f t="shared" ref="G66:G89" si="18">100*(F66-E66)/F66</f>
         <v>82.371794871794876</v>
       </c>
       <c r="H66" s="75">
@@ -68839,7 +68838,7 @@
         <v>120.99</v>
       </c>
       <c r="P66" s="70">
-        <f t="shared" ref="P66:P97" si="19">O66/I66</f>
+        <f t="shared" ref="P66:P89" si="19">O66/I66</f>
         <v>16.003968253968253</v>
       </c>
       <c r="Q66" s="75">
@@ -68872,7 +68871,7 @@
         <v>4</v>
       </c>
       <c r="AC66" s="70">
-        <f t="shared" ref="AC66:AC97" si="21">IF(AB66&gt;6.2,1,0)+AB66/5</f>
+        <f t="shared" ref="AC66:AC89" si="21">IF(AB66&gt;6.2,1,0)+AB66/5</f>
         <v>0.8</v>
       </c>
       <c r="AD66" s="71">
@@ -68889,11 +68888,11 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="AH66" s="70">
-        <f t="shared" ref="AH66:AH97" si="23">AG66+IF(X66&lt;1.35,0,1)+IF(Y66&lt;1.35,0,1)+AC66+AA66</f>
+        <f t="shared" ref="AH66:AH89" si="23">AG66+IF(X66&lt;1.35,0,1)+IF(Y66&lt;1.35,0,1)+AC66+AA66</f>
         <v>8.8999999999999986</v>
       </c>
       <c r="AI66" s="70">
-        <f t="shared" ref="AI66:AI97" si="24">AG66+AH66*1.4</f>
+        <f t="shared" ref="AI66:AI89" si="24">AG66+AH66*1.4</f>
         <v>17.559999999999995</v>
       </c>
       <c r="AJ66" s="71" t="str">

--- a/General.xlsx
+++ b/General.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CapitalFund1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14A5690-B6E9-4A0E-96F5-4D1D17E6013A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IPOSME" sheetId="1" r:id="rId1"/>
     <sheet name="IPOMB" sheetId="2" r:id="rId2"/>
     <sheet name="IPOSME (2)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -800,9 +801,6 @@
     <t>Last Day of Close &gt;8</t>
   </si>
   <si>
-    <t>Total &gt;25.2</t>
-  </si>
-  <si>
     <t>Closing Date</t>
   </si>
   <si>
@@ -1126,11 +1124,14 @@
   <si>
     <t>0: NA, 1: RII, 2: NIIA, 3: NIIB</t>
   </si>
+  <si>
+    <t>Total &gt;23</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -2539,83 +2540,83 @@
     </dxf>
   </dxfs>
   <tableStyles count="19" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3">
+    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="headerRow" dxfId="108"/>
       <tableStyleElement type="firstRowStripe" dxfId="107"/>
       <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style" pivot="0" count="3">
+    <tableStyle name="SME IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="105"/>
       <tableStyleElement type="firstRowStripe" dxfId="104"/>
       <tableStyleElement type="secondRowStripe" dxfId="103"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="firstRowStripe" dxfId="102"/>
       <tableStyleElement type="secondRowStripe" dxfId="101"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
       <tableStyleElement type="firstRowStripe" dxfId="100"/>
       <tableStyleElement type="secondRowStripe" dxfId="99"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
       <tableStyleElement type="firstRowStripe" dxfId="98"/>
       <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
       <tableStyleElement type="firstRowStripe" dxfId="96"/>
       <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2">
+    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
       <tableStyleElement type="firstRowStripe" dxfId="94"/>
       <tableStyleElement type="secondRowStripe" dxfId="93"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style" pivot="0" count="3">
+    <tableStyle name="SME IPO v2-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
       <tableStyleElement type="headerRow" dxfId="92"/>
       <tableStyleElement type="firstRowStripe" dxfId="91"/>
       <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
       <tableStyleElement type="firstRowStripe" dxfId="89"/>
       <tableStyleElement type="secondRowStripe" dxfId="88"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
       <tableStyleElement type="firstRowStripe" dxfId="87"/>
       <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
       <tableStyleElement type="firstRowStripe" dxfId="85"/>
       <tableStyleElement type="secondRowStripe" dxfId="84"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
       <tableStyleElement type="firstRowStripe" dxfId="83"/>
       <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2">
+    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
       <tableStyleElement type="firstRowStripe" dxfId="81"/>
       <tableStyleElement type="secondRowStripe" dxfId="80"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style" pivot="0" count="3">
+    <tableStyle name="SME IPO v3-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
       <tableStyleElement type="headerRow" dxfId="79"/>
       <tableStyleElement type="firstRowStripe" dxfId="78"/>
       <tableStyleElement type="secondRowStripe" dxfId="77"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
       <tableStyleElement type="firstRowStripe" dxfId="76"/>
       <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
       <tableStyleElement type="firstRowStripe" dxfId="74"/>
       <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF10000000}">
       <tableStyleElement type="firstRowStripe" dxfId="72"/>
       <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF11000000}">
       <tableStyleElement type="firstRowStripe" dxfId="70"/>
       <tableStyleElement type="secondRowStripe" dxfId="69"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2">
+    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF12000000}">
       <tableStyleElement type="firstRowStripe" dxfId="68"/>
       <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
@@ -2828,52 +2829,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DF466"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" style="108" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" customWidth="1"/>
-    <col min="24" max="24" width="7.28515625" customWidth="1"/>
-    <col min="25" max="25" width="10.28515625" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" customWidth="1"/>
-    <col min="27" max="27" width="5.85546875" customWidth="1"/>
-    <col min="28" max="28" width="7.28515625" customWidth="1"/>
-    <col min="29" max="29" width="5.85546875" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" customWidth="1"/>
-    <col min="31" max="31" width="7.7109375" customWidth="1"/>
-    <col min="32" max="32" width="8.42578125" customWidth="1"/>
-    <col min="33" max="33" width="7.28515625" customWidth="1"/>
-    <col min="34" max="36" width="6.28515625" customWidth="1"/>
-    <col min="37" max="37" width="8.85546875" customWidth="1"/>
-    <col min="38" max="38" width="4.42578125" customWidth="1"/>
-    <col min="39" max="39" width="20.140625" customWidth="1"/>
-    <col min="40" max="40" width="6.5703125" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" style="108" customWidth="1"/>
+    <col min="20" max="20" width="5.33203125" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" customWidth="1"/>
+    <col min="24" max="24" width="7.33203125" customWidth="1"/>
+    <col min="25" max="25" width="10.33203125" customWidth="1"/>
+    <col min="26" max="26" width="8.5546875" customWidth="1"/>
+    <col min="27" max="27" width="5.88671875" customWidth="1"/>
+    <col min="28" max="28" width="7.33203125" customWidth="1"/>
+    <col min="29" max="29" width="5.88671875" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" customWidth="1"/>
+    <col min="31" max="31" width="7.6640625" customWidth="1"/>
+    <col min="32" max="32" width="8.44140625" customWidth="1"/>
+    <col min="33" max="33" width="7.33203125" customWidth="1"/>
+    <col min="34" max="36" width="6.33203125" customWidth="1"/>
+    <col min="37" max="37" width="8.88671875" customWidth="1"/>
+    <col min="38" max="38" width="4.44140625" customWidth="1"/>
+    <col min="39" max="39" width="20.109375" customWidth="1"/>
+    <col min="40" max="40" width="6.5546875" customWidth="1"/>
     <col min="42" max="48" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" ht="92.45" customHeight="1">
+    <row r="1" spans="1:59" ht="92.4" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -23269,24 +23270,24 @@
         <v>1</v>
       </c>
       <c r="X138">
-        <v>0.04</v>
+        <v>18.190000000000001</v>
       </c>
       <c r="Y138">
-        <v>11.77</v>
+        <v>123.19</v>
       </c>
       <c r="Z138">
-        <v>12.25</v>
+        <v>73</v>
       </c>
       <c r="AA138" s="2">
         <f t="shared" si="32"/>
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="AB138">
-        <v>0.23499999999999999</v>
+        <v>20</v>
       </c>
       <c r="AC138" s="16">
         <f t="shared" si="39"/>
-        <v>1.9583333333333331E-2</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="AD138">
         <v>5.44</v>
@@ -23303,7 +23304,7 @@
       </c>
       <c r="AH138" s="16">
         <f t="shared" si="34"/>
-        <v>4.0195833333333333</v>
+        <v>9.3666666666666671</v>
       </c>
       <c r="AI138" s="16"/>
       <c r="AJ138" s="16">
@@ -23311,7 +23312,7 @@
       </c>
       <c r="AK138" s="16">
         <f t="shared" si="35"/>
-        <v>9.6595833333333339</v>
+        <v>15.006666666666668</v>
       </c>
       <c r="AL138" s="15">
         <f t="shared" si="36"/>
@@ -23328,11 +23329,11 @@
       </c>
       <c r="AP138" s="17">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ138" s="17">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>0.27397260273972601</v>
       </c>
       <c r="AR138" s="17"/>
     </row>
@@ -23404,24 +23405,24 @@
         <v>1</v>
       </c>
       <c r="X139">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="Y139">
-        <v>0.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z139">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="AA139" s="2">
         <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="AB139">
-        <v>0.23499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC139" s="16">
         <f t="shared" si="39"/>
-        <v>1.9583333333333331E-2</v>
+        <v>0</v>
       </c>
       <c r="AD139">
         <v>372.9</v>
@@ -23438,7 +23439,7 @@
       </c>
       <c r="AH139" s="16">
         <f t="shared" si="34"/>
-        <v>7.1195833333333329</v>
+        <v>9.1</v>
       </c>
       <c r="AI139" s="16"/>
       <c r="AJ139" s="16">
@@ -23446,7 +23447,7 @@
       </c>
       <c r="AK139" s="16">
         <f t="shared" si="35"/>
-        <v>14.439583333333331</v>
+        <v>16.419999999999998</v>
       </c>
       <c r="AL139" s="15">
         <f t="shared" si="36"/>
@@ -23467,7 +23468,7 @@
       </c>
       <c r="AQ139" s="17">
         <f t="shared" si="38"/>
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AR139" s="17"/>
     </row>
@@ -40696,59 +40697,59 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BB166"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" customWidth="1"/>
-    <col min="12" max="12" width="4.140625" customWidth="1"/>
-    <col min="13" max="14" width="6.5703125" customWidth="1"/>
-    <col min="15" max="15" width="7.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="4.88671875" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" customWidth="1"/>
+    <col min="12" max="12" width="4.109375" customWidth="1"/>
+    <col min="13" max="14" width="6.5546875" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.140625" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="5.5703125" customWidth="1"/>
-    <col min="22" max="22" width="6.140625" customWidth="1"/>
-    <col min="23" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="8.28515625" customWidth="1"/>
-    <col min="26" max="26" width="5.42578125" customWidth="1"/>
-    <col min="27" max="27" width="5.140625" customWidth="1"/>
-    <col min="28" max="28" width="4.5703125" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" customWidth="1"/>
-    <col min="30" max="30" width="6.5703125" customWidth="1"/>
-    <col min="31" max="31" width="5.7109375" customWidth="1"/>
-    <col min="32" max="32" width="6.28515625" customWidth="1"/>
-    <col min="33" max="36" width="4.85546875" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
+    <col min="21" max="21" width="5.5546875" customWidth="1"/>
+    <col min="22" max="22" width="6.109375" customWidth="1"/>
+    <col min="23" max="24" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="8.33203125" customWidth="1"/>
+    <col min="26" max="26" width="5.44140625" customWidth="1"/>
+    <col min="27" max="27" width="5.109375" customWidth="1"/>
+    <col min="28" max="28" width="4.5546875" customWidth="1"/>
+    <col min="29" max="29" width="4.88671875" customWidth="1"/>
+    <col min="30" max="30" width="6.5546875" customWidth="1"/>
+    <col min="31" max="31" width="5.6640625" customWidth="1"/>
+    <col min="32" max="32" width="6.33203125" customWidth="1"/>
+    <col min="33" max="36" width="4.88671875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
-    <col min="38" max="38" width="5.7109375" customWidth="1"/>
-    <col min="39" max="39" width="13.7109375" customWidth="1"/>
-    <col min="40" max="40" width="4.5703125" customWidth="1"/>
-    <col min="41" max="41" width="5.42578125" customWidth="1"/>
-    <col min="42" max="44" width="10.85546875" customWidth="1"/>
+    <col min="38" max="38" width="5.6640625" customWidth="1"/>
+    <col min="39" max="39" width="13.6640625" customWidth="1"/>
+    <col min="40" max="40" width="4.5546875" customWidth="1"/>
+    <col min="41" max="41" width="5.44140625" customWidth="1"/>
+    <col min="42" max="44" width="10.88671875" customWidth="1"/>
     <col min="45" max="45" width="6" customWidth="1"/>
-    <col min="46" max="46" width="6.140625" customWidth="1"/>
+    <col min="46" max="46" width="6.109375" customWidth="1"/>
     <col min="47" max="47" width="4" customWidth="1"/>
-    <col min="48" max="48" width="4.140625" customWidth="1"/>
-    <col min="49" max="50" width="5.28515625" customWidth="1"/>
-    <col min="51" max="51" width="6.7109375" customWidth="1"/>
-    <col min="52" max="52" width="3.85546875" customWidth="1"/>
+    <col min="48" max="48" width="4.109375" customWidth="1"/>
+    <col min="49" max="50" width="5.33203125" customWidth="1"/>
+    <col min="51" max="51" width="6.6640625" customWidth="1"/>
+    <col min="52" max="52" width="3.88671875" customWidth="1"/>
     <col min="53" max="53" width="4" customWidth="1"/>
-    <col min="54" max="54" width="4.7109375" customWidth="1"/>
+    <col min="54" max="54" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="92.45" customHeight="1">
+    <row r="1" spans="1:54" ht="92.4" customHeight="1">
       <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
@@ -40854,7 +40855,7 @@
       <c r="AI1" s="69"/>
       <c r="AJ1" s="69"/>
       <c r="AK1" s="69" t="s">
-        <v>259</v>
+        <v>367</v>
       </c>
       <c r="AL1" s="44" t="s">
         <v>244</v>
@@ -40863,10 +40864,10 @@
         <v>1</v>
       </c>
       <c r="AN1" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="AO1" s="39" t="s">
         <v>260</v>
-      </c>
-      <c r="AO1" s="39" t="s">
-        <v>261</v>
       </c>
       <c r="AP1" s="39" t="s">
         <v>39</v>
@@ -40896,7 +40897,7 @@
         <v>47</v>
       </c>
       <c r="AY1" s="45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AZ1" s="45" t="s">
         <v>53</v>
@@ -40911,7 +40912,7 @@
     <row r="2" spans="1:54">
       <c r="A2" s="101"/>
       <c r="B2" s="46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C2" s="47">
         <v>2025</v>
@@ -41056,7 +41057,7 @@
     <row r="3" spans="1:54">
       <c r="A3" s="101"/>
       <c r="B3" s="46" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C3" s="47">
         <v>2025</v>
@@ -41201,7 +41202,7 @@
     <row r="4" spans="1:54">
       <c r="A4" s="101"/>
       <c r="B4" s="46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C4" s="47">
         <v>2025</v>
@@ -41346,7 +41347,7 @@
     <row r="5" spans="1:54">
       <c r="A5" s="101"/>
       <c r="B5" s="53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C5" s="54">
         <v>2025</v>
@@ -41491,7 +41492,7 @@
     <row r="6" spans="1:54">
       <c r="A6" s="101"/>
       <c r="B6" s="53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C6" s="54">
         <v>2025</v>
@@ -41636,7 +41637,7 @@
     <row r="7" spans="1:54">
       <c r="A7" s="101"/>
       <c r="B7" s="53" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7" s="54">
         <v>2025</v>
@@ -41781,7 +41782,7 @@
     <row r="8" spans="1:54">
       <c r="A8" s="101"/>
       <c r="B8" s="53" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C8" s="54">
         <v>2025</v>
@@ -41926,7 +41927,7 @@
     <row r="9" spans="1:54">
       <c r="A9" s="101"/>
       <c r="B9" s="53" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="54">
         <v>2025</v>
@@ -42071,7 +42072,7 @@
     <row r="10" spans="1:54">
       <c r="A10" s="101"/>
       <c r="B10" s="53" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C10" s="54">
         <v>2025</v>
@@ -42216,7 +42217,7 @@
     <row r="11" spans="1:54">
       <c r="A11" s="101"/>
       <c r="B11" s="53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C11" s="47">
         <v>2024</v>
@@ -42361,7 +42362,7 @@
     <row r="12" spans="1:54">
       <c r="A12" s="101"/>
       <c r="B12" s="53" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C12" s="47">
         <v>2024</v>
@@ -42506,7 +42507,7 @@
     <row r="13" spans="1:54">
       <c r="A13" s="101"/>
       <c r="B13" s="53" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C13" s="47">
         <v>2024</v>
@@ -42651,7 +42652,7 @@
     <row r="14" spans="1:54">
       <c r="A14" s="101"/>
       <c r="B14" s="53" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C14" s="47">
         <v>2024</v>
@@ -42796,7 +42797,7 @@
     <row r="15" spans="1:54">
       <c r="A15" s="101"/>
       <c r="B15" s="53" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C15" s="47">
         <v>2024</v>
@@ -42941,7 +42942,7 @@
     <row r="16" spans="1:54">
       <c r="A16" s="101"/>
       <c r="B16" s="53" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C16" s="54">
         <v>2024</v>
@@ -43086,7 +43087,7 @@
     <row r="17" spans="1:54">
       <c r="A17" s="101"/>
       <c r="B17" s="53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C17" s="54">
         <v>2024</v>
@@ -43231,7 +43232,7 @@
     <row r="18" spans="1:54">
       <c r="A18" s="101"/>
       <c r="B18" s="53" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C18" s="54">
         <v>2024</v>
@@ -43376,7 +43377,7 @@
     <row r="19" spans="1:54">
       <c r="A19" s="101"/>
       <c r="B19" s="53" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="54">
         <v>2024</v>
@@ -43521,7 +43522,7 @@
     <row r="20" spans="1:54">
       <c r="A20" s="101"/>
       <c r="B20" s="57" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C20" s="54">
         <v>2025</v>
@@ -43666,7 +43667,7 @@
     <row r="21" spans="1:54">
       <c r="A21" s="101"/>
       <c r="B21" s="57" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="54">
         <v>2025</v>
@@ -43811,7 +43812,7 @@
     <row r="22" spans="1:54">
       <c r="A22" s="101"/>
       <c r="B22" s="59" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="54">
         <v>2024</v>
@@ -43950,7 +43951,7 @@
     <row r="23" spans="1:54">
       <c r="A23" s="101"/>
       <c r="B23" s="59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C23" s="54">
         <v>2024</v>
@@ -44089,7 +44090,7 @@
     <row r="24" spans="1:54">
       <c r="A24" s="101"/>
       <c r="B24" s="59" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C24" s="54">
         <v>2024</v>
@@ -44228,7 +44229,7 @@
     <row r="25" spans="1:54">
       <c r="A25" s="101"/>
       <c r="B25" s="59" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C25" s="54">
         <v>2024</v>
@@ -44367,7 +44368,7 @@
     <row r="26" spans="1:54">
       <c r="A26" s="101"/>
       <c r="B26" s="59" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C26" s="54">
         <v>2024</v>
@@ -44506,7 +44507,7 @@
     <row r="27" spans="1:54">
       <c r="A27" s="101"/>
       <c r="B27" s="59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C27" s="54">
         <v>2024</v>
@@ -44645,7 +44646,7 @@
     <row r="28" spans="1:54">
       <c r="A28" s="101"/>
       <c r="B28" s="59" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C28" s="54">
         <v>2024</v>
@@ -44786,7 +44787,7 @@
     <row r="29" spans="1:54">
       <c r="A29" s="101"/>
       <c r="B29" s="59" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C29" s="54">
         <v>2024</v>
@@ -44927,7 +44928,7 @@
     <row r="30" spans="1:54">
       <c r="A30" s="101"/>
       <c r="B30" s="59" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C30" s="54">
         <v>2024</v>
@@ -45066,7 +45067,7 @@
     <row r="31" spans="1:54">
       <c r="A31" s="101"/>
       <c r="B31" s="61" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C31" s="47">
         <v>2025</v>
@@ -45205,7 +45206,7 @@
     <row r="32" spans="1:54">
       <c r="A32" s="101"/>
       <c r="B32" s="59" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C32" s="54">
         <v>2025</v>
@@ -45346,7 +45347,7 @@
     <row r="33" spans="1:54">
       <c r="A33" s="101"/>
       <c r="B33" s="59" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C33" s="54">
         <v>2025</v>
@@ -45489,7 +45490,7 @@
     <row r="34" spans="1:54">
       <c r="A34" s="101"/>
       <c r="B34" s="59" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C34" s="54">
         <v>2025</v>
@@ -45628,7 +45629,7 @@
     <row r="35" spans="1:54">
       <c r="A35" s="101"/>
       <c r="B35" s="59" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C35" s="54">
         <v>2025</v>
@@ -45767,7 +45768,7 @@
     <row r="36" spans="1:54">
       <c r="A36" s="101"/>
       <c r="B36" s="59" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C36" s="54">
         <v>2025</v>
@@ -45906,7 +45907,7 @@
     <row r="37" spans="1:54">
       <c r="A37" s="101"/>
       <c r="B37" s="59" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C37" s="54">
         <v>2025</v>
@@ -46045,7 +46046,7 @@
     <row r="38" spans="1:54">
       <c r="A38" s="101"/>
       <c r="B38" s="59" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C38" s="54">
         <v>2025</v>
@@ -46184,7 +46185,7 @@
     <row r="39" spans="1:54">
       <c r="A39" s="101"/>
       <c r="B39" s="59" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C39" s="54">
         <v>2025</v>
@@ -46323,7 +46324,7 @@
     <row r="40" spans="1:54">
       <c r="A40" s="101"/>
       <c r="B40" s="62" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C40" s="58">
         <v>2024</v>
@@ -46462,7 +46463,7 @@
     <row r="41" spans="1:54">
       <c r="A41" s="101"/>
       <c r="B41" s="62" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C41" s="54">
         <v>2024</v>
@@ -46607,7 +46608,7 @@
     <row r="42" spans="1:54">
       <c r="A42" s="101"/>
       <c r="B42" s="62" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C42" s="54">
         <v>2025</v>
@@ -46748,7 +46749,7 @@
     <row r="43" spans="1:54">
       <c r="A43" s="101"/>
       <c r="B43" s="63" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C43" s="54">
         <v>2025</v>
@@ -46893,7 +46894,7 @@
     <row r="44" spans="1:54">
       <c r="A44" s="101"/>
       <c r="B44" s="63" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C44" s="54">
         <v>2025</v>
@@ -47032,7 +47033,7 @@
     <row r="45" spans="1:54">
       <c r="A45" s="101"/>
       <c r="B45" s="63" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C45" s="54">
         <v>2025</v>
@@ -47171,7 +47172,7 @@
     <row r="46" spans="1:54">
       <c r="A46" s="101"/>
       <c r="B46" s="63" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C46" s="54">
         <v>2025</v>
@@ -47312,7 +47313,7 @@
     <row r="47" spans="1:54">
       <c r="A47" s="101"/>
       <c r="B47" s="63" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C47" s="54">
         <v>2025</v>
@@ -47362,7 +47363,7 @@
         <v>-1</v>
       </c>
       <c r="T47" s="54" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U47" s="54"/>
       <c r="V47" s="54">
@@ -47459,7 +47460,7 @@
     <row r="48" spans="1:54">
       <c r="A48" s="101"/>
       <c r="B48" s="63" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C48" s="54">
         <v>2025</v>
@@ -47598,7 +47599,7 @@
     <row r="49" spans="1:54">
       <c r="A49" s="101"/>
       <c r="B49" s="63" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C49" s="54">
         <v>2025</v>
@@ -47737,7 +47738,7 @@
     <row r="50" spans="1:54">
       <c r="A50" s="101"/>
       <c r="B50" s="63" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C50" s="54">
         <v>2025</v>
@@ -47876,7 +47877,7 @@
     <row r="51" spans="1:54">
       <c r="A51" s="101"/>
       <c r="B51" s="63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C51" s="54">
         <v>2025</v>
@@ -48015,7 +48016,7 @@
     <row r="52" spans="1:54">
       <c r="A52" s="101"/>
       <c r="B52" s="63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C52" s="54">
         <v>2025</v>
@@ -48154,7 +48155,7 @@
     <row r="53" spans="1:54">
       <c r="A53" s="101"/>
       <c r="B53" s="63" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C53" s="54">
         <v>2025</v>
@@ -48293,7 +48294,7 @@
     <row r="54" spans="1:54">
       <c r="A54" s="101"/>
       <c r="B54" s="63" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C54" s="54">
         <v>2025</v>
@@ -48432,7 +48433,7 @@
     <row r="55" spans="1:54">
       <c r="A55" s="101"/>
       <c r="B55" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C55" s="47">
         <v>2025</v>
@@ -48571,7 +48572,7 @@
     <row r="56" spans="1:54">
       <c r="A56" s="101"/>
       <c r="B56" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C56" s="47">
         <v>2025</v>
@@ -48710,7 +48711,7 @@
     <row r="57" spans="1:54">
       <c r="A57" s="101"/>
       <c r="B57" s="102" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C57" s="47">
         <v>2025</v>
@@ -48847,7 +48848,7 @@
     <row r="58" spans="1:54">
       <c r="A58" s="101"/>
       <c r="B58" s="102" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C58" s="47">
         <v>2025</v>
@@ -48983,10 +48984,10 @@
     </row>
     <row r="59" spans="1:54">
       <c r="A59" s="101" t="s">
+        <v>320</v>
+      </c>
+      <c r="B59" s="104" t="s">
         <v>321</v>
-      </c>
-      <c r="B59" s="104" t="s">
-        <v>322</v>
       </c>
       <c r="C59" s="47">
         <v>2025</v>
@@ -49122,10 +49123,10 @@
     </row>
     <row r="60" spans="1:54">
       <c r="A60" s="101" t="s">
+        <v>322</v>
+      </c>
+      <c r="B60" s="104" t="s">
         <v>323</v>
-      </c>
-      <c r="B60" s="104" t="s">
-        <v>324</v>
       </c>
       <c r="C60" s="47">
         <v>2025</v>
@@ -49260,7 +49261,7 @@
     <row r="61" spans="1:54">
       <c r="A61" s="101"/>
       <c r="B61" s="104" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C61" s="47">
         <v>2025</v>
@@ -49397,7 +49398,7 @@
     <row r="62" spans="1:54">
       <c r="A62" s="101"/>
       <c r="B62" s="104" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C62" s="47">
         <v>2025</v>
@@ -49532,7 +49533,7 @@
     <row r="63" spans="1:54">
       <c r="A63" s="101"/>
       <c r="B63" s="104" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C63" s="58">
         <v>2025</v>
@@ -49666,10 +49667,10 @@
     </row>
     <row r="64" spans="1:54">
       <c r="A64" s="101" t="s">
+        <v>327</v>
+      </c>
+      <c r="B64" s="101" t="s">
         <v>328</v>
-      </c>
-      <c r="B64" s="101" t="s">
-        <v>329</v>
       </c>
       <c r="C64" s="101" t="s">
         <v>162</v>
@@ -49815,10 +49816,10 @@
     </row>
     <row r="65" spans="1:54">
       <c r="A65" s="101" t="s">
+        <v>329</v>
+      </c>
+      <c r="B65" s="101" t="s">
         <v>330</v>
-      </c>
-      <c r="B65" s="101" t="s">
-        <v>331</v>
       </c>
       <c r="C65" s="101" t="s">
         <v>162</v>
@@ -49964,10 +49965,10 @@
     </row>
     <row r="66" spans="1:54">
       <c r="A66" s="101" t="s">
+        <v>331</v>
+      </c>
+      <c r="B66" s="101" t="s">
         <v>332</v>
-      </c>
-      <c r="B66" s="101" t="s">
-        <v>333</v>
       </c>
       <c r="C66" s="101" t="s">
         <v>162</v>
@@ -50113,10 +50114,10 @@
     </row>
     <row r="67" spans="1:54">
       <c r="A67" s="101" t="s">
+        <v>333</v>
+      </c>
+      <c r="B67" s="101" t="s">
         <v>334</v>
-      </c>
-      <c r="B67" s="101" t="s">
-        <v>335</v>
       </c>
       <c r="C67" s="101" t="s">
         <v>162</v>
@@ -50262,10 +50263,10 @@
     </row>
     <row r="68" spans="1:54">
       <c r="A68" s="101" t="s">
+        <v>335</v>
+      </c>
+      <c r="B68" s="101" t="s">
         <v>336</v>
-      </c>
-      <c r="B68" s="101" t="s">
-        <v>337</v>
       </c>
       <c r="C68" s="101" t="s">
         <v>162</v>
@@ -50409,10 +50410,10 @@
     </row>
     <row r="69" spans="1:54">
       <c r="A69" s="101" t="s">
+        <v>337</v>
+      </c>
+      <c r="B69" s="101" t="s">
         <v>338</v>
-      </c>
-      <c r="B69" s="101" t="s">
-        <v>339</v>
       </c>
       <c r="C69" s="101" t="s">
         <v>162</v>
@@ -50525,7 +50526,7 @@
         <v>Pos</v>
       </c>
       <c r="AM69" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AN69" s="101">
         <v>24</v>
@@ -50559,10 +50560,10 @@
     </row>
     <row r="70" spans="1:54">
       <c r="A70" s="101" t="s">
+        <v>339</v>
+      </c>
+      <c r="B70" s="101" t="s">
         <v>340</v>
-      </c>
-      <c r="B70" s="101" t="s">
-        <v>341</v>
       </c>
       <c r="C70" s="101" t="s">
         <v>162</v>
@@ -50675,7 +50676,7 @@
         <v>Neg</v>
       </c>
       <c r="AM70" s="107" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AN70" s="101">
         <v>25</v>
@@ -50707,10 +50708,10 @@
     </row>
     <row r="71" spans="1:54">
       <c r="A71" s="101" t="s">
+        <v>341</v>
+      </c>
+      <c r="B71" s="101" t="s">
         <v>342</v>
-      </c>
-      <c r="B71" s="101" t="s">
-        <v>343</v>
       </c>
       <c r="C71" s="101" t="s">
         <v>162</v>
@@ -50823,7 +50824,7 @@
         <v>Neg</v>
       </c>
       <c r="AM71" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN71" s="101">
         <v>25</v>
@@ -50855,10 +50856,10 @@
     </row>
     <row r="72" spans="1:54">
       <c r="A72" s="101" t="s">
+        <v>343</v>
+      </c>
+      <c r="B72" s="101" t="s">
         <v>344</v>
-      </c>
-      <c r="B72" s="101" t="s">
-        <v>345</v>
       </c>
       <c r="C72" s="101" t="s">
         <v>162</v>
@@ -50971,7 +50972,7 @@
         <v>Pos</v>
       </c>
       <c r="AM72" s="107" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AN72" s="101">
         <v>26</v>
@@ -51003,10 +51004,10 @@
     </row>
     <row r="73" spans="1:54">
       <c r="A73" s="101" t="s">
+        <v>345</v>
+      </c>
+      <c r="B73" s="101" t="s">
         <v>346</v>
-      </c>
-      <c r="B73" s="101" t="s">
-        <v>347</v>
       </c>
       <c r="C73" s="101" t="s">
         <v>162</v>
@@ -51119,7 +51120,7 @@
         <v>Neg</v>
       </c>
       <c r="AM73" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AN73" s="101">
         <v>27</v>
@@ -51151,10 +51152,10 @@
     </row>
     <row r="74" spans="1:54">
       <c r="A74" s="101" t="s">
+        <v>347</v>
+      </c>
+      <c r="B74" s="101" t="s">
         <v>348</v>
-      </c>
-      <c r="B74" s="101" t="s">
-        <v>349</v>
       </c>
       <c r="C74" s="101" t="s">
         <v>162</v>
@@ -51267,7 +51268,7 @@
         <v>Pos</v>
       </c>
       <c r="AM74" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN74" s="101">
         <v>6</v>
@@ -51299,10 +51300,10 @@
     </row>
     <row r="75" spans="1:54">
       <c r="A75" s="101" t="s">
+        <v>349</v>
+      </c>
+      <c r="B75" s="101" t="s">
         <v>350</v>
-      </c>
-      <c r="B75" s="101" t="s">
-        <v>351</v>
       </c>
       <c r="C75" s="101" t="s">
         <v>162</v>
@@ -51415,7 +51416,7 @@
         <v>Neg</v>
       </c>
       <c r="AM75" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AN75" s="101">
         <v>11</v>
@@ -51445,10 +51446,10 @@
     </row>
     <row r="76" spans="1:54">
       <c r="A76" s="101" t="s">
+        <v>351</v>
+      </c>
+      <c r="B76" s="101" t="s">
         <v>352</v>
-      </c>
-      <c r="B76" s="101" t="s">
-        <v>353</v>
       </c>
       <c r="C76" s="101" t="s">
         <v>162</v>
@@ -51561,7 +51562,7 @@
         <v>Neg</v>
       </c>
       <c r="AM76" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AN76" s="101">
         <v>12</v>
@@ -51591,10 +51592,10 @@
     </row>
     <row r="77" spans="1:54">
       <c r="A77" s="101" t="s">
+        <v>353</v>
+      </c>
+      <c r="B77" s="101" t="s">
         <v>354</v>
-      </c>
-      <c r="B77" s="101" t="s">
-        <v>355</v>
       </c>
       <c r="C77" s="101" t="s">
         <v>162</v>
@@ -51707,7 +51708,7 @@
         <v>Pos</v>
       </c>
       <c r="AM77" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AN77" s="101">
         <v>13</v>
@@ -51737,10 +51738,10 @@
     </row>
     <row r="78" spans="1:54">
       <c r="A78" s="101" t="s">
+        <v>355</v>
+      </c>
+      <c r="B78" s="101" t="s">
         <v>356</v>
-      </c>
-      <c r="B78" s="101" t="s">
-        <v>357</v>
       </c>
       <c r="C78" s="101" t="s">
         <v>162</v>
@@ -51851,7 +51852,7 @@
         <v>0</v>
       </c>
       <c r="AM78" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN78" s="101">
         <v>18</v>
@@ -51881,10 +51882,10 @@
     </row>
     <row r="79" spans="1:54">
       <c r="A79" s="101" t="s">
+        <v>357</v>
+      </c>
+      <c r="B79" s="101" t="s">
         <v>358</v>
-      </c>
-      <c r="B79" s="101" t="s">
-        <v>359</v>
       </c>
       <c r="C79" s="101" t="s">
         <v>162</v>
@@ -51995,7 +51996,7 @@
         <v>0</v>
       </c>
       <c r="AM79" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AN79" s="101">
         <v>26</v>
@@ -52025,10 +52026,10 @@
     </row>
     <row r="80" spans="1:54">
       <c r="A80" s="101" t="s">
+        <v>359</v>
+      </c>
+      <c r="B80" s="101" t="s">
         <v>360</v>
-      </c>
-      <c r="B80" s="101" t="s">
-        <v>361</v>
       </c>
       <c r="C80" s="101" t="s">
         <v>162</v>
@@ -52139,7 +52140,7 @@
         <v>0</v>
       </c>
       <c r="AM80" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AN80" s="101">
         <v>27</v>
@@ -52169,10 +52170,10 @@
     </row>
     <row r="81" spans="1:54">
       <c r="A81" s="101" t="s">
+        <v>361</v>
+      </c>
+      <c r="B81" s="101" t="s">
         <v>362</v>
-      </c>
-      <c r="B81" s="101" t="s">
-        <v>363</v>
       </c>
       <c r="C81" s="101" t="s">
         <v>162</v>
@@ -52283,7 +52284,7 @@
         <v>0</v>
       </c>
       <c r="AM81" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN81" s="101">
         <v>27</v>
@@ -52313,10 +52314,10 @@
     </row>
     <row r="82" spans="1:54">
       <c r="A82" s="101" t="s">
+        <v>363</v>
+      </c>
+      <c r="B82" s="101" t="s">
         <v>364</v>
-      </c>
-      <c r="B82" s="101" t="s">
-        <v>365</v>
       </c>
       <c r="C82" s="101" t="s">
         <v>162</v>
@@ -52380,10 +52381,10 @@
         <v>1</v>
       </c>
       <c r="X82" s="101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y82" s="101">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z82" s="101">
         <v>2</v>
@@ -52427,7 +52428,7 @@
         <v>0</v>
       </c>
       <c r="AM82" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AN82" s="101">
         <v>27</v>
@@ -59969,52 +59970,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:DA484"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" customWidth="1"/>
-    <col min="25" max="25" width="5.5703125" customWidth="1"/>
-    <col min="26" max="26" width="3.42578125" customWidth="1"/>
-    <col min="27" max="27" width="5.85546875" customWidth="1"/>
-    <col min="28" max="28" width="7.28515625" customWidth="1"/>
-    <col min="29" max="29" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="7.140625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="5.5703125" customWidth="1"/>
-    <col min="34" max="34" width="6.28515625" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" customWidth="1"/>
-    <col min="36" max="36" width="4.42578125" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" customWidth="1"/>
+    <col min="20" max="20" width="5.33203125" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.33203125" customWidth="1"/>
+    <col min="25" max="25" width="5.5546875" customWidth="1"/>
+    <col min="26" max="26" width="3.44140625" customWidth="1"/>
+    <col min="27" max="27" width="5.88671875" customWidth="1"/>
+    <col min="28" max="28" width="7.33203125" customWidth="1"/>
+    <col min="29" max="29" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.109375" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="5.5546875" customWidth="1"/>
+    <col min="34" max="34" width="6.33203125" customWidth="1"/>
+    <col min="35" max="35" width="8.88671875" customWidth="1"/>
+    <col min="36" max="36" width="4.44140625" customWidth="1"/>
     <col min="38" max="42" width="13" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="1.5703125" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="1.5546875" hidden="1" customWidth="1"/>
     <col min="53" max="54" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104" ht="92.45" customHeight="1">
+    <row r="1" spans="1:104" ht="92.4" customHeight="1">
       <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
@@ -60070,7 +60071,7 @@
         <v>17</v>
       </c>
       <c r="S1" s="72" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="T1" s="72" t="s">
         <v>19</v>
@@ -60127,13 +60128,13 @@
         <v>36</v>
       </c>
       <c r="AL1" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="AM1" s="72" t="s">
         <v>260</v>
       </c>
-      <c r="AM1" s="72" t="s">
-        <v>261</v>
-      </c>
       <c r="AN1" s="72" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AO1" s="72" t="s">
         <v>42</v>

--- a/General.xlsx
+++ b/General.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CapitalFund1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14A5690-B6E9-4A0E-96F5-4D1D17E6013A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="23235" windowHeight="12435" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="IPOSME" sheetId="1" r:id="rId1"/>
     <sheet name="IPOMB" sheetId="2" r:id="rId2"/>
     <sheet name="IPOSME (2)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1131,7 +1130,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -2540,83 +2539,83 @@
     </dxf>
   </dxfs>
   <tableStyles count="19" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="108"/>
       <tableStyleElement type="firstRowStripe" dxfId="107"/>
       <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="SME IPO v1-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="105"/>
       <tableStyleElement type="firstRowStripe" dxfId="104"/>
       <tableStyleElement type="secondRowStripe" dxfId="103"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+    <tableStyle name="SME IPO v1-style 2" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="102"/>
       <tableStyleElement type="secondRowStripe" dxfId="101"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+    <tableStyle name="SME IPO v1-style 3" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="100"/>
       <tableStyleElement type="secondRowStripe" dxfId="99"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+    <tableStyle name="SME IPO v1-style 4" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="98"/>
       <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
+    <tableStyle name="SME IPO v1-style 5" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="96"/>
       <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
-    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
+    <tableStyle name="SME IPO v1-style 6" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="94"/>
       <tableStyleElement type="secondRowStripe" dxfId="93"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
+    <tableStyle name="SME IPO v2-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="92"/>
       <tableStyleElement type="firstRowStripe" dxfId="91"/>
       <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
+    <tableStyle name="SME IPO v2-style 2" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="89"/>
       <tableStyleElement type="secondRowStripe" dxfId="88"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
+    <tableStyle name="SME IPO v2-style 3" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="87"/>
       <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
+    <tableStyle name="SME IPO v2-style 4" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="85"/>
       <tableStyleElement type="secondRowStripe" dxfId="84"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
+    <tableStyle name="SME IPO v2-style 5" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="83"/>
       <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
-    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
+    <tableStyle name="SME IPO v2-style 6" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="81"/>
       <tableStyleElement type="secondRowStripe" dxfId="80"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
+    <tableStyle name="SME IPO v3-style" pivot="0" count="3">
       <tableStyleElement type="headerRow" dxfId="79"/>
       <tableStyleElement type="firstRowStripe" dxfId="78"/>
       <tableStyleElement type="secondRowStripe" dxfId="77"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
+    <tableStyle name="SME IPO v3-style 2" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="76"/>
       <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
+    <tableStyle name="SME IPO v3-style 3" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="74"/>
       <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF10000000}">
+    <tableStyle name="SME IPO v3-style 4" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="72"/>
       <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF11000000}">
+    <tableStyle name="SME IPO v3-style 5" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="70"/>
       <tableStyleElement type="secondRowStripe" dxfId="69"/>
     </tableStyle>
-    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF12000000}">
+    <tableStyle name="SME IPO v3-style 6" pivot="0" count="2">
       <tableStyleElement type="firstRowStripe" dxfId="68"/>
       <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
@@ -2829,52 +2828,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:DF466"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
-    <col min="4" max="4" width="3.88671875" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="6.6640625" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="6.6640625" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" style="108" customWidth="1"/>
-    <col min="20" max="20" width="5.33203125" customWidth="1"/>
-    <col min="21" max="21" width="4.6640625" customWidth="1"/>
-    <col min="22" max="22" width="4.33203125" customWidth="1"/>
-    <col min="23" max="23" width="6.6640625" customWidth="1"/>
-    <col min="24" max="24" width="7.33203125" customWidth="1"/>
-    <col min="25" max="25" width="10.33203125" customWidth="1"/>
-    <col min="26" max="26" width="8.5546875" customWidth="1"/>
-    <col min="27" max="27" width="5.88671875" customWidth="1"/>
-    <col min="28" max="28" width="7.33203125" customWidth="1"/>
-    <col min="29" max="29" width="5.88671875" customWidth="1"/>
-    <col min="30" max="30" width="6.6640625" customWidth="1"/>
-    <col min="31" max="31" width="7.6640625" customWidth="1"/>
-    <col min="32" max="32" width="8.44140625" customWidth="1"/>
-    <col min="33" max="33" width="7.33203125" customWidth="1"/>
-    <col min="34" max="36" width="6.33203125" customWidth="1"/>
-    <col min="37" max="37" width="8.88671875" customWidth="1"/>
-    <col min="38" max="38" width="4.44140625" customWidth="1"/>
-    <col min="39" max="39" width="20.109375" customWidth="1"/>
-    <col min="40" max="40" width="6.5546875" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" style="108" customWidth="1"/>
+    <col min="20" max="20" width="5.28515625" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" customWidth="1"/>
+    <col min="25" max="25" width="10.28515625" customWidth="1"/>
+    <col min="26" max="26" width="8.5703125" customWidth="1"/>
+    <col min="27" max="27" width="5.85546875" customWidth="1"/>
+    <col min="28" max="28" width="7.28515625" customWidth="1"/>
+    <col min="29" max="29" width="5.85546875" customWidth="1"/>
+    <col min="30" max="30" width="6.7109375" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" customWidth="1"/>
+    <col min="32" max="32" width="8.42578125" customWidth="1"/>
+    <col min="33" max="33" width="7.28515625" customWidth="1"/>
+    <col min="34" max="36" width="6.28515625" customWidth="1"/>
+    <col min="37" max="37" width="8.85546875" customWidth="1"/>
+    <col min="38" max="38" width="4.42578125" customWidth="1"/>
+    <col min="39" max="39" width="20.140625" customWidth="1"/>
+    <col min="40" max="40" width="6.5703125" customWidth="1"/>
     <col min="42" max="48" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" ht="92.4" customHeight="1">
+    <row r="1" spans="1:59" ht="92.45" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -40697,59 +40696,59 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BB166"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" customWidth="1"/>
-    <col min="4" max="4" width="4.33203125" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="4.88671875" customWidth="1"/>
-    <col min="11" max="11" width="6.109375" customWidth="1"/>
-    <col min="12" max="12" width="4.109375" customWidth="1"/>
-    <col min="13" max="14" width="6.5546875" customWidth="1"/>
-    <col min="15" max="15" width="7.5546875" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" customWidth="1"/>
+    <col min="12" max="12" width="4.140625" customWidth="1"/>
+    <col min="13" max="14" width="6.5703125" customWidth="1"/>
+    <col min="15" max="15" width="7.5703125" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.109375" customWidth="1"/>
+    <col min="18" max="18" width="6.140625" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="5.5546875" customWidth="1"/>
-    <col min="22" max="22" width="6.109375" customWidth="1"/>
-    <col min="23" max="24" width="6.6640625" customWidth="1"/>
-    <col min="25" max="25" width="8.33203125" customWidth="1"/>
-    <col min="26" max="26" width="5.44140625" customWidth="1"/>
-    <col min="27" max="27" width="5.109375" customWidth="1"/>
-    <col min="28" max="28" width="4.5546875" customWidth="1"/>
-    <col min="29" max="29" width="4.88671875" customWidth="1"/>
-    <col min="30" max="30" width="6.5546875" customWidth="1"/>
-    <col min="31" max="31" width="5.6640625" customWidth="1"/>
-    <col min="32" max="32" width="6.33203125" customWidth="1"/>
-    <col min="33" max="36" width="4.88671875" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="5.5703125" customWidth="1"/>
+    <col min="22" max="22" width="6.140625" customWidth="1"/>
+    <col min="23" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="8.28515625" customWidth="1"/>
+    <col min="26" max="26" width="5.42578125" customWidth="1"/>
+    <col min="27" max="27" width="5.140625" customWidth="1"/>
+    <col min="28" max="28" width="4.5703125" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" customWidth="1"/>
+    <col min="30" max="30" width="6.5703125" customWidth="1"/>
+    <col min="31" max="31" width="5.7109375" customWidth="1"/>
+    <col min="32" max="32" width="6.28515625" customWidth="1"/>
+    <col min="33" max="36" width="4.85546875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
-    <col min="38" max="38" width="5.6640625" customWidth="1"/>
-    <col min="39" max="39" width="13.6640625" customWidth="1"/>
-    <col min="40" max="40" width="4.5546875" customWidth="1"/>
-    <col min="41" max="41" width="5.44140625" customWidth="1"/>
-    <col min="42" max="44" width="10.88671875" customWidth="1"/>
+    <col min="38" max="38" width="5.7109375" customWidth="1"/>
+    <col min="39" max="39" width="13.7109375" customWidth="1"/>
+    <col min="40" max="40" width="4.5703125" customWidth="1"/>
+    <col min="41" max="41" width="5.42578125" customWidth="1"/>
+    <col min="42" max="44" width="10.85546875" customWidth="1"/>
     <col min="45" max="45" width="6" customWidth="1"/>
-    <col min="46" max="46" width="6.109375" customWidth="1"/>
+    <col min="46" max="46" width="6.140625" customWidth="1"/>
     <col min="47" max="47" width="4" customWidth="1"/>
-    <col min="48" max="48" width="4.109375" customWidth="1"/>
-    <col min="49" max="50" width="5.33203125" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" customWidth="1"/>
-    <col min="52" max="52" width="3.88671875" customWidth="1"/>
+    <col min="48" max="48" width="4.140625" customWidth="1"/>
+    <col min="49" max="50" width="5.28515625" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" customWidth="1"/>
+    <col min="52" max="52" width="3.85546875" customWidth="1"/>
     <col min="53" max="53" width="4" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" customWidth="1"/>
+    <col min="54" max="54" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="92.4" customHeight="1">
+    <row r="1" spans="1:54" ht="92.45" customHeight="1">
       <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
@@ -52381,17 +52380,17 @@
         <v>1</v>
       </c>
       <c r="X82" s="101">
-        <v>3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="Y82" s="101">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z82" s="101">
         <v>2</v>
       </c>
       <c r="AA82" s="51">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB82" s="101">
         <v>0.25</v>
@@ -52415,13 +52414,13 @@
       </c>
       <c r="AH82" s="49">
         <f t="shared" si="27"/>
-        <v>6.6333333333333329</v>
+        <v>7.6333333333333329</v>
       </c>
       <c r="AI82" s="49"/>
       <c r="AJ82" s="49"/>
       <c r="AK82" s="49">
         <f t="shared" si="28"/>
-        <v>23.283333333333331</v>
+        <v>24.283333333333331</v>
       </c>
       <c r="AL82" s="2">
         <f t="shared" si="29"/>
@@ -59970,52 +59969,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:DA484"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
-    <col min="4" max="4" width="3.88671875" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="6.6640625" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="6.6640625" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" customWidth="1"/>
-    <col min="20" max="20" width="5.33203125" customWidth="1"/>
-    <col min="21" max="21" width="4.6640625" customWidth="1"/>
-    <col min="22" max="22" width="4.33203125" customWidth="1"/>
-    <col min="23" max="23" width="6.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.33203125" customWidth="1"/>
-    <col min="25" max="25" width="5.5546875" customWidth="1"/>
-    <col min="26" max="26" width="3.44140625" customWidth="1"/>
-    <col min="27" max="27" width="5.88671875" customWidth="1"/>
-    <col min="28" max="28" width="7.33203125" customWidth="1"/>
-    <col min="29" max="29" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="6.6640625" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="7.109375" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="5.5546875" customWidth="1"/>
-    <col min="34" max="34" width="6.33203125" customWidth="1"/>
-    <col min="35" max="35" width="8.88671875" customWidth="1"/>
-    <col min="36" max="36" width="4.44140625" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" customWidth="1"/>
+    <col min="20" max="20" width="5.28515625" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.28515625" customWidth="1"/>
+    <col min="25" max="25" width="5.5703125" customWidth="1"/>
+    <col min="26" max="26" width="3.42578125" customWidth="1"/>
+    <col min="27" max="27" width="5.85546875" customWidth="1"/>
+    <col min="28" max="28" width="7.28515625" customWidth="1"/>
+    <col min="29" max="29" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="6.7109375" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="5.5703125" customWidth="1"/>
+    <col min="34" max="34" width="6.28515625" customWidth="1"/>
+    <col min="35" max="35" width="8.85546875" customWidth="1"/>
+    <col min="36" max="36" width="4.42578125" customWidth="1"/>
     <col min="38" max="42" width="13" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="1.5546875" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="1.5703125" hidden="1" customWidth="1"/>
     <col min="53" max="54" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104" ht="92.4" customHeight="1">
+    <row r="1" spans="1:104" ht="92.45" customHeight="1">
       <c r="A1" s="75" t="s">
         <v>0</v>
       </c>

--- a/General.xlsx
+++ b/General.xlsx
@@ -52236,24 +52236,24 @@
         <v>1</v>
       </c>
       <c r="X81" s="101">
-        <v>5</v>
+        <v>1.18</v>
       </c>
       <c r="Y81" s="101">
-        <v>9</v>
+        <v>13.4</v>
       </c>
       <c r="Z81" s="101">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="AA81" s="51">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB81" s="101">
-        <v>3.77</v>
+        <v>2.59</v>
       </c>
       <c r="AC81" s="52">
         <f t="shared" si="25"/>
-        <v>1.2566666666666666</v>
+        <v>0.86333333333333329</v>
       </c>
       <c r="AD81" s="101">
         <v>100</v>
@@ -52270,13 +52270,13 @@
       </c>
       <c r="AH81" s="49">
         <f t="shared" si="27"/>
-        <v>3.3566666666666665</v>
+        <v>3.9633333333333329</v>
       </c>
       <c r="AI81" s="49"/>
       <c r="AJ81" s="49"/>
       <c r="AK81" s="49">
         <f t="shared" si="28"/>
-        <v>9.6566666666666663</v>
+        <v>10.263333333333334</v>
       </c>
       <c r="AL81" s="2">
         <f t="shared" si="29"/>
@@ -52383,21 +52383,21 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="Y82" s="101">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="Z82" s="101">
-        <v>2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AA82" s="51">
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB82" s="101">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="AC82" s="52">
         <f t="shared" si="25"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.14666666666666667</v>
       </c>
       <c r="AD82" s="101">
         <v>-22.24</v>
@@ -52414,13 +52414,13 @@
       </c>
       <c r="AH82" s="49">
         <f t="shared" si="27"/>
-        <v>7.6333333333333329</v>
+        <v>6.6966666666666663</v>
       </c>
       <c r="AI82" s="49"/>
       <c r="AJ82" s="49"/>
       <c r="AK82" s="49">
         <f t="shared" si="28"/>
-        <v>24.283333333333331</v>
+        <v>23.346666666666664</v>
       </c>
       <c r="AL82" s="2">
         <f t="shared" si="29"/>
@@ -52441,7 +52441,7 @@
       </c>
       <c r="AQ82" s="16">
         <f t="shared" si="31"/>
-        <v>5</v>
+        <v>71.428571428571416</v>
       </c>
       <c r="AR82" s="101"/>
       <c r="AS82" s="101"/>

--- a/General.xlsx
+++ b/General.xlsx
@@ -1850,7 +1850,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="153">
+  <dxfs count="109">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1980,336 +1980,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6B26B"/>
-          <bgColor rgb="FFF6B26B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00FF00"/>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00FF00"/>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00FF00"/>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3021,84 +2691,84 @@
   </dxfs>
   <tableStyles count="19" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Mnbrd IPO v1-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="152"/>
-      <tableStyleElement type="firstRowStripe" dxfId="151"/>
-      <tableStyleElement type="secondRowStripe" dxfId="150"/>
+      <tableStyleElement type="headerRow" dxfId="108"/>
+      <tableStyleElement type="firstRowStripe" dxfId="107"/>
+      <tableStyleElement type="secondRowStripe" dxfId="106"/>
     </tableStyle>
     <tableStyle name="SME IPO v1-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="149"/>
-      <tableStyleElement type="firstRowStripe" dxfId="148"/>
-      <tableStyleElement type="secondRowStripe" dxfId="147"/>
+      <tableStyleElement type="headerRow" dxfId="105"/>
+      <tableStyleElement type="firstRowStripe" dxfId="104"/>
+      <tableStyleElement type="secondRowStripe" dxfId="103"/>
     </tableStyle>
     <tableStyle name="SME IPO v1-style 2" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="146"/>
-      <tableStyleElement type="secondRowStripe" dxfId="145"/>
+      <tableStyleElement type="firstRowStripe" dxfId="102"/>
+      <tableStyleElement type="secondRowStripe" dxfId="101"/>
     </tableStyle>
     <tableStyle name="SME IPO v1-style 3" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="144"/>
-      <tableStyleElement type="secondRowStripe" dxfId="143"/>
+      <tableStyleElement type="firstRowStripe" dxfId="100"/>
+      <tableStyleElement type="secondRowStripe" dxfId="99"/>
     </tableStyle>
     <tableStyle name="SME IPO v1-style 4" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="142"/>
-      <tableStyleElement type="secondRowStripe" dxfId="141"/>
+      <tableStyleElement type="firstRowStripe" dxfId="98"/>
+      <tableStyleElement type="secondRowStripe" dxfId="97"/>
     </tableStyle>
     <tableStyle name="SME IPO v1-style 5" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="140"/>
-      <tableStyleElement type="secondRowStripe" dxfId="139"/>
+      <tableStyleElement type="firstRowStripe" dxfId="96"/>
+      <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
     <tableStyle name="SME IPO v1-style 6" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="138"/>
-      <tableStyleElement type="secondRowStripe" dxfId="137"/>
+      <tableStyleElement type="firstRowStripe" dxfId="94"/>
+      <tableStyleElement type="secondRowStripe" dxfId="93"/>
     </tableStyle>
     <tableStyle name="SME IPO v2-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="136"/>
-      <tableStyleElement type="firstRowStripe" dxfId="135"/>
-      <tableStyleElement type="secondRowStripe" dxfId="134"/>
+      <tableStyleElement type="headerRow" dxfId="92"/>
+      <tableStyleElement type="firstRowStripe" dxfId="91"/>
+      <tableStyleElement type="secondRowStripe" dxfId="90"/>
     </tableStyle>
     <tableStyle name="SME IPO v2-style 2" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="133"/>
-      <tableStyleElement type="secondRowStripe" dxfId="132"/>
+      <tableStyleElement type="firstRowStripe" dxfId="89"/>
+      <tableStyleElement type="secondRowStripe" dxfId="88"/>
     </tableStyle>
     <tableStyle name="SME IPO v2-style 3" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="131"/>
-      <tableStyleElement type="secondRowStripe" dxfId="130"/>
+      <tableStyleElement type="firstRowStripe" dxfId="87"/>
+      <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
     <tableStyle name="SME IPO v2-style 4" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="129"/>
-      <tableStyleElement type="secondRowStripe" dxfId="128"/>
+      <tableStyleElement type="firstRowStripe" dxfId="85"/>
+      <tableStyleElement type="secondRowStripe" dxfId="84"/>
     </tableStyle>
     <tableStyle name="SME IPO v2-style 5" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="127"/>
-      <tableStyleElement type="secondRowStripe" dxfId="126"/>
+      <tableStyleElement type="firstRowStripe" dxfId="83"/>
+      <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
     <tableStyle name="SME IPO v2-style 6" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="125"/>
-      <tableStyleElement type="secondRowStripe" dxfId="124"/>
+      <tableStyleElement type="firstRowStripe" dxfId="81"/>
+      <tableStyleElement type="secondRowStripe" dxfId="80"/>
     </tableStyle>
     <tableStyle name="SME IPO v3-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="123"/>
-      <tableStyleElement type="firstRowStripe" dxfId="122"/>
-      <tableStyleElement type="secondRowStripe" dxfId="121"/>
+      <tableStyleElement type="headerRow" dxfId="79"/>
+      <tableStyleElement type="firstRowStripe" dxfId="78"/>
+      <tableStyleElement type="secondRowStripe" dxfId="77"/>
     </tableStyle>
     <tableStyle name="SME IPO v3-style 2" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="120"/>
-      <tableStyleElement type="secondRowStripe" dxfId="119"/>
+      <tableStyleElement type="firstRowStripe" dxfId="76"/>
+      <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
     <tableStyle name="SME IPO v3-style 3" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="118"/>
-      <tableStyleElement type="secondRowStripe" dxfId="117"/>
+      <tableStyleElement type="firstRowStripe" dxfId="74"/>
+      <tableStyleElement type="secondRowStripe" dxfId="73"/>
     </tableStyle>
     <tableStyle name="SME IPO v3-style 4" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="116"/>
-      <tableStyleElement type="secondRowStripe" dxfId="115"/>
+      <tableStyleElement type="firstRowStripe" dxfId="72"/>
+      <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
     <tableStyle name="SME IPO v3-style 5" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="114"/>
-      <tableStyleElement type="secondRowStripe" dxfId="113"/>
+      <tableStyleElement type="firstRowStripe" dxfId="70"/>
+      <tableStyleElement type="secondRowStripe" dxfId="69"/>
     </tableStyle>
     <tableStyle name="SME IPO v3-style 6" pivot="0" count="2">
-      <tableStyleElement type="firstRowStripe" dxfId="112"/>
-      <tableStyleElement type="secondRowStripe" dxfId="111"/>
+      <tableStyleElement type="firstRowStripe" dxfId="68"/>
+      <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3339,7 +3009,9 @@
     <col min="39" max="39" width="20.5703125" customWidth="1"/>
     <col min="40" max="42" width="7.28515625" customWidth="1"/>
     <col min="43" max="43" width="7.28515625" style="111" customWidth="1"/>
-    <col min="44" max="59" width="7.28515625" customWidth="1"/>
+    <col min="44" max="46" width="7.28515625" customWidth="1"/>
+    <col min="47" max="51" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="52" max="59" width="7.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="92.45" customHeight="1">
@@ -27794,7 +27466,7 @@
       </c>
       <c r="AI176" s="16"/>
       <c r="AJ176" s="16">
-        <f t="shared" ref="AJ173:AJ236" si="50">IF(AI176&gt;13,IF(AI176&gt;17,0.6,0.8),1)</f>
+        <f t="shared" ref="AJ176:AJ236" si="50">IF(AI176&gt;13,IF(AI176&gt;17,0.6,0.8),1)</f>
         <v>1</v>
       </c>
       <c r="AK176" s="16" t="e">
@@ -60094,7 +59766,7 @@
         <v>1</v>
       </c>
       <c r="AK116" s="49" t="e">
-        <f t="shared" ref="AK97:AK128" si="46">AG116*2.6+AH116</f>
+        <f t="shared" ref="AK116:AK128" si="46">AG116*2.6+AH116</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL116" s="2">

--- a/General.xlsx
+++ b/General.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF98B39-423F-4CE3-A5E3-443E28215D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0050F243-E910-426C-BEAE-928D63382D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18413,7 +18413,7 @@
         <v>2</v>
       </c>
       <c r="AO98" s="16">
-        <f t="shared" ref="AO98:AO129" si="37">AN98+1</f>
+        <f t="shared" ref="AO98:AO123" si="37">AN98+1</f>
         <v>3</v>
       </c>
       <c r="AP98" s="16">
@@ -23250,7 +23250,7 @@
         <v>14.88</v>
       </c>
       <c r="G130" s="15">
-        <f t="shared" ref="G130:G161" si="38">100*(F130-E130)/F130</f>
+        <f t="shared" ref="G130:G142" si="38">100*(F130-E130)/F130</f>
         <v>-38.104838709677416</v>
       </c>
       <c r="H130">
@@ -23278,7 +23278,7 @@
         <v>61.95</v>
       </c>
       <c r="P130" s="15">
-        <f t="shared" ref="P130:P161" si="39">O130/I130</f>
+        <f t="shared" ref="P130:P142" si="39">O130/I130</f>
         <v>7.3662306777645661</v>
       </c>
       <c r="Q130">
@@ -23319,7 +23319,7 @@
         <v>0</v>
       </c>
       <c r="AC130" s="15">
-        <f t="shared" ref="AC130:AC161" si="41">IF(AB130&gt;4,1,0)+AB130/7</f>
+        <f t="shared" ref="AC130:AC143" si="41">IF(AB130&gt;4,1,0)+AB130/7</f>
         <v>0</v>
       </c>
       <c r="AD130">
@@ -25582,13 +25582,13 @@
         <v>1</v>
       </c>
       <c r="X145">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y145">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Z145">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AA145" s="2">
         <f t="shared" si="40"/>
@@ -25644,14 +25644,14 @@
       </c>
       <c r="AP145" s="16">
         <f t="shared" si="48"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ145" s="15">
         <v>1</v>
       </c>
       <c r="AR145" s="16">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AS145" s="16"/>
       <c r="AT145" s="15">
@@ -25728,13 +25728,13 @@
         <v>1</v>
       </c>
       <c r="X146">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y146">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Z146">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AA146" s="2">
         <f t="shared" si="40"/>
@@ -25790,14 +25790,14 @@
       </c>
       <c r="AP146" s="16">
         <f t="shared" si="48"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ146" s="15">
         <v>0.95</v>
       </c>
       <c r="AR146" s="16">
         <f t="shared" si="49"/>
-        <v>2.3420000000000001</v>
+        <v>23.42</v>
       </c>
       <c r="AS146" s="16"/>
       <c r="AT146" s="15">
@@ -34064,7 +34064,7 @@
         <v>1</v>
       </c>
       <c r="AC272" s="15">
-        <f t="shared" ref="AC272:AC303" si="82">IF(AB272&gt;4,1,0)+AB272/12</f>
+        <f t="shared" ref="AC272:AC276" si="82">IF(AB272&gt;4,1,0)+AB272/12</f>
         <v>0</v>
       </c>
       <c r="AG272" s="85" t="e">
@@ -34282,7 +34282,7 @@
         <v>0</v>
       </c>
       <c r="AO275" s="16">
-        <f t="shared" ref="AO275:AO306" si="86">AN275+1</f>
+        <f t="shared" ref="AO275:AO288" si="86">AN275+1</f>
         <v>1</v>
       </c>
       <c r="AP275" s="16" t="e">
@@ -38069,11 +38069,11 @@
     </row>
     <row r="339" spans="7:52">
       <c r="G339" s="15" t="e">
-        <f t="shared" ref="G339:G402" si="98">100*(F339-E339)/F339</f>
+        <f t="shared" ref="G339:G400" si="98">100*(F339-E339)/F339</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P339" s="15" t="e">
-        <f t="shared" ref="P339:P402" si="99">O339/I339</f>
+        <f t="shared" ref="P339:P400" si="99">O339/I339</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R339" s="78"/>
@@ -40723,7 +40723,7 @@
         <v>5</v>
       </c>
       <c r="AA386" s="2">
-        <f t="shared" ref="AA386:AA449" si="103">IF(X386&lt;50,IF(Y386&gt;(2.3*X386),0,1),1)-IF(Z386&gt;Y386,1.7,0)</f>
+        <f t="shared" ref="AA386:AA396" si="103">IF(X386&lt;50,IF(Y386&gt;(2.3*X386),0,1),1)-IF(Z386&gt;Y386,1.7,0)</f>
         <v>1</v>
       </c>
       <c r="AC386" s="15">
@@ -40735,16 +40735,16 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH386" s="15" t="e">
-        <f t="shared" ref="AH386:AH449" si="105">AG386+IF(X386&lt;1.35,0,1)+IF(Y386&lt;1.35,0,1)+AC386+AA386</f>
+        <f t="shared" ref="AH386:AH397" si="105">AG386+IF(X386&lt;1.35,0,1)+IF(Y386&lt;1.35,0,1)+AC386+AA386</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI386" s="15"/>
       <c r="AJ386" s="15">
-        <f t="shared" ref="AJ386:AJ449" si="106">IF(AI386&gt;12.7,IF(AI386&gt;15.8,0.93,0.98),1)</f>
+        <f t="shared" ref="AJ386:AJ403" si="106">IF(AI386&gt;12.7,IF(AI386&gt;15.8,0.93,0.98),1)</f>
         <v>1</v>
       </c>
       <c r="AK386" s="15" t="e">
-        <f t="shared" ref="AK386:AK449" si="107">(1.2*AG386+AH386)*AJ386*AQ386</f>
+        <f t="shared" ref="AK386:AK403" si="107">(1.2*AG386+AH386)*AJ386*AQ386</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL386" s="14">
@@ -51493,7 +51493,7 @@
         <v>660.43</v>
       </c>
       <c r="G66" s="43">
-        <f t="shared" ref="G66:G97" si="24">100*(F66-E66)/F66</f>
+        <f t="shared" ref="G66:G67" si="24">100*(F66-E66)/F66</f>
         <v>79.978196023802667</v>
       </c>
       <c r="H66" s="68">
@@ -51521,7 +51521,7 @@
         <v>2514.66</v>
       </c>
       <c r="P66" s="43">
-        <f t="shared" ref="P66:P97" si="25">O66/I66</f>
+        <f t="shared" ref="P66:P67" si="25">O66/I66</f>
         <v>414.96039603960395</v>
       </c>
       <c r="Q66" s="68">
@@ -54196,11 +54196,11 @@
         <v>1</v>
       </c>
       <c r="AB83" s="68">
-        <v>0.23499999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="AC83" s="48">
         <f t="shared" si="27"/>
-        <v>7.8333333333333324E-2</v>
+        <v>0.77999999999999992</v>
       </c>
       <c r="AD83" s="68">
         <v>-18.59</v>
@@ -54217,7 +54217,7 @@
       </c>
       <c r="AH83" s="45">
         <f t="shared" si="29"/>
-        <v>3.7783333333333333</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AI83" s="45">
         <v>18.46</v>
@@ -54228,7 +54228,7 @@
       </c>
       <c r="AK83" s="45">
         <f t="shared" si="31"/>
-        <v>9.2325750000000006</v>
+        <v>9.8324999999999996</v>
       </c>
       <c r="AL83" s="2">
         <f t="shared" si="32"/>
@@ -55665,18 +55665,18 @@
       </c>
       <c r="AB98" s="68"/>
       <c r="AC98" s="48">
-        <f t="shared" ref="AC98:AC129" si="39">IF(AB98&gt;9,1,0)+AB98/3</f>
+        <f t="shared" ref="AC98:AC119" si="39">IF(AB98&gt;9,1,0)+AB98/3</f>
         <v>0</v>
       </c>
       <c r="AD98" s="68"/>
       <c r="AE98" s="68"/>
       <c r="AF98" s="68"/>
       <c r="AG98" s="45" t="e">
-        <f t="shared" ref="AG98:AG129" si="40">IF(G98&lt;0,0,1.2)+IF(G98&lt;14,0,0.9)+IF(P98&lt;0,0.7,0)+IF(P98&lt;6.5,1,0)+IF(P98&lt;23,1,0)+IF(R98&gt;88,0,1)+S98+IF(AD98&lt;20,0,1)+IF(AE98&lt;14,0,1)+IF(AF98&lt;26,0,1)</f>
+        <f t="shared" ref="AG98:AG127" si="40">IF(G98&lt;0,0,1.2)+IF(G98&lt;14,0,0.9)+IF(P98&lt;0,0.7,0)+IF(P98&lt;6.5,1,0)+IF(P98&lt;23,1,0)+IF(R98&gt;88,0,1)+S98+IF(AD98&lt;20,0,1)+IF(AE98&lt;14,0,1)+IF(AF98&lt;26,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH98" s="45" t="e">
-        <f t="shared" ref="AH98:AH129" si="41">AG98+IF(AG98&gt;6,1,0)+IF(X98&lt;17,0,1)+IF(Y98&lt;11,0,1)+IF(Z98&lt;1.35,0,1)+AC98+AA98</f>
+        <f t="shared" ref="AH98:AH123" si="41">AG98+IF(AG98&gt;6,1,0)+IF(X98&lt;17,0,1)+IF(Y98&lt;11,0,1)+IF(Z98&lt;1.35,0,1)+AC98+AA98</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI98" s="45"/>
@@ -58596,11 +58596,11 @@
     </row>
     <row r="130" spans="1:55">
       <c r="AJ130" s="2">
-        <f t="shared" ref="AJ130:AJ161" si="47">IF(AI130&gt;12.8,IF(AI130&gt;15.8,0.9,0.97),1)</f>
+        <f t="shared" ref="AJ130:AJ135" si="47">IF(AI130&gt;12.8,IF(AI130&gt;15.8,0.9,0.97),1)</f>
         <v>1</v>
       </c>
       <c r="AK130" s="45">
-        <f t="shared" ref="AK130:AK161" si="48">(AG130*2.6+AH130)*AJ130*AQ130</f>
+        <f t="shared" ref="AK130" si="48">(AG130*2.6+AH130)*AJ130*AQ130</f>
         <v>0</v>
       </c>
       <c r="AP130" s="16">

--- a/General.xlsx
+++ b/General.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U168213\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CFrepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="395">
   <si>
     <t>URL</t>
   </si>
@@ -1631,7 +1631,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="152">
+  <dxfs count="71">
     <dxf>
       <fill>
         <patternFill>
@@ -1944,573 +1944,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF6B26B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF6B26B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF6B26B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3296,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="AP2" s="13">
-        <f>IF(AK2&gt;13.55,IF(Z2&lt;101,IF(Z2&lt;35,IF(Z2&lt;6,3,2),1),0),0)</f>
+        <f>IF(AK2&gt;13.7,IF(Z2&lt;101,IF(Z2&lt;35,IF(Z2&lt;6,3,2),1),0),0)</f>
         <v>3</v>
       </c>
       <c r="AQ2" s="11">
@@ -3469,7 +2902,7 @@
         <v>1</v>
       </c>
       <c r="AP3" s="13">
-        <f t="shared" ref="AP3:AP66" si="13">IF(AK3&gt;13.55,IF(Z3&lt;101,IF(Z3&lt;35,IF(Z3&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP3:AP66" si="13">IF(AK3&gt;13.7,IF(Z3&lt;101,IF(Z3&lt;35,IF(Z3&lt;6,3,2),1),0),0)</f>
         <v>3</v>
       </c>
       <c r="AQ3" s="11">
@@ -13803,7 +13236,7 @@
         <v>5</v>
       </c>
       <c r="AP67" s="13">
-        <f t="shared" ref="AP67:AP130" si="33">IF(AK67&gt;13.55,IF(Z67&lt;101,IF(Z67&lt;35,IF(Z67&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP67:AP130" si="33">IF(AK67&gt;13.7,IF(Z67&lt;101,IF(Z67&lt;35,IF(Z67&lt;6,3,2),1),0),0)</f>
         <v>2</v>
       </c>
       <c r="AQ67" s="11">
@@ -16136,14 +15569,14 @@
       </c>
       <c r="AP82" s="13">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ82" s="11">
         <v>1</v>
       </c>
       <c r="AR82" s="11">
         <f t="shared" si="31"/>
-        <v>1.4947683109118086</v>
+        <v>0</v>
       </c>
       <c r="AS82" s="11"/>
       <c r="AT82" s="11">
@@ -18023,14 +17456,14 @@
       </c>
       <c r="AP94" s="13">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ94" s="11">
         <v>1</v>
       </c>
       <c r="AR94" s="11">
         <f t="shared" si="31"/>
-        <v>0.29940119760479045</v>
+        <v>0</v>
       </c>
       <c r="AS94" s="11"/>
       <c r="AT94" s="11">
@@ -18630,7 +18063,7 @@
         <v>2</v>
       </c>
       <c r="AO98" s="13">
-        <f t="shared" ref="AO98:AO129" si="38">AN98+1</f>
+        <f t="shared" ref="AO98:AO123" si="38">AN98+1</f>
         <v>3</v>
       </c>
       <c r="AP98" s="13">
@@ -23467,7 +22900,7 @@
         <v>14.88</v>
       </c>
       <c r="G130" s="11">
-        <f t="shared" ref="G130:G161" si="40">100*(F130-E130)/F130</f>
+        <f t="shared" ref="G130:G142" si="40">100*(F130-E130)/F130</f>
         <v>-38.104838709677416</v>
       </c>
       <c r="H130">
@@ -23495,7 +22928,7 @@
         <v>61.95</v>
       </c>
       <c r="P130" s="11">
-        <f t="shared" ref="P130:P161" si="41">O130/I130</f>
+        <f t="shared" ref="P130:P142" si="41">O130/I130</f>
         <v>7.3662306777645661</v>
       </c>
       <c r="Q130">
@@ -23536,7 +22969,7 @@
         <v>0</v>
       </c>
       <c r="AC130" s="11">
-        <f t="shared" ref="AC130:AC161" si="43">IF(AB130&gt;4,1,0)+AB130/7</f>
+        <f t="shared" ref="AC130:AC143" si="43">IF(AB130&gt;4,1,0)+AB130/7</f>
         <v>0</v>
       </c>
       <c r="AD130">
@@ -23736,7 +23169,7 @@
         <v>5</v>
       </c>
       <c r="AP131" s="13">
-        <f t="shared" ref="AP131:AP194" si="52">IF(AK131&gt;13.55,IF(Z131&lt;101,IF(Z131&lt;35,IF(Z131&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP131:AP194" si="52">IF(AK131&gt;13.7,IF(Z131&lt;101,IF(Z131&lt;35,IF(Z131&lt;6,3,2),1),0),0)</f>
         <v>3</v>
       </c>
       <c r="AQ131" s="11">
@@ -25896,6 +25329,9 @@
       <c r="C146" t="s">
         <v>164</v>
       </c>
+      <c r="D146" s="17" t="s">
+        <v>58</v>
+      </c>
       <c r="E146">
         <v>7.56</v>
       </c>
@@ -26001,9 +25437,9 @@
         <f t="shared" si="47"/>
         <v>16.751896249999998</v>
       </c>
-      <c r="AL146" s="10">
+      <c r="AL146" s="10" t="str">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>Pos</v>
       </c>
       <c r="AM146" s="14" t="s">
         <v>261</v>
@@ -29581,7 +29017,7 @@
         <v>1</v>
       </c>
       <c r="AP195" s="13" t="e">
-        <f t="shared" ref="AP195:AP258" si="69">IF(AK195&gt;13.55,IF(Z195&lt;101,IF(Z195&lt;35,IF(Z195&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP195:AP258" si="69">IF(AK195&gt;13.7,IF(Z195&lt;101,IF(Z195&lt;35,IF(Z195&lt;6,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ195" s="11">
@@ -32413,7 +31849,7 @@
         <v>1</v>
       </c>
       <c r="AC240" s="11">
-        <f t="shared" ref="AC240:AC271" si="75">IF(AB240&gt;4,1,0)+AB240/12</f>
+        <f t="shared" ref="AC240:AC257" si="75">IF(AB240&gt;4,1,0)+AB240/12</f>
         <v>0</v>
       </c>
       <c r="AG240" s="12" t="e">
@@ -32820,7 +32256,7 @@
         <v>0</v>
       </c>
       <c r="AO246" s="13">
-        <f t="shared" ref="AO246:AO277" si="76">AN246+1</f>
+        <f t="shared" ref="AO246:AO269" si="76">AN246+1</f>
         <v>1</v>
       </c>
       <c r="AP246" s="13" t="e">
@@ -33643,7 +33079,7 @@
         <v>1</v>
       </c>
       <c r="AP259" s="13" t="e">
-        <f t="shared" ref="AP259:AP322" si="85">IF(AK259&gt;13.55,IF(Z259&lt;101,IF(Z259&lt;35,IF(Z259&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP259:AP322" si="85">IF(AK259&gt;13.7,IF(Z259&lt;101,IF(Z259&lt;35,IF(Z259&lt;6,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ259" s="11">
@@ -37359,7 +36795,7 @@
         <v>5</v>
       </c>
       <c r="AA322" s="11">
-        <f t="shared" ref="AA322:AA385" si="91">IF(X322&lt;50,IF(Y322&gt;(2.3*X322),0,1),1)-IF(Z322&gt;Y322,1.7,0)</f>
+        <f t="shared" ref="AA322:AA377" si="91">IF(X322&lt;50,IF(Y322&gt;(2.3*X322),0,1),1)-IF(Z322&gt;Y322,1.7,0)</f>
         <v>1</v>
       </c>
       <c r="AC322" s="11">
@@ -37371,16 +36807,16 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH322" s="11" t="e">
-        <f t="shared" ref="AH322:AH385" si="93">AG322+IF(X322&lt;1.35,0,1)+IF(Y322&lt;1.35,0,1)+AC322+AA322</f>
+        <f t="shared" ref="AH322:AH378" si="93">AG322+IF(X322&lt;1.35,0,1)+IF(Y322&lt;1.35,0,1)+AC322+AA322</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI322" s="11"/>
       <c r="AJ322" s="11">
-        <f t="shared" ref="AJ322:AJ385" si="94">IF(AI322&gt;12.7,IF(AI322&gt;15.8,0.93,0.98),1)</f>
+        <f t="shared" ref="AJ322:AJ384" si="94">IF(AI322&gt;12.7,IF(AI322&gt;15.8,0.93,0.98),1)</f>
         <v>1</v>
       </c>
       <c r="AK322" s="11" t="e">
-        <f t="shared" ref="AK322:AK385" si="95">(1.2*AG322+AH322)*AJ322*AQ322</f>
+        <f t="shared" ref="AK322:AK384" si="95">(1.2*AG322+AH322)*AJ322*AQ322</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL322" s="10">
@@ -37447,7 +36883,7 @@
         <v>0</v>
       </c>
       <c r="AP323" s="13" t="e">
-        <f t="shared" ref="AP323:AP383" si="97">IF(AK323&gt;13.55,IF(Z323&lt;101,IF(Z323&lt;35,IF(Z323&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP323:AP379" si="97">IF(AK323&gt;13.7,IF(Z323&lt;101,IF(Z323&lt;35,IF(Z323&lt;6,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ323" s="11">
@@ -38447,11 +37883,11 @@
     </row>
     <row r="342" spans="7:52" ht="12.75" customHeight="1">
       <c r="G342" s="11" t="e">
-        <f t="shared" ref="G342:G405" si="98">100*(F342-E342)/F342</f>
+        <f t="shared" ref="G342:G381" si="98">100*(F342-E342)/F342</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P342" s="11" t="e">
-        <f t="shared" ref="P342:P405" si="99">O342/I342</f>
+        <f t="shared" ref="P342:P381" si="99">O342/I342</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R342" s="2"/>
@@ -40616,7 +40052,7 @@
         <v>0</v>
       </c>
       <c r="AP380" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" ref="AP323:AP383" si="103">IF(AK380&gt;13.55,IF(Z380&lt;101,IF(Z380&lt;35,IF(Z380&lt;6,3,2),1),0),0)</f>
         <v>0</v>
       </c>
       <c r="AZ380" s="13">
@@ -40651,7 +40087,7 @@
         <v>0</v>
       </c>
       <c r="AP381" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="AZ381" s="13">
@@ -40678,7 +40114,7 @@
         <v>0</v>
       </c>
       <c r="AP382" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="AZ382" s="13">
@@ -40705,7 +40141,7 @@
         <v>0</v>
       </c>
       <c r="AP383" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="AZ383" s="13">
@@ -40757,7 +40193,7 @@
     </row>
   </sheetData>
   <autoFilter ref="AB1:AB389"/>
-  <conditionalFormatting sqref="D2:D145">
+  <conditionalFormatting sqref="D2:D146">
     <cfRule type="containsText" dxfId="53" priority="27" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH("neg",D2)))</formula>
     </cfRule>
@@ -40798,13 +40234,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH378">
-    <cfRule type="cellIs" dxfId="27" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="23" operator="greaterThan">
       <formula>7.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK384">
-    <cfRule type="cellIs" dxfId="45" priority="26" operator="greaterThan">
-      <formula>13.55</formula>
+    <cfRule type="cellIs" dxfId="27" priority="26" operator="greaterThan">
+      <formula>13.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL384">
@@ -50685,7 +50121,7 @@
         <v>660.43</v>
       </c>
       <c r="G66" s="13">
-        <f t="shared" ref="G66:G97" si="24">100*(F66-E66)/F66</f>
+        <f t="shared" ref="G66:G67" si="24">100*(F66-E66)/F66</f>
         <v>79.978196023802667</v>
       </c>
       <c r="H66" s="17">
@@ -50713,7 +50149,7 @@
         <v>2514.66</v>
       </c>
       <c r="P66" s="13">
-        <f t="shared" ref="P66:P97" si="25">O66/I66</f>
+        <f t="shared" ref="P66:P67" si="25">O66/I66</f>
         <v>414.96039603960395</v>
       </c>
       <c r="Q66" s="17">
@@ -54861,18 +54297,18 @@
       </c>
       <c r="AB98" s="17"/>
       <c r="AC98" s="12">
-        <f t="shared" ref="AC98:AC129" si="39">IF(AB98&gt;9,1,0)+AB98/3</f>
+        <f t="shared" ref="AC98:AC119" si="39">IF(AB98&gt;9,1,0)+AB98/3</f>
         <v>0</v>
       </c>
       <c r="AD98" s="17"/>
       <c r="AE98" s="17"/>
       <c r="AF98" s="17"/>
       <c r="AG98" s="12" t="e">
-        <f t="shared" ref="AG98:AG129" si="40">IF(G98&lt;0,0,1.2)+IF(G98&lt;14,0,0.9)+IF(P98&lt;0,0.7,0)+IF(P98&lt;6.5,1,0)+IF(P98&lt;23,1,0)+IF(R98&gt;88,0,1)+S98+IF(AD98&lt;20,0,1)+IF(AE98&lt;14,0,1)+IF(AF98&lt;26,0,1)</f>
+        <f t="shared" ref="AG98:AG127" si="40">IF(G98&lt;0,0,1.2)+IF(G98&lt;14,0,0.9)+IF(P98&lt;0,0.7,0)+IF(P98&lt;6.5,1,0)+IF(P98&lt;23,1,0)+IF(R98&gt;88,0,1)+S98+IF(AD98&lt;20,0,1)+IF(AE98&lt;14,0,1)+IF(AF98&lt;26,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH98" s="12" t="e">
-        <f t="shared" ref="AH98:AH129" si="41">AG98+IF(AG98&gt;6,1,0)+IF(X98&lt;17,0,1)+IF(Y98&lt;11,0,1)+IF(Z98&lt;1.35,0,1)+AC98+AA98</f>
+        <f t="shared" ref="AH98:AH123" si="41">AG98+IF(AG98&gt;6,1,0)+IF(X98&lt;17,0,1)+IF(Y98&lt;11,0,1)+IF(Z98&lt;1.35,0,1)+AC98+AA98</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI98" s="12"/>
@@ -57792,11 +57228,11 @@
     </row>
     <row r="130" spans="1:55" ht="12.75" customHeight="1">
       <c r="AJ130" s="11">
-        <f t="shared" ref="AJ130:AJ161" si="47">IF(AI130&gt;12.8,IF(AI130&gt;15.8,0.9,0.97),1)</f>
+        <f t="shared" ref="AJ130:AJ135" si="47">IF(AI130&gt;12.8,IF(AI130&gt;15.8,0.9,0.97),1)</f>
         <v>1</v>
       </c>
       <c r="AK130" s="12">
-        <f t="shared" ref="AK130:AK161" si="48">(AG130*2.6+AH130)*AJ130*AQ130</f>
+        <f t="shared" ref="AK130" si="48">(AG130*2.6+AH130)*AJ130*AQ130</f>
         <v>0</v>
       </c>
       <c r="AP130" s="13">
@@ -57860,81 +57296,81 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G129 H56">
-    <cfRule type="cellIs" dxfId="151" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P129 Q60:R60">
-    <cfRule type="cellIs" dxfId="150" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="15" operator="greaterThan">
       <formula>23</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R366">
-    <cfRule type="cellIs" dxfId="149" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="17" operator="greaterThan">
       <formula>88</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X63">
-    <cfRule type="cellIs" dxfId="148" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="67" priority="14" operator="lessThan">
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X48">
-    <cfRule type="cellIs" dxfId="147" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="66" priority="9" operator="lessThan">
       <formula>19</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y63">
-    <cfRule type="cellIs" dxfId="146" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="65" priority="13" operator="lessThan">
       <formula>11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y48">
-    <cfRule type="cellIs" dxfId="145" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="8" operator="lessThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z48">
-    <cfRule type="cellIs" dxfId="144" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="63" priority="10" operator="lessThan">
       <formula>3.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA123">
-    <cfRule type="cellIs" dxfId="143" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="16" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF63">
-    <cfRule type="cellIs" dxfId="142" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="61" priority="12" operator="lessThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG51:AG66">
-    <cfRule type="cellIs" dxfId="141" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="5" operator="greaterThan">
       <formula>6.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK177">
-    <cfRule type="cellIs" dxfId="140" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="18" operator="greaterThan">
       <formula>23.73</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL423">
-    <cfRule type="containsText" dxfId="139" priority="6" operator="containsText" text="Neg">
+    <cfRule type="containsText" dxfId="58" priority="6" operator="containsText" text="Neg">
       <formula>NOT(ISERROR(SEARCH("Neg",AL2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="138" priority="7" operator="containsText" text="Pos">
+    <cfRule type="containsText" dxfId="57" priority="7" operator="containsText" text="Pos">
       <formula>NOT(ISERROR(SEARCH("Pos",AL2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP135">
-    <cfRule type="cellIs" dxfId="137" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="4" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>

--- a/General.xlsx
+++ b/General.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CFrepo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C5B4A1-B9F8-43CB-AE23-CB7AAB285126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9510" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IPOSME" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IPOSME!$AB$1:$AB$389</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -1213,7 +1214,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -1631,7 +1632,126 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="44">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39988402966399123"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39988402966399123"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39988402966399123"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39988402966399123"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39988402966399123"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39988402966399123"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1783,314 +1903,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF6B26B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39988402966399123"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2385,45 +2197,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DG389"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" customWidth="1"/>
-    <col min="23" max="34" width="7.28515625" customWidth="1"/>
-    <col min="35" max="36" width="7.28515625" hidden="1" customWidth="1"/>
-    <col min="37" max="38" width="7.28515625" customWidth="1"/>
-    <col min="39" max="39" width="20.5703125" customWidth="1"/>
-    <col min="40" max="42" width="7.28515625" customWidth="1"/>
-    <col min="43" max="43" width="7.28515625" style="2" customWidth="1"/>
-    <col min="44" max="45" width="7.28515625" customWidth="1"/>
-    <col min="47" max="47" width="10.85546875" customWidth="1"/>
-    <col min="48" max="48" width="6.140625" customWidth="1"/>
-    <col min="49" max="49" width="8.5703125" customWidth="1"/>
-    <col min="50" max="50" width="10.42578125" customWidth="1"/>
-    <col min="51" max="51" width="7.42578125" customWidth="1"/>
-    <col min="52" max="59" width="7.28515625" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.33203125" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" customWidth="1"/>
+    <col min="23" max="34" width="7.33203125" customWidth="1"/>
+    <col min="35" max="36" width="7.33203125" hidden="1" customWidth="1"/>
+    <col min="37" max="38" width="7.33203125" customWidth="1"/>
+    <col min="39" max="39" width="20.5546875" customWidth="1"/>
+    <col min="40" max="42" width="7.33203125" customWidth="1"/>
+    <col min="43" max="43" width="7.33203125" style="2" customWidth="1"/>
+    <col min="44" max="45" width="7.33203125" customWidth="1"/>
+    <col min="47" max="47" width="10.88671875" customWidth="1"/>
+    <col min="48" max="48" width="6.109375" customWidth="1"/>
+    <col min="49" max="49" width="8.5546875" customWidth="1"/>
+    <col min="50" max="50" width="10.44140625" customWidth="1"/>
+    <col min="51" max="51" width="7.44140625" customWidth="1"/>
+    <col min="52" max="59" width="7.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="92.25" customHeight="1">
@@ -2729,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="AP2" s="13">
-        <f>IF(AK2&gt;13.7,IF(Z2&lt;101,IF(Z2&lt;35,IF(Z2&lt;6,3,2),1),0),0)</f>
+        <f>IF(AK2&gt;13.78,IF(Z2&lt;101,IF(Z2&lt;35,IF(Z2&lt;6,3,2),1),0),0)</f>
         <v>3</v>
       </c>
       <c r="AQ2" s="11">
@@ -2902,7 +2714,7 @@
         <v>1</v>
       </c>
       <c r="AP3" s="13">
-        <f t="shared" ref="AP3:AP66" si="13">IF(AK3&gt;13.7,IF(Z3&lt;101,IF(Z3&lt;35,IF(Z3&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP3:AP66" si="13">IF(AK3&gt;13.78,IF(Z3&lt;101,IF(Z3&lt;35,IF(Z3&lt;6,3,2),1),0),0)</f>
         <v>3</v>
       </c>
       <c r="AQ3" s="11">
@@ -13236,7 +13048,7 @@
         <v>5</v>
       </c>
       <c r="AP67" s="13">
-        <f t="shared" ref="AP67:AP130" si="33">IF(AK67&gt;13.7,IF(Z67&lt;101,IF(Z67&lt;35,IF(Z67&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP67:AP130" si="33">IF(AK67&gt;13.78,IF(Z67&lt;101,IF(Z67&lt;35,IF(Z67&lt;6,3,2),1),0),0)</f>
         <v>2</v>
       </c>
       <c r="AQ67" s="11">
@@ -23169,7 +22981,7 @@
         <v>5</v>
       </c>
       <c r="AP131" s="13">
-        <f t="shared" ref="AP131:AP194" si="52">IF(AK131&gt;13.7,IF(Z131&lt;101,IF(Z131&lt;35,IF(Z131&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP131:AP194" si="52">IF(AK131&gt;13.78,IF(Z131&lt;101,IF(Z131&lt;35,IF(Z131&lt;6,3,2),1),0),0)</f>
         <v>3</v>
       </c>
       <c r="AQ131" s="11">
@@ -25445,7 +25257,7 @@
         <v>261</v>
       </c>
       <c r="AN146">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AO146" s="13">
         <v>8</v>
@@ -25536,13 +25348,13 @@
         <v>1</v>
       </c>
       <c r="X147">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="Y147">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="Z147">
-        <v>3.36</v>
+        <v>70</v>
       </c>
       <c r="AA147" s="11">
         <f t="shared" si="42"/>
@@ -25598,14 +25410,14 @@
       </c>
       <c r="AP147" s="13">
         <f t="shared" si="52"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ147" s="11">
         <v>0.95</v>
       </c>
       <c r="AR147" s="13">
         <f t="shared" si="50"/>
-        <v>3.7410714285714288</v>
+        <v>0.17957142857142858</v>
       </c>
       <c r="AS147" s="13"/>
       <c r="AT147" s="11">
@@ -25828,17 +25640,17 @@
         <v>1</v>
       </c>
       <c r="X149">
-        <v>20</v>
+        <v>1.31</v>
       </c>
       <c r="Y149">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="Z149">
-        <v>10</v>
+        <v>139</v>
       </c>
       <c r="AA149" s="11">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB149">
         <v>37.51</v>
@@ -25862,7 +25674,7 @@
       </c>
       <c r="AH149" s="11">
         <f t="shared" si="45"/>
-        <v>10.625833333333333</v>
+        <v>8.6258333333333326</v>
       </c>
       <c r="AI149" s="11">
         <v>16.7775</v>
@@ -25873,7 +25685,7 @@
       </c>
       <c r="AK149" s="11">
         <f t="shared" si="47"/>
-        <v>13.788024999999999</v>
+        <v>11.928025</v>
       </c>
       <c r="AL149" s="10">
         <f t="shared" si="48"/>
@@ -25890,19 +25702,19 @@
       </c>
       <c r="AP149" s="13">
         <f t="shared" si="52"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ149" s="11">
         <v>1</v>
       </c>
       <c r="AR149" s="13">
         <f t="shared" si="50"/>
-        <v>3.7509999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS149" s="13"/>
       <c r="AT149" s="11">
         <f t="shared" si="51"/>
-        <v>1278.8025</v>
+        <v>1092.8025</v>
       </c>
       <c r="AZ149" s="13"/>
     </row>
@@ -29017,7 +28829,7 @@
         <v>1</v>
       </c>
       <c r="AP195" s="13" t="e">
-        <f t="shared" ref="AP195:AP258" si="69">IF(AK195&gt;13.7,IF(Z195&lt;101,IF(Z195&lt;35,IF(Z195&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP195:AP258" si="69">IF(AK195&gt;13.78,IF(Z195&lt;101,IF(Z195&lt;35,IF(Z195&lt;6,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ195" s="11">
@@ -33079,7 +32891,7 @@
         <v>1</v>
       </c>
       <c r="AP259" s="13" t="e">
-        <f t="shared" ref="AP259:AP322" si="85">IF(AK259&gt;13.7,IF(Z259&lt;101,IF(Z259&lt;35,IF(Z259&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP259:AP322" si="85">IF(AK259&gt;13.78,IF(Z259&lt;101,IF(Z259&lt;35,IF(Z259&lt;6,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ259" s="11">
@@ -36883,7 +36695,7 @@
         <v>0</v>
       </c>
       <c r="AP323" s="13" t="e">
-        <f t="shared" ref="AP323:AP379" si="97">IF(AK323&gt;13.7,IF(Z323&lt;101,IF(Z323&lt;35,IF(Z323&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP323:AP378" si="97">IF(AK323&gt;13.78,IF(Z323&lt;101,IF(Z323&lt;35,IF(Z323&lt;6,3,2),1),0),0)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ323" s="11">
@@ -40014,7 +39826,7 @@
         <v>0</v>
       </c>
       <c r="AP379" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" ref="AP379" si="103">IF(AK379&gt;13.7,IF(Z379&lt;101,IF(Z379&lt;35,IF(Z379&lt;6,3,2),1),0),0)</f>
         <v>0</v>
       </c>
       <c r="AQ379" s="11">
@@ -40052,7 +39864,7 @@
         <v>0</v>
       </c>
       <c r="AP380" s="13">
-        <f t="shared" ref="AP323:AP383" si="103">IF(AK380&gt;13.55,IF(Z380&lt;101,IF(Z380&lt;35,IF(Z380&lt;6,3,2),1),0),0)</f>
+        <f t="shared" ref="AP380:AP383" si="104">IF(AK380&gt;13.55,IF(Z380&lt;101,IF(Z380&lt;35,IF(Z380&lt;6,3,2),1),0),0)</f>
         <v>0</v>
       </c>
       <c r="AZ380" s="13">
@@ -40087,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="AP381" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="AZ381" s="13">
@@ -40114,7 +39926,7 @@
         <v>0</v>
       </c>
       <c r="AP382" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="AZ382" s="13">
@@ -40141,7 +39953,7 @@
         <v>0</v>
       </c>
       <c r="AP383" s="13">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="AZ383" s="13">
@@ -40192,113 +40004,113 @@
       <c r="R389" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="AB1:AB389"/>
+  <autoFilter ref="AB1:AB389" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="D2:D146">
-    <cfRule type="containsText" dxfId="53" priority="27" operator="containsText" text="neg">
+    <cfRule type="containsText" dxfId="43" priority="27" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH("neg",D2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G381">
-    <cfRule type="cellIs" dxfId="52" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="20" operator="lessThan">
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P381">
-    <cfRule type="cellIs" dxfId="51" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="21" operator="greaterThan">
       <formula>14.56</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q137">
-    <cfRule type="cellIs" dxfId="50" priority="24" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="24" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R137">
-    <cfRule type="cellIs" dxfId="49" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="18" operator="greaterThan">
       <formula>33.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2">
-    <cfRule type="expression" dxfId="48" priority="28">
+    <cfRule type="expression" dxfId="38" priority="28">
       <formula>LEN(TRIM(X2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE137">
-    <cfRule type="cellIs" dxfId="47" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="19" operator="lessThan">
       <formula>10.56</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG378">
-    <cfRule type="cellIs" dxfId="46" priority="25" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="25" operator="greaterThan">
       <formula>5.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH378">
-    <cfRule type="cellIs" dxfId="45" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="23" operator="greaterThan">
       <formula>7.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK384">
-    <cfRule type="cellIs" dxfId="27" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="26" operator="greaterThan">
       <formula>13.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL384">
-    <cfRule type="containsText" dxfId="44" priority="5" operator="containsText" text="Rec">
+    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="Rec">
       <formula>NOT(ISERROR(SEARCH("Rec",AL2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="6" operator="containsText" text="neg">
+    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH("neg",AL2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="7" operator="containsText" text="Pos">
+    <cfRule type="containsText" dxfId="31" priority="7" operator="containsText" text="Pos">
       <formula>NOT(ISERROR(SEARCH("Pos",AL2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN2:AN142">
-    <cfRule type="endsWith" dxfId="41" priority="8" operator="endsWith" text="4">
+    <cfRule type="endsWith" dxfId="30" priority="8" operator="endsWith" text="4">
       <formula>RIGHT(AN2,LEN("4"))="4"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="40" priority="9" operator="endsWith" text="2">
+    <cfRule type="endsWith" dxfId="29" priority="9" operator="endsWith" text="2">
       <formula>RIGHT(AN2,LEN("2"))="2"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="39" priority="10" operator="endsWith" text="7">
+    <cfRule type="endsWith" dxfId="28" priority="10" operator="endsWith" text="7">
       <formula>RIGHT(AN2,LEN("7"))="7"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="38" priority="11" operator="endsWith" text="0">
+    <cfRule type="endsWith" dxfId="27" priority="11" operator="endsWith" text="0">
       <formula>RIGHT(AN2,LEN("0"))="0"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="37" priority="12" operator="endsWith" text="8">
+    <cfRule type="endsWith" dxfId="26" priority="12" operator="endsWith" text="8">
       <formula>RIGHT(AN2,LEN("8"))="8"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="36" priority="13" operator="endsWith" text="9">
+    <cfRule type="endsWith" dxfId="25" priority="13" operator="endsWith" text="9">
       <formula>RIGHT(AN2,LEN("9"))="9"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="35" priority="14" operator="endsWith" text="6">
+    <cfRule type="endsWith" dxfId="24" priority="14" operator="endsWith" text="6">
       <formula>RIGHT(AN2,LEN("6"))="6"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="34" priority="15" operator="endsWith" text="1">
+    <cfRule type="endsWith" dxfId="23" priority="15" operator="endsWith" text="1">
       <formula>RIGHT(AN2,LEN("1"))="1"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="33" priority="16" operator="endsWith" text="3">
+    <cfRule type="endsWith" dxfId="22" priority="16" operator="endsWith" text="3">
       <formula>RIGHT(AN2,LEN("3"))="3"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="32" priority="17" operator="endsWith" text="5">
+    <cfRule type="endsWith" dxfId="21" priority="17" operator="endsWith" text="5">
       <formula>RIGHT(AN2,LEN("5"))="5"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP383">
-    <cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="2">
+    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="2">
       <formula>NOT(ISERROR(SEARCH("2",AP2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BH85 BB87:BH97 BC86:BH86">
-    <cfRule type="cellIs" dxfId="28" priority="22" operator="lessThan">
+  <conditionalFormatting sqref="BB2:BH85 BC86:BH86 BB87:BH97">
+    <cfRule type="cellIs" dxfId="17" priority="22" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40308,58 +40120,58 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BC135"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" customWidth="1"/>
-    <col min="12" max="12" width="4.140625" customWidth="1"/>
-    <col min="13" max="14" width="6.5703125" customWidth="1"/>
-    <col min="15" max="15" width="7.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="4.88671875" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" customWidth="1"/>
+    <col min="12" max="12" width="4.109375" customWidth="1"/>
+    <col min="13" max="14" width="6.5546875" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.140625" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="5.5703125" customWidth="1"/>
-    <col min="22" max="22" width="6.140625" customWidth="1"/>
-    <col min="23" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="8.28515625" customWidth="1"/>
-    <col min="26" max="26" width="5.42578125" customWidth="1"/>
-    <col min="27" max="27" width="5.140625" customWidth="1"/>
-    <col min="28" max="28" width="4.5703125" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" customWidth="1"/>
-    <col min="30" max="30" width="6.5703125" customWidth="1"/>
-    <col min="31" max="31" width="5.7109375" customWidth="1"/>
-    <col min="32" max="32" width="6.28515625" customWidth="1"/>
-    <col min="33" max="36" width="4.85546875" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
+    <col min="21" max="21" width="5.5546875" customWidth="1"/>
+    <col min="22" max="22" width="6.109375" customWidth="1"/>
+    <col min="23" max="24" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="8.33203125" customWidth="1"/>
+    <col min="26" max="26" width="5.44140625" customWidth="1"/>
+    <col min="27" max="27" width="5.109375" customWidth="1"/>
+    <col min="28" max="28" width="4.5546875" customWidth="1"/>
+    <col min="29" max="29" width="4.88671875" customWidth="1"/>
+    <col min="30" max="30" width="6.5546875" customWidth="1"/>
+    <col min="31" max="31" width="5.6640625" customWidth="1"/>
+    <col min="32" max="32" width="6.33203125" customWidth="1"/>
+    <col min="33" max="36" width="4.88671875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
-    <col min="38" max="38" width="5.7109375" customWidth="1"/>
-    <col min="39" max="39" width="19.140625" customWidth="1"/>
-    <col min="40" max="40" width="4.5703125" customWidth="1"/>
-    <col min="41" max="41" width="5.42578125" customWidth="1"/>
-    <col min="42" max="42" width="10.85546875" customWidth="1"/>
+    <col min="38" max="38" width="5.6640625" customWidth="1"/>
+    <col min="39" max="39" width="19.109375" customWidth="1"/>
+    <col min="40" max="40" width="4.5546875" customWidth="1"/>
+    <col min="41" max="41" width="5.44140625" customWidth="1"/>
+    <col min="42" max="42" width="10.88671875" customWidth="1"/>
     <col min="43" max="43" width="7" customWidth="1"/>
-    <col min="44" max="45" width="10.85546875" customWidth="1"/>
+    <col min="44" max="45" width="10.88671875" customWidth="1"/>
     <col min="46" max="46" width="6" customWidth="1"/>
-    <col min="47" max="47" width="6.140625" customWidth="1"/>
+    <col min="47" max="47" width="6.109375" customWidth="1"/>
     <col min="48" max="48" width="4" customWidth="1"/>
-    <col min="49" max="49" width="4.140625" customWidth="1"/>
-    <col min="50" max="51" width="5.28515625" customWidth="1"/>
-    <col min="52" max="52" width="6.7109375" customWidth="1"/>
-    <col min="53" max="53" width="3.85546875" customWidth="1"/>
+    <col min="49" max="49" width="4.109375" customWidth="1"/>
+    <col min="50" max="51" width="5.33203125" customWidth="1"/>
+    <col min="52" max="52" width="6.6640625" customWidth="1"/>
+    <col min="53" max="53" width="3.88671875" customWidth="1"/>
     <col min="54" max="54" width="4" customWidth="1"/>
-    <col min="55" max="55" width="4.7109375" customWidth="1"/>
+    <col min="55" max="55" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="92.25" customHeight="1">
@@ -57296,81 +57108,81 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G129 H56">
-    <cfRule type="cellIs" dxfId="70" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P129 Q60:R60">
-    <cfRule type="cellIs" dxfId="69" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="greaterThan">
       <formula>23</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R366">
-    <cfRule type="cellIs" dxfId="68" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="17" operator="greaterThan">
       <formula>88</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X63">
-    <cfRule type="cellIs" dxfId="67" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X48">
-    <cfRule type="cellIs" dxfId="66" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThan">
       <formula>19</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y63">
-    <cfRule type="cellIs" dxfId="65" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="lessThan">
       <formula>11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y48">
-    <cfRule type="cellIs" dxfId="64" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="lessThan">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z48">
-    <cfRule type="cellIs" dxfId="63" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
       <formula>3.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA123">
-    <cfRule type="cellIs" dxfId="62" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF63">
-    <cfRule type="cellIs" dxfId="61" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="12" operator="lessThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG51:AG66">
-    <cfRule type="cellIs" dxfId="60" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="greaterThan">
       <formula>6.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK177">
-    <cfRule type="cellIs" dxfId="59" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="18" operator="greaterThan">
       <formula>23.73</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL423">
-    <cfRule type="containsText" dxfId="58" priority="6" operator="containsText" text="Neg">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Neg">
       <formula>NOT(ISERROR(SEARCH("Neg",AL2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="7" operator="containsText" text="Pos">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="Pos">
       <formula>NOT(ISERROR(SEARCH("Pos",AL2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP135">
-    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>

--- a/General.xlsx
+++ b/General.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CapitalFund1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A28508-6C3B-4F5E-9370-FF323014B48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="360"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IPOSME" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IPOSME!$AB$1:$AB$387</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1288,7 +1289,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -2271,46 +2272,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DG514"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.88671875" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" customWidth="1"/>
-    <col min="23" max="34" width="7.28515625" customWidth="1"/>
-    <col min="35" max="35" width="5.5703125" customWidth="1"/>
-    <col min="36" max="36" width="5.85546875" customWidth="1"/>
-    <col min="37" max="38" width="7.28515625" customWidth="1"/>
-    <col min="39" max="39" width="20.5703125" customWidth="1"/>
-    <col min="40" max="42" width="7.28515625" customWidth="1"/>
-    <col min="43" max="43" width="7.28515625" style="2" customWidth="1"/>
-    <col min="44" max="45" width="7.28515625" customWidth="1"/>
-    <col min="47" max="47" width="10.85546875" customWidth="1"/>
-    <col min="48" max="48" width="6.140625" customWidth="1"/>
-    <col min="49" max="49" width="8.5703125" customWidth="1"/>
-    <col min="50" max="50" width="10.42578125" customWidth="1"/>
-    <col min="51" max="51" width="7.42578125" customWidth="1"/>
-    <col min="52" max="59" width="7.28515625" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.33203125" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" customWidth="1"/>
+    <col min="23" max="34" width="7.33203125" customWidth="1"/>
+    <col min="35" max="35" width="5.5546875" customWidth="1"/>
+    <col min="36" max="36" width="5.88671875" customWidth="1"/>
+    <col min="37" max="38" width="7.33203125" customWidth="1"/>
+    <col min="39" max="39" width="20.5546875" customWidth="1"/>
+    <col min="40" max="42" width="7.33203125" customWidth="1"/>
+    <col min="43" max="43" width="7.33203125" style="2" customWidth="1"/>
+    <col min="44" max="45" width="7.33203125" customWidth="1"/>
+    <col min="47" max="47" width="10.88671875" customWidth="1"/>
+    <col min="48" max="48" width="6.109375" customWidth="1"/>
+    <col min="49" max="49" width="8.5546875" customWidth="1"/>
+    <col min="50" max="50" width="10.44140625" customWidth="1"/>
+    <col min="51" max="51" width="7.44140625" customWidth="1"/>
+    <col min="52" max="59" width="7.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="92.25" customHeight="1">
@@ -26155,24 +26156,24 @@
         <v>1</v>
       </c>
       <c r="X152">
-        <v>8.24</v>
+        <v>1</v>
       </c>
       <c r="Y152">
-        <v>12.43</v>
+        <v>9.24</v>
       </c>
       <c r="Z152">
-        <v>8.39</v>
+        <v>4.47</v>
       </c>
       <c r="AA152" s="11">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB152">
-        <v>3.9</v>
+        <v>6.49</v>
       </c>
       <c r="AC152" s="11">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD152">
         <v>77.16</v>
@@ -26189,10 +26190,10 @@
       </c>
       <c r="AH152" s="11">
         <f t="shared" si="45"/>
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="AI152" s="11">
-        <v>18.392499999999998</v>
+        <v>17.782499999999999</v>
       </c>
       <c r="AJ152" s="11">
         <f t="shared" si="46"/>
@@ -26200,7 +26201,7 @@
       </c>
       <c r="AK152" s="11">
         <f t="shared" si="47"/>
-        <v>16.9725</v>
+        <v>16.0425</v>
       </c>
       <c r="AL152" s="10">
         <f t="shared" si="40"/>
@@ -26217,19 +26218,19 @@
       </c>
       <c r="AP152" s="13">
         <f t="shared" si="49"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ152" s="11">
         <v>1</v>
       </c>
       <c r="AR152" s="13">
         <f t="shared" si="50"/>
-        <v>1.1918951132300357</v>
+        <v>2.2371364653243848</v>
       </c>
       <c r="AS152" s="13"/>
       <c r="AT152" s="11">
         <f t="shared" si="51"/>
-        <v>1597.25</v>
+        <v>1504.25</v>
       </c>
       <c r="AZ152" s="13"/>
     </row>
@@ -26304,14 +26305,14 @@
         <v>1</v>
       </c>
       <c r="Y153">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="Z153">
-        <v>0.21</v>
+        <v>0.05</v>
       </c>
       <c r="AA153" s="11">
         <f t="shared" si="43"/>
-        <v>-0.7</v>
+        <v>1</v>
       </c>
       <c r="AB153">
         <v>0</v>
@@ -26335,10 +26336,10 @@
       </c>
       <c r="AH153" s="11">
         <f t="shared" si="45"/>
-        <v>0.89999999999999969</v>
+        <v>2.5999999999999996</v>
       </c>
       <c r="AI153" s="11">
-        <v>18.3825</v>
+        <v>17.762499999999999</v>
       </c>
       <c r="AJ153" s="11">
         <f t="shared" si="46"/>
@@ -26346,7 +26347,7 @@
       </c>
       <c r="AK153" s="11">
         <f t="shared" si="47"/>
-        <v>3.0689999999999991</v>
+        <v>4.6499999999999995</v>
       </c>
       <c r="AL153" s="10">
         <f t="shared" si="40"/>
@@ -26375,7 +26376,7 @@
       <c r="AS153" s="13"/>
       <c r="AT153" s="11">
         <f t="shared" si="51"/>
-        <v>206.89999999999992</v>
+        <v>364.99999999999994</v>
       </c>
       <c r="AZ153" s="13"/>
     </row>
@@ -42199,7 +42200,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="AB1:AB387"/>
+  <autoFilter ref="AB1:AB387" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="D2:D147">
     <cfRule type="containsText" dxfId="43" priority="27" operator="containsText" text="neg">
       <formula>NOT(ISERROR(SEARCH("neg",D2)))</formula>
@@ -42304,7 +42305,7 @@
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BH85 BB87:BH97 BC86:BH86">
+  <conditionalFormatting sqref="BB2:BH85 BC86:BH86 BB87:BH97">
     <cfRule type="cellIs" dxfId="17" priority="22" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -42315,58 +42316,58 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BC135"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" customWidth="1"/>
-    <col min="12" max="12" width="4.140625" customWidth="1"/>
-    <col min="13" max="14" width="6.5703125" customWidth="1"/>
-    <col min="15" max="15" width="7.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="4.88671875" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" customWidth="1"/>
+    <col min="12" max="12" width="4.109375" customWidth="1"/>
+    <col min="13" max="14" width="6.5546875" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.140625" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="5.5703125" customWidth="1"/>
-    <col min="22" max="22" width="6.140625" customWidth="1"/>
-    <col min="23" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="8.28515625" customWidth="1"/>
-    <col min="26" max="26" width="5.42578125" customWidth="1"/>
-    <col min="27" max="27" width="5.140625" customWidth="1"/>
-    <col min="28" max="28" width="4.5703125" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" customWidth="1"/>
-    <col min="30" max="30" width="6.5703125" customWidth="1"/>
-    <col min="31" max="31" width="5.7109375" customWidth="1"/>
-    <col min="32" max="32" width="6.28515625" customWidth="1"/>
-    <col min="33" max="36" width="4.85546875" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
+    <col min="21" max="21" width="5.5546875" customWidth="1"/>
+    <col min="22" max="22" width="6.109375" customWidth="1"/>
+    <col min="23" max="24" width="6.6640625" customWidth="1"/>
+    <col min="25" max="25" width="8.33203125" customWidth="1"/>
+    <col min="26" max="26" width="5.44140625" customWidth="1"/>
+    <col min="27" max="27" width="5.109375" customWidth="1"/>
+    <col min="28" max="28" width="4.5546875" customWidth="1"/>
+    <col min="29" max="29" width="4.88671875" customWidth="1"/>
+    <col min="30" max="30" width="6.5546875" customWidth="1"/>
+    <col min="31" max="31" width="5.6640625" customWidth="1"/>
+    <col min="32" max="32" width="6.33203125" customWidth="1"/>
+    <col min="33" max="36" width="4.88671875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
-    <col min="38" max="38" width="5.7109375" customWidth="1"/>
-    <col min="39" max="39" width="19.140625" customWidth="1"/>
-    <col min="40" max="40" width="4.5703125" customWidth="1"/>
-    <col min="41" max="41" width="5.42578125" customWidth="1"/>
-    <col min="42" max="42" width="10.85546875" customWidth="1"/>
+    <col min="38" max="38" width="5.6640625" customWidth="1"/>
+    <col min="39" max="39" width="19.109375" customWidth="1"/>
+    <col min="40" max="40" width="4.5546875" customWidth="1"/>
+    <col min="41" max="41" width="5.44140625" customWidth="1"/>
+    <col min="42" max="42" width="10.88671875" customWidth="1"/>
     <col min="43" max="43" width="7" customWidth="1"/>
-    <col min="44" max="45" width="10.85546875" customWidth="1"/>
+    <col min="44" max="45" width="10.88671875" customWidth="1"/>
     <col min="46" max="46" width="6" customWidth="1"/>
-    <col min="47" max="47" width="6.140625" customWidth="1"/>
+    <col min="47" max="47" width="6.109375" customWidth="1"/>
     <col min="48" max="48" width="4" customWidth="1"/>
-    <col min="49" max="49" width="4.140625" customWidth="1"/>
-    <col min="50" max="51" width="5.28515625" customWidth="1"/>
-    <col min="52" max="52" width="6.7109375" customWidth="1"/>
-    <col min="53" max="53" width="3.85546875" customWidth="1"/>
+    <col min="49" max="49" width="4.109375" customWidth="1"/>
+    <col min="50" max="51" width="5.33203125" customWidth="1"/>
+    <col min="52" max="52" width="6.6640625" customWidth="1"/>
+    <col min="53" max="53" width="3.88671875" customWidth="1"/>
     <col min="54" max="54" width="4" customWidth="1"/>
-    <col min="55" max="55" width="4.7109375" customWidth="1"/>
+    <col min="55" max="55" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="92.25" customHeight="1">

--- a/General.xlsx
+++ b/General.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A28508-6C3B-4F5E-9370-FF323014B48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A1385F-9F23-40BE-A15D-1BD2E9482ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1293,7 +1293,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1391,6 +1391,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1509,7 +1516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1701,6 +1708,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -16062,7 +16072,7 @@
         <f t="shared" si="27"/>
         <v>Neg</v>
       </c>
-      <c r="AM86" s="14" t="str">
+      <c r="AM86" s="77" t="str">
         <f t="shared" si="28"/>
         <v>MARC Technocrats</v>
       </c>
@@ -17002,7 +17012,7 @@
         <f t="shared" si="27"/>
         <v>Rec</v>
       </c>
-      <c r="AM92" s="14" t="str">
+      <c r="AM92" s="77" t="str">
         <f t="shared" si="28"/>
         <v>Admach Systems</v>
       </c>
@@ -17951,7 +17961,7 @@
         <v>2</v>
       </c>
       <c r="AO98" s="13">
-        <f t="shared" ref="AO98:AO129" si="38">AN98+1</f>
+        <f t="shared" ref="AO98:AO123" si="38">AN98+1</f>
         <v>3</v>
       </c>
       <c r="AP98" s="13">
@@ -22283,7 +22293,7 @@
         <f t="shared" si="36"/>
         <v>Neg</v>
       </c>
-      <c r="AM126" s="14" t="str">
+      <c r="AM126" s="77" t="str">
         <f t="shared" si="37"/>
         <v xml:space="preserve">Kiaasa Retail Date, </v>
       </c>
@@ -22787,7 +22797,7 @@
         <v>14.88</v>
       </c>
       <c r="G130" s="11">
-        <f t="shared" ref="G130:G161" si="41">100*(F130-E130)/F130</f>
+        <f t="shared" ref="G130:G142" si="41">100*(F130-E130)/F130</f>
         <v>-38.104838709677416</v>
       </c>
       <c r="H130">
@@ -22815,7 +22825,7 @@
         <v>61.95</v>
       </c>
       <c r="P130" s="11">
-        <f t="shared" ref="P130:P161" si="42">O130/I130</f>
+        <f t="shared" ref="P130:P142" si="42">O130/I130</f>
         <v>7.3662306777645661</v>
       </c>
       <c r="Q130">
@@ -25179,7 +25189,7 @@
         <f t="shared" si="40"/>
         <v>Neg</v>
       </c>
-      <c r="AM145" s="14" t="s">
+      <c r="AM145" s="77" t="s">
         <v>260</v>
       </c>
       <c r="AN145">
@@ -25477,7 +25487,7 @@
         <f t="shared" si="40"/>
         <v>Neg</v>
       </c>
-      <c r="AM147" s="14" t="s">
+      <c r="AM147" s="77" t="s">
         <v>264</v>
       </c>
       <c r="AN147">
@@ -34119,7 +34129,7 @@
         <v>0</v>
       </c>
       <c r="AO258" s="13">
-        <f t="shared" ref="AO258:AO289" si="78">AN258+1</f>
+        <f t="shared" ref="AO258:AO267" si="78">AN258+1</f>
         <v>1</v>
       </c>
       <c r="AP258" s="13" t="e">
@@ -38078,7 +38088,7 @@
         <v>70</v>
       </c>
       <c r="AA322" s="11">
-        <f t="shared" ref="AA322:AA385" si="86">IF(X322&lt;50,IF(Y322&gt;(2.3*X322),0,1),1)-IF(Z322&gt;Y322,1.7,0)</f>
+        <f t="shared" ref="AA322:AA375" si="86">IF(X322&lt;50,IF(Y322&gt;(2.3*X322),0,1),1)-IF(Z322&gt;Y322,1.7,0)</f>
         <v>0</v>
       </c>
       <c r="AC322" s="11">
@@ -38090,16 +38100,16 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AH322" s="11" t="e">
-        <f t="shared" ref="AH322:AH385" si="88">AG322+IF(X322&lt;1.35,0,1)+IF(Y322&lt;1.35,0,1)+AC322+AA322</f>
+        <f t="shared" ref="AH322:AH376" si="88">AG322+IF(X322&lt;1.35,0,1)+IF(Y322&lt;1.35,0,1)+AC322+AA322</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI322" s="11"/>
       <c r="AJ322" s="11">
-        <f t="shared" ref="AJ322:AJ385" si="89">IF(AI322&gt;12.7,IF(AI322&gt;15.8,0.93,0.98),1)</f>
+        <f t="shared" ref="AJ322:AJ382" si="89">IF(AI322&gt;12.7,IF(AI322&gt;15.8,0.93,0.98),1)</f>
         <v>1</v>
       </c>
       <c r="AK322" s="11" t="e">
-        <f t="shared" ref="AK322:AK385" si="90">(1.5*AG322+AH322)*AJ322*AQ322</f>
+        <f t="shared" ref="AK322:AK375" si="90">(1.5*AG322+AH322)*AJ322*AQ322</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL322" s="10">
@@ -38140,7 +38150,7 @@
         <v>0</v>
       </c>
       <c r="AC323" s="11">
-        <f t="shared" ref="AC323:AC386" si="92">IF(AB323&gt;4,1,0)+IF(AB323&gt;10,1,0)</f>
+        <f t="shared" ref="AC323:AC376" si="92">IF(AB323&gt;4,1,0)+IF(AB323&gt;10,1,0)</f>
         <v>0</v>
       </c>
       <c r="AG323" s="12" t="e">
@@ -39943,11 +39953,11 @@
     </row>
     <row r="354" spans="7:52" ht="12.75" customHeight="1">
       <c r="G354" s="11" t="e">
-        <f t="shared" ref="G354:G417" si="94">100*(F354-E354)/F354</f>
+        <f t="shared" ref="G354:G379" si="94">100*(F354-E354)/F354</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P354" s="11" t="e">
-        <f t="shared" ref="P354:P417" si="95">O354/I354</f>
+        <f t="shared" ref="P354:P379" si="95">O354/I354</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R354" s="2"/>
@@ -42311,7 +42321,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -52129,7 +52139,7 @@
         <v>660.43</v>
       </c>
       <c r="G66" s="13">
-        <f t="shared" ref="G66:G97" si="24">100*(F66-E66)/F66</f>
+        <f t="shared" ref="G66:G67" si="24">100*(F66-E66)/F66</f>
         <v>79.978196023802667</v>
       </c>
       <c r="H66" s="17">
@@ -52157,7 +52167,7 @@
         <v>2514.66</v>
       </c>
       <c r="P66" s="13">
-        <f t="shared" ref="P66:P97" si="25">O66/I66</f>
+        <f t="shared" ref="P66:P67" si="25">O66/I66</f>
         <v>414.96039603960395</v>
       </c>
       <c r="Q66" s="17">
@@ -52222,7 +52232,7 @@
         <v>13</v>
       </c>
       <c r="AJ66" s="11">
-        <f t="shared" ref="AJ66:AJ97" si="30">IF(AI66&gt;12.8,IF(AI66&gt;15.8,0.9,0.97),1)</f>
+        <f t="shared" ref="AJ66:AJ78" si="30">IF(AI66&gt;12.8,IF(AI66&gt;15.8,0.9,0.97),1)</f>
         <v>0.97</v>
       </c>
       <c r="AK66" s="12">
@@ -56304,18 +56314,18 @@
       </c>
       <c r="AB98" s="17"/>
       <c r="AC98" s="12">
-        <f t="shared" ref="AC98:AC129" si="40">IF(AB98&gt;9,1,0)+AB98/3</f>
+        <f t="shared" ref="AC98:AC119" si="40">IF(AB98&gt;9,1,0)+AB98/3</f>
         <v>0</v>
       </c>
       <c r="AD98" s="17"/>
       <c r="AE98" s="17"/>
       <c r="AF98" s="17"/>
       <c r="AG98" s="12" t="e">
-        <f t="shared" ref="AG98:AG129" si="41">IF(G98&lt;0,0,1.2)+IF(G98&lt;14,0,0.9)+IF(P98&lt;0,0.7,0)+IF(P98&lt;6.5,1,0)+IF(P98&lt;23,1,0)+IF(R98&gt;88,0,1)+S98+IF(AD98&lt;20,0,1)+IF(AE98&lt;14,0,1)+IF(AF98&lt;26,0,1)</f>
+        <f t="shared" ref="AG98:AG127" si="41">IF(G98&lt;0,0,1.2)+IF(G98&lt;14,0,0.9)+IF(P98&lt;0,0.7,0)+IF(P98&lt;6.5,1,0)+IF(P98&lt;23,1,0)+IF(R98&gt;88,0,1)+S98+IF(AD98&lt;20,0,1)+IF(AE98&lt;14,0,1)+IF(AF98&lt;26,0,1)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AH98" s="12" t="e">
-        <f t="shared" ref="AH98:AH129" si="42">AG98+IF(AG98&gt;6,1,0)+IF(X98&lt;17,0,1)+IF(Y98&lt;11,0,1)+IF(Z98&lt;1.35,0,1)+AC98+AA98</f>
+        <f t="shared" ref="AH98:AH123" si="42">AG98+IF(AG98&gt;6,1,0)+IF(X98&lt;17,0,1)+IF(Y98&lt;11,0,1)+IF(Z98&lt;1.35,0,1)+AC98+AA98</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI98" s="12"/>
@@ -57678,7 +57688,7 @@
       </c>
       <c r="AI112" s="12"/>
       <c r="AJ112" s="11">
-        <f t="shared" ref="AJ112:AJ143" si="47">IF(AI112&gt;12.8,IF(AI112&gt;15.8,0.9,0.97),1)</f>
+        <f t="shared" ref="AJ112:AJ135" si="47">IF(AI112&gt;12.8,IF(AI112&gt;15.8,0.9,0.97),1)</f>
         <v>1</v>
       </c>
       <c r="AK112" s="12" t="e">
@@ -59239,7 +59249,7 @@
         <v>1</v>
       </c>
       <c r="AK130" s="12">
-        <f t="shared" ref="AK130:AK161" si="49">(AG130*2.6+AH130)*AJ130*AQ130</f>
+        <f t="shared" ref="AK130" si="49">(AG130*2.6+AH130)*AJ130*AQ130</f>
         <v>0</v>
       </c>
       <c r="AP130" s="13">
